--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260619--01</t>
+  </si>
+  <si>
+    <t>02:24</t>
+  </si>
+  <si>
+    <t>01:14:39</t>
+  </si>
+  <si>
+    <t>01:17:57</t>
+  </si>
+  <si>
+    <t>01:19:09</t>
+  </si>
+  <si>
+    <t>01:20:21</t>
+  </si>
+  <si>
+    <t>01:23:40</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>01:17:56</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -77,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +126,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +144,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +212,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +693,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-10.3</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
+        <v>3</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +824,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +846,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -76,25 +76,25 @@
     <t>02:24</t>
   </si>
   <si>
-    <t>01:14:39</t>
-  </si>
-  <si>
-    <t>01:17:57</t>
-  </si>
-  <si>
-    <t>01:19:09</t>
-  </si>
-  <si>
-    <t>01:20:21</t>
-  </si>
-  <si>
-    <t>01:23:40</t>
+    <t>01:14:35</t>
+  </si>
+  <si>
+    <t>01:17:53</t>
+  </si>
+  <si>
+    <t>01:19:05</t>
+  </si>
+  <si>
+    <t>01:20:17</t>
+  </si>
+  <si>
+    <t>01:23:36</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>01:17:56</t>
+    <t>01:17:52</t>
   </si>
   <si>
     <t>A</t>
@@ -134,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,13 +149,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +223,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,7 +746,7 @@
         <v>28</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -745,8 +754,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>2</v>
+      <c r="R2" s="8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -73,34 +73,70 @@
     <t>20260619--01</t>
   </si>
   <si>
+    <t>20260621--01</t>
+  </si>
+  <si>
     <t>02:24</t>
   </si>
   <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
     <t>01:14:35</t>
   </si>
   <si>
+    <t>01:19:29</t>
+  </si>
+  <si>
     <t>01:17:53</t>
   </si>
   <si>
+    <t>01:21:56</t>
+  </si>
+  <si>
     <t>01:19:05</t>
   </si>
   <si>
+    <t>01:24:31</t>
+  </si>
+  <si>
     <t>01:20:17</t>
   </si>
   <si>
+    <t>01:27:08</t>
+  </si>
+  <si>
     <t>01:23:36</t>
   </si>
   <si>
+    <t>01:29:36</t>
+  </si>
+  <si>
     <t>10°</t>
   </si>
   <si>
+    <t>15°</t>
+  </si>
+  <si>
     <t>01:17:52</t>
   </si>
   <si>
+    <t>01:22:50</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -134,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,13 +191,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -226,6 +280,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -710,111 +773,167 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L2" s="4">
         <v>-10.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="6">
+        <v>45</v>
+      </c>
+      <c r="P2" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="6">
-        <v>5</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>5</v>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-9.9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="6">
+        <v>39</v>
+      </c>
+      <c r="P3" s="10">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>3</v>
+      </c>
+      <c r="R3" s="11">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -833,12 +952,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -855,22 +974,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>Datum</t>
   </si>
@@ -76,55 +76,115 @@
     <t>20260621--01</t>
   </si>
   <si>
+    <t>20260622--01</t>
+  </si>
+  <si>
+    <t>20260622--02</t>
+  </si>
+  <si>
     <t>02:24</t>
   </si>
   <si>
     <t>05:12</t>
   </si>
   <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>03:44</t>
+  </si>
+  <si>
     <t>04:18</t>
   </si>
   <si>
+    <t>02:27</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
     <t>01:14:35</t>
   </si>
   <si>
     <t>01:19:29</t>
   </si>
   <si>
+    <t>00:33:53</t>
+  </si>
+  <si>
+    <t>23:48:18</t>
+  </si>
+  <si>
     <t>01:17:53</t>
   </si>
   <si>
     <t>01:21:56</t>
   </si>
   <si>
+    <t>00:36:29</t>
+  </si>
+  <si>
+    <t>23:51:09</t>
+  </si>
+  <si>
     <t>01:19:05</t>
   </si>
   <si>
     <t>01:24:31</t>
   </si>
   <si>
+    <t>00:38:47</t>
+  </si>
+  <si>
+    <t>23:53:01</t>
+  </si>
+  <si>
     <t>01:20:17</t>
   </si>
   <si>
     <t>01:27:08</t>
   </si>
   <si>
+    <t>00:41:06</t>
+  </si>
+  <si>
+    <t>23:54:53</t>
+  </si>
+  <si>
     <t>01:23:36</t>
   </si>
   <si>
     <t>01:29:36</t>
   </si>
   <si>
+    <t>00:43:43</t>
+  </si>
+  <si>
+    <t>23:57:44</t>
+  </si>
+  <si>
     <t>10°</t>
   </si>
   <si>
     <t>15°</t>
   </si>
   <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
     <t>01:17:52</t>
   </si>
   <si>
     <t>01:22:50</t>
+  </si>
+  <si>
+    <t>00:38:39</t>
+  </si>
+  <si>
+    <t>23:54:25</t>
   </si>
   <si>
     <t>A</t>
@@ -170,7 +230,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,13 +245,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,7 +257,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,7 +269,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -256,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -289,6 +361,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -773,52 +851,52 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="L2" s="4">
         <v>-10.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O2" s="6">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="P2" s="7">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>45</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -829,111 +907,223 @@
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="L3" s="4">
         <v>-9.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="8">
+        <v>100</v>
+      </c>
+      <c r="P3" s="9">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>84</v>
+      </c>
+      <c r="R3" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-13.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="6">
-        <v>39</v>
-      </c>
-      <c r="P3" s="10">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>3</v>
-      </c>
-      <c r="R3" s="11">
-        <v>39</v>
+      <c r="H5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-15.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="6">
+        <v>12</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B5">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -952,12 +1142,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -974,22 +1164,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P5">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
   <si>
     <t>Datum</t>
   </si>
@@ -82,85 +82,133 @@
     <t>20260622--02</t>
   </si>
   <si>
-    <t>02:24</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>03:44</t>
-  </si>
-  <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>02:27</t>
-  </si>
-  <si>
-    <t>00:28</t>
-  </si>
-  <si>
-    <t>01:14:35</t>
-  </si>
-  <si>
-    <t>01:19:29</t>
-  </si>
-  <si>
-    <t>00:33:53</t>
-  </si>
-  <si>
-    <t>23:48:18</t>
-  </si>
-  <si>
-    <t>01:17:53</t>
-  </si>
-  <si>
-    <t>01:21:56</t>
-  </si>
-  <si>
-    <t>00:36:29</t>
-  </si>
-  <si>
-    <t>23:51:09</t>
-  </si>
-  <si>
-    <t>01:19:05</t>
-  </si>
-  <si>
-    <t>01:24:31</t>
-  </si>
-  <si>
-    <t>00:38:47</t>
-  </si>
-  <si>
-    <t>23:53:01</t>
-  </si>
-  <si>
-    <t>01:20:17</t>
-  </si>
-  <si>
-    <t>01:27:08</t>
-  </si>
-  <si>
-    <t>00:41:06</t>
-  </si>
-  <si>
-    <t>23:54:53</t>
-  </si>
-  <si>
-    <t>01:23:36</t>
-  </si>
-  <si>
-    <t>01:29:36</t>
-  </si>
-  <si>
-    <t>00:43:43</t>
-  </si>
-  <si>
-    <t>23:57:44</t>
+    <t>20260623--01</t>
+  </si>
+  <si>
+    <t>20260623--02</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>02:28</t>
+  </si>
+  <si>
+    <t>00:29</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>01:14:41</t>
+  </si>
+  <si>
+    <t>01:19:42</t>
+  </si>
+  <si>
+    <t>00:34:11</t>
+  </si>
+  <si>
+    <t>23:48:42</t>
+  </si>
+  <si>
+    <t>01:25:00</t>
+  </si>
+  <si>
+    <t>23:03:14</t>
+  </si>
+  <si>
+    <t>01:17:58</t>
+  </si>
+  <si>
+    <t>01:22:09</t>
+  </si>
+  <si>
+    <t>00:36:47</t>
+  </si>
+  <si>
+    <t>23:51:32</t>
+  </si>
+  <si>
+    <t>01:27:16</t>
+  </si>
+  <si>
+    <t>23:06:38</t>
+  </si>
+  <si>
+    <t>01:19:10</t>
+  </si>
+  <si>
+    <t>01:24:45</t>
+  </si>
+  <si>
+    <t>00:39:05</t>
+  </si>
+  <si>
+    <t>23:53:24</t>
+  </si>
+  <si>
+    <t>01:30:15</t>
+  </si>
+  <si>
+    <t>23:07:41</t>
+  </si>
+  <si>
+    <t>01:20:23</t>
+  </si>
+  <si>
+    <t>01:27:22</t>
+  </si>
+  <si>
+    <t>00:41:25</t>
+  </si>
+  <si>
+    <t>23:55:17</t>
+  </si>
+  <si>
+    <t>01:33:16</t>
+  </si>
+  <si>
+    <t>23:08:45</t>
+  </si>
+  <si>
+    <t>01:23:42</t>
+  </si>
+  <si>
+    <t>01:29:50</t>
+  </si>
+  <si>
+    <t>00:44:01</t>
+  </si>
+  <si>
+    <t>23:58:08</t>
+  </si>
+  <si>
+    <t>01:35:33</t>
+  </si>
+  <si>
+    <t>23:12:09</t>
   </si>
   <si>
     <t>10°</t>
@@ -175,22 +223,37 @@
     <t>12°</t>
   </si>
   <si>
-    <t>01:17:52</t>
-  </si>
-  <si>
-    <t>01:22:50</t>
-  </si>
-  <si>
-    <t>00:38:39</t>
-  </si>
-  <si>
-    <t>23:54:25</t>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>01:17:57</t>
+  </si>
+  <si>
+    <t>01:23:02</t>
+  </si>
+  <si>
+    <t>00:38:57</t>
+  </si>
+  <si>
+    <t>23:54:48</t>
+  </si>
+  <si>
+    <t>01:27:51</t>
+  </si>
+  <si>
+    <t>23:10:36</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>4</t>
@@ -230,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,7 +308,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,37 +320,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -361,12 +412,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -770,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -851,43 +896,43 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
         <v>-10.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O2" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -895,8 +940,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>2</v>
+      <c r="R2" s="8">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -907,52 +952,52 @@
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="L3" s="4">
         <v>-9.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O3" s="8">
-        <v>100</v>
-      </c>
-      <c r="P3" s="9">
-        <v>14</v>
+        <v>81</v>
+      </c>
+      <c r="O3" s="9">
+        <v>4</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
       </c>
       <c r="Q3" s="10">
-        <v>84</v>
-      </c>
-      <c r="R3" s="11">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -963,52 +1008,52 @@
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
         <v>-13.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" s="12">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="O4" s="6">
+        <v>19</v>
+      </c>
+      <c r="P4" s="8">
+        <v>14</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1019,111 +1064,199 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
         <v>-15.2</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="6">
+        <v>25</v>
+      </c>
+      <c r="P5" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>25</v>
+      </c>
+      <c r="R5" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-9.5</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="6">
-        <v>12</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>12</v>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-15.9</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1142,12 +1275,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1164,22 +1297,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O5">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
   <si>
     <t>Datum</t>
   </si>
@@ -88,6 +88,18 @@
     <t>20260623--02</t>
   </si>
   <si>
+    <t>20260624--01</t>
+  </si>
+  <si>
+    <t>20260624--02</t>
+  </si>
+  <si>
+    <t>20260625--01</t>
+  </si>
+  <si>
+    <t>20260625--02</t>
+  </si>
+  <si>
     <t>02:25</t>
   </si>
   <si>
@@ -106,6 +118,18 @@
     <t>02:07</t>
   </si>
   <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
     <t>04:20</t>
   </si>
   <si>
@@ -121,6 +145,12 @@
     <t>00:00</t>
   </si>
   <si>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>00:07</t>
+  </si>
+  <si>
     <t>01:14:41</t>
   </si>
   <si>
@@ -139,6 +169,18 @@
     <t>23:03:14</t>
   </si>
   <si>
+    <t>00:39:15</t>
+  </si>
+  <si>
+    <t>23:53:30</t>
+  </si>
+  <si>
+    <t>01:30:19</t>
+  </si>
+  <si>
+    <t>23:07:44</t>
+  </si>
+  <si>
     <t>01:17:58</t>
   </si>
   <si>
@@ -157,6 +199,18 @@
     <t>23:06:38</t>
   </si>
   <si>
+    <t>00:41:33</t>
+  </si>
+  <si>
+    <t>23:55:52</t>
+  </si>
+  <si>
+    <t>01:32:34</t>
+  </si>
+  <si>
+    <t>23:10:12</t>
+  </si>
+  <si>
     <t>01:19:10</t>
   </si>
   <si>
@@ -169,12 +223,24 @@
     <t>23:53:24</t>
   </si>
   <si>
-    <t>01:30:15</t>
+    <t>01:30:16</t>
   </si>
   <si>
     <t>23:07:41</t>
   </si>
   <si>
+    <t>00:44:28</t>
+  </si>
+  <si>
+    <t>23:58:37</t>
+  </si>
+  <si>
+    <t>01:35:37</t>
+  </si>
+  <si>
+    <t>23:12:45</t>
+  </si>
+  <si>
     <t>01:20:23</t>
   </si>
   <si>
@@ -193,6 +259,18 @@
     <t>23:08:45</t>
   </si>
   <si>
+    <t>00:47:22</t>
+  </si>
+  <si>
+    <t>00:01:24</t>
+  </si>
+  <si>
+    <t>01:38:42</t>
+  </si>
+  <si>
+    <t>23:15:19</t>
+  </si>
+  <si>
     <t>01:23:42</t>
   </si>
   <si>
@@ -211,6 +289,18 @@
     <t>23:12:09</t>
   </si>
   <si>
+    <t>00:49:41</t>
+  </si>
+  <si>
+    <t>00:03:46</t>
+  </si>
+  <si>
+    <t>01:40:57</t>
+  </si>
+  <si>
+    <t>23:17:48</t>
+  </si>
+  <si>
     <t>10°</t>
   </si>
   <si>
@@ -229,6 +319,15 @@
     <t>5°</t>
   </si>
   <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
     <t>01:17:57</t>
   </si>
   <si>
@@ -247,6 +346,18 @@
     <t>23:10:36</t>
   </si>
   <si>
+    <t>00:43:39</t>
+  </si>
+  <si>
+    <t>23:59:26</t>
+  </si>
+  <si>
+    <t>01:32:29</t>
+  </si>
+  <si>
+    <t>23:15:12</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -260,6 +371,12 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -293,7 +410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,7 +431,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,19 +473,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,6 +565,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -896,52 +1067,52 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="L2" s="4">
         <v>-10.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="O2" s="6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>2</v>
+      </c>
+      <c r="R2" s="9">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -952,52 +1123,52 @@
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="L3" s="4">
         <v>-9.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="9">
-        <v>4</v>
-      </c>
-      <c r="P3" s="7">
+        <v>118</v>
+      </c>
+      <c r="O3" s="6">
+        <v>46</v>
+      </c>
+      <c r="P3" s="8">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>4</v>
-      </c>
-      <c r="R3" s="7">
+      <c r="Q3" s="8">
         <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1008,52 +1179,52 @@
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="L4" s="4">
         <v>-13.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O4" s="6">
-        <v>19</v>
+        <v>118</v>
+      </c>
+      <c r="O4" s="11">
+        <v>85</v>
       </c>
       <c r="P4" s="8">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>1</v>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1064,52 +1235,52 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="L5" s="4">
         <v>-15.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="6">
-        <v>25</v>
-      </c>
-      <c r="P5" s="10">
+        <v>117</v>
+      </c>
+      <c r="O5" s="11">
+        <v>42</v>
+      </c>
+      <c r="P5" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="14">
         <v>4</v>
       </c>
-      <c r="Q5" s="11">
-        <v>25</v>
-      </c>
-      <c r="R5" s="11">
-        <v>25</v>
+      <c r="R5" s="7">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1120,40 +1291,52 @@
         <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="L6" s="4">
         <v>-9.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>81</v>
+        <v>118</v>
+      </c>
+      <c r="O6" s="11">
+        <v>53</v>
+      </c>
+      <c r="P6" s="14">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>28</v>
+      </c>
+      <c r="R6" s="10">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1164,99 +1347,335 @@
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="L7" s="4">
         <v>-15.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>80</v>
+        <v>117</v>
+      </c>
+      <c r="O7" s="11">
+        <v>71</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-12.9</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O8" s="11">
+        <v>85</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-15.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" s="17">
+        <v>11</v>
+      </c>
+      <c r="P9" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-9.1</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" s="17">
+        <v>8</v>
+      </c>
+      <c r="P10" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-16</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O11" s="6">
+        <v>30</v>
+      </c>
+      <c r="P11" s="9">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1275,12 +1694,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1297,22 +1716,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260619--01</t>
-  </si>
-  <si>
     <t>20260621--01</t>
   </si>
   <si>
@@ -100,7 +97,10 @@
     <t>20260625--02</t>
   </si>
   <si>
-    <t>02:25</t>
+    <t>20260626--01</t>
+  </si>
+  <si>
+    <t>20260626--02</t>
   </si>
   <si>
     <t>05:13</t>
@@ -115,7 +115,7 @@
     <t>06:00</t>
   </si>
   <si>
-    <t>02:07</t>
+    <t>02:06</t>
   </si>
   <si>
     <t>05:49</t>
@@ -130,6 +130,9 @@
     <t>05:07</t>
   </si>
   <si>
+    <t>04:30</t>
+  </si>
+  <si>
     <t>04:20</t>
   </si>
   <si>
@@ -151,13 +154,13 @@
     <t>00:07</t>
   </si>
   <si>
-    <t>01:14:41</t>
-  </si>
-  <si>
-    <t>01:19:42</t>
-  </si>
-  <si>
-    <t>00:34:11</t>
+    <t>04:32</t>
+  </si>
+  <si>
+    <t>01:19:43</t>
+  </si>
+  <si>
+    <t>00:34:12</t>
   </si>
   <si>
     <t>23:48:42</t>
@@ -172,19 +175,22 @@
     <t>00:39:15</t>
   </si>
   <si>
-    <t>23:53:30</t>
-  </si>
-  <si>
-    <t>01:30:19</t>
-  </si>
-  <si>
-    <t>23:07:44</t>
-  </si>
-  <si>
-    <t>01:17:58</t>
-  </si>
-  <si>
-    <t>01:22:09</t>
+    <t>23:53:28</t>
+  </si>
+  <si>
+    <t>01:30:18</t>
+  </si>
+  <si>
+    <t>23:07:41</t>
+  </si>
+  <si>
+    <t>00:44:22</t>
+  </si>
+  <si>
+    <t>22:21:55</t>
+  </si>
+  <si>
+    <t>01:22:10</t>
   </si>
   <si>
     <t>00:36:47</t>
@@ -202,22 +208,25 @@
     <t>00:41:33</t>
   </si>
   <si>
-    <t>23:55:52</t>
-  </si>
-  <si>
-    <t>01:32:34</t>
-  </si>
-  <si>
-    <t>23:10:12</t>
-  </si>
-  <si>
-    <t>01:19:10</t>
-  </si>
-  <si>
-    <t>01:24:45</t>
-  </si>
-  <si>
-    <t>00:39:05</t>
+    <t>23:55:50</t>
+  </si>
+  <si>
+    <t>01:32:32</t>
+  </si>
+  <si>
+    <t>23:10:09</t>
+  </si>
+  <si>
+    <t>00:46:36</t>
+  </si>
+  <si>
+    <t>22:24:32</t>
+  </si>
+  <si>
+    <t>01:24:46</t>
+  </si>
+  <si>
+    <t>00:39:06</t>
   </si>
   <si>
     <t>23:53:24</t>
@@ -226,25 +235,25 @@
     <t>01:30:16</t>
   </si>
   <si>
-    <t>23:07:41</t>
-  </si>
-  <si>
-    <t>00:44:28</t>
-  </si>
-  <si>
-    <t>23:58:37</t>
-  </si>
-  <si>
-    <t>01:35:37</t>
-  </si>
-  <si>
-    <t>23:12:45</t>
-  </si>
-  <si>
-    <t>01:20:23</t>
-  </si>
-  <si>
-    <t>01:27:22</t>
+    <t>00:44:27</t>
+  </si>
+  <si>
+    <t>23:58:36</t>
+  </si>
+  <si>
+    <t>01:35:36</t>
+  </si>
+  <si>
+    <t>23:12:42</t>
+  </si>
+  <si>
+    <t>00:49:40</t>
+  </si>
+  <si>
+    <t>22:26:47</t>
+  </si>
+  <si>
+    <t>01:27:23</t>
   </si>
   <si>
     <t>00:41:25</t>
@@ -256,28 +265,31 @@
     <t>01:33:16</t>
   </si>
   <si>
-    <t>23:08:45</t>
+    <t>23:08:44</t>
   </si>
   <si>
     <t>00:47:22</t>
   </si>
   <si>
-    <t>00:01:24</t>
-  </si>
-  <si>
-    <t>01:38:42</t>
-  </si>
-  <si>
-    <t>23:15:19</t>
-  </si>
-  <si>
-    <t>01:23:42</t>
-  </si>
-  <si>
-    <t>01:29:50</t>
-  </si>
-  <si>
-    <t>00:44:01</t>
+    <t>00:01:22</t>
+  </si>
+  <si>
+    <t>01:38:40</t>
+  </si>
+  <si>
+    <t>23:15:16</t>
+  </si>
+  <si>
+    <t>00:52:44</t>
+  </si>
+  <si>
+    <t>22:29:02</t>
+  </si>
+  <si>
+    <t>01:29:51</t>
+  </si>
+  <si>
+    <t>00:44:02</t>
   </si>
   <si>
     <t>23:58:08</t>
@@ -292,46 +304,55 @@
     <t>00:49:41</t>
   </si>
   <si>
-    <t>00:03:46</t>
-  </si>
-  <si>
-    <t>01:40:57</t>
-  </si>
-  <si>
-    <t>23:17:48</t>
+    <t>00:03:45</t>
+  </si>
+  <si>
+    <t>01:40:55</t>
+  </si>
+  <si>
+    <t>23:17:45</t>
+  </si>
+  <si>
+    <t>00:54:59</t>
+  </si>
+  <si>
+    <t>22:31:40</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>21°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
     <t>11°</t>
   </si>
   <si>
-    <t>01:17:57</t>
-  </si>
-  <si>
-    <t>01:23:02</t>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>01:23:03</t>
   </si>
   <si>
     <t>00:38:57</t>
@@ -349,28 +370,34 @@
     <t>00:43:39</t>
   </si>
   <si>
-    <t>23:59:26</t>
-  </si>
-  <si>
-    <t>01:32:29</t>
-  </si>
-  <si>
-    <t>23:15:12</t>
+    <t>23:59:24</t>
+  </si>
+  <si>
+    <t>01:32:27</t>
+  </si>
+  <si>
+    <t>23:15:09</t>
+  </si>
+  <si>
+    <t>00:48:12</t>
+  </si>
+  <si>
+    <t>22:30:56</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>3</t>
@@ -431,13 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,13 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,31 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1064,55 +1091,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L2" s="4">
-        <v>-10.3</v>
+        <v>-9.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O2" s="6">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>2</v>
-      </c>
-      <c r="R2" s="9">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1120,55 +1147,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.9</v>
+        <v>-13.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="6">
-        <v>46</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>36</v>
+        <v>126</v>
+      </c>
+      <c r="O3" s="9">
+        <v>40</v>
+      </c>
+      <c r="P3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>23</v>
+      </c>
+      <c r="R3" s="11">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1176,55 +1203,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-15.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O4" s="9">
+        <v>86</v>
+      </c>
+      <c r="P4" s="12">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="13">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-13.2</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O4" s="11">
-        <v>85</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>85</v>
+      <c r="R4" s="14">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1232,55 +1259,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.2</v>
+        <v>-9.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="11">
-        <v>42</v>
-      </c>
-      <c r="P5" s="13">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>4</v>
-      </c>
-      <c r="R5" s="7">
-        <v>11</v>
+        <v>126</v>
+      </c>
+      <c r="O5" s="9">
+        <v>67</v>
+      </c>
+      <c r="P5" s="10">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="15">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1288,55 +1315,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="L6" s="4">
-        <v>-9.5</v>
+        <v>-15.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O6" s="11">
-        <v>53</v>
-      </c>
-      <c r="P6" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>28</v>
-      </c>
-      <c r="R6" s="10">
-        <v>33</v>
+        <v>127</v>
+      </c>
+      <c r="O6" s="16">
+        <v>2</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1344,55 +1371,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.9</v>
+        <v>-12.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O7" s="11">
-        <v>71</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="16">
-        <v>71</v>
+        <v>126</v>
+      </c>
+      <c r="O7" s="16">
+        <v>5</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1400,55 +1427,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.9</v>
+        <v>-15.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="11">
-        <v>85</v>
+        <v>128</v>
+      </c>
+      <c r="O8" s="16">
+        <v>4</v>
       </c>
       <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
-        <v>85</v>
+        <v>4</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1456,54 +1483,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.1</v>
+        <v>-9.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O9" s="17">
+        <v>129</v>
+      </c>
+      <c r="O9" s="16">
         <v>11</v>
       </c>
-      <c r="P9" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="P9" s="17">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1512,54 +1539,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="L10" s="4">
-        <v>-9.1</v>
+        <v>-16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="O10" s="17">
-        <v>8</v>
+        <v>126</v>
+      </c>
+      <c r="O10" s="16">
+        <v>5</v>
       </c>
       <c r="P10" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1568,114 +1595,170 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L11" s="4">
-        <v>-16</v>
+        <v>-12.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O11" s="6">
-        <v>30</v>
-      </c>
-      <c r="P11" s="9">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="O11" s="16">
+        <v>3</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-15.5</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O12" s="16">
+        <v>4</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A12">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H12">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I12">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1694,12 +1777,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1716,22 +1799,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P12">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="168">
   <si>
     <t>Datum</t>
   </si>
@@ -103,22 +103,34 @@
     <t>20260626--02</t>
   </si>
   <si>
+    <t>20260627--01</t>
+  </si>
+  <si>
+    <t>20260627--02</t>
+  </si>
+  <si>
+    <t>20260627--03</t>
+  </si>
+  <si>
+    <t>20260627--04</t>
+  </si>
+  <si>
     <t>05:13</t>
   </si>
   <si>
     <t>04:38</t>
   </si>
   <si>
-    <t>03:45</t>
+    <t>03:44</t>
   </si>
   <si>
     <t>06:00</t>
   </si>
   <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>05:49</t>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>05:48</t>
   </si>
   <si>
     <t>05:32</t>
@@ -130,9 +142,24 @@
     <t>05:07</t>
   </si>
   <si>
+    <t>06:07</t>
+  </si>
+  <si>
     <t>04:30</t>
   </si>
   <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
     <t>04:20</t>
   </si>
   <si>
@@ -157,133 +184,190 @@
     <t>04:32</t>
   </si>
   <si>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>00:41</t>
+  </si>
+  <si>
     <t>01:19:43</t>
   </si>
   <si>
     <t>00:34:12</t>
   </si>
   <si>
-    <t>23:48:42</t>
-  </si>
-  <si>
-    <t>01:25:00</t>
-  </si>
-  <si>
-    <t>23:03:14</t>
+    <t>23:48:43</t>
+  </si>
+  <si>
+    <t>01:25:01</t>
+  </si>
+  <si>
+    <t>23:03:15</t>
   </si>
   <si>
     <t>00:39:15</t>
   </si>
   <si>
-    <t>23:53:28</t>
-  </si>
-  <si>
-    <t>01:30:18</t>
+    <t>23:53:29</t>
+  </si>
+  <si>
+    <t>01:30:19</t>
+  </si>
+  <si>
+    <t>23:07:43</t>
+  </si>
+  <si>
+    <t>00:44:23</t>
+  </si>
+  <si>
+    <t>22:21:56</t>
+  </si>
+  <si>
+    <t>23:58:25</t>
+  </si>
+  <si>
+    <t>01:35:31</t>
+  </si>
+  <si>
+    <t>21:36:11</t>
+  </si>
+  <si>
+    <t>23:12:26</t>
+  </si>
+  <si>
+    <t>01:22:10</t>
+  </si>
+  <si>
+    <t>00:36:48</t>
+  </si>
+  <si>
+    <t>23:51:33</t>
+  </si>
+  <si>
+    <t>01:27:17</t>
+  </si>
+  <si>
+    <t>23:06:38</t>
+  </si>
+  <si>
+    <t>00:41:34</t>
+  </si>
+  <si>
+    <t>23:55:51</t>
+  </si>
+  <si>
+    <t>01:32:33</t>
+  </si>
+  <si>
+    <t>23:10:10</t>
+  </si>
+  <si>
+    <t>00:46:38</t>
+  </si>
+  <si>
+    <t>22:24:33</t>
+  </si>
+  <si>
+    <t>00:00:40</t>
+  </si>
+  <si>
+    <t>01:37:50</t>
+  </si>
+  <si>
+    <t>21:39:05</t>
+  </si>
+  <si>
+    <t>23:14:42</t>
+  </si>
+  <si>
+    <t>01:24:46</t>
+  </si>
+  <si>
+    <t>00:39:06</t>
+  </si>
+  <si>
+    <t>23:53:25</t>
+  </si>
+  <si>
+    <t>01:30:16</t>
   </si>
   <si>
     <t>23:07:41</t>
   </si>
   <si>
-    <t>00:44:22</t>
-  </si>
-  <si>
-    <t>22:21:55</t>
-  </si>
-  <si>
-    <t>01:22:10</t>
-  </si>
-  <si>
-    <t>00:36:47</t>
-  </si>
-  <si>
-    <t>23:51:32</t>
-  </si>
-  <si>
-    <t>01:27:16</t>
-  </si>
-  <si>
-    <t>23:06:38</t>
-  </si>
-  <si>
-    <t>00:41:33</t>
-  </si>
-  <si>
-    <t>23:55:50</t>
-  </si>
-  <si>
-    <t>01:32:32</t>
-  </si>
-  <si>
-    <t>23:10:09</t>
-  </si>
-  <si>
-    <t>00:46:36</t>
-  </si>
-  <si>
-    <t>22:24:32</t>
-  </si>
-  <si>
-    <t>01:24:46</t>
-  </si>
-  <si>
-    <t>00:39:06</t>
-  </si>
-  <si>
-    <t>23:53:24</t>
-  </si>
-  <si>
-    <t>01:30:16</t>
-  </si>
-  <si>
     <t>00:44:27</t>
   </si>
   <si>
     <t>23:58:36</t>
   </si>
   <si>
-    <t>01:35:36</t>
-  </si>
-  <si>
-    <t>23:12:42</t>
-  </si>
-  <si>
-    <t>00:49:40</t>
-  </si>
-  <si>
-    <t>22:26:47</t>
+    <t>01:35:37</t>
+  </si>
+  <si>
+    <t>23:12:44</t>
+  </si>
+  <si>
+    <t>00:49:41</t>
+  </si>
+  <si>
+    <t>22:26:48</t>
+  </si>
+  <si>
+    <t>00:03:42</t>
+  </si>
+  <si>
+    <t>01:40:43</t>
+  </si>
+  <si>
+    <t>21:40:51</t>
+  </si>
+  <si>
+    <t>23:17:40</t>
   </si>
   <si>
     <t>01:27:23</t>
   </si>
   <si>
-    <t>00:41:25</t>
+    <t>00:41:26</t>
   </si>
   <si>
     <t>23:55:17</t>
   </si>
   <si>
-    <t>01:33:16</t>
-  </si>
-  <si>
-    <t>23:08:44</t>
+    <t>01:33:17</t>
+  </si>
+  <si>
+    <t>23:08:45</t>
   </si>
   <si>
     <t>00:47:22</t>
   </si>
   <si>
-    <t>00:01:22</t>
-  </si>
-  <si>
-    <t>01:38:40</t>
-  </si>
-  <si>
-    <t>23:15:16</t>
-  </si>
-  <si>
-    <t>00:52:44</t>
-  </si>
-  <si>
-    <t>22:29:02</t>
+    <t>00:01:23</t>
+  </si>
+  <si>
+    <t>01:38:41</t>
+  </si>
+  <si>
+    <t>23:15:17</t>
+  </si>
+  <si>
+    <t>00:52:45</t>
+  </si>
+  <si>
+    <t>22:29:03</t>
+  </si>
+  <si>
+    <t>00:06:44</t>
+  </si>
+  <si>
+    <t>01:43:36</t>
+  </si>
+  <si>
+    <t>21:42:37</t>
+  </si>
+  <si>
+    <t>23:20:39</t>
   </si>
   <si>
     <t>01:29:51</t>
@@ -292,31 +376,43 @@
     <t>00:44:02</t>
   </si>
   <si>
-    <t>23:58:08</t>
+    <t>23:58:09</t>
   </si>
   <si>
     <t>01:35:33</t>
   </si>
   <si>
-    <t>23:12:09</t>
-  </si>
-  <si>
-    <t>00:49:41</t>
-  </si>
-  <si>
-    <t>00:03:45</t>
-  </si>
-  <si>
-    <t>01:40:55</t>
-  </si>
-  <si>
-    <t>23:17:45</t>
-  </si>
-  <si>
-    <t>00:54:59</t>
-  </si>
-  <si>
-    <t>22:31:40</t>
+    <t>23:12:10</t>
+  </si>
+  <si>
+    <t>00:49:42</t>
+  </si>
+  <si>
+    <t>00:03:46</t>
+  </si>
+  <si>
+    <t>01:40:56</t>
+  </si>
+  <si>
+    <t>23:17:46</t>
+  </si>
+  <si>
+    <t>00:55:00</t>
+  </si>
+  <si>
+    <t>22:31:41</t>
+  </si>
+  <si>
+    <t>00:09:00</t>
+  </si>
+  <si>
+    <t>01:45:55</t>
+  </si>
+  <si>
+    <t>21:45:32</t>
+  </si>
+  <si>
+    <t>23:22:56</t>
   </si>
   <si>
     <t>15°</t>
@@ -352,16 +448,25 @@
     <t>2°</t>
   </si>
   <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
     <t>01:23:03</t>
   </si>
   <si>
-    <t>00:38:57</t>
+    <t>00:38:58</t>
   </si>
   <si>
     <t>23:54:48</t>
   </si>
   <si>
-    <t>01:27:51</t>
+    <t>01:27:52</t>
   </si>
   <si>
     <t>23:10:36</t>
@@ -370,19 +475,28 @@
     <t>00:43:39</t>
   </si>
   <si>
-    <t>23:59:24</t>
-  </si>
-  <si>
-    <t>01:32:27</t>
-  </si>
-  <si>
-    <t>23:15:09</t>
-  </si>
-  <si>
-    <t>00:48:12</t>
-  </si>
-  <si>
-    <t>22:30:56</t>
+    <t>23:59:25</t>
+  </si>
+  <si>
+    <t>01:32:28</t>
+  </si>
+  <si>
+    <t>23:15:10</t>
+  </si>
+  <si>
+    <t>00:48:13</t>
+  </si>
+  <si>
+    <t>22:30:58</t>
+  </si>
+  <si>
+    <t>00:04:01</t>
+  </si>
+  <si>
+    <t>01:37:05</t>
+  </si>
+  <si>
+    <t>23:19:58</t>
   </si>
   <si>
     <t>A+B</t>
@@ -437,7 +551,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,7 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +584,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +644,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,6 +748,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1094,52 +1244,52 @@
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="L2" s="4">
         <v>-9.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1150,52 +1300,52 @@
         <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="L3" s="4">
         <v>-13.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="O3" s="9">
-        <v>40</v>
-      </c>
-      <c r="P3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>23</v>
-      </c>
-      <c r="R3" s="11">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="P3" s="10">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>79</v>
+      </c>
+      <c r="R3" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1206,52 +1356,52 @@
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="L4" s="4">
         <v>-15.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O4" s="9">
-        <v>86</v>
-      </c>
-      <c r="P4" s="12">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>17</v>
+        <v>165</v>
+      </c>
+      <c r="O4" s="13">
+        <v>47</v>
+      </c>
+      <c r="P4" s="10">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
       </c>
       <c r="R4" s="14">
-        <v>86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1262,52 +1412,52 @@
         <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="L5" s="4">
         <v>-9.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="O5" s="9">
-        <v>67</v>
-      </c>
-      <c r="P5" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="15">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="P5" s="15">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="16">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1318,51 +1468,51 @@
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="L6" s="4">
         <v>-15.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O6" s="16">
-        <v>2</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
+        <v>165</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1374,51 +1524,51 @@
         <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="L7" s="4">
         <v>-12.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" s="16">
-        <v>5</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
+        <v>164</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1430,52 +1580,52 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="L8" s="4">
         <v>-15.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O8" s="16">
-        <v>4</v>
-      </c>
-      <c r="P8" s="8">
-        <v>4</v>
+        <v>166</v>
+      </c>
+      <c r="O8" s="9">
+        <v>49</v>
+      </c>
+      <c r="P8" s="15">
+        <v>17</v>
       </c>
       <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="17">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1486,51 +1636,51 @@
         <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="L9" s="4">
         <v>-9.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O9" s="16">
-        <v>11</v>
-      </c>
-      <c r="P9" s="17">
-        <v>11</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
+        <v>167</v>
+      </c>
+      <c r="O9" s="13">
+        <v>30</v>
+      </c>
+      <c r="P9" s="18">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1542,52 +1692,52 @@
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="L10" s="4">
         <v>-16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O10" s="16">
-        <v>5</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="O10" s="6">
+        <v>4</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1598,52 +1748,52 @@
         <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="L11" s="4">
         <v>-12.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O11" s="16">
-        <v>3</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="O11" s="6">
+        <v>6</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1654,111 +1804,335 @@
         <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="L12" s="4">
         <v>-15.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12" s="16">
+        <v>166</v>
+      </c>
+      <c r="O12" s="6">
+        <v>18</v>
+      </c>
+      <c r="P12" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-15</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O13" s="6">
+        <v>17</v>
+      </c>
+      <c r="P13" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>26</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O14" s="6">
+        <v>16</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="19">
         <v>4</v>
       </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O15" s="13">
+        <v>39</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>1</v>
+      </c>
+      <c r="R15" s="20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-16</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O16" s="9">
+        <v>59</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="19">
         <v>3</v>
+      </c>
+      <c r="R16" s="21">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A12">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H12">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1777,12 +2151,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N12">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1799,22 +2173,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O12">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="182">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260621--01</t>
-  </si>
-  <si>
     <t>20260622--01</t>
   </si>
   <si>
@@ -115,7 +112,13 @@
     <t>20260627--04</t>
   </si>
   <si>
-    <t>05:13</t>
+    <t>20260628--01</t>
+  </si>
+  <si>
+    <t>20260628--02</t>
+  </si>
+  <si>
+    <t>20260628--03</t>
   </si>
   <si>
     <t>04:38</t>
@@ -160,7 +163,10 @@
     <t>05:57</t>
   </si>
   <si>
-    <t>04:20</t>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>05:45</t>
   </si>
   <si>
     <t>02:28</t>
@@ -190,7 +196,7 @@
     <t>00:41</t>
   </si>
   <si>
-    <t>01:19:43</t>
+    <t>04:37</t>
   </si>
   <si>
     <t>00:34:12</t>
@@ -235,7 +241,13 @@
     <t>23:12:26</t>
   </si>
   <si>
-    <t>01:22:10</t>
+    <t>00:49:26</t>
+  </si>
+  <si>
+    <t>20:50:28</t>
+  </si>
+  <si>
+    <t>22:26:25</t>
   </si>
   <si>
     <t>00:36:48</t>
@@ -280,7 +292,13 @@
     <t>23:14:42</t>
   </si>
   <si>
-    <t>01:24:46</t>
+    <t>00:51:43</t>
+  </si>
+  <si>
+    <t>20:54:04</t>
+  </si>
+  <si>
+    <t>22:28:44</t>
   </si>
   <si>
     <t>00:39:06</t>
@@ -325,7 +343,13 @@
     <t>23:17:40</t>
   </si>
   <si>
-    <t>01:27:23</t>
+    <t>00:54:42</t>
+  </si>
+  <si>
+    <t>20:54:52</t>
+  </si>
+  <si>
+    <t>22:31:36</t>
   </si>
   <si>
     <t>00:41:26</t>
@@ -370,7 +394,13 @@
     <t>23:20:39</t>
   </si>
   <si>
-    <t>01:29:51</t>
+    <t>00:57:40</t>
+  </si>
+  <si>
+    <t>20:55:40</t>
+  </si>
+  <si>
+    <t>22:34:29</t>
   </si>
   <si>
     <t>00:44:02</t>
@@ -415,7 +445,13 @@
     <t>23:22:56</t>
   </si>
   <si>
-    <t>15°</t>
+    <t>00:59:57</t>
+  </si>
+  <si>
+    <t>20:59:16</t>
+  </si>
+  <si>
+    <t>22:36:48</t>
   </si>
   <si>
     <t>17°</t>
@@ -457,7 +493,7 @@
     <t>0°</t>
   </si>
   <si>
-    <t>01:23:03</t>
+    <t>19°</t>
   </si>
   <si>
     <t>00:38:58</t>
@@ -497,6 +533,12 @@
   </si>
   <si>
     <t>23:19:58</t>
+  </si>
+  <si>
+    <t>00:53:03</t>
+  </si>
+  <si>
+    <t>22:36:20</t>
   </si>
   <si>
     <t>A+B</t>
@@ -551,7 +593,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,7 +608,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,37 +656,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,43 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,12 +784,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1241,55 +1265,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.9</v>
+        <v>-13.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="O2" s="6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1297,55 +1321,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="L3" s="4">
-        <v>-13.2</v>
+        <v>-15.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="O3" s="9">
-        <v>100</v>
-      </c>
-      <c r="P3" s="10">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>79</v>
-      </c>
-      <c r="R3" s="12">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1353,55 +1377,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.2</v>
+        <v>-9.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="13">
-        <v>47</v>
-      </c>
-      <c r="P4" s="10">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="14">
-        <v>46</v>
+        <v>178</v>
+      </c>
+      <c r="O4" s="6">
+        <v>55</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1409,55 +1433,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="L5" s="4">
-        <v>-9.5</v>
+        <v>-15.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="O5" s="9">
-        <v>98</v>
-      </c>
-      <c r="P5" s="15">
-        <v>17</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="16">
-        <v>97</v>
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1465,55 +1489,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.9</v>
+        <v>-12.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="O6" s="9">
+        <v>5</v>
+      </c>
+      <c r="P6" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1521,55 +1545,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="L7" s="4">
-        <v>-12.9</v>
+        <v>-15.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
+        <v>180</v>
+      </c>
+      <c r="O7" s="9">
+        <v>3</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1577,55 +1601,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="L8" s="4">
-        <v>-15.1</v>
+        <v>-9.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="O8" s="9">
-        <v>49</v>
-      </c>
-      <c r="P8" s="15">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
       </c>
       <c r="Q8" s="7">
-        <v>11</v>
-      </c>
-      <c r="R8" s="17">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1633,54 +1657,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="L9" s="4">
-        <v>-9.1</v>
+        <v>-16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O9" s="13">
-        <v>30</v>
-      </c>
-      <c r="P9" s="18">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+        <v>178</v>
+      </c>
+      <c r="O9" s="12">
+        <v>29</v>
+      </c>
+      <c r="P9" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>10</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1689,55 +1713,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L10" s="4">
-        <v>-16</v>
+        <v>-12.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O10" s="6">
-        <v>4</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+        <v>178</v>
+      </c>
+      <c r="O10" s="12">
+        <v>27</v>
+      </c>
+      <c r="P10" s="7">
         <v>2</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>5</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1745,55 +1769,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="L11" s="4">
-        <v>-12.6</v>
+        <v>-15.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O11" s="6">
-        <v>6</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="19">
-        <v>4</v>
+        <v>180</v>
+      </c>
+      <c r="O11" s="9">
+        <v>3</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1801,55 +1825,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="L12" s="4">
-        <v>-15.5</v>
+        <v>-15</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O12" s="6">
-        <v>18</v>
+        <v>178</v>
+      </c>
+      <c r="O12" s="12">
+        <v>19</v>
       </c>
       <c r="P12" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1857,55 +1881,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="L13" s="4">
-        <v>-15</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O13" s="6">
-        <v>17</v>
-      </c>
-      <c r="P13" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="19">
-        <v>3</v>
+        <v>181</v>
+      </c>
+      <c r="O13" s="12">
+        <v>26</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1913,55 +1937,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="L14" s="4">
-        <v>-8.800000000000001</v>
+        <v>-13.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="O14" s="6">
-        <v>16</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="19">
-        <v>4</v>
+        <v>74</v>
+      </c>
+      <c r="P14" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>7</v>
+      </c>
+      <c r="R14" s="16">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1969,55 +1993,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-16</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O15" s="12">
         <v>46</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-13.6</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O15" s="13">
-        <v>39</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>1</v>
-      </c>
-      <c r="R15" s="20">
-        <v>39</v>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="17">
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2028,111 +2052,223 @@
         <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="L16" s="4">
-        <v>-16</v>
+        <v>-12.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O16" s="9">
-        <v>59</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>3</v>
-      </c>
-      <c r="R16" s="21">
+        <v>178</v>
+      </c>
+      <c r="O16" s="12">
+        <v>33</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>11</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-10.5</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O17" s="6">
         <v>58</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-15.7</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O18" s="6">
+        <v>80</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="19">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A18">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2151,12 +2287,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2173,22 +2309,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O18">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P18">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q18">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R18">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="196">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260622--01</t>
-  </si>
-  <si>
-    <t>20260622--02</t>
-  </si>
-  <si>
     <t>20260623--01</t>
   </si>
   <si>
@@ -121,424 +115,472 @@
     <t>20260628--03</t>
   </si>
   <si>
+    <t>20260629--01</t>
+  </si>
+  <si>
+    <t>20260629--02</t>
+  </si>
+  <si>
+    <t>20260629--03</t>
+  </si>
+  <si>
+    <t>20260629--04</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>01:39</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:44</t>
+  </si>
+  <si>
+    <t>00:07</t>
+  </si>
+  <si>
+    <t>04:32</t>
+  </si>
+  <si>
+    <t>02:44</t>
+  </si>
+  <si>
+    <t>00:41</t>
+  </si>
+  <si>
     <t>04:38</t>
   </si>
   <si>
-    <t>03:44</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>02:07</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>06:07</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>01:36</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>02:28</t>
-  </si>
-  <si>
-    <t>00:29</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>00:07</t>
-  </si>
-  <si>
-    <t>04:32</t>
-  </si>
-  <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:41</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>00:34:12</t>
-  </si>
-  <si>
-    <t>23:48:43</t>
-  </si>
-  <si>
-    <t>01:25:01</t>
-  </si>
-  <si>
-    <t>23:03:15</t>
-  </si>
-  <si>
-    <t>00:39:15</t>
-  </si>
-  <si>
-    <t>23:53:29</t>
-  </si>
-  <si>
-    <t>01:30:19</t>
-  </si>
-  <si>
-    <t>23:07:43</t>
-  </si>
-  <si>
-    <t>00:44:23</t>
-  </si>
-  <si>
-    <t>22:21:56</t>
-  </si>
-  <si>
-    <t>23:58:25</t>
-  </si>
-  <si>
-    <t>01:35:31</t>
-  </si>
-  <si>
-    <t>21:36:11</t>
-  </si>
-  <si>
-    <t>23:12:26</t>
-  </si>
-  <si>
-    <t>00:49:26</t>
-  </si>
-  <si>
-    <t>20:50:28</t>
-  </si>
-  <si>
-    <t>22:26:25</t>
-  </si>
-  <si>
-    <t>00:36:48</t>
-  </si>
-  <si>
-    <t>23:51:33</t>
-  </si>
-  <si>
-    <t>01:27:17</t>
-  </si>
-  <si>
-    <t>23:06:38</t>
-  </si>
-  <si>
-    <t>00:41:34</t>
-  </si>
-  <si>
-    <t>23:55:51</t>
+    <t>02:12</t>
+  </si>
+  <si>
+    <t>01:25:02</t>
+  </si>
+  <si>
+    <t>23:03:18</t>
+  </si>
+  <si>
+    <t>00:39:19</t>
+  </si>
+  <si>
+    <t>23:53:34</t>
+  </si>
+  <si>
+    <t>01:30:24</t>
+  </si>
+  <si>
+    <t>23:07:50</t>
+  </si>
+  <si>
+    <t>00:44:31</t>
+  </si>
+  <si>
+    <t>22:22:07</t>
+  </si>
+  <si>
+    <t>23:58:36</t>
+  </si>
+  <si>
+    <t>01:35:42</t>
+  </si>
+  <si>
+    <t>21:36:25</t>
+  </si>
+  <si>
+    <t>23:12:40</t>
+  </si>
+  <si>
+    <t>00:49:41</t>
+  </si>
+  <si>
+    <t>20:50:46</t>
+  </si>
+  <si>
+    <t>22:26:43</t>
+  </si>
+  <si>
+    <t>00:03:38</t>
+  </si>
+  <si>
+    <t>01:40:56</t>
+  </si>
+  <si>
+    <t>21:40:46</t>
+  </si>
+  <si>
+    <t>23:17:33</t>
+  </si>
+  <si>
+    <t>01:27:18</t>
+  </si>
+  <si>
+    <t>23:06:41</t>
+  </si>
+  <si>
+    <t>00:41:37</t>
+  </si>
+  <si>
+    <t>23:55:56</t>
+  </si>
+  <si>
+    <t>01:32:39</t>
+  </si>
+  <si>
+    <t>23:10:18</t>
+  </si>
+  <si>
+    <t>00:46:45</t>
+  </si>
+  <si>
+    <t>22:24:44</t>
+  </si>
+  <si>
+    <t>00:00:51</t>
+  </si>
+  <si>
+    <t>01:38:01</t>
+  </si>
+  <si>
+    <t>21:39:18</t>
+  </si>
+  <si>
+    <t>23:14:56</t>
+  </si>
+  <si>
+    <t>00:51:58</t>
+  </si>
+  <si>
+    <t>20:54:20</t>
+  </si>
+  <si>
+    <t>22:29:02</t>
+  </si>
+  <si>
+    <t>00:05:53</t>
+  </si>
+  <si>
+    <t>01:43:34</t>
+  </si>
+  <si>
+    <t>21:43:08</t>
+  </si>
+  <si>
+    <t>23:19:48</t>
+  </si>
+  <si>
+    <t>01:30:18</t>
+  </si>
+  <si>
+    <t>23:07:44</t>
+  </si>
+  <si>
+    <t>23:58:42</t>
+  </si>
+  <si>
+    <t>23:12:51</t>
+  </si>
+  <si>
+    <t>00:49:49</t>
+  </si>
+  <si>
+    <t>22:26:59</t>
+  </si>
+  <si>
+    <t>00:03:53</t>
+  </si>
+  <si>
+    <t>01:40:54</t>
+  </si>
+  <si>
+    <t>21:41:05</t>
+  </si>
+  <si>
+    <t>23:17:54</t>
+  </si>
+  <si>
+    <t>00:54:56</t>
+  </si>
+  <si>
+    <t>20:55:09</t>
+  </si>
+  <si>
+    <t>22:31:54</t>
+  </si>
+  <si>
+    <t>00:08:55</t>
+  </si>
+  <si>
+    <t>01:45:49</t>
+  </si>
+  <si>
+    <t>21:45:52</t>
+  </si>
+  <si>
+    <t>23:22:51</t>
+  </si>
+  <si>
+    <t>01:33:18</t>
+  </si>
+  <si>
+    <t>23:08:48</t>
+  </si>
+  <si>
+    <t>00:47:26</t>
+  </si>
+  <si>
+    <t>00:01:28</t>
+  </si>
+  <si>
+    <t>01:38:46</t>
+  </si>
+  <si>
+    <t>23:15:25</t>
+  </si>
+  <si>
+    <t>00:52:53</t>
+  </si>
+  <si>
+    <t>22:29:14</t>
+  </si>
+  <si>
+    <t>00:06:55</t>
+  </si>
+  <si>
+    <t>01:43:47</t>
+  </si>
+  <si>
+    <t>21:42:51</t>
+  </si>
+  <si>
+    <t>23:20:53</t>
+  </si>
+  <si>
+    <t>00:57:54</t>
+  </si>
+  <si>
+    <t>20:55:59</t>
+  </si>
+  <si>
+    <t>22:34:47</t>
+  </si>
+  <si>
+    <t>00:11:57</t>
+  </si>
+  <si>
+    <t>01:48:03</t>
+  </si>
+  <si>
+    <t>21:48:36</t>
+  </si>
+  <si>
+    <t>23:25:54</t>
+  </si>
+  <si>
+    <t>01:35:35</t>
+  </si>
+  <si>
+    <t>23:12:13</t>
+  </si>
+  <si>
+    <t>00:49:45</t>
+  </si>
+  <si>
+    <t>00:03:51</t>
+  </si>
+  <si>
+    <t>01:41:01</t>
+  </si>
+  <si>
+    <t>23:17:53</t>
+  </si>
+  <si>
+    <t>00:55:08</t>
+  </si>
+  <si>
+    <t>22:31:52</t>
+  </si>
+  <si>
+    <t>00:09:11</t>
+  </si>
+  <si>
+    <t>01:46:06</t>
+  </si>
+  <si>
+    <t>21:45:46</t>
+  </si>
+  <si>
+    <t>23:23:10</t>
+  </si>
+  <si>
+    <t>01:00:11</t>
+  </si>
+  <si>
+    <t>20:59:34</t>
+  </si>
+  <si>
+    <t>22:37:06</t>
+  </si>
+  <si>
+    <t>00:14:12</t>
+  </si>
+  <si>
+    <t>01:50:41</t>
+  </si>
+  <si>
+    <t>21:50:59</t>
+  </si>
+  <si>
+    <t>23:28:09</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>01:27:53</t>
+  </si>
+  <si>
+    <t>23:10:39</t>
+  </si>
+  <si>
+    <t>00:43:42</t>
+  </si>
+  <si>
+    <t>23:59:30</t>
   </si>
   <si>
     <t>01:32:33</t>
   </si>
   <si>
-    <t>23:10:10</t>
-  </si>
-  <si>
-    <t>00:46:38</t>
-  </si>
-  <si>
-    <t>22:24:33</t>
-  </si>
-  <si>
-    <t>00:00:40</t>
-  </si>
-  <si>
-    <t>01:37:50</t>
-  </si>
-  <si>
-    <t>21:39:05</t>
-  </si>
-  <si>
-    <t>23:14:42</t>
-  </si>
-  <si>
-    <t>00:51:43</t>
-  </si>
-  <si>
-    <t>20:54:04</t>
-  </si>
-  <si>
-    <t>22:28:44</t>
-  </si>
-  <si>
-    <t>00:39:06</t>
-  </si>
-  <si>
-    <t>23:53:25</t>
-  </si>
-  <si>
-    <t>01:30:16</t>
-  </si>
-  <si>
-    <t>23:07:41</t>
-  </si>
-  <si>
-    <t>00:44:27</t>
-  </si>
-  <si>
-    <t>23:58:36</t>
-  </si>
-  <si>
-    <t>01:35:37</t>
-  </si>
-  <si>
-    <t>23:12:44</t>
-  </si>
-  <si>
-    <t>00:49:41</t>
-  </si>
-  <si>
-    <t>22:26:48</t>
-  </si>
-  <si>
-    <t>00:03:42</t>
-  </si>
-  <si>
-    <t>01:40:43</t>
-  </si>
-  <si>
-    <t>21:40:51</t>
-  </si>
-  <si>
-    <t>23:17:40</t>
-  </si>
-  <si>
-    <t>00:54:42</t>
-  </si>
-  <si>
-    <t>20:54:52</t>
-  </si>
-  <si>
-    <t>22:31:36</t>
-  </si>
-  <si>
-    <t>00:41:26</t>
-  </si>
-  <si>
-    <t>23:55:17</t>
-  </si>
-  <si>
-    <t>01:33:17</t>
-  </si>
-  <si>
-    <t>23:08:45</t>
-  </si>
-  <si>
-    <t>00:47:22</t>
-  </si>
-  <si>
-    <t>00:01:23</t>
-  </si>
-  <si>
-    <t>01:38:41</t>
-  </si>
-  <si>
-    <t>23:15:17</t>
-  </si>
-  <si>
-    <t>00:52:45</t>
-  </si>
-  <si>
-    <t>22:29:03</t>
-  </si>
-  <si>
-    <t>00:06:44</t>
-  </si>
-  <si>
-    <t>01:43:36</t>
-  </si>
-  <si>
-    <t>21:42:37</t>
-  </si>
-  <si>
-    <t>23:20:39</t>
-  </si>
-  <si>
-    <t>00:57:40</t>
-  </si>
-  <si>
-    <t>20:55:40</t>
-  </si>
-  <si>
-    <t>22:34:29</t>
-  </si>
-  <si>
-    <t>00:44:02</t>
-  </si>
-  <si>
-    <t>23:58:09</t>
-  </si>
-  <si>
-    <t>01:35:33</t>
-  </si>
-  <si>
-    <t>23:12:10</t>
-  </si>
-  <si>
-    <t>00:49:42</t>
-  </si>
-  <si>
-    <t>00:03:46</t>
-  </si>
-  <si>
-    <t>01:40:56</t>
-  </si>
-  <si>
-    <t>23:17:46</t>
-  </si>
-  <si>
-    <t>00:55:00</t>
-  </si>
-  <si>
-    <t>22:31:41</t>
-  </si>
-  <si>
-    <t>00:09:00</t>
-  </si>
-  <si>
-    <t>01:45:55</t>
-  </si>
-  <si>
-    <t>21:45:32</t>
-  </si>
-  <si>
-    <t>23:22:56</t>
-  </si>
-  <si>
-    <t>00:59:57</t>
-  </si>
-  <si>
-    <t>20:59:16</t>
-  </si>
-  <si>
-    <t>22:36:48</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>00:38:58</t>
-  </si>
-  <si>
-    <t>23:54:48</t>
-  </si>
-  <si>
-    <t>01:27:52</t>
-  </si>
-  <si>
-    <t>23:10:36</t>
-  </si>
-  <si>
-    <t>00:43:39</t>
-  </si>
-  <si>
-    <t>23:59:25</t>
-  </si>
-  <si>
-    <t>01:32:28</t>
-  </si>
-  <si>
-    <t>23:15:10</t>
-  </si>
-  <si>
-    <t>00:48:13</t>
-  </si>
-  <si>
-    <t>22:30:58</t>
-  </si>
-  <si>
-    <t>00:04:01</t>
-  </si>
-  <si>
-    <t>01:37:05</t>
-  </si>
-  <si>
-    <t>23:19:58</t>
-  </si>
-  <si>
-    <t>00:53:03</t>
-  </si>
-  <si>
-    <t>22:36:20</t>
+    <t>23:15:18</t>
+  </si>
+  <si>
+    <t>00:48:21</t>
+  </si>
+  <si>
+    <t>22:31:08</t>
+  </si>
+  <si>
+    <t>00:04:11</t>
+  </si>
+  <si>
+    <t>01:37:15</t>
+  </si>
+  <si>
+    <t>23:20:12</t>
+  </si>
+  <si>
+    <t>00:53:16</t>
+  </si>
+  <si>
+    <t>22:36:38</t>
+  </si>
+  <si>
+    <t>00:09:45</t>
+  </si>
+  <si>
+    <t>01:42:53</t>
+  </si>
+  <si>
+    <t>21:42:30</t>
+  </si>
+  <si>
+    <t>23:27:22</t>
   </si>
   <si>
     <t>A+B</t>
@@ -593,7 +635,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -608,7 +650,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,43 +686,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +704,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,13 +734,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -784,6 +850,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1187,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1265,55 +1343,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.2</v>
+        <v>-9.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>62</v>
+        <v>20</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>7</v>
+      </c>
+      <c r="R2" s="9">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1321,55 +1399,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O3" s="9">
+        <v>193</v>
+      </c>
+      <c r="O3" s="10">
         <v>4</v>
       </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
+      <c r="P3" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
         <v>4</v>
+      </c>
+      <c r="R3" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1377,55 +1455,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="L4" s="4">
-        <v>-9.5</v>
+        <v>-12.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" s="6">
-        <v>55</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
+        <v>192</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
+      </c>
+      <c r="P4" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
         <v>0</v>
       </c>
       <c r="R4" s="11">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1433,55 +1511,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.9</v>
+        <v>-15.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
+        <v>194</v>
+      </c>
+      <c r="O5" s="6">
+        <v>22</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
         <v>0</v>
       </c>
       <c r="R5" s="7">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1489,55 +1567,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.9</v>
+        <v>-9.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O6" s="9">
-        <v>5</v>
-      </c>
-      <c r="P6" s="10">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
+        <v>195</v>
+      </c>
+      <c r="O6" s="10">
         <v>3</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1545,55 +1623,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.1</v>
+        <v>-16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O7" s="9">
-        <v>3</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>2</v>
+        <v>192</v>
+      </c>
+      <c r="O7" s="10">
+        <v>17</v>
+      </c>
+      <c r="P7" s="12">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1604,52 +1682,52 @@
         <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="L8" s="4">
-        <v>-9.1</v>
+        <v>-12.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O8" s="9">
-        <v>3</v>
+        <v>192</v>
+      </c>
+      <c r="O8" s="6">
+        <v>19</v>
       </c>
       <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1657,54 +1735,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="L9" s="4">
-        <v>-16</v>
+        <v>-15.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O9" s="12">
-        <v>29</v>
-      </c>
-      <c r="P9" s="10">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>10</v>
-      </c>
-      <c r="R9" s="7">
+        <v>194</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1713,54 +1791,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L10" s="4">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O10" s="12">
-        <v>27</v>
-      </c>
-      <c r="P10" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>5</v>
-      </c>
-      <c r="R10" s="7">
+        <v>192</v>
+      </c>
+      <c r="O10" s="10">
+        <v>16</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1769,55 +1847,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="L11" s="4">
-        <v>-15.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O11" s="9">
-        <v>3</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>2</v>
+        <v>195</v>
+      </c>
+      <c r="O11" s="6">
+        <v>25</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1825,55 +1903,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="L12" s="4">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O12" s="12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="14">
-        <v>14</v>
+        <v>193</v>
+      </c>
+      <c r="O12" s="6">
+        <v>20</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1881,55 +1959,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>157</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L13" s="4">
-        <v>-8.800000000000001</v>
+        <v>-16</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O13" s="12">
-        <v>26</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15">
-        <v>23</v>
+        <v>192</v>
+      </c>
+      <c r="O13" s="10">
+        <v>12</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1937,55 +2015,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="L14" s="4">
-        <v>-13.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O14" s="6">
-        <v>74</v>
-      </c>
-      <c r="P14" s="10">
-        <v>6</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>7</v>
-      </c>
-      <c r="R14" s="16">
-        <v>74</v>
+        <v>192</v>
+      </c>
+      <c r="O14" s="10">
+        <v>5</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1993,55 +2071,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="L15" s="4">
-        <v>-16</v>
+        <v>-10.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O15" s="12">
-        <v>46</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>46</v>
+        <v>193</v>
+      </c>
+      <c r="O15" s="13">
+        <v>79</v>
+      </c>
+      <c r="P15" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>24</v>
+      </c>
+      <c r="R15" s="15">
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2049,55 +2127,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="L16" s="4">
-        <v>-12.4</v>
+        <v>-15.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O16" s="12">
-        <v>33</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="18">
-        <v>33</v>
+        <v>194</v>
+      </c>
+      <c r="O16" s="13">
+        <v>56</v>
+      </c>
+      <c r="P16" s="9">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>37</v>
+      </c>
+      <c r="R16" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2105,55 +2183,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="L17" s="4">
-        <v>-10.5</v>
+        <v>-14.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O17" s="6">
-        <v>58</v>
-      </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>58</v>
+        <v>192</v>
+      </c>
+      <c r="O17" s="13">
+        <v>89</v>
+      </c>
+      <c r="P17" s="17">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>61</v>
+      </c>
+      <c r="R17" s="15">
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2161,114 +2239,226 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O18" s="13">
+        <v>100</v>
+      </c>
+      <c r="P18" s="19">
+        <v>47</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>69</v>
+      </c>
+      <c r="R18" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-13.9</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O19" s="13">
+        <v>91</v>
+      </c>
+      <c r="P19" s="21">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>2</v>
+      </c>
+      <c r="R19" s="22">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>31</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-15.7</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O18" s="6">
+      <c r="D20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-16.1</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O20" s="13">
         <v>80</v>
       </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="19">
-        <v>80</v>
+      <c r="P20" s="21">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>0</v>
+      </c>
+      <c r="R20" s="23">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A18">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J18">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K18">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L18">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2287,12 +2477,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N18">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2309,22 +2499,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O18">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P18">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q18">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R18">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="207">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260623--01</t>
-  </si>
-  <si>
-    <t>20260623--02</t>
-  </si>
-  <si>
     <t>20260624--01</t>
   </si>
   <si>
@@ -127,10 +121,13 @@
     <t>20260629--04</t>
   </si>
   <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>02:07</t>
+    <t>20260630--01</t>
+  </si>
+  <si>
+    <t>20260630--02</t>
+  </si>
+  <si>
+    <t>20260630--03</t>
   </si>
   <si>
     <t>05:49</t>
@@ -139,19 +136,19 @@
     <t>05:32</t>
   </si>
   <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
     <t>06:07</t>
   </si>
   <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
     <t>04:30</t>
   </si>
   <si>
-    <t>06:04</t>
+    <t>06:03</t>
   </si>
   <si>
     <t>05:46</t>
@@ -166,7 +163,7 @@
     <t>05:56</t>
   </si>
   <si>
-    <t>01:39</t>
+    <t>01:38</t>
   </si>
   <si>
     <t>05:45</t>
@@ -175,28 +172,31 @@
     <t>04:29</t>
   </si>
   <si>
-    <t>05:28</t>
+    <t>05:27</t>
   </si>
   <si>
     <t>06:06</t>
   </si>
   <si>
-    <t>05:25</t>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>03:43</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:44</t>
-  </si>
-  <si>
-    <t>00:07</t>
-  </si>
-  <si>
-    <t>04:32</t>
-  </si>
-  <si>
-    <t>02:44</t>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>02:43</t>
   </si>
   <si>
     <t>00:41</t>
@@ -205,13 +205,16 @@
     <t>04:38</t>
   </si>
   <si>
-    <t>02:12</t>
-  </si>
-  <si>
-    <t>01:25:02</t>
-  </si>
-  <si>
-    <t>23:03:18</t>
+    <t>02:11</t>
+  </si>
+  <si>
+    <t>01:43</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>00:17</t>
   </si>
   <si>
     <t>00:39:19</t>
@@ -229,154 +232,166 @@
     <t>00:44:31</t>
   </si>
   <si>
-    <t>22:22:07</t>
+    <t>22:22:06</t>
   </si>
   <si>
     <t>23:58:36</t>
   </si>
   <si>
+    <t>01:35:41</t>
+  </si>
+  <si>
+    <t>21:36:24</t>
+  </si>
+  <si>
+    <t>23:12:39</t>
+  </si>
+  <si>
+    <t>00:49:40</t>
+  </si>
+  <si>
+    <t>20:50:44</t>
+  </si>
+  <si>
+    <t>22:26:42</t>
+  </si>
+  <si>
+    <t>00:03:37</t>
+  </si>
+  <si>
+    <t>01:40:54</t>
+  </si>
+  <si>
+    <t>21:40:44</t>
+  </si>
+  <si>
+    <t>23:17:31</t>
+  </si>
+  <si>
+    <t>00:54:44</t>
+  </si>
+  <si>
+    <t>20:54:46</t>
+  </si>
+  <si>
+    <t>22:31:24</t>
+  </si>
+  <si>
+    <t>00:41:37</t>
+  </si>
+  <si>
+    <t>23:55:56</t>
+  </si>
+  <si>
+    <t>01:32:38</t>
+  </si>
+  <si>
+    <t>23:10:18</t>
+  </si>
+  <si>
+    <t>00:46:45</t>
+  </si>
+  <si>
+    <t>22:24:43</t>
+  </si>
+  <si>
+    <t>00:00:51</t>
+  </si>
+  <si>
+    <t>01:38:00</t>
+  </si>
+  <si>
+    <t>21:39:17</t>
+  </si>
+  <si>
+    <t>23:14:55</t>
+  </si>
+  <si>
+    <t>00:51:57</t>
+  </si>
+  <si>
+    <t>20:54:19</t>
+  </si>
+  <si>
+    <t>22:29:00</t>
+  </si>
+  <si>
+    <t>00:05:52</t>
+  </si>
+  <si>
+    <t>01:43:32</t>
+  </si>
+  <si>
+    <t>21:43:06</t>
+  </si>
+  <si>
+    <t>23:19:46</t>
+  </si>
+  <si>
+    <t>00:57:13</t>
+  </si>
+  <si>
+    <t>20:57:15</t>
+  </si>
+  <si>
+    <t>22:33:38</t>
+  </si>
+  <si>
+    <t>23:58:41</t>
+  </si>
+  <si>
     <t>01:35:42</t>
   </si>
   <si>
-    <t>21:36:25</t>
-  </si>
-  <si>
-    <t>23:12:40</t>
-  </si>
-  <si>
-    <t>00:49:41</t>
-  </si>
-  <si>
-    <t>20:50:46</t>
-  </si>
-  <si>
-    <t>22:26:43</t>
-  </si>
-  <si>
-    <t>00:03:38</t>
-  </si>
-  <si>
-    <t>01:40:56</t>
-  </si>
-  <si>
-    <t>21:40:46</t>
-  </si>
-  <si>
-    <t>23:17:33</t>
-  </si>
-  <si>
-    <t>01:27:18</t>
-  </si>
-  <si>
-    <t>23:06:41</t>
-  </si>
-  <si>
-    <t>00:41:37</t>
-  </si>
-  <si>
-    <t>23:55:56</t>
-  </si>
-  <si>
-    <t>01:32:39</t>
-  </si>
-  <si>
-    <t>23:10:18</t>
-  </si>
-  <si>
-    <t>00:46:45</t>
-  </si>
-  <si>
-    <t>22:24:44</t>
-  </si>
-  <si>
-    <t>00:00:51</t>
-  </si>
-  <si>
-    <t>01:38:01</t>
-  </si>
-  <si>
-    <t>21:39:18</t>
-  </si>
-  <si>
-    <t>23:14:56</t>
-  </si>
-  <si>
-    <t>00:51:58</t>
-  </si>
-  <si>
-    <t>20:54:20</t>
-  </si>
-  <si>
-    <t>22:29:02</t>
-  </si>
-  <si>
-    <t>00:05:53</t>
-  </si>
-  <si>
-    <t>01:43:34</t>
-  </si>
-  <si>
-    <t>21:43:08</t>
-  </si>
-  <si>
-    <t>23:19:48</t>
-  </si>
-  <si>
-    <t>01:30:18</t>
-  </si>
-  <si>
-    <t>23:07:44</t>
-  </si>
-  <si>
-    <t>23:58:42</t>
-  </si>
-  <si>
-    <t>23:12:51</t>
-  </si>
-  <si>
-    <t>00:49:49</t>
-  </si>
-  <si>
-    <t>22:26:59</t>
-  </si>
-  <si>
-    <t>00:03:53</t>
-  </si>
-  <si>
-    <t>01:40:54</t>
-  </si>
-  <si>
-    <t>21:41:05</t>
-  </si>
-  <si>
-    <t>23:17:54</t>
-  </si>
-  <si>
-    <t>00:54:56</t>
-  </si>
-  <si>
-    <t>20:55:09</t>
-  </si>
-  <si>
-    <t>22:31:54</t>
-  </si>
-  <si>
-    <t>00:08:55</t>
-  </si>
-  <si>
-    <t>01:45:49</t>
-  </si>
-  <si>
-    <t>21:45:52</t>
-  </si>
-  <si>
-    <t>23:22:51</t>
-  </si>
-  <si>
-    <t>01:33:18</t>
-  </si>
-  <si>
-    <t>23:08:48</t>
+    <t>23:12:50</t>
+  </si>
+  <si>
+    <t>00:49:48</t>
+  </si>
+  <si>
+    <t>22:26:58</t>
+  </si>
+  <si>
+    <t>00:03:52</t>
+  </si>
+  <si>
+    <t>01:40:53</t>
+  </si>
+  <si>
+    <t>21:41:04</t>
+  </si>
+  <si>
+    <t>23:17:53</t>
+  </si>
+  <si>
+    <t>00:54:55</t>
+  </si>
+  <si>
+    <t>20:55:08</t>
+  </si>
+  <si>
+    <t>22:31:53</t>
+  </si>
+  <si>
+    <t>00:08:53</t>
+  </si>
+  <si>
+    <t>01:45:47</t>
+  </si>
+  <si>
+    <t>21:45:50</t>
+  </si>
+  <si>
+    <t>23:22:49</t>
+  </si>
+  <si>
+    <t>00:59:45</t>
+  </si>
+  <si>
+    <t>20:59:45</t>
+  </si>
+  <si>
+    <t>22:36:41</t>
   </si>
   <si>
     <t>00:47:26</t>
@@ -391,49 +406,52 @@
     <t>23:15:25</t>
   </si>
   <si>
-    <t>00:52:53</t>
-  </si>
-  <si>
-    <t>22:29:14</t>
-  </si>
-  <si>
-    <t>00:06:55</t>
-  </si>
-  <si>
-    <t>01:43:47</t>
-  </si>
-  <si>
-    <t>21:42:51</t>
-  </si>
-  <si>
-    <t>23:20:53</t>
-  </si>
-  <si>
-    <t>00:57:54</t>
-  </si>
-  <si>
-    <t>20:55:59</t>
-  </si>
-  <si>
-    <t>22:34:47</t>
-  </si>
-  <si>
-    <t>00:11:57</t>
-  </si>
-  <si>
-    <t>01:48:03</t>
-  </si>
-  <si>
-    <t>21:48:36</t>
-  </si>
-  <si>
-    <t>23:25:54</t>
-  </si>
-  <si>
-    <t>01:35:35</t>
-  </si>
-  <si>
-    <t>23:12:13</t>
+    <t>00:52:52</t>
+  </si>
+  <si>
+    <t>22:29:13</t>
+  </si>
+  <si>
+    <t>00:06:54</t>
+  </si>
+  <si>
+    <t>01:43:46</t>
+  </si>
+  <si>
+    <t>21:42:50</t>
+  </si>
+  <si>
+    <t>23:20:52</t>
+  </si>
+  <si>
+    <t>00:57:53</t>
+  </si>
+  <si>
+    <t>20:55:57</t>
+  </si>
+  <si>
+    <t>22:34:45</t>
+  </si>
+  <si>
+    <t>00:11:55</t>
+  </si>
+  <si>
+    <t>01:48:01</t>
+  </si>
+  <si>
+    <t>21:48:33</t>
+  </si>
+  <si>
+    <t>23:25:52</t>
+  </si>
+  <si>
+    <t>01:02:18</t>
+  </si>
+  <si>
+    <t>21:02:15</t>
+  </si>
+  <si>
+    <t>22:39:44</t>
   </si>
   <si>
     <t>00:49:45</t>
@@ -445,81 +463,84 @@
     <t>01:41:01</t>
   </si>
   <si>
-    <t>23:17:53</t>
-  </si>
-  <si>
-    <t>00:55:08</t>
-  </si>
-  <si>
-    <t>22:31:52</t>
-  </si>
-  <si>
-    <t>00:09:11</t>
+    <t>00:55:07</t>
+  </si>
+  <si>
+    <t>22:31:51</t>
+  </si>
+  <si>
+    <t>00:09:10</t>
   </si>
   <si>
     <t>01:46:06</t>
   </si>
   <si>
-    <t>21:45:46</t>
-  </si>
-  <si>
-    <t>23:23:10</t>
-  </si>
-  <si>
-    <t>01:00:11</t>
-  </si>
-  <si>
-    <t>20:59:34</t>
-  </si>
-  <si>
-    <t>22:37:06</t>
-  </si>
-  <si>
-    <t>00:14:12</t>
-  </si>
-  <si>
-    <t>01:50:41</t>
-  </si>
-  <si>
-    <t>21:50:59</t>
-  </si>
-  <si>
-    <t>23:28:09</t>
+    <t>21:45:45</t>
+  </si>
+  <si>
+    <t>23:23:09</t>
+  </si>
+  <si>
+    <t>01:00:10</t>
+  </si>
+  <si>
+    <t>20:59:32</t>
+  </si>
+  <si>
+    <t>22:37:05</t>
+  </si>
+  <si>
+    <t>00:14:10</t>
+  </si>
+  <si>
+    <t>01:50:40</t>
+  </si>
+  <si>
+    <t>21:50:57</t>
+  </si>
+  <si>
+    <t>23:28:06</t>
+  </si>
+  <si>
+    <t>01:04:47</t>
+  </si>
+  <si>
+    <t>21:04:45</t>
+  </si>
+  <si>
+    <t>22:41:59</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>0°</t>
   </si>
   <si>
     <t>14°</t>
   </si>
   <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
     <t>19°</t>
   </si>
   <si>
@@ -532,13 +553,16 @@
     <t>7°</t>
   </si>
   <si>
-    <t>01:27:53</t>
-  </si>
-  <si>
-    <t>23:10:39</t>
-  </si>
-  <si>
-    <t>00:43:42</t>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>00:43:43</t>
   </si>
   <si>
     <t>23:59:30</t>
@@ -547,13 +571,13 @@
     <t>01:32:33</t>
   </si>
   <si>
-    <t>23:15:18</t>
+    <t>23:15:17</t>
   </si>
   <si>
     <t>00:48:21</t>
   </si>
   <si>
-    <t>22:31:08</t>
+    <t>22:31:07</t>
   </si>
   <si>
     <t>00:04:11</t>
@@ -562,25 +586,34 @@
     <t>01:37:15</t>
   </si>
   <si>
-    <t>23:20:12</t>
-  </si>
-  <si>
-    <t>00:53:16</t>
-  </si>
-  <si>
-    <t>22:36:38</t>
-  </si>
-  <si>
-    <t>00:09:45</t>
-  </si>
-  <si>
-    <t>01:42:53</t>
-  </si>
-  <si>
-    <t>21:42:30</t>
-  </si>
-  <si>
-    <t>23:27:22</t>
+    <t>23:20:11</t>
+  </si>
+  <si>
+    <t>00:53:15</t>
+  </si>
+  <si>
+    <t>22:36:36</t>
+  </si>
+  <si>
+    <t>00:09:44</t>
+  </si>
+  <si>
+    <t>01:42:51</t>
+  </si>
+  <si>
+    <t>21:42:28</t>
+  </si>
+  <si>
+    <t>23:27:20</t>
+  </si>
+  <si>
+    <t>01:00:35</t>
+  </si>
+  <si>
+    <t>21:00:45</t>
+  </si>
+  <si>
+    <t>22:33:55</t>
   </si>
   <si>
     <t>A+B</t>
@@ -595,13 +628,13 @@
     <t>2</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -635,7 +668,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,30 +678,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +695,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,31 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,19 +725,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -793,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -856,12 +877,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1265,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1343,55 +1358,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.5</v>
+        <v>-12.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="O2" s="6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>7</v>
-      </c>
-      <c r="R2" s="9">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1399,55 +1414,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.9</v>
+        <v>-15.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O3" s="10">
-        <v>4</v>
-      </c>
-      <c r="P3" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>4</v>
-      </c>
-      <c r="R3" s="11">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O3" s="6">
+        <v>3</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1455,55 +1470,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L4" s="4">
-        <v>-12.9</v>
+        <v>-9.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O4" s="6">
+        <v>3</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1511,55 +1526,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.1</v>
+        <v>-16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="O5" s="6">
-        <v>22</v>
-      </c>
-      <c r="P5" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
       <c r="R5" s="7">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1570,52 +1585,52 @@
         <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L6" s="4">
-        <v>-9.1</v>
+        <v>-12.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O6" s="10">
-        <v>3</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>2</v>
+        <v>203</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1623,54 +1638,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L7" s="4">
-        <v>-16</v>
+        <v>-15.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O7" s="10">
-        <v>17</v>
-      </c>
-      <c r="P7" s="12">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
+        <v>204</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1679,55 +1694,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="O8" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P8" s="7">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1735,54 +1750,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
+        <v>205</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1791,55 +1806,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L10" s="4">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O10" s="10">
-        <v>16</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O10" s="6">
+        <v>15</v>
+      </c>
+      <c r="P10" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+      <c r="R10" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1847,55 +1862,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L11" s="4">
-        <v>-8.699999999999999</v>
+        <v>-16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="O11" s="6">
-        <v>25</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0</v>
-      </c>
-      <c r="R11" s="11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1903,55 +1918,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="L12" s="4">
-        <v>-13.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="O12" s="6">
-        <v>20</v>
-      </c>
-      <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
         <v>0</v>
       </c>
       <c r="R12" s="7">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1959,55 +1974,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="L13" s="4">
-        <v>-16</v>
+        <v>-10.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O13" s="10">
-        <v>12</v>
-      </c>
-      <c r="P13" s="11">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O13" s="9">
+        <v>100</v>
+      </c>
+      <c r="P13" s="10">
+        <v>17</v>
       </c>
       <c r="Q13" s="11">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9">
-        <v>12</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2015,55 +2030,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="L14" s="4">
-        <v>-12.4</v>
+        <v>-15.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O14" s="10">
-        <v>5</v>
-      </c>
-      <c r="P14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>5</v>
+        <v>204</v>
+      </c>
+      <c r="O14" s="9">
+        <v>100</v>
+      </c>
+      <c r="P14" s="13">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>56</v>
+      </c>
+      <c r="R14" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2071,55 +2086,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="L15" s="4">
-        <v>-10.5</v>
+        <v>-14.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O15" s="13">
-        <v>79</v>
-      </c>
-      <c r="P15" s="8">
-        <v>3</v>
+        <v>203</v>
+      </c>
+      <c r="O15" s="9">
+        <v>92</v>
+      </c>
+      <c r="P15" s="10">
+        <v>17</v>
       </c>
       <c r="Q15" s="14">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="R15" s="15">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2127,55 +2142,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.7</v>
+        <v>-8.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="13">
-        <v>56</v>
-      </c>
-      <c r="P16" s="9">
-        <v>11</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>37</v>
-      </c>
-      <c r="R16" s="8">
-        <v>3</v>
+        <v>203</v>
+      </c>
+      <c r="O16" s="9">
+        <v>83</v>
+      </c>
+      <c r="P16" s="16">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>54</v>
+      </c>
+      <c r="R16" s="11">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2183,55 +2198,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-13.9</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O17" s="9">
+        <v>95</v>
+      </c>
+      <c r="P17" s="13">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>93</v>
+      </c>
+      <c r="R17" s="11">
         <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-14.9</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O17" s="13">
-        <v>89</v>
-      </c>
-      <c r="P17" s="17">
-        <v>39</v>
-      </c>
-      <c r="Q17" s="18">
-        <v>61</v>
-      </c>
-      <c r="R17" s="15">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2239,55 +2254,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L18" s="4">
-        <v>-8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O18" s="13">
-        <v>100</v>
-      </c>
-      <c r="P18" s="19">
-        <v>47</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>69</v>
+        <v>204</v>
+      </c>
+      <c r="O18" s="9">
+        <v>96</v>
+      </c>
+      <c r="P18" s="18">
+        <v>31</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>87</v>
       </c>
       <c r="R18" s="20">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2295,55 +2310,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L19" s="4">
-        <v>-13.9</v>
+        <v>-12.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O19" s="13">
-        <v>91</v>
-      </c>
-      <c r="P19" s="21">
-        <v>30</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>2</v>
-      </c>
-      <c r="R19" s="22">
-        <v>91</v>
+        <v>203</v>
+      </c>
+      <c r="O19" s="9">
+        <v>98</v>
+      </c>
+      <c r="P19" s="11">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="19">
+        <v>83</v>
+      </c>
+      <c r="R19" s="15">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2351,114 +2366,170 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-11</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O20" s="9">
+        <v>61</v>
+      </c>
+      <c r="P20" s="21">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>17</v>
+      </c>
+      <c r="R20" s="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
         <v>31</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O20" s="13">
+      <c r="J21" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-15.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O21" s="9">
         <v>80</v>
       </c>
-      <c r="P20" s="21">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>0</v>
-      </c>
-      <c r="R20" s="23">
-        <v>66</v>
+      <c r="P21" s="16">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>14</v>
+      </c>
+      <c r="R21" s="14">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2477,12 +2548,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2499,22 +2570,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260624--01</t>
-  </si>
-  <si>
-    <t>20260624--02</t>
-  </si>
-  <si>
     <t>20260625--01</t>
   </si>
   <si>
@@ -130,10 +124,16 @@
     <t>20260630--03</t>
   </si>
   <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>05:32</t>
+    <t>20260701--01</t>
+  </si>
+  <si>
+    <t>20260701--02</t>
+  </si>
+  <si>
+    <t>20260701--03</t>
+  </si>
+  <si>
+    <t>20260701--04</t>
   </si>
   <si>
     <t>06:08</t>
@@ -184,18 +184,24 @@
     <t>05:00</t>
   </si>
   <si>
-    <t>03:43</t>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>04:31</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
     <t>02:43</t>
   </si>
   <si>
@@ -217,10 +223,7 @@
     <t>00:17</t>
   </si>
   <si>
-    <t>00:39:19</t>
-  </si>
-  <si>
-    <t>23:53:34</t>
+    <t>03:03</t>
   </si>
   <si>
     <t>01:30:24</t>
@@ -277,10 +280,16 @@
     <t>22:31:24</t>
   </si>
   <si>
-    <t>00:41:37</t>
-  </si>
-  <si>
-    <t>23:55:56</t>
+    <t>00:08:32</t>
+  </si>
+  <si>
+    <t>20:08:48</t>
+  </si>
+  <si>
+    <t>21:45:15</t>
+  </si>
+  <si>
+    <t>23:22:19</t>
   </si>
   <si>
     <t>01:32:38</t>
@@ -337,7 +346,16 @@
     <t>22:33:38</t>
   </si>
   <si>
-    <t>23:58:41</t>
+    <t>00:10:55</t>
+  </si>
+  <si>
+    <t>20:11:28</t>
+  </si>
+  <si>
+    <t>21:47:30</t>
+  </si>
+  <si>
+    <t>23:24:38</t>
   </si>
   <si>
     <t>01:35:42</t>
@@ -394,10 +412,16 @@
     <t>22:36:41</t>
   </si>
   <si>
-    <t>00:47:26</t>
-  </si>
-  <si>
-    <t>00:01:28</t>
+    <t>00:13:40</t>
+  </si>
+  <si>
+    <t>20:13:38</t>
+  </si>
+  <si>
+    <t>21:50:31</t>
+  </si>
+  <si>
+    <t>23:27:31</t>
   </si>
   <si>
     <t>01:38:46</t>
@@ -454,10 +478,16 @@
     <t>22:39:44</t>
   </si>
   <si>
-    <t>00:49:45</t>
-  </si>
-  <si>
-    <t>00:03:51</t>
+    <t>00:16:25</t>
+  </si>
+  <si>
+    <t>20:15:49</t>
+  </si>
+  <si>
+    <t>21:53:32</t>
+  </si>
+  <si>
+    <t>23:30:24</t>
   </si>
   <si>
     <t>01:41:01</t>
@@ -511,10 +541,16 @@
     <t>22:41:59</t>
   </si>
   <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>21°</t>
+    <t>00:18:48</t>
+  </si>
+  <si>
+    <t>20:18:29</t>
+  </si>
+  <si>
+    <t>21:55:47</t>
+  </si>
+  <si>
+    <t>23:32:43</t>
   </si>
   <si>
     <t>10°</t>
@@ -562,10 +598,10 @@
     <t>12°</t>
   </si>
   <si>
-    <t>00:43:43</t>
-  </si>
-  <si>
-    <t>23:59:30</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>5°</t>
   </si>
   <si>
     <t>01:32:33</t>
@@ -616,22 +652,31 @@
     <t>22:33:55</t>
   </si>
   <si>
+    <t>20:17:28</t>
+  </si>
+  <si>
+    <t>21:50:33</t>
+  </si>
+  <si>
+    <t>23:23:38</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
+    <t>1</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>4</t>
@@ -668,7 +713,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,7 +764,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,37 +806,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,7 +830,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -877,6 +934,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1358,46 +1421,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.9</v>
+        <v>-9.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1405,8 +1468,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1414,55 +1477,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.1</v>
+        <v>-16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O3" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P3" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
       </c>
       <c r="R3" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1473,43 +1536,43 @@
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="L4" s="4">
-        <v>-9.1</v>
+        <v>-12.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="O4" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1517,8 +1580,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>3</v>
+      <c r="R4" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1526,55 +1589,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="L5" s="4">
-        <v>-16</v>
+        <v>-15.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="Q5" s="8">
+        <v>6</v>
+      </c>
+      <c r="R5" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1582,55 +1645,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="O6" s="9">
+        <v>50</v>
+      </c>
+      <c r="P6" s="10">
+        <v>13</v>
       </c>
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>0</v>
+      <c r="R6" s="11">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1638,46 +1701,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="O7" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1685,8 +1748,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>0</v>
+      <c r="R7" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1694,55 +1757,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O8" s="6">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="O8" s="12">
+        <v>29</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1</v>
+      <c r="Q8" s="13">
+        <v>21</v>
+      </c>
+      <c r="R8" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1750,55 +1813,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L9" s="4">
-        <v>-8.699999999999999</v>
+        <v>-16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="O9" s="12">
+        <v>20</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
+      <c r="Q9" s="8">
+        <v>4</v>
+      </c>
+      <c r="R9" s="13">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1806,55 +1869,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="L10" s="4">
-        <v>-13.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="O10" s="6">
-        <v>15</v>
-      </c>
-      <c r="P10" s="8">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
       </c>
       <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1862,55 +1925,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="L11" s="4">
-        <v>-16</v>
+        <v>-10.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O11" s="6">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="O11" s="9">
+        <v>73</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
       </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>1</v>
+      <c r="Q11" s="10">
+        <v>16</v>
+      </c>
+      <c r="R11" s="15">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1918,55 +1981,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="L12" s="4">
-        <v>-12.4</v>
+        <v>-15.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="O12" s="9">
+        <v>47</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
       </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0</v>
+      <c r="Q12" s="13">
+        <v>20</v>
+      </c>
+      <c r="R12" s="16">
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1974,55 +2037,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="L13" s="4">
-        <v>-10.5</v>
+        <v>-14.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="O13" s="9">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="P13" s="10">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>45</v>
-      </c>
-      <c r="R13" s="12">
-        <v>100</v>
+        <v>16</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>29</v>
+      </c>
+      <c r="R13" s="13">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2030,55 +2093,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L14" s="4">
-        <v>-15.7</v>
+        <v>-8.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O14" s="9">
-        <v>100</v>
-      </c>
-      <c r="P14" s="13">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>56</v>
-      </c>
-      <c r="R14" s="12">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="P14" s="18">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>33</v>
+      </c>
+      <c r="R14" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2086,55 +2149,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L15" s="4">
-        <v>-14.9</v>
+        <v>-13.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="O15" s="9">
-        <v>92</v>
-      </c>
-      <c r="P15" s="10">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>53</v>
-      </c>
-      <c r="R15" s="15">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="P15" s="19">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>57</v>
+      </c>
+      <c r="R15" s="21">
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2142,55 +2205,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="L16" s="4">
-        <v>-8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="O16" s="9">
-        <v>83</v>
-      </c>
-      <c r="P16" s="16">
-        <v>12</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>54</v>
-      </c>
-      <c r="R16" s="11">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="P16" s="22">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>36</v>
+      </c>
+      <c r="R16" s="17">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2198,55 +2261,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="L17" s="4">
-        <v>-13.9</v>
+        <v>-12.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O17" s="9">
-        <v>95</v>
-      </c>
-      <c r="P17" s="13">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>93</v>
-      </c>
-      <c r="R17" s="11">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="P17" s="21">
+        <v>41</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>33</v>
+      </c>
+      <c r="R17" s="21">
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2254,55 +2317,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="L18" s="4">
-        <v>-16.1</v>
+        <v>-11</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="O18" s="9">
-        <v>96</v>
-      </c>
-      <c r="P18" s="18">
-        <v>31</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>87</v>
-      </c>
-      <c r="R18" s="20">
-        <v>50</v>
+        <v>80</v>
+      </c>
+      <c r="P18" s="23">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>54</v>
+      </c>
+      <c r="R18" s="17">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2310,55 +2373,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
+        <v>31</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-15.9</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O19" s="9">
+        <v>76</v>
+      </c>
+      <c r="P19" s="23">
+        <v>62</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>34</v>
+      </c>
+      <c r="R19" s="13">
         <v>20</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-12.2</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O19" s="9">
-        <v>98</v>
-      </c>
-      <c r="P19" s="11">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="19">
-        <v>83</v>
-      </c>
-      <c r="R19" s="15">
-        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2366,55 +2429,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-14.8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O20" s="9">
         <v>85</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-11</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O20" s="9">
-        <v>61</v>
-      </c>
-      <c r="P20" s="21">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>17</v>
+      <c r="P20" s="16">
+        <v>36</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>50</v>
       </c>
       <c r="R20" s="21">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2422,114 +2485,226 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-6.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O21" s="9">
+        <v>84</v>
+      </c>
+      <c r="P21" s="15">
+        <v>63</v>
+      </c>
+      <c r="Q21" s="21">
+        <v>39</v>
+      </c>
+      <c r="R21" s="17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>30</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-14.3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O22" s="9">
+        <v>76</v>
+      </c>
+      <c r="P22" s="22">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>36</v>
+      </c>
+      <c r="R22" s="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>26</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O23" s="9">
         <v>66</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-15.9</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O21" s="9">
-        <v>80</v>
-      </c>
-      <c r="P21" s="16">
-        <v>9</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>14</v>
-      </c>
-      <c r="R21" s="14">
-        <v>57</v>
+      <c r="P23" s="16">
+        <v>35</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>33</v>
+      </c>
+      <c r="R23" s="22">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2548,12 +2723,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2570,22 +2745,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="228">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260625--01</t>
-  </si>
-  <si>
-    <t>20260625--02</t>
-  </si>
-  <si>
     <t>20260626--01</t>
   </si>
   <si>
@@ -136,459 +130,483 @@
     <t>20260701--04</t>
   </si>
   <si>
-    <t>06:08</t>
+    <t>20260702--01</t>
+  </si>
+  <si>
+    <t>20260702--02</t>
+  </si>
+  <si>
+    <t>20260702--03</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>00:41</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>01:42</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>00:17</t>
+  </si>
+  <si>
+    <t>03:04</t>
   </si>
   <si>
     <t>05:07</t>
   </si>
   <si>
-    <t>06:07</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>01:38</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:29</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>06:06</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:41</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>02:11</t>
-  </si>
-  <si>
-    <t>01:43</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>00:17</t>
-  </si>
-  <si>
-    <t>03:03</t>
-  </si>
-  <si>
-    <t>01:30:24</t>
-  </si>
-  <si>
-    <t>23:07:50</t>
-  </si>
-  <si>
-    <t>00:44:31</t>
-  </si>
-  <si>
-    <t>22:22:06</t>
-  </si>
-  <si>
-    <t>23:58:36</t>
-  </si>
-  <si>
-    <t>01:35:41</t>
-  </si>
-  <si>
-    <t>21:36:24</t>
-  </si>
-  <si>
-    <t>23:12:39</t>
-  </si>
-  <si>
-    <t>00:49:40</t>
-  </si>
-  <si>
-    <t>20:50:44</t>
-  </si>
-  <si>
-    <t>22:26:42</t>
-  </si>
-  <si>
-    <t>00:03:37</t>
-  </si>
-  <si>
-    <t>01:40:54</t>
-  </si>
-  <si>
-    <t>21:40:44</t>
-  </si>
-  <si>
-    <t>23:17:31</t>
-  </si>
-  <si>
-    <t>00:54:44</t>
-  </si>
-  <si>
-    <t>20:54:46</t>
-  </si>
-  <si>
-    <t>22:31:24</t>
-  </si>
-  <si>
-    <t>00:08:32</t>
-  </si>
-  <si>
-    <t>20:08:48</t>
-  </si>
-  <si>
-    <t>21:45:15</t>
-  </si>
-  <si>
-    <t>23:22:19</t>
-  </si>
-  <si>
-    <t>01:32:38</t>
-  </si>
-  <si>
-    <t>23:10:18</t>
-  </si>
-  <si>
-    <t>00:46:45</t>
-  </si>
-  <si>
-    <t>22:24:43</t>
-  </si>
-  <si>
-    <t>00:00:51</t>
-  </si>
-  <si>
-    <t>01:38:00</t>
-  </si>
-  <si>
-    <t>21:39:17</t>
-  </si>
-  <si>
-    <t>23:14:55</t>
-  </si>
-  <si>
-    <t>00:51:57</t>
-  </si>
-  <si>
-    <t>20:54:19</t>
-  </si>
-  <si>
-    <t>22:29:00</t>
-  </si>
-  <si>
-    <t>00:05:52</t>
-  </si>
-  <si>
-    <t>01:43:32</t>
-  </si>
-  <si>
-    <t>21:43:06</t>
-  </si>
-  <si>
-    <t>23:19:46</t>
-  </si>
-  <si>
-    <t>00:57:13</t>
-  </si>
-  <si>
-    <t>20:57:15</t>
-  </si>
-  <si>
-    <t>22:33:38</t>
-  </si>
-  <si>
-    <t>00:10:55</t>
-  </si>
-  <si>
-    <t>20:11:28</t>
-  </si>
-  <si>
-    <t>21:47:30</t>
-  </si>
-  <si>
-    <t>23:24:38</t>
-  </si>
-  <si>
-    <t>01:35:42</t>
-  </si>
-  <si>
-    <t>23:12:50</t>
-  </si>
-  <si>
-    <t>00:49:48</t>
-  </si>
-  <si>
-    <t>22:26:58</t>
-  </si>
-  <si>
-    <t>00:03:52</t>
-  </si>
-  <si>
-    <t>01:40:53</t>
-  </si>
-  <si>
-    <t>21:41:04</t>
-  </si>
-  <si>
-    <t>23:17:53</t>
-  </si>
-  <si>
-    <t>00:54:55</t>
-  </si>
-  <si>
-    <t>20:55:08</t>
-  </si>
-  <si>
-    <t>22:31:53</t>
-  </si>
-  <si>
-    <t>00:08:53</t>
-  </si>
-  <si>
-    <t>01:45:47</t>
-  </si>
-  <si>
-    <t>21:45:50</t>
-  </si>
-  <si>
-    <t>23:22:49</t>
-  </si>
-  <si>
-    <t>00:59:45</t>
-  </si>
-  <si>
-    <t>20:59:45</t>
-  </si>
-  <si>
-    <t>22:36:41</t>
-  </si>
-  <si>
-    <t>00:13:40</t>
-  </si>
-  <si>
-    <t>20:13:38</t>
-  </si>
-  <si>
-    <t>21:50:31</t>
-  </si>
-  <si>
-    <t>23:27:31</t>
-  </si>
-  <si>
-    <t>01:38:46</t>
-  </si>
-  <si>
-    <t>23:15:25</t>
-  </si>
-  <si>
-    <t>00:52:52</t>
-  </si>
-  <si>
-    <t>22:29:13</t>
-  </si>
-  <si>
-    <t>00:06:54</t>
-  </si>
-  <si>
-    <t>01:43:46</t>
-  </si>
-  <si>
-    <t>21:42:50</t>
-  </si>
-  <si>
-    <t>23:20:52</t>
-  </si>
-  <si>
-    <t>00:57:53</t>
-  </si>
-  <si>
-    <t>20:55:57</t>
-  </si>
-  <si>
-    <t>22:34:45</t>
-  </si>
-  <si>
-    <t>00:11:55</t>
-  </si>
-  <si>
-    <t>01:48:01</t>
-  </si>
-  <si>
-    <t>21:48:33</t>
-  </si>
-  <si>
-    <t>23:25:52</t>
-  </si>
-  <si>
-    <t>01:02:18</t>
-  </si>
-  <si>
-    <t>21:02:15</t>
-  </si>
-  <si>
-    <t>22:39:44</t>
-  </si>
-  <si>
-    <t>00:16:25</t>
-  </si>
-  <si>
-    <t>20:15:49</t>
-  </si>
-  <si>
-    <t>21:53:32</t>
-  </si>
-  <si>
-    <t>23:30:24</t>
-  </si>
-  <si>
-    <t>01:41:01</t>
-  </si>
-  <si>
-    <t>00:55:07</t>
-  </si>
-  <si>
-    <t>22:31:51</t>
-  </si>
-  <si>
-    <t>00:09:10</t>
-  </si>
-  <si>
-    <t>01:46:06</t>
-  </si>
-  <si>
-    <t>21:45:45</t>
-  </si>
-  <si>
-    <t>23:23:09</t>
-  </si>
-  <si>
-    <t>01:00:10</t>
-  </si>
-  <si>
-    <t>20:59:32</t>
-  </si>
-  <si>
-    <t>22:37:05</t>
-  </si>
-  <si>
-    <t>00:14:10</t>
-  </si>
-  <si>
-    <t>01:50:40</t>
-  </si>
-  <si>
-    <t>21:50:57</t>
-  </si>
-  <si>
-    <t>23:28:06</t>
-  </si>
-  <si>
-    <t>01:04:47</t>
-  </si>
-  <si>
-    <t>21:04:45</t>
-  </si>
-  <si>
-    <t>22:41:59</t>
-  </si>
-  <si>
-    <t>00:18:48</t>
-  </si>
-  <si>
-    <t>20:18:29</t>
-  </si>
-  <si>
-    <t>21:55:47</t>
-  </si>
-  <si>
-    <t>23:32:43</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>01:13</t>
+  </si>
+  <si>
+    <t>00:44:29</t>
+  </si>
+  <si>
+    <t>22:22:02</t>
+  </si>
+  <si>
+    <t>23:58:31</t>
+  </si>
+  <si>
+    <t>01:35:36</t>
+  </si>
+  <si>
+    <t>21:36:15</t>
+  </si>
+  <si>
+    <t>23:12:30</t>
+  </si>
+  <si>
+    <t>00:49:30</t>
+  </si>
+  <si>
+    <t>20:50:30</t>
+  </si>
+  <si>
+    <t>22:26:27</t>
+  </si>
+  <si>
+    <t>00:03:21</t>
+  </si>
+  <si>
+    <t>01:40:38</t>
+  </si>
+  <si>
+    <t>21:40:22</t>
+  </si>
+  <si>
+    <t>23:17:09</t>
+  </si>
+  <si>
+    <t>00:54:21</t>
+  </si>
+  <si>
+    <t>20:54:16</t>
+  </si>
+  <si>
+    <t>22:30:53</t>
+  </si>
+  <si>
+    <t>00:08:01</t>
+  </si>
+  <si>
+    <t>20:08:09</t>
+  </si>
+  <si>
+    <t>21:44:34</t>
+  </si>
+  <si>
+    <t>23:21:37</t>
+  </si>
+  <si>
+    <t>00:59:06</t>
+  </si>
+  <si>
+    <t>20:58:13</t>
+  </si>
+  <si>
+    <t>22:35:11</t>
+  </si>
+  <si>
+    <t>00:46:43</t>
+  </si>
+  <si>
+    <t>22:24:39</t>
+  </si>
+  <si>
+    <t>00:00:46</t>
+  </si>
+  <si>
+    <t>01:37:55</t>
+  </si>
+  <si>
+    <t>21:39:09</t>
+  </si>
+  <si>
+    <t>23:14:46</t>
+  </si>
+  <si>
+    <t>00:51:47</t>
+  </si>
+  <si>
+    <t>20:54:06</t>
+  </si>
+  <si>
+    <t>22:28:46</t>
+  </si>
+  <si>
+    <t>00:05:36</t>
+  </si>
+  <si>
+    <t>01:43:16</t>
+  </si>
+  <si>
+    <t>21:42:45</t>
+  </si>
+  <si>
+    <t>23:19:23</t>
+  </si>
+  <si>
+    <t>00:56:49</t>
+  </si>
+  <si>
+    <t>20:56:45</t>
+  </si>
+  <si>
+    <t>22:33:07</t>
+  </si>
+  <si>
+    <t>00:10:23</t>
+  </si>
+  <si>
+    <t>20:10:49</t>
+  </si>
+  <si>
+    <t>21:46:49</t>
+  </si>
+  <si>
+    <t>23:23:56</t>
+  </si>
+  <si>
+    <t>01:02:31</t>
+  </si>
+  <si>
+    <t>21:00:30</t>
+  </si>
+  <si>
+    <t>22:37:27</t>
+  </si>
+  <si>
+    <t>00:49:46</t>
+  </si>
+  <si>
+    <t>22:26:53</t>
+  </si>
+  <si>
+    <t>00:03:47</t>
+  </si>
+  <si>
+    <t>01:40:48</t>
+  </si>
+  <si>
+    <t>21:40:55</t>
+  </si>
+  <si>
+    <t>23:17:44</t>
+  </si>
+  <si>
+    <t>00:54:45</t>
+  </si>
+  <si>
+    <t>20:54:53</t>
+  </si>
+  <si>
+    <t>22:31:37</t>
+  </si>
+  <si>
+    <t>00:08:38</t>
+  </si>
+  <si>
+    <t>01:45:31</t>
+  </si>
+  <si>
+    <t>21:45:27</t>
+  </si>
+  <si>
+    <t>23:22:26</t>
+  </si>
+  <si>
+    <t>00:59:22</t>
+  </si>
+  <si>
+    <t>20:59:14</t>
+  </si>
+  <si>
+    <t>22:36:10</t>
+  </si>
+  <si>
+    <t>00:13:08</t>
+  </si>
+  <si>
+    <t>20:12:58</t>
+  </si>
+  <si>
+    <t>21:49:50</t>
+  </si>
+  <si>
+    <t>23:26:49</t>
+  </si>
+  <si>
+    <t>01:03:34</t>
+  </si>
+  <si>
+    <t>21:03:26</t>
+  </si>
+  <si>
+    <t>22:40:25</t>
+  </si>
+  <si>
+    <t>00:52:50</t>
+  </si>
+  <si>
+    <t>22:29:08</t>
+  </si>
+  <si>
+    <t>00:06:49</t>
+  </si>
+  <si>
+    <t>01:43:41</t>
+  </si>
+  <si>
+    <t>21:42:41</t>
+  </si>
+  <si>
+    <t>23:20:43</t>
+  </si>
+  <si>
+    <t>00:57:44</t>
+  </si>
+  <si>
+    <t>20:55:41</t>
+  </si>
+  <si>
+    <t>22:34:30</t>
+  </si>
+  <si>
+    <t>00:11:39</t>
+  </si>
+  <si>
+    <t>01:47:46</t>
+  </si>
+  <si>
+    <t>21:48:11</t>
+  </si>
+  <si>
+    <t>23:25:29</t>
+  </si>
+  <si>
+    <t>01:01:55</t>
+  </si>
+  <si>
+    <t>21:01:44</t>
+  </si>
+  <si>
+    <t>22:39:13</t>
+  </si>
+  <si>
+    <t>00:15:53</t>
+  </si>
+  <si>
+    <t>20:15:08</t>
+  </si>
+  <si>
+    <t>21:52:51</t>
+  </si>
+  <si>
+    <t>23:29:43</t>
+  </si>
+  <si>
+    <t>01:04:36</t>
+  </si>
+  <si>
+    <t>21:06:23</t>
+  </si>
+  <si>
+    <t>22:43:24</t>
+  </si>
+  <si>
+    <t>00:55:05</t>
+  </si>
+  <si>
+    <t>22:31:46</t>
+  </si>
+  <si>
+    <t>00:09:05</t>
+  </si>
+  <si>
+    <t>01:46:00</t>
+  </si>
+  <si>
+    <t>21:45:35</t>
+  </si>
+  <si>
+    <t>23:23:00</t>
+  </si>
+  <si>
+    <t>01:00:01</t>
+  </si>
+  <si>
+    <t>20:59:18</t>
+  </si>
+  <si>
+    <t>22:36:49</t>
+  </si>
+  <si>
+    <t>00:13:55</t>
+  </si>
+  <si>
+    <t>01:50:24</t>
+  </si>
+  <si>
+    <t>21:50:34</t>
+  </si>
+  <si>
+    <t>23:27:44</t>
+  </si>
+  <si>
+    <t>01:04:24</t>
+  </si>
+  <si>
+    <t>21:04:14</t>
+  </si>
+  <si>
+    <t>22:41:27</t>
+  </si>
+  <si>
+    <t>00:18:16</t>
+  </si>
+  <si>
+    <t>20:17:48</t>
+  </si>
+  <si>
+    <t>21:55:06</t>
+  </si>
+  <si>
+    <t>23:32:01</t>
+  </si>
+  <si>
+    <t>01:08:01</t>
+  </si>
+  <si>
+    <t>21:08:40</t>
+  </si>
+  <si>
+    <t>22:45:40</t>
   </si>
   <si>
     <t>22°</t>
   </si>
   <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
     <t>3°</t>
   </si>
   <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
     <t>18°</t>
   </si>
   <si>
@@ -598,85 +616,85 @@
     <t>12°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
-    <t>01:32:33</t>
-  </si>
-  <si>
-    <t>23:15:17</t>
-  </si>
-  <si>
-    <t>00:48:21</t>
-  </si>
-  <si>
-    <t>22:31:07</t>
-  </si>
-  <si>
-    <t>00:04:11</t>
-  </si>
-  <si>
-    <t>01:37:15</t>
-  </si>
-  <si>
-    <t>23:20:11</t>
-  </si>
-  <si>
-    <t>00:53:15</t>
-  </si>
-  <si>
-    <t>22:36:36</t>
-  </si>
-  <si>
-    <t>00:09:44</t>
-  </si>
-  <si>
-    <t>01:42:51</t>
-  </si>
-  <si>
-    <t>21:42:28</t>
-  </si>
-  <si>
-    <t>23:27:20</t>
-  </si>
-  <si>
-    <t>01:00:35</t>
-  </si>
-  <si>
-    <t>21:00:45</t>
-  </si>
-  <si>
-    <t>22:33:55</t>
-  </si>
-  <si>
-    <t>20:17:28</t>
-  </si>
-  <si>
-    <t>21:50:33</t>
-  </si>
-  <si>
-    <t>23:23:38</t>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>00:48:19</t>
+  </si>
+  <si>
+    <t>22:31:03</t>
+  </si>
+  <si>
+    <t>00:04:06</t>
+  </si>
+  <si>
+    <t>01:37:10</t>
+  </si>
+  <si>
+    <t>23:20:02</t>
+  </si>
+  <si>
+    <t>00:53:07</t>
+  </si>
+  <si>
+    <t>22:36:22</t>
+  </si>
+  <si>
+    <t>00:09:29</t>
+  </si>
+  <si>
+    <t>01:42:37</t>
+  </si>
+  <si>
+    <t>21:42:06</t>
+  </si>
+  <si>
+    <t>23:26:59</t>
+  </si>
+  <si>
+    <t>01:00:13</t>
+  </si>
+  <si>
+    <t>21:00:15</t>
+  </si>
+  <si>
+    <t>22:33:24</t>
+  </si>
+  <si>
+    <t>20:16:49</t>
+  </si>
+  <si>
+    <t>21:49:53</t>
+  </si>
+  <si>
+    <t>23:22:57</t>
+  </si>
+  <si>
+    <t>21:05:37</t>
+  </si>
+  <si>
+    <t>22:38:40</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -713,7 +731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -752,6 +770,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -764,13 +794,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,55 +842,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -940,6 +976,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1424,52 +1469,52 @@
         <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.1</v>
+        <v>-12.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="8">
+        <v>5</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1477,52 +1522,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L3" s="4">
-        <v>-16</v>
+        <v>-15.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O3" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="7">
         <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>5</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1533,43 +1578,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L4" s="4">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -1589,55 +1634,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O5" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>6</v>
-      </c>
-      <c r="R5" s="8">
-        <v>3</v>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1645,55 +1690,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="L6" s="4">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O6" s="9">
-        <v>50</v>
-      </c>
-      <c r="P6" s="10">
-        <v>13</v>
-      </c>
-      <c r="Q6" s="7">
+        <v>227</v>
+      </c>
+      <c r="O6" s="6">
+        <v>5</v>
+      </c>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="11">
-        <v>47</v>
+      <c r="Q6" s="8">
+        <v>5</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1701,46 +1746,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L7" s="4">
-        <v>-8.699999999999999</v>
+        <v>-16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O7" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1748,8 +1793,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>3</v>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1757,55 +1802,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="L8" s="4">
-        <v>-13.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O8" s="12">
-        <v>29</v>
+        <v>224</v>
+      </c>
+      <c r="O8" s="9">
+        <v>53</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="13">
-        <v>21</v>
-      </c>
-      <c r="R8" s="14">
-        <v>11</v>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1813,55 +1858,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="L9" s="4">
-        <v>-16</v>
+        <v>-10.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" s="12">
-        <v>20</v>
+        <v>227</v>
+      </c>
+      <c r="O9" s="9">
+        <v>74</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="8">
-        <v>4</v>
-      </c>
-      <c r="R9" s="13">
-        <v>20</v>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1869,55 +1914,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="L10" s="4">
-        <v>-12.4</v>
+        <v>-15.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O10" s="6">
-        <v>13</v>
+        <v>225</v>
+      </c>
+      <c r="O10" s="9">
+        <v>18</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="12">
+        <v>17</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
-      </c>
-      <c r="R10" s="10">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1925,55 +1970,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.5</v>
+        <v>-14.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O11" s="9">
-        <v>73</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>16</v>
-      </c>
-      <c r="R11" s="15">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="P11" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>46</v>
+      </c>
+      <c r="R11" s="13">
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1981,55 +2026,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O12" s="9">
+        <v>65</v>
+      </c>
+      <c r="P12" s="14">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>43</v>
+      </c>
+      <c r="R12" s="11">
         <v>50</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-15.7</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O12" s="9">
-        <v>47</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>20</v>
-      </c>
-      <c r="R12" s="16">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2037,55 +2082,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="L13" s="4">
-        <v>-14.9</v>
+        <v>-13.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O13" s="9">
-        <v>54</v>
-      </c>
-      <c r="P13" s="10">
-        <v>16</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>29</v>
-      </c>
-      <c r="R13" s="13">
-        <v>18</v>
+        <v>100</v>
+      </c>
+      <c r="P13" s="15">
+        <v>37</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>89</v>
+      </c>
+      <c r="R13" s="17">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2093,55 +2138,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L14" s="4">
-        <v>-8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O14" s="9">
-        <v>53</v>
-      </c>
-      <c r="P14" s="18">
-        <v>24</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>33</v>
-      </c>
-      <c r="R14" s="8">
-        <v>7</v>
+        <v>100</v>
+      </c>
+      <c r="P14" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>54</v>
+      </c>
+      <c r="R14" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2149,55 +2194,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L15" s="4">
-        <v>-13.9</v>
+        <v>-12.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O15" s="9">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="P15" s="19">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="20">
-        <v>57</v>
-      </c>
-      <c r="R15" s="21">
         <v>42</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>44</v>
+      </c>
+      <c r="R15" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2205,55 +2250,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L16" s="4">
-        <v>-16.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O16" s="9">
-        <v>58</v>
-      </c>
-      <c r="P16" s="22">
-        <v>52</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>36</v>
-      </c>
-      <c r="R16" s="17">
-        <v>32</v>
+        <v>98</v>
+      </c>
+      <c r="P16" s="16">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>33</v>
+      </c>
+      <c r="R16" s="20">
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2261,55 +2306,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="L17" s="4">
-        <v>-12.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O17" s="9">
-        <v>54</v>
-      </c>
-      <c r="P17" s="21">
-        <v>41</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>33</v>
-      </c>
-      <c r="R17" s="21">
-        <v>39</v>
+        <v>98</v>
+      </c>
+      <c r="P17" s="17">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>8</v>
+      </c>
+      <c r="R17" s="17">
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2317,55 +2362,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>-11</v>
+        <v>-14.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O18" s="9">
-        <v>80</v>
-      </c>
-      <c r="P18" s="23">
-        <v>58</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>54</v>
-      </c>
-      <c r="R18" s="17">
-        <v>28</v>
+        <v>99</v>
+      </c>
+      <c r="P18" s="16">
+        <v>92</v>
+      </c>
+      <c r="Q18" s="22">
+        <v>69</v>
+      </c>
+      <c r="R18" s="23">
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2373,55 +2418,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L19" s="4">
-        <v>-15.9</v>
+        <v>-6.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O19" s="9">
-        <v>76</v>
-      </c>
-      <c r="P19" s="23">
-        <v>62</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>34</v>
+        <v>85</v>
+      </c>
+      <c r="P19" s="24">
+        <v>80</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
       </c>
       <c r="R19" s="13">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2429,55 +2474,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="L20" s="4">
-        <v>-14.8</v>
+        <v>-14.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O20" s="9">
-        <v>85</v>
-      </c>
-      <c r="P20" s="16">
-        <v>36</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>50</v>
-      </c>
-      <c r="R20" s="21">
-        <v>39</v>
+        <v>67</v>
+      </c>
+      <c r="P20" s="25">
+        <v>59</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2485,55 +2530,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L21" s="4">
-        <v>-6.9</v>
+        <v>-16.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O21" s="9">
-        <v>84</v>
-      </c>
-      <c r="P21" s="15">
-        <v>63</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>39</v>
-      </c>
-      <c r="R21" s="17">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="P21" s="26">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>1</v>
+      </c>
+      <c r="R21" s="13">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2541,55 +2586,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>213</v>
+        <v>92</v>
       </c>
       <c r="L22" s="4">
-        <v>-14.3</v>
+        <v>-12.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="O22" s="9">
-        <v>76</v>
-      </c>
-      <c r="P22" s="22">
-        <v>50</v>
-      </c>
-      <c r="Q22" s="16">
-        <v>36</v>
-      </c>
-      <c r="R22" s="20">
-        <v>54</v>
+        <v>43</v>
+      </c>
+      <c r="P22" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>2</v>
+      </c>
+      <c r="R22" s="13">
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2597,114 +2642,170 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L23" s="4">
-        <v>-16.2</v>
+        <v>-11.3</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N23" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O23" s="9">
+        <v>49</v>
+      </c>
+      <c r="P23" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>37</v>
+      </c>
+      <c r="R23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="O23" s="9">
-        <v>66</v>
-      </c>
-      <c r="P23" s="16">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="16">
-        <v>33</v>
-      </c>
-      <c r="R23" s="22">
+      <c r="L24" s="4">
+        <v>-16.1</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O24" s="9">
         <v>50</v>
+      </c>
+      <c r="P24" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>42</v>
+      </c>
+      <c r="R24" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A24">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D24">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I24">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J24">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K24">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2723,12 +2824,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N24">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2745,22 +2846,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O24">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P24">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q24">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R24">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="245">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260626--01</t>
-  </si>
-  <si>
-    <t>20260626--02</t>
-  </si>
-  <si>
     <t>20260627--01</t>
   </si>
   <si>
@@ -139,73 +133,94 @@
     <t>20260702--03</t>
   </si>
   <si>
-    <t>06:07</t>
+    <t>20260703--01</t>
+  </si>
+  <si>
+    <t>20260703--02</t>
+  </si>
+  <si>
+    <t>20260703--03</t>
+  </si>
+  <si>
+    <t>20260703--04</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>01:34</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>06:03</t>
   </si>
   <si>
     <t>04:29</t>
   </si>
   <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>03:32</t>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>05:53</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>06:06</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:19</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>04:31</t>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>02:43</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:41</t>
+    <t>00:40</t>
   </si>
   <si>
     <t>04:37</t>
@@ -217,387 +232,417 @@
     <t>01:42</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>00:17</t>
-  </si>
-  <si>
-    <t>03:04</t>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>03:03</t>
   </si>
   <si>
     <t>05:07</t>
   </si>
   <si>
-    <t>01:13</t>
-  </si>
-  <si>
-    <t>00:44:29</t>
-  </si>
-  <si>
-    <t>22:22:02</t>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>03:05</t>
   </si>
   <si>
     <t>23:58:31</t>
   </si>
   <si>
-    <t>01:35:36</t>
-  </si>
-  <si>
-    <t>21:36:15</t>
-  </si>
-  <si>
-    <t>23:12:30</t>
-  </si>
-  <si>
-    <t>00:49:30</t>
-  </si>
-  <si>
-    <t>20:50:30</t>
-  </si>
-  <si>
-    <t>22:26:27</t>
-  </si>
-  <si>
-    <t>00:03:21</t>
-  </si>
-  <si>
-    <t>01:40:38</t>
-  </si>
-  <si>
-    <t>21:40:22</t>
-  </si>
-  <si>
-    <t>23:17:09</t>
-  </si>
-  <si>
-    <t>00:54:21</t>
-  </si>
-  <si>
-    <t>20:54:16</t>
-  </si>
-  <si>
-    <t>22:30:53</t>
-  </si>
-  <si>
-    <t>00:08:01</t>
-  </si>
-  <si>
-    <t>20:08:09</t>
-  </si>
-  <si>
-    <t>21:44:34</t>
-  </si>
-  <si>
-    <t>23:21:37</t>
-  </si>
-  <si>
-    <t>00:59:06</t>
-  </si>
-  <si>
-    <t>20:58:13</t>
-  </si>
-  <si>
-    <t>22:35:11</t>
-  </si>
-  <si>
-    <t>00:46:43</t>
-  </si>
-  <si>
-    <t>22:24:39</t>
+    <t>01:35:37</t>
+  </si>
+  <si>
+    <t>21:36:17</t>
+  </si>
+  <si>
+    <t>23:12:32</t>
+  </si>
+  <si>
+    <t>00:49:32</t>
+  </si>
+  <si>
+    <t>20:50:34</t>
+  </si>
+  <si>
+    <t>22:26:30</t>
+  </si>
+  <si>
+    <t>00:03:25</t>
+  </si>
+  <si>
+    <t>01:40:42</t>
+  </si>
+  <si>
+    <t>21:40:28</t>
+  </si>
+  <si>
+    <t>23:17:15</t>
+  </si>
+  <si>
+    <t>00:54:27</t>
+  </si>
+  <si>
+    <t>20:54:24</t>
+  </si>
+  <si>
+    <t>22:31:02</t>
+  </si>
+  <si>
+    <t>00:08:10</t>
+  </si>
+  <si>
+    <t>20:08:22</t>
+  </si>
+  <si>
+    <t>21:44:47</t>
+  </si>
+  <si>
+    <t>23:21:51</t>
+  </si>
+  <si>
+    <t>00:59:20</t>
+  </si>
+  <si>
+    <t>20:58:30</t>
+  </si>
+  <si>
+    <t>22:35:29</t>
+  </si>
+  <si>
+    <t>00:12:50</t>
+  </si>
+  <si>
+    <t>20:12:12</t>
+  </si>
+  <si>
+    <t>21:49:04</t>
+  </si>
+  <si>
+    <t>23:26:19</t>
   </si>
   <si>
     <t>00:00:46</t>
   </si>
   <si>
-    <t>01:37:55</t>
-  </si>
-  <si>
-    <t>21:39:09</t>
-  </si>
-  <si>
-    <t>23:14:46</t>
-  </si>
-  <si>
-    <t>00:51:47</t>
-  </si>
-  <si>
-    <t>20:54:06</t>
-  </si>
-  <si>
-    <t>22:28:46</t>
-  </si>
-  <si>
-    <t>00:05:36</t>
-  </si>
-  <si>
-    <t>01:43:16</t>
-  </si>
-  <si>
-    <t>21:42:45</t>
-  </si>
-  <si>
-    <t>23:19:23</t>
-  </si>
-  <si>
-    <t>00:56:49</t>
-  </si>
-  <si>
-    <t>20:56:45</t>
-  </si>
-  <si>
-    <t>22:33:07</t>
-  </si>
-  <si>
-    <t>00:10:23</t>
-  </si>
-  <si>
-    <t>20:10:49</t>
-  </si>
-  <si>
-    <t>21:46:49</t>
-  </si>
-  <si>
-    <t>23:23:56</t>
-  </si>
-  <si>
-    <t>01:02:31</t>
-  </si>
-  <si>
-    <t>21:00:30</t>
-  </si>
-  <si>
-    <t>22:37:27</t>
-  </si>
-  <si>
-    <t>00:49:46</t>
-  </si>
-  <si>
-    <t>22:26:53</t>
-  </si>
-  <si>
-    <t>00:03:47</t>
+    <t>01:37:56</t>
+  </si>
+  <si>
+    <t>21:39:11</t>
+  </si>
+  <si>
+    <t>23:14:48</t>
+  </si>
+  <si>
+    <t>00:51:49</t>
+  </si>
+  <si>
+    <t>20:54:10</t>
+  </si>
+  <si>
+    <t>22:28:49</t>
+  </si>
+  <si>
+    <t>00:05:40</t>
+  </si>
+  <si>
+    <t>01:43:20</t>
+  </si>
+  <si>
+    <t>21:42:50</t>
+  </si>
+  <si>
+    <t>23:19:29</t>
+  </si>
+  <si>
+    <t>00:56:55</t>
+  </si>
+  <si>
+    <t>20:56:54</t>
+  </si>
+  <si>
+    <t>22:33:17</t>
+  </si>
+  <si>
+    <t>00:10:33</t>
+  </si>
+  <si>
+    <t>20:11:01</t>
+  </si>
+  <si>
+    <t>21:47:02</t>
+  </si>
+  <si>
+    <t>23:24:09</t>
+  </si>
+  <si>
+    <t>01:02:45</t>
+  </si>
+  <si>
+    <t>21:00:47</t>
+  </si>
+  <si>
+    <t>22:37:45</t>
+  </si>
+  <si>
+    <t>00:15:41</t>
+  </si>
+  <si>
+    <t>20:14:31</t>
+  </si>
+  <si>
+    <t>21:51:19</t>
+  </si>
+  <si>
+    <t>23:28:55</t>
+  </si>
+  <si>
+    <t>00:03:48</t>
   </si>
   <si>
     <t>01:40:48</t>
   </si>
   <si>
-    <t>21:40:55</t>
-  </si>
-  <si>
-    <t>23:17:44</t>
-  </si>
-  <si>
-    <t>00:54:45</t>
-  </si>
-  <si>
-    <t>20:54:53</t>
-  </si>
-  <si>
-    <t>22:31:37</t>
-  </si>
-  <si>
-    <t>00:08:38</t>
-  </si>
-  <si>
-    <t>01:45:31</t>
-  </si>
-  <si>
-    <t>21:45:27</t>
-  </si>
-  <si>
-    <t>23:22:26</t>
-  </si>
-  <si>
-    <t>00:59:22</t>
-  </si>
-  <si>
-    <t>20:59:14</t>
-  </si>
-  <si>
-    <t>22:36:10</t>
-  </si>
-  <si>
-    <t>00:13:08</t>
-  </si>
-  <si>
-    <t>20:12:58</t>
-  </si>
-  <si>
-    <t>21:49:50</t>
-  </si>
-  <si>
-    <t>23:26:49</t>
-  </si>
-  <si>
-    <t>01:03:34</t>
-  </si>
-  <si>
-    <t>21:03:26</t>
-  </si>
-  <si>
-    <t>22:40:25</t>
-  </si>
-  <si>
-    <t>00:52:50</t>
-  </si>
-  <si>
-    <t>22:29:08</t>
-  </si>
-  <si>
-    <t>00:06:49</t>
+    <t>21:40:56</t>
+  </si>
+  <si>
+    <t>23:17:46</t>
+  </si>
+  <si>
+    <t>00:54:47</t>
+  </si>
+  <si>
+    <t>20:54:56</t>
+  </si>
+  <si>
+    <t>22:31:41</t>
+  </si>
+  <si>
+    <t>00:08:41</t>
+  </si>
+  <si>
+    <t>01:45:35</t>
+  </si>
+  <si>
+    <t>21:45:33</t>
+  </si>
+  <si>
+    <t>23:22:32</t>
+  </si>
+  <si>
+    <t>00:59:28</t>
+  </si>
+  <si>
+    <t>20:59:23</t>
+  </si>
+  <si>
+    <t>22:36:19</t>
+  </si>
+  <si>
+    <t>00:13:18</t>
+  </si>
+  <si>
+    <t>20:13:11</t>
+  </si>
+  <si>
+    <t>21:50:03</t>
+  </si>
+  <si>
+    <t>23:27:02</t>
+  </si>
+  <si>
+    <t>01:03:47</t>
+  </si>
+  <si>
+    <t>21:03:43</t>
+  </si>
+  <si>
+    <t>22:40:43</t>
+  </si>
+  <si>
+    <t>00:17:32</t>
+  </si>
+  <si>
+    <t>20:17:21</t>
+  </si>
+  <si>
+    <t>21:54:20</t>
+  </si>
+  <si>
+    <t>23:31:13</t>
+  </si>
+  <si>
+    <t>00:06:50</t>
   </si>
   <si>
     <t>01:43:41</t>
   </si>
   <si>
-    <t>21:42:41</t>
-  </si>
-  <si>
-    <t>23:20:43</t>
-  </si>
-  <si>
-    <t>00:57:44</t>
-  </si>
-  <si>
-    <t>20:55:41</t>
-  </si>
-  <si>
-    <t>22:34:30</t>
-  </si>
-  <si>
-    <t>00:11:39</t>
-  </si>
-  <si>
-    <t>01:47:46</t>
-  </si>
-  <si>
-    <t>21:48:11</t>
-  </si>
-  <si>
-    <t>23:25:29</t>
-  </si>
-  <si>
-    <t>01:01:55</t>
-  </si>
-  <si>
-    <t>21:01:44</t>
-  </si>
-  <si>
-    <t>22:39:13</t>
-  </si>
-  <si>
-    <t>00:15:53</t>
-  </si>
-  <si>
-    <t>20:15:08</t>
-  </si>
-  <si>
-    <t>21:52:51</t>
-  </si>
-  <si>
-    <t>23:29:43</t>
-  </si>
-  <si>
-    <t>01:04:36</t>
-  </si>
-  <si>
-    <t>21:06:23</t>
-  </si>
-  <si>
-    <t>22:43:24</t>
-  </si>
-  <si>
-    <t>00:55:05</t>
-  </si>
-  <si>
-    <t>22:31:46</t>
+    <t>21:42:42</t>
+  </si>
+  <si>
+    <t>23:20:44</t>
+  </si>
+  <si>
+    <t>00:57:45</t>
+  </si>
+  <si>
+    <t>20:55:44</t>
+  </si>
+  <si>
+    <t>22:34:33</t>
+  </si>
+  <si>
+    <t>00:11:43</t>
+  </si>
+  <si>
+    <t>01:47:49</t>
+  </si>
+  <si>
+    <t>21:48:17</t>
+  </si>
+  <si>
+    <t>23:25:35</t>
+  </si>
+  <si>
+    <t>01:02:01</t>
+  </si>
+  <si>
+    <t>21:01:53</t>
+  </si>
+  <si>
+    <t>22:39:22</t>
+  </si>
+  <si>
+    <t>00:16:03</t>
+  </si>
+  <si>
+    <t>20:15:21</t>
+  </si>
+  <si>
+    <t>21:53:03</t>
+  </si>
+  <si>
+    <t>23:29:56</t>
+  </si>
+  <si>
+    <t>01:04:49</t>
+  </si>
+  <si>
+    <t>21:06:40</t>
+  </si>
+  <si>
+    <t>22:43:42</t>
+  </si>
+  <si>
+    <t>00:19:24</t>
+  </si>
+  <si>
+    <t>20:20:12</t>
+  </si>
+  <si>
+    <t>21:57:22</t>
+  </si>
+  <si>
+    <t>23:33:31</t>
   </si>
   <si>
     <t>00:09:05</t>
   </si>
   <si>
-    <t>01:46:00</t>
-  </si>
-  <si>
-    <t>21:45:35</t>
-  </si>
-  <si>
-    <t>23:23:00</t>
-  </si>
-  <si>
-    <t>01:00:01</t>
-  </si>
-  <si>
-    <t>20:59:18</t>
-  </si>
-  <si>
-    <t>22:36:49</t>
-  </si>
-  <si>
-    <t>00:13:55</t>
-  </si>
-  <si>
-    <t>01:50:24</t>
-  </si>
-  <si>
-    <t>21:50:34</t>
-  </si>
-  <si>
-    <t>23:27:44</t>
-  </si>
-  <si>
-    <t>01:04:24</t>
-  </si>
-  <si>
-    <t>21:04:14</t>
-  </si>
-  <si>
-    <t>22:41:27</t>
-  </si>
-  <si>
-    <t>00:18:16</t>
-  </si>
-  <si>
-    <t>20:17:48</t>
-  </si>
-  <si>
-    <t>21:55:06</t>
-  </si>
-  <si>
-    <t>23:32:01</t>
-  </si>
-  <si>
-    <t>01:08:01</t>
-  </si>
-  <si>
-    <t>21:08:40</t>
-  </si>
-  <si>
-    <t>22:45:40</t>
-  </si>
-  <si>
-    <t>22°</t>
+    <t>01:46:01</t>
+  </si>
+  <si>
+    <t>21:45:37</t>
+  </si>
+  <si>
+    <t>23:23:01</t>
+  </si>
+  <si>
+    <t>01:00:02</t>
+  </si>
+  <si>
+    <t>20:59:21</t>
+  </si>
+  <si>
+    <t>22:36:53</t>
+  </si>
+  <si>
+    <t>00:13:58</t>
+  </si>
+  <si>
+    <t>01:50:27</t>
+  </si>
+  <si>
+    <t>21:50:40</t>
+  </si>
+  <si>
+    <t>23:27:50</t>
+  </si>
+  <si>
+    <t>01:04:30</t>
+  </si>
+  <si>
+    <t>21:04:23</t>
+  </si>
+  <si>
+    <t>22:41:36</t>
+  </si>
+  <si>
+    <t>00:18:25</t>
+  </si>
+  <si>
+    <t>20:18:01</t>
+  </si>
+  <si>
+    <t>21:55:19</t>
+  </si>
+  <si>
+    <t>23:32:14</t>
+  </si>
+  <si>
+    <t>01:08:14</t>
+  </si>
+  <si>
+    <t>21:08:57</t>
+  </si>
+  <si>
+    <t>22:45:58</t>
+  </si>
+  <si>
+    <t>00:22:15</t>
+  </si>
+  <si>
+    <t>20:22:32</t>
+  </si>
+  <si>
+    <t>21:59:37</t>
+  </si>
+  <si>
+    <t>23:36:07</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>19°</t>
   </si>
   <si>
     <t>2°</t>
   </si>
   <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
     <t>26°</t>
   </si>
   <si>
@@ -622,82 +667,88 @@
     <t>15°</t>
   </si>
   <si>
-    <t>00:48:19</t>
-  </si>
-  <si>
-    <t>22:31:03</t>
-  </si>
-  <si>
-    <t>00:04:06</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>00:04:07</t>
   </si>
   <si>
     <t>01:37:10</t>
   </si>
   <si>
-    <t>23:20:02</t>
-  </si>
-  <si>
-    <t>00:53:07</t>
-  </si>
-  <si>
-    <t>22:36:22</t>
-  </si>
-  <si>
-    <t>00:09:29</t>
-  </si>
-  <si>
-    <t>01:42:37</t>
-  </si>
-  <si>
-    <t>21:42:06</t>
-  </si>
-  <si>
-    <t>23:26:59</t>
-  </si>
-  <si>
-    <t>01:00:13</t>
-  </si>
-  <si>
-    <t>21:00:15</t>
-  </si>
-  <si>
-    <t>22:33:24</t>
-  </si>
-  <si>
-    <t>20:16:49</t>
-  </si>
-  <si>
-    <t>21:49:53</t>
-  </si>
-  <si>
-    <t>23:22:57</t>
-  </si>
-  <si>
-    <t>21:05:37</t>
-  </si>
-  <si>
-    <t>22:38:40</t>
+    <t>23:20:04</t>
+  </si>
+  <si>
+    <t>00:53:08</t>
+  </si>
+  <si>
+    <t>22:36:26</t>
+  </si>
+  <si>
+    <t>00:09:33</t>
+  </si>
+  <si>
+    <t>01:42:40</t>
+  </si>
+  <si>
+    <t>21:42:11</t>
+  </si>
+  <si>
+    <t>23:27:05</t>
+  </si>
+  <si>
+    <t>01:00:19</t>
+  </si>
+  <si>
+    <t>21:00:23</t>
+  </si>
+  <si>
+    <t>22:33:32</t>
+  </si>
+  <si>
+    <t>20:17:01</t>
+  </si>
+  <si>
+    <t>21:50:05</t>
+  </si>
+  <si>
+    <t>23:23:09</t>
+  </si>
+  <si>
+    <t>21:05:54</t>
+  </si>
+  <si>
+    <t>22:38:56</t>
+  </si>
+  <si>
+    <t>20:21:22</t>
+  </si>
+  <si>
+    <t>21:54:24</t>
+  </si>
+  <si>
+    <t>23:27:25</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -731,7 +782,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,7 +809,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,67 +839,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,7 +869,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -860,7 +929,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -907,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -985,6 +1054,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1388,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1466,52 +1544,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.6</v>
+        <v>-15</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="O2" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>5</v>
+      <c r="Q2" s="7">
+        <v>0</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -1522,52 +1600,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="O3" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="8">
-        <v>5</v>
+      <c r="Q3" s="7">
+        <v>0</v>
       </c>
       <c r="R3" s="7">
         <v>0</v>
@@ -1578,55 +1656,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
+        <v>243</v>
+      </c>
+      <c r="O4" s="8">
+        <v>25</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="Q4" s="9">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1634,55 +1712,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="L5" s="4">
-        <v>-8.699999999999999</v>
+        <v>-16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="Q5" s="9">
+        <v>3</v>
+      </c>
+      <c r="R5" s="9">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1690,55 +1768,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="L6" s="4">
-        <v>-13.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="O6" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>5</v>
-      </c>
-      <c r="R6" s="7">
-        <v>1</v>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1746,55 +1824,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-10.5</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="O7" s="12">
         <v>100</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-16</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+      <c r="Q7" s="11">
+        <v>17</v>
+      </c>
+      <c r="R7" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1802,55 +1880,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.4</v>
+        <v>-15.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O8" s="9">
-        <v>53</v>
+        <v>244</v>
+      </c>
+      <c r="O8" s="12">
+        <v>67</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>53</v>
+      <c r="Q8" s="14">
+        <v>28</v>
+      </c>
+      <c r="R8" s="15">
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1858,55 +1936,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="L9" s="4">
-        <v>-10.5</v>
+        <v>-14.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O9" s="9">
-        <v>74</v>
+        <v>241</v>
+      </c>
+      <c r="O9" s="12">
+        <v>100</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <v>51</v>
+      <c r="Q9" s="16">
+        <v>10</v>
+      </c>
+      <c r="R9" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1914,55 +1992,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="L10" s="4">
-        <v>-15.7</v>
+        <v>-8.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" s="9">
-        <v>18</v>
+        <v>241</v>
+      </c>
+      <c r="O10" s="12">
+        <v>79</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="12">
-        <v>17</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
+      <c r="Q10" s="15">
+        <v>54</v>
+      </c>
+      <c r="R10" s="17">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1970,55 +2048,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="L11" s="4">
-        <v>-14.9</v>
+        <v>-13.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O11" s="9">
-        <v>71</v>
-      </c>
-      <c r="P11" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>46</v>
+        <v>244</v>
+      </c>
+      <c r="O11" s="12">
+        <v>100</v>
+      </c>
+      <c r="P11" s="18">
+        <v>66</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>92</v>
       </c>
       <c r="R11" s="13">
-        <v>43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2026,55 +2104,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="L12" s="4">
-        <v>-8.4</v>
+        <v>-16.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O12" s="9">
-        <v>65</v>
-      </c>
-      <c r="P12" s="14">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>43</v>
-      </c>
-      <c r="R12" s="11">
-        <v>50</v>
+        <v>244</v>
+      </c>
+      <c r="O12" s="12">
+        <v>100</v>
+      </c>
+      <c r="P12" s="20">
+        <v>77</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>75</v>
+      </c>
+      <c r="R12" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2082,55 +2160,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="L13" s="4">
-        <v>-13.9</v>
+        <v>-12.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O13" s="9">
+        <v>241</v>
+      </c>
+      <c r="O13" s="12">
         <v>100</v>
       </c>
-      <c r="P13" s="15">
-        <v>37</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>89</v>
-      </c>
-      <c r="R13" s="17">
-        <v>87</v>
+      <c r="P13" s="21">
+        <v>86</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>70</v>
+      </c>
+      <c r="R13" s="22">
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2138,54 +2216,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="L14" s="4">
-        <v>-16.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" s="9">
+        <v>241</v>
+      </c>
+      <c r="O14" s="12">
         <v>100</v>
       </c>
-      <c r="P14" s="15">
-        <v>35</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>54</v>
-      </c>
-      <c r="R14" s="18">
+      <c r="P14" s="23">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="24">
+        <v>46</v>
+      </c>
+      <c r="R14" s="13">
         <v>100</v>
       </c>
     </row>
@@ -2194,55 +2272,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="L15" s="4">
-        <v>-12.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O15" s="9">
-        <v>100</v>
-      </c>
-      <c r="P15" s="19">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>44</v>
-      </c>
-      <c r="R15" s="18">
-        <v>100</v>
+        <v>241</v>
+      </c>
+      <c r="O15" s="12">
+        <v>70</v>
+      </c>
+      <c r="P15" s="24">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>49</v>
+      </c>
+      <c r="R15" s="17">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2250,55 +2328,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="L16" s="4">
-        <v>-10.9</v>
+        <v>-14.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O16" s="9">
-        <v>98</v>
-      </c>
-      <c r="P16" s="16">
-        <v>89</v>
+        <v>244</v>
+      </c>
+      <c r="O16" s="12">
+        <v>76</v>
+      </c>
+      <c r="P16" s="18">
+        <v>67</v>
       </c>
       <c r="Q16" s="15">
-        <v>33</v>
-      </c>
-      <c r="R16" s="20">
-        <v>76</v>
+        <v>53</v>
+      </c>
+      <c r="R16" s="17">
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2306,55 +2384,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="L17" s="4">
-        <v>-15.9</v>
+        <v>-6.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O17" s="9">
+        <v>241</v>
+      </c>
+      <c r="O17" s="12">
         <v>98</v>
       </c>
-      <c r="P17" s="17">
-        <v>84</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>8</v>
-      </c>
-      <c r="R17" s="17">
-        <v>83</v>
+      <c r="P17" s="15">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>47</v>
+      </c>
+      <c r="R17" s="23">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2362,55 +2440,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="L18" s="4">
-        <v>-14.9</v>
+        <v>-14.3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O18" s="9">
-        <v>99</v>
-      </c>
-      <c r="P18" s="16">
-        <v>92</v>
-      </c>
-      <c r="Q18" s="22">
-        <v>69</v>
-      </c>
-      <c r="R18" s="23">
-        <v>96</v>
+        <v>241</v>
+      </c>
+      <c r="O18" s="12">
+        <v>97</v>
+      </c>
+      <c r="P18" s="15">
+        <v>53</v>
+      </c>
+      <c r="Q18" s="26">
+        <v>38</v>
+      </c>
+      <c r="R18" s="27">
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2418,55 +2496,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="O19" s="12">
+        <v>82</v>
+      </c>
+      <c r="P19" s="24">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="11">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-6.8</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O19" s="9">
-        <v>85</v>
-      </c>
-      <c r="P19" s="24">
-        <v>80</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>46</v>
+      <c r="R19" s="27">
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2474,55 +2552,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="L20" s="4">
-        <v>-14.3</v>
+        <v>-12.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O20" s="9">
-        <v>67</v>
-      </c>
-      <c r="P20" s="25">
-        <v>59</v>
+        <v>243</v>
+      </c>
+      <c r="O20" s="12">
+        <v>64</v>
+      </c>
+      <c r="P20" s="28">
+        <v>34</v>
       </c>
       <c r="Q20" s="7">
         <v>0</v>
       </c>
-      <c r="R20" s="19">
-        <v>40</v>
+      <c r="R20" s="18">
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2530,55 +2608,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-11.4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="O21" s="12">
+        <v>78</v>
+      </c>
+      <c r="P21" s="29">
         <v>26</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-16.2</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O21" s="9">
-        <v>46</v>
-      </c>
-      <c r="P21" s="26">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="7">
+      <c r="Q21" s="20">
+        <v>74</v>
+      </c>
+      <c r="R21" s="7">
         <v>1</v>
-      </c>
-      <c r="R21" s="13">
-        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2586,55 +2664,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>92</v>
+        <v>234</v>
       </c>
       <c r="L22" s="4">
-        <v>-12.1</v>
+        <v>-16.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O22" s="9">
-        <v>43</v>
-      </c>
-      <c r="P22" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="7">
+        <v>241</v>
+      </c>
+      <c r="O22" s="12">
+        <v>84</v>
+      </c>
+      <c r="P22" s="29">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="21">
+        <v>84</v>
+      </c>
+      <c r="R22" s="7">
         <v>2</v>
-      </c>
-      <c r="R22" s="13">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2642,55 +2720,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="L23" s="4">
-        <v>-11.3</v>
+        <v>-14.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O23" s="9">
-        <v>49</v>
-      </c>
-      <c r="P23" s="12">
-        <v>13</v>
-      </c>
-      <c r="Q23" s="15">
-        <v>37</v>
+        <v>243</v>
+      </c>
+      <c r="O23" s="12">
+        <v>83</v>
+      </c>
+      <c r="P23" s="15">
+        <v>54</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>65</v>
       </c>
       <c r="R23" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2698,114 +2776,226 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
+        <v>25</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-7.4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O24" s="12">
+        <v>53</v>
+      </c>
+      <c r="P24" s="26">
+        <v>38</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>20</v>
+      </c>
+      <c r="R24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2">
+        <v>30</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-14.6</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" s="8">
+        <v>42</v>
+      </c>
+      <c r="P25" s="14">
         <v>29</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O24" s="9">
-        <v>50</v>
-      </c>
-      <c r="P24" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="19">
+      <c r="Q25" s="16">
+        <v>10</v>
+      </c>
+      <c r="R25" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R24" s="7">
+      <c r="B26" s="2">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-16.3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="O26" s="8">
+        <v>32</v>
+      </c>
+      <c r="P26" s="10">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A24">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K24">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L24">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2824,12 +3014,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2846,22 +3036,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O24">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q24">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="227">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260627--01</t>
-  </si>
-  <si>
-    <t>20260627--02</t>
-  </si>
-  <si>
-    <t>20260627--03</t>
-  </si>
-  <si>
-    <t>20260627--04</t>
-  </si>
-  <si>
     <t>20260628--01</t>
   </si>
   <si>
@@ -145,121 +133,106 @@
     <t>20260703--04</t>
   </si>
   <si>
-    <t>06:04</t>
+    <t>20260704--01</t>
+  </si>
+  <si>
+    <t>20260704--02</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>01:34</t>
   </si>
   <si>
     <t>05:45</t>
   </si>
   <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>01:34</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
     <t>06:03</t>
   </si>
   <si>
     <t>04:29</t>
   </si>
   <si>
-    <t>05:27</t>
+    <t>05:26</t>
   </si>
   <si>
     <t>06:06</t>
   </si>
   <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>02:03</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:09</t>
+  </si>
+  <si>
+    <t>01:42</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>00:16</t>
+  </si>
+  <si>
+    <t>03:03</t>
+  </si>
+  <si>
     <t>05:06</t>
   </si>
   <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>02:04</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>01:42</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>03:03</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
     <t>01:11</t>
   </si>
   <si>
     <t>03:05</t>
   </si>
   <si>
-    <t>23:58:31</t>
-  </si>
-  <si>
-    <t>01:35:37</t>
-  </si>
-  <si>
-    <t>21:36:17</t>
-  </si>
-  <si>
-    <t>23:12:32</t>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>00:27</t>
   </si>
   <si>
     <t>00:49:32</t>
@@ -268,73 +241,67 @@
     <t>20:50:34</t>
   </si>
   <si>
-    <t>22:26:30</t>
+    <t>22:26:31</t>
   </si>
   <si>
     <t>00:03:25</t>
   </si>
   <si>
-    <t>01:40:42</t>
-  </si>
-  <si>
-    <t>21:40:28</t>
-  </si>
-  <si>
-    <t>23:17:15</t>
-  </si>
-  <si>
-    <t>00:54:27</t>
-  </si>
-  <si>
-    <t>20:54:24</t>
-  </si>
-  <si>
-    <t>22:31:02</t>
-  </si>
-  <si>
-    <t>00:08:10</t>
-  </si>
-  <si>
-    <t>20:08:22</t>
-  </si>
-  <si>
-    <t>21:44:47</t>
-  </si>
-  <si>
-    <t>23:21:51</t>
-  </si>
-  <si>
-    <t>00:59:20</t>
-  </si>
-  <si>
-    <t>20:58:30</t>
-  </si>
-  <si>
-    <t>22:35:29</t>
-  </si>
-  <si>
-    <t>00:12:50</t>
-  </si>
-  <si>
-    <t>20:12:12</t>
-  </si>
-  <si>
-    <t>21:49:04</t>
-  </si>
-  <si>
-    <t>23:26:19</t>
-  </si>
-  <si>
-    <t>00:00:46</t>
-  </si>
-  <si>
-    <t>01:37:56</t>
-  </si>
-  <si>
-    <t>21:39:11</t>
-  </si>
-  <si>
-    <t>23:14:48</t>
+    <t>01:40:43</t>
+  </si>
+  <si>
+    <t>21:40:29</t>
+  </si>
+  <si>
+    <t>23:17:16</t>
+  </si>
+  <si>
+    <t>00:54:28</t>
+  </si>
+  <si>
+    <t>20:54:26</t>
+  </si>
+  <si>
+    <t>22:31:04</t>
+  </si>
+  <si>
+    <t>00:08:12</t>
+  </si>
+  <si>
+    <t>20:08:24</t>
+  </si>
+  <si>
+    <t>21:44:50</t>
+  </si>
+  <si>
+    <t>23:21:54</t>
+  </si>
+  <si>
+    <t>00:59:23</t>
+  </si>
+  <si>
+    <t>20:58:34</t>
+  </si>
+  <si>
+    <t>22:35:33</t>
+  </si>
+  <si>
+    <t>00:12:54</t>
+  </si>
+  <si>
+    <t>20:12:17</t>
+  </si>
+  <si>
+    <t>21:49:09</t>
+  </si>
+  <si>
+    <t>23:26:25</t>
+  </si>
+  <si>
+    <t>21:02:44</t>
+  </si>
+  <si>
+    <t>22:39:54</t>
   </si>
   <si>
     <t>00:51:49</t>
@@ -349,142 +316,130 @@
     <t>00:05:40</t>
   </si>
   <si>
-    <t>01:43:20</t>
-  </si>
-  <si>
-    <t>21:42:50</t>
-  </si>
-  <si>
-    <t>23:19:29</t>
-  </si>
-  <si>
-    <t>00:56:55</t>
-  </si>
-  <si>
-    <t>20:56:54</t>
-  </si>
-  <si>
-    <t>22:33:17</t>
-  </si>
-  <si>
-    <t>00:10:33</t>
-  </si>
-  <si>
-    <t>20:11:01</t>
-  </si>
-  <si>
-    <t>21:47:02</t>
-  </si>
-  <si>
-    <t>23:24:09</t>
-  </si>
-  <si>
-    <t>01:02:45</t>
-  </si>
-  <si>
-    <t>21:00:47</t>
-  </si>
-  <si>
-    <t>22:37:45</t>
-  </si>
-  <si>
-    <t>00:15:41</t>
-  </si>
-  <si>
-    <t>20:14:31</t>
-  </si>
-  <si>
-    <t>21:51:19</t>
-  </si>
-  <si>
-    <t>23:28:55</t>
-  </si>
-  <si>
-    <t>00:03:48</t>
-  </si>
-  <si>
-    <t>01:40:48</t>
-  </si>
-  <si>
-    <t>21:40:56</t>
-  </si>
-  <si>
-    <t>23:17:46</t>
+    <t>01:43:21</t>
+  </si>
+  <si>
+    <t>21:42:51</t>
+  </si>
+  <si>
+    <t>23:19:30</t>
+  </si>
+  <si>
+    <t>00:56:57</t>
+  </si>
+  <si>
+    <t>20:56:55</t>
+  </si>
+  <si>
+    <t>22:33:18</t>
+  </si>
+  <si>
+    <t>00:10:34</t>
+  </si>
+  <si>
+    <t>20:11:04</t>
+  </si>
+  <si>
+    <t>21:47:05</t>
+  </si>
+  <si>
+    <t>23:24:12</t>
+  </si>
+  <si>
+    <t>01:02:48</t>
+  </si>
+  <si>
+    <t>21:00:51</t>
+  </si>
+  <si>
+    <t>22:37:49</t>
+  </si>
+  <si>
+    <t>00:15:45</t>
+  </si>
+  <si>
+    <t>20:14:37</t>
+  </si>
+  <si>
+    <t>21:51:24</t>
+  </si>
+  <si>
+    <t>23:29:01</t>
+  </si>
+  <si>
+    <t>21:04:58</t>
+  </si>
+  <si>
+    <t>22:42:21</t>
   </si>
   <si>
     <t>00:54:47</t>
   </si>
   <si>
-    <t>20:54:56</t>
+    <t>20:54:57</t>
   </si>
   <si>
     <t>22:31:41</t>
   </si>
   <si>
-    <t>00:08:41</t>
+    <t>00:08:42</t>
   </si>
   <si>
     <t>01:45:35</t>
   </si>
   <si>
-    <t>21:45:33</t>
-  </si>
-  <si>
-    <t>23:22:32</t>
-  </si>
-  <si>
-    <t>00:59:28</t>
-  </si>
-  <si>
-    <t>20:59:23</t>
-  </si>
-  <si>
-    <t>22:36:19</t>
-  </si>
-  <si>
-    <t>00:13:18</t>
-  </si>
-  <si>
-    <t>20:13:11</t>
-  </si>
-  <si>
-    <t>21:50:03</t>
-  </si>
-  <si>
-    <t>23:27:02</t>
-  </si>
-  <si>
-    <t>01:03:47</t>
-  </si>
-  <si>
-    <t>21:03:43</t>
-  </si>
-  <si>
-    <t>22:40:43</t>
-  </si>
-  <si>
-    <t>00:17:32</t>
-  </si>
-  <si>
-    <t>20:17:21</t>
-  </si>
-  <si>
-    <t>21:54:20</t>
-  </si>
-  <si>
-    <t>23:31:13</t>
-  </si>
-  <si>
-    <t>00:06:50</t>
-  </si>
-  <si>
-    <t>01:43:41</t>
-  </si>
-  <si>
-    <t>21:42:42</t>
-  </si>
-  <si>
-    <t>23:20:44</t>
+    <t>21:45:34</t>
+  </si>
+  <si>
+    <t>23:22:33</t>
+  </si>
+  <si>
+    <t>00:59:29</t>
+  </si>
+  <si>
+    <t>20:59:25</t>
+  </si>
+  <si>
+    <t>22:36:21</t>
+  </si>
+  <si>
+    <t>00:13:19</t>
+  </si>
+  <si>
+    <t>20:13:13</t>
+  </si>
+  <si>
+    <t>21:50:06</t>
+  </si>
+  <si>
+    <t>23:27:05</t>
+  </si>
+  <si>
+    <t>01:03:50</t>
+  </si>
+  <si>
+    <t>21:03:47</t>
+  </si>
+  <si>
+    <t>22:40:47</t>
+  </si>
+  <si>
+    <t>00:17:36</t>
+  </si>
+  <si>
+    <t>20:17:26</t>
+  </si>
+  <si>
+    <t>21:54:26</t>
+  </si>
+  <si>
+    <t>23:31:19</t>
+  </si>
+  <si>
+    <t>21:08:00</t>
+  </si>
+  <si>
+    <t>22:44:56</t>
   </si>
   <si>
     <t>00:57:45</t>
@@ -493,73 +448,67 @@
     <t>20:55:44</t>
   </si>
   <si>
-    <t>22:34:33</t>
+    <t>22:34:34</t>
   </si>
   <si>
     <t>00:11:43</t>
   </si>
   <si>
-    <t>01:47:49</t>
+    <t>01:47:50</t>
   </si>
   <si>
     <t>21:48:17</t>
   </si>
   <si>
-    <t>23:25:35</t>
-  </si>
-  <si>
-    <t>01:02:01</t>
-  </si>
-  <si>
-    <t>21:01:53</t>
-  </si>
-  <si>
-    <t>22:39:22</t>
-  </si>
-  <si>
-    <t>00:16:03</t>
-  </si>
-  <si>
-    <t>20:15:21</t>
-  </si>
-  <si>
-    <t>21:53:03</t>
-  </si>
-  <si>
-    <t>23:29:56</t>
-  </si>
-  <si>
-    <t>01:04:49</t>
-  </si>
-  <si>
-    <t>21:06:40</t>
-  </si>
-  <si>
-    <t>22:43:42</t>
-  </si>
-  <si>
-    <t>00:19:24</t>
-  </si>
-  <si>
-    <t>20:20:12</t>
-  </si>
-  <si>
-    <t>21:57:22</t>
-  </si>
-  <si>
-    <t>23:33:31</t>
-  </si>
-  <si>
-    <t>00:09:05</t>
-  </si>
-  <si>
-    <t>01:46:01</t>
-  </si>
-  <si>
-    <t>21:45:37</t>
-  </si>
-  <si>
-    <t>23:23:01</t>
+    <t>23:25:36</t>
+  </si>
+  <si>
+    <t>01:02:02</t>
+  </si>
+  <si>
+    <t>21:01:55</t>
+  </si>
+  <si>
+    <t>22:39:23</t>
+  </si>
+  <si>
+    <t>00:16:04</t>
+  </si>
+  <si>
+    <t>20:15:23</t>
+  </si>
+  <si>
+    <t>21:53:06</t>
+  </si>
+  <si>
+    <t>23:29:58</t>
+  </si>
+  <si>
+    <t>01:04:51</t>
+  </si>
+  <si>
+    <t>21:06:44</t>
+  </si>
+  <si>
+    <t>22:43:46</t>
+  </si>
+  <si>
+    <t>00:19:28</t>
+  </si>
+  <si>
+    <t>20:20:17</t>
+  </si>
+  <si>
+    <t>21:57:27</t>
+  </si>
+  <si>
+    <t>23:33:37</t>
+  </si>
+  <si>
+    <t>21:11:03</t>
+  </si>
+  <si>
+    <t>22:47:32</t>
   </si>
   <si>
     <t>01:00:02</t>
@@ -571,13 +520,13 @@
     <t>22:36:53</t>
   </si>
   <si>
-    <t>00:13:58</t>
+    <t>00:13:59</t>
   </si>
   <si>
     <t>01:50:27</t>
   </si>
   <si>
-    <t>21:50:40</t>
+    <t>21:50:41</t>
   </si>
   <si>
     <t>23:27:50</t>
@@ -586,81 +535,81 @@
     <t>01:04:30</t>
   </si>
   <si>
-    <t>21:04:23</t>
-  </si>
-  <si>
-    <t>22:41:36</t>
-  </si>
-  <si>
-    <t>00:18:25</t>
-  </si>
-  <si>
-    <t>20:18:01</t>
-  </si>
-  <si>
-    <t>21:55:19</t>
-  </si>
-  <si>
-    <t>23:32:14</t>
-  </si>
-  <si>
-    <t>01:08:14</t>
-  </si>
-  <si>
-    <t>21:08:57</t>
-  </si>
-  <si>
-    <t>22:45:58</t>
-  </si>
-  <si>
-    <t>00:22:15</t>
-  </si>
-  <si>
-    <t>20:22:32</t>
-  </si>
-  <si>
-    <t>21:59:37</t>
-  </si>
-  <si>
-    <t>23:36:07</t>
+    <t>21:04:25</t>
+  </si>
+  <si>
+    <t>22:41:38</t>
+  </si>
+  <si>
+    <t>00:18:27</t>
+  </si>
+  <si>
+    <t>20:18:04</t>
+  </si>
+  <si>
+    <t>21:55:22</t>
+  </si>
+  <si>
+    <t>23:32:17</t>
+  </si>
+  <si>
+    <t>01:08:17</t>
+  </si>
+  <si>
+    <t>21:09:01</t>
+  </si>
+  <si>
+    <t>22:46:02</t>
+  </si>
+  <si>
+    <t>00:22:19</t>
+  </si>
+  <si>
+    <t>20:22:37</t>
+  </si>
+  <si>
+    <t>21:59:42</t>
+  </si>
+  <si>
+    <t>23:36:12</t>
+  </si>
+  <si>
+    <t>21:13:18</t>
+  </si>
+  <si>
+    <t>22:49:58</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
   </si>
   <si>
     <t>30°</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
@@ -670,85 +619,82 @@
     <t>4°</t>
   </si>
   <si>
-    <t>00:04:07</t>
-  </si>
-  <si>
-    <t>01:37:10</t>
-  </si>
-  <si>
-    <t>23:20:04</t>
-  </si>
-  <si>
-    <t>00:53:08</t>
+    <t>00:53:09</t>
   </si>
   <si>
     <t>22:36:26</t>
   </si>
   <si>
-    <t>00:09:33</t>
-  </si>
-  <si>
-    <t>01:42:40</t>
+    <t>00:09:34</t>
+  </si>
+  <si>
+    <t>01:42:41</t>
   </si>
   <si>
     <t>21:42:11</t>
   </si>
   <si>
-    <t>23:27:05</t>
-  </si>
-  <si>
-    <t>01:00:19</t>
-  </si>
-  <si>
-    <t>21:00:23</t>
-  </si>
-  <si>
-    <t>22:33:32</t>
-  </si>
-  <si>
-    <t>20:17:01</t>
-  </si>
-  <si>
-    <t>21:50:05</t>
-  </si>
-  <si>
-    <t>23:23:09</t>
-  </si>
-  <si>
-    <t>21:05:54</t>
-  </si>
-  <si>
-    <t>22:38:56</t>
-  </si>
-  <si>
-    <t>20:21:22</t>
-  </si>
-  <si>
-    <t>21:54:24</t>
-  </si>
-  <si>
-    <t>23:27:25</t>
+    <t>23:27:06</t>
+  </si>
+  <si>
+    <t>01:00:20</t>
+  </si>
+  <si>
+    <t>21:00:25</t>
+  </si>
+  <si>
+    <t>22:33:34</t>
+  </si>
+  <si>
+    <t>20:17:03</t>
+  </si>
+  <si>
+    <t>21:50:08</t>
+  </si>
+  <si>
+    <t>23:23:12</t>
+  </si>
+  <si>
+    <t>21:05:57</t>
+  </si>
+  <si>
+    <t>22:39:00</t>
+  </si>
+  <si>
+    <t>20:21:27</t>
+  </si>
+  <si>
+    <t>21:54:29</t>
+  </si>
+  <si>
+    <t>23:27:30</t>
+  </si>
+  <si>
+    <t>21:09:47</t>
+  </si>
+  <si>
+    <t>22:42:48</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -782,7 +728,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,7 +743,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,7 +755,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -822,120 +870,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -976,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1057,12 +991,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1466,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1544,46 +1472,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="L2" s="4">
-        <v>-15</v>
+        <v>-12.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1591,8 +1519,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1600,55 +1528,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="L3" s="4">
-        <v>-8.699999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>224</v>
+      </c>
+      <c r="O3" s="9">
+        <v>61</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="Q3" s="10">
+        <v>34</v>
+      </c>
+      <c r="R3" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1656,55 +1584,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="L4" s="4">
-        <v>-13.6</v>
+        <v>-15.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O4" s="8">
-        <v>25</v>
+        <v>225</v>
+      </c>
+      <c r="O4" s="9">
+        <v>61</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="9">
-        <v>5</v>
-      </c>
-      <c r="R4" s="10">
-        <v>19</v>
+      <c r="Q4" s="12">
+        <v>17</v>
+      </c>
+      <c r="R4" s="13">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1712,55 +1640,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-14.9</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="L5" s="4">
-        <v>-16</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O5" s="6">
-        <v>11</v>
+        <v>223</v>
+      </c>
+      <c r="O5" s="9">
+        <v>87</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="9">
-        <v>3</v>
-      </c>
-      <c r="R5" s="9">
-        <v>7</v>
+      <c r="Q5" s="14">
+        <v>24</v>
+      </c>
+      <c r="R5" s="15">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1768,55 +1696,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.4</v>
+        <v>-8.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O6" s="6">
-        <v>16</v>
+        <v>223</v>
+      </c>
+      <c r="O6" s="9">
+        <v>54</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>15</v>
+      <c r="Q6" s="16">
+        <v>44</v>
+      </c>
+      <c r="R6" s="13">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1824,54 +1752,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="L7" s="4">
-        <v>-10.5</v>
+        <v>-13.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O7" s="12">
+        <v>225</v>
+      </c>
+      <c r="O7" s="9">
         <v>100</v>
       </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>17</v>
-      </c>
-      <c r="R7" s="13">
+      <c r="P7" s="17">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>76</v>
+      </c>
+      <c r="R7" s="19">
         <v>100</v>
       </c>
     </row>
@@ -1880,55 +1808,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="L8" s="4">
-        <v>-15.7</v>
+        <v>-16.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O8" s="12">
-        <v>67</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>28</v>
-      </c>
-      <c r="R8" s="15">
-        <v>54</v>
+        <v>225</v>
+      </c>
+      <c r="O8" s="9">
+        <v>100</v>
+      </c>
+      <c r="P8" s="20">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>89</v>
+      </c>
+      <c r="R8" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1936,54 +1864,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-12.2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="L9" s="4">
-        <v>-14.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O9" s="12">
+      <c r="O9" s="9">
         <v>100</v>
       </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>10</v>
-      </c>
-      <c r="R9" s="13">
+      <c r="P9" s="19">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>65</v>
+      </c>
+      <c r="R9" s="19">
         <v>100</v>
       </c>
     </row>
@@ -1992,55 +1920,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="L10" s="4">
-        <v>-8.4</v>
+        <v>-10.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O10" s="12">
+        <v>223</v>
+      </c>
+      <c r="O10" s="9">
         <v>79</v>
       </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="15">
+      <c r="P10" s="16">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>49</v>
+      </c>
+      <c r="R10" s="13">
         <v>54</v>
-      </c>
-      <c r="R10" s="17">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2048,55 +1976,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L11" s="4">
-        <v>-13.9</v>
+        <v>-15.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O11" s="12">
-        <v>100</v>
-      </c>
-      <c r="P11" s="18">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>92</v>
-      </c>
-      <c r="R11" s="13">
-        <v>100</v>
+        <v>223</v>
+      </c>
+      <c r="O11" s="9">
+        <v>82</v>
+      </c>
+      <c r="P11" s="22">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>32</v>
+      </c>
+      <c r="R11" s="24">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2104,54 +2032,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.1</v>
+        <v>-14.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O12" s="12">
+        <v>225</v>
+      </c>
+      <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12" s="20">
-        <v>77</v>
-      </c>
-      <c r="Q12" s="20">
-        <v>75</v>
-      </c>
-      <c r="R12" s="13">
+      <c r="P12" s="13">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>37</v>
+      </c>
+      <c r="R12" s="19">
         <v>100</v>
       </c>
     </row>
@@ -2160,55 +2088,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="L13" s="4">
-        <v>-12.2</v>
+        <v>-6.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O13" s="12">
-        <v>100</v>
-      </c>
-      <c r="P13" s="21">
+        <v>223</v>
+      </c>
+      <c r="O13" s="9">
         <v>86</v>
       </c>
-      <c r="Q13" s="17">
-        <v>70</v>
-      </c>
-      <c r="R13" s="22">
-        <v>97</v>
+      <c r="P13" s="23">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>31</v>
+      </c>
+      <c r="R13" s="16">
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2216,55 +2144,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="L14" s="4">
-        <v>-10.9</v>
+        <v>-14.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O14" s="12">
-        <v>100</v>
-      </c>
-      <c r="P14" s="23">
-        <v>59</v>
-      </c>
-      <c r="Q14" s="24">
-        <v>46</v>
-      </c>
-      <c r="R14" s="13">
-        <v>100</v>
+        <v>223</v>
+      </c>
+      <c r="O14" s="9">
+        <v>63</v>
+      </c>
+      <c r="P14" s="12">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>36</v>
+      </c>
+      <c r="R14" s="24">
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2272,55 +2200,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="L15" s="4">
-        <v>-15.9</v>
+        <v>-16.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O15" s="12">
-        <v>70</v>
-      </c>
-      <c r="P15" s="24">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>49</v>
-      </c>
-      <c r="R15" s="17">
-        <v>70</v>
+        <v>225</v>
+      </c>
+      <c r="O15" s="6">
+        <v>48</v>
+      </c>
+      <c r="P15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>25</v>
+      </c>
+      <c r="R15" s="11">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2328,55 +2256,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L16" s="4">
-        <v>-14.9</v>
+        <v>-12</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O16" s="12">
-        <v>76</v>
-      </c>
-      <c r="P16" s="18">
-        <v>67</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>53</v>
-      </c>
-      <c r="R16" s="17">
-        <v>70</v>
+        <v>224</v>
+      </c>
+      <c r="O16" s="25">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2384,55 +2312,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="L17" s="4">
-        <v>-6.9</v>
+        <v>-11.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O17" s="12">
-        <v>98</v>
-      </c>
-      <c r="P17" s="15">
-        <v>57</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>47</v>
-      </c>
-      <c r="R17" s="23">
-        <v>61</v>
+        <v>223</v>
+      </c>
+      <c r="O17" s="9">
+        <v>50</v>
+      </c>
+      <c r="P17" s="16">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>50</v>
+      </c>
+      <c r="R17" s="26">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2440,55 +2368,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="L18" s="4">
-        <v>-14.3</v>
+        <v>-16.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O18" s="12">
-        <v>97</v>
-      </c>
-      <c r="P18" s="15">
-        <v>53</v>
-      </c>
-      <c r="Q18" s="26">
-        <v>38</v>
-      </c>
-      <c r="R18" s="27">
-        <v>79</v>
+        <v>223</v>
+      </c>
+      <c r="O18" s="9">
+        <v>73</v>
+      </c>
+      <c r="P18" s="21">
+        <v>66</v>
+      </c>
+      <c r="Q18" s="21">
+        <v>65</v>
+      </c>
+      <c r="R18" s="26">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2496,55 +2424,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-16.2</v>
+        <v>-14.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O19" s="12">
-        <v>82</v>
-      </c>
-      <c r="P19" s="24">
-        <v>44</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>16</v>
-      </c>
-      <c r="R19" s="27">
-        <v>82</v>
+        <v>224</v>
+      </c>
+      <c r="O19" s="9">
+        <v>55</v>
+      </c>
+      <c r="P19" s="22">
+        <v>41</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>55</v>
+      </c>
+      <c r="R19" s="11">
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2552,55 +2480,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-7.4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="O20" s="9">
+        <v>55</v>
+      </c>
+      <c r="P20" s="8">
         <v>11</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-12.1</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O20" s="12">
-        <v>64</v>
-      </c>
-      <c r="P20" s="28">
-        <v>34</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="18">
-        <v>64</v>
+      <c r="Q20" s="22">
+        <v>41</v>
+      </c>
+      <c r="R20" s="12">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2608,55 +2536,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="L21" s="4">
-        <v>-11.4</v>
+        <v>-14.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O21" s="12">
-        <v>78</v>
-      </c>
-      <c r="P21" s="29">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="20">
-        <v>74</v>
-      </c>
-      <c r="R21" s="7">
-        <v>1</v>
+        <v>223</v>
+      </c>
+      <c r="O21" s="9">
+        <v>53</v>
+      </c>
+      <c r="P21" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>38</v>
+      </c>
+      <c r="R21" s="27">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2664,55 +2592,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="L22" s="4">
-        <v>-16.1</v>
+        <v>-16.3</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O22" s="12">
-        <v>84</v>
-      </c>
-      <c r="P22" s="29">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="21">
-        <v>84</v>
-      </c>
-      <c r="R22" s="7">
-        <v>2</v>
+        <v>225</v>
+      </c>
+      <c r="O22" s="9">
+        <v>46</v>
+      </c>
+      <c r="P22" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>39</v>
+      </c>
+      <c r="R22" s="12">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2720,55 +2648,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="L23" s="4">
-        <v>-14.8</v>
+        <v>-11.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O23" s="12">
-        <v>83</v>
-      </c>
-      <c r="P23" s="15">
-        <v>54</v>
-      </c>
-      <c r="Q23" s="18">
-        <v>65</v>
-      </c>
-      <c r="R23" s="7">
-        <v>1</v>
+        <v>223</v>
+      </c>
+      <c r="O23" s="6">
+        <v>48</v>
+      </c>
+      <c r="P23" s="14">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0</v>
+      </c>
+      <c r="R23" s="26">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2776,226 +2704,114 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="L24" s="4">
-        <v>-7.4</v>
+        <v>-16.4</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="O24" s="12">
-        <v>53</v>
-      </c>
-      <c r="P24" s="26">
-        <v>38</v>
-      </c>
-      <c r="Q24" s="10">
-        <v>20</v>
-      </c>
-      <c r="R24" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2">
+        <v>223</v>
+      </c>
+      <c r="O24" s="9">
+        <v>52</v>
+      </c>
+      <c r="P24" s="23">
         <v>30</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-14.6</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="O25" s="8">
-        <v>42</v>
-      </c>
-      <c r="P25" s="14">
-        <v>29</v>
-      </c>
-      <c r="Q25" s="16">
-        <v>10</v>
-      </c>
-      <c r="R25" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>17</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-16.3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="O26" s="8">
-        <v>32</v>
-      </c>
-      <c r="P26" s="10">
-        <v>20</v>
-      </c>
-      <c r="Q26" s="7">
+      <c r="Q24" s="7">
         <v>0</v>
       </c>
-      <c r="R26" s="7">
-        <v>0</v>
+      <c r="R24" s="26">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A24">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D24">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I24">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J24">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K24">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -3014,12 +2830,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N24">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3036,22 +2852,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O24">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P24">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q24">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R24">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260628--01</t>
-  </si>
-  <si>
-    <t>20260628--02</t>
-  </si>
-  <si>
-    <t>20260628--03</t>
-  </si>
-  <si>
     <t>20260629--01</t>
   </si>
   <si>
@@ -139,13 +130,10 @@
     <t>20260704--02</t>
   </si>
   <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>01:34</t>
-  </si>
-  <si>
-    <t>05:45</t>
+    <t>20260705--01</t>
+  </si>
+  <si>
+    <t>20260705--02</t>
   </si>
   <si>
     <t>06:03</t>
@@ -157,22 +145,19 @@
     <t>05:26</t>
   </si>
   <si>
-    <t>06:06</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
     <t>06:05</t>
   </si>
   <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
     <t>05:30</t>
   </si>
   <si>
-    <t>04:19</t>
+    <t>04:20</t>
   </si>
   <si>
     <t>06:01</t>
@@ -196,37 +181,46 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>06:02</t>
+  </si>
+  <si>
     <t>04:36</t>
   </si>
   <si>
     <t>05:11</t>
   </si>
   <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>02:09</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:09</t>
-  </si>
-  <si>
     <t>01:42</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>00:16</t>
-  </si>
-  <si>
-    <t>03:03</t>
-  </si>
-  <si>
-    <t>05:06</t>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>03:02</t>
+  </si>
+  <si>
+    <t>05:07</t>
   </si>
   <si>
     <t>01:11</t>
   </si>
   <si>
-    <t>03:05</t>
+    <t>03:04</t>
   </si>
   <si>
     <t>04:49</t>
@@ -235,22 +229,16 @@
     <t>00:27</t>
   </si>
   <si>
-    <t>00:49:32</t>
-  </si>
-  <si>
-    <t>20:50:34</t>
-  </si>
-  <si>
-    <t>22:26:31</t>
+    <t>02:16</t>
   </si>
   <si>
     <t>00:03:25</t>
   </si>
   <si>
-    <t>01:40:43</t>
-  </si>
-  <si>
-    <t>21:40:29</t>
+    <t>01:40:42</t>
+  </si>
+  <si>
+    <t>21:40:28</t>
   </si>
   <si>
     <t>23:17:16</t>
@@ -274,7 +262,7 @@
     <t>21:44:50</t>
   </si>
   <si>
-    <t>23:21:54</t>
+    <t>23:21:53</t>
   </si>
   <si>
     <t>00:59:23</t>
@@ -283,40 +271,37 @@
     <t>20:58:34</t>
   </si>
   <si>
-    <t>22:35:33</t>
-  </si>
-  <si>
-    <t>00:12:54</t>
-  </si>
-  <si>
-    <t>20:12:17</t>
+    <t>22:35:32</t>
+  </si>
+  <si>
+    <t>00:12:53</t>
+  </si>
+  <si>
+    <t>20:12:16</t>
   </si>
   <si>
     <t>21:49:09</t>
   </si>
   <si>
-    <t>23:26:25</t>
-  </si>
-  <si>
-    <t>21:02:44</t>
-  </si>
-  <si>
-    <t>22:39:54</t>
-  </si>
-  <si>
-    <t>00:51:49</t>
-  </si>
-  <si>
-    <t>20:54:10</t>
-  </si>
-  <si>
-    <t>22:28:49</t>
+    <t>23:26:24</t>
+  </si>
+  <si>
+    <t>21:02:43</t>
+  </si>
+  <si>
+    <t>22:39:53</t>
+  </si>
+  <si>
+    <t>20:16:14</t>
+  </si>
+  <si>
+    <t>21:53:20</t>
   </si>
   <si>
     <t>00:05:40</t>
   </si>
   <si>
-    <t>01:43:21</t>
+    <t>01:43:20</t>
   </si>
   <si>
     <t>21:42:51</t>
@@ -325,7 +310,7 @@
     <t>23:19:30</t>
   </si>
   <si>
-    <t>00:56:57</t>
+    <t>00:56:56</t>
   </si>
   <si>
     <t>20:56:55</t>
@@ -337,7 +322,7 @@
     <t>00:10:34</t>
   </si>
   <si>
-    <t>20:11:04</t>
+    <t>20:11:03</t>
   </si>
   <si>
     <t>21:47:05</t>
@@ -349,37 +334,34 @@
     <t>01:02:48</t>
   </si>
   <si>
-    <t>21:00:51</t>
-  </si>
-  <si>
-    <t>22:37:49</t>
-  </si>
-  <si>
-    <t>00:15:45</t>
-  </si>
-  <si>
-    <t>20:14:37</t>
+    <t>21:00:50</t>
+  </si>
+  <si>
+    <t>22:37:48</t>
+  </si>
+  <si>
+    <t>00:15:44</t>
+  </si>
+  <si>
+    <t>20:14:36</t>
   </si>
   <si>
     <t>21:51:24</t>
   </si>
   <si>
-    <t>23:29:01</t>
-  </si>
-  <si>
-    <t>21:04:58</t>
-  </si>
-  <si>
-    <t>22:42:21</t>
-  </si>
-  <si>
-    <t>00:54:47</t>
-  </si>
-  <si>
-    <t>20:54:57</t>
-  </si>
-  <si>
-    <t>22:31:41</t>
+    <t>23:29:00</t>
+  </si>
+  <si>
+    <t>21:04:57</t>
+  </si>
+  <si>
+    <t>22:42:20</t>
+  </si>
+  <si>
+    <t>20:18:29</t>
+  </si>
+  <si>
+    <t>21:55:42</t>
   </si>
   <si>
     <t>00:08:42</t>
@@ -397,10 +379,10 @@
     <t>00:59:29</t>
   </si>
   <si>
-    <t>20:59:25</t>
-  </si>
-  <si>
-    <t>22:36:21</t>
+    <t>20:59:24</t>
+  </si>
+  <si>
+    <t>22:36:20</t>
   </si>
   <si>
     <t>00:13:19</t>
@@ -409,19 +391,19 @@
     <t>20:13:13</t>
   </si>
   <si>
-    <t>21:50:06</t>
+    <t>21:50:05</t>
   </si>
   <si>
     <t>23:27:05</t>
   </si>
   <si>
-    <t>01:03:50</t>
+    <t>01:03:49</t>
   </si>
   <si>
     <t>21:03:47</t>
   </si>
   <si>
-    <t>22:40:47</t>
+    <t>22:40:46</t>
   </si>
   <si>
     <t>00:17:36</t>
@@ -430,43 +412,40 @@
     <t>20:17:26</t>
   </si>
   <si>
-    <t>21:54:26</t>
-  </si>
-  <si>
-    <t>23:31:19</t>
-  </si>
-  <si>
-    <t>21:08:00</t>
-  </si>
-  <si>
-    <t>22:44:56</t>
-  </si>
-  <si>
-    <t>00:57:45</t>
-  </si>
-  <si>
-    <t>20:55:44</t>
-  </si>
-  <si>
-    <t>22:34:34</t>
+    <t>21:54:25</t>
+  </si>
+  <si>
+    <t>23:31:18</t>
+  </si>
+  <si>
+    <t>21:07:59</t>
+  </si>
+  <si>
+    <t>22:44:55</t>
+  </si>
+  <si>
+    <t>20:21:31</t>
+  </si>
+  <si>
+    <t>21:58:28</t>
   </si>
   <si>
     <t>00:11:43</t>
   </si>
   <si>
-    <t>01:47:50</t>
+    <t>01:47:49</t>
   </si>
   <si>
     <t>21:48:17</t>
   </si>
   <si>
-    <t>23:25:36</t>
+    <t>23:25:35</t>
   </si>
   <si>
     <t>01:02:02</t>
   </si>
   <si>
-    <t>21:01:55</t>
+    <t>21:01:54</t>
   </si>
   <si>
     <t>22:39:23</t>
@@ -487,40 +466,37 @@
     <t>01:04:51</t>
   </si>
   <si>
-    <t>21:06:44</t>
-  </si>
-  <si>
-    <t>22:43:46</t>
-  </si>
-  <si>
-    <t>00:19:28</t>
-  </si>
-  <si>
-    <t>20:20:17</t>
-  </si>
-  <si>
-    <t>21:57:27</t>
-  </si>
-  <si>
-    <t>23:33:37</t>
-  </si>
-  <si>
-    <t>21:11:03</t>
-  </si>
-  <si>
-    <t>22:47:32</t>
-  </si>
-  <si>
-    <t>01:00:02</t>
-  </si>
-  <si>
-    <t>20:59:21</t>
-  </si>
-  <si>
-    <t>22:36:53</t>
-  </si>
-  <si>
-    <t>00:13:59</t>
+    <t>21:06:43</t>
+  </si>
+  <si>
+    <t>22:43:45</t>
+  </si>
+  <si>
+    <t>00:19:27</t>
+  </si>
+  <si>
+    <t>20:20:16</t>
+  </si>
+  <si>
+    <t>21:57:26</t>
+  </si>
+  <si>
+    <t>23:33:36</t>
+  </si>
+  <si>
+    <t>21:11:02</t>
+  </si>
+  <si>
+    <t>22:47:31</t>
+  </si>
+  <si>
+    <t>20:24:33</t>
+  </si>
+  <si>
+    <t>22:01:15</t>
+  </si>
+  <si>
+    <t>00:13:58</t>
   </si>
   <si>
     <t>01:50:27</t>
@@ -535,94 +511,97 @@
     <t>01:04:30</t>
   </si>
   <si>
-    <t>21:04:25</t>
+    <t>21:04:24</t>
   </si>
   <si>
     <t>22:41:38</t>
   </si>
   <si>
-    <t>00:18:27</t>
-  </si>
-  <si>
-    <t>20:18:04</t>
-  </si>
-  <si>
-    <t>21:55:22</t>
+    <t>00:18:26</t>
+  </si>
+  <si>
+    <t>20:18:03</t>
+  </si>
+  <si>
+    <t>21:55:21</t>
   </si>
   <si>
     <t>23:32:17</t>
   </si>
   <si>
-    <t>01:08:17</t>
+    <t>01:08:16</t>
   </si>
   <si>
     <t>21:09:01</t>
   </si>
   <si>
-    <t>22:46:02</t>
-  </si>
-  <si>
-    <t>00:22:19</t>
-  </si>
-  <si>
-    <t>20:22:37</t>
-  </si>
-  <si>
-    <t>21:59:42</t>
-  </si>
-  <si>
-    <t>23:36:12</t>
-  </si>
-  <si>
-    <t>21:13:18</t>
-  </si>
-  <si>
-    <t>22:49:58</t>
+    <t>22:46:01</t>
+  </si>
+  <si>
+    <t>00:22:18</t>
+  </si>
+  <si>
+    <t>20:22:36</t>
+  </si>
+  <si>
+    <t>21:59:41</t>
+  </si>
+  <si>
+    <t>23:36:11</t>
+  </si>
+  <si>
+    <t>21:13:16</t>
+  </si>
+  <si>
+    <t>22:49:57</t>
+  </si>
+  <si>
+    <t>20:26:47</t>
+  </si>
+  <si>
+    <t>22:03:36</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>4°</t>
   </si>
   <si>
     <t>19°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>00:53:09</t>
-  </si>
-  <si>
-    <t>22:36:26</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>23°</t>
   </si>
   <si>
     <t>00:09:34</t>
@@ -640,58 +619,64 @@
     <t>01:00:20</t>
   </si>
   <si>
-    <t>21:00:25</t>
-  </si>
-  <si>
-    <t>22:33:34</t>
-  </si>
-  <si>
-    <t>20:17:03</t>
-  </si>
-  <si>
-    <t>21:50:08</t>
-  </si>
-  <si>
-    <t>23:23:12</t>
+    <t>21:00:24</t>
+  </si>
+  <si>
+    <t>22:33:33</t>
+  </si>
+  <si>
+    <t>20:17:02</t>
+  </si>
+  <si>
+    <t>21:50:07</t>
+  </si>
+  <si>
+    <t>23:23:11</t>
   </si>
   <si>
     <t>21:05:57</t>
   </si>
   <si>
-    <t>22:39:00</t>
-  </si>
-  <si>
-    <t>20:21:27</t>
-  </si>
-  <si>
-    <t>21:54:29</t>
-  </si>
-  <si>
-    <t>23:27:30</t>
-  </si>
-  <si>
-    <t>21:09:47</t>
-  </si>
-  <si>
-    <t>22:42:48</t>
+    <t>22:38:59</t>
+  </si>
+  <si>
+    <t>20:21:26</t>
+  </si>
+  <si>
+    <t>21:54:28</t>
+  </si>
+  <si>
+    <t>23:27:29</t>
+  </si>
+  <si>
+    <t>21:09:46</t>
+  </si>
+  <si>
+    <t>22:42:47</t>
+  </si>
+  <si>
+    <t>20:24:57</t>
+  </si>
+  <si>
+    <t>21:57:58</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>1</t>
@@ -728,7 +713,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -743,7 +728,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,13 +740,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,19 +794,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,49 +806,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -851,7 +824,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,13 +848,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -910,7 +889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -988,9 +967,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1394,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1472,55 +1448,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.4</v>
+        <v>-14.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O2" s="6">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>12</v>
+      <c r="Q2" s="8">
+        <v>6</v>
+      </c>
+      <c r="R2" s="9">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1528,55 +1504,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
       <c r="L3" s="4">
-        <v>-10.5</v>
+        <v>-8.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O3" s="9">
-        <v>61</v>
+        <v>218</v>
+      </c>
+      <c r="O3" s="6">
+        <v>79</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>34</v>
-      </c>
-      <c r="R3" s="11">
-        <v>50</v>
+      <c r="Q3" s="8">
+        <v>3</v>
+      </c>
+      <c r="R3" s="10">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1584,55 +1560,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.7</v>
+        <v>-13.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O4" s="9">
-        <v>61</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="11">
+        <v>57</v>
       </c>
       <c r="Q4" s="12">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="R4" s="13">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1640,55 +1616,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-16.1</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O5" s="6">
         <v>99</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-14.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O5" s="9">
-        <v>87</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>24</v>
-      </c>
-      <c r="R5" s="15">
-        <v>80</v>
+      <c r="P5" s="10">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>54</v>
+      </c>
+      <c r="R5" s="14">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1696,55 +1672,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L6" s="4">
-        <v>-8.4</v>
+        <v>-12.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O6" s="9">
-        <v>54</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>44</v>
-      </c>
-      <c r="R6" s="13">
-        <v>54</v>
+        <v>218</v>
+      </c>
+      <c r="O6" s="6">
+        <v>96</v>
+      </c>
+      <c r="P6" s="10">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>55</v>
+      </c>
+      <c r="R6" s="15">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1752,55 +1728,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L7" s="4">
-        <v>-13.9</v>
+        <v>-10.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="9">
-        <v>100</v>
-      </c>
-      <c r="P7" s="17">
-        <v>84</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>76</v>
-      </c>
-      <c r="R7" s="19">
-        <v>100</v>
+        <v>218</v>
+      </c>
+      <c r="O7" s="6">
+        <v>99</v>
+      </c>
+      <c r="P7" s="16">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>59</v>
+      </c>
+      <c r="R7" s="13">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1811,52 +1787,52 @@
         <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.1</v>
+        <v>-15.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" s="9">
-        <v>100</v>
-      </c>
-      <c r="P8" s="20">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>89</v>
-      </c>
-      <c r="R8" s="19">
-        <v>100</v>
+        <v>218</v>
+      </c>
+      <c r="O8" s="6">
+        <v>91</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>59</v>
+      </c>
+      <c r="R8" s="17">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1864,55 +1840,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="L9" s="4">
-        <v>-12.2</v>
+        <v>-14.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O9" s="9">
-        <v>100</v>
-      </c>
-      <c r="P9" s="19">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>65</v>
-      </c>
-      <c r="R9" s="19">
-        <v>100</v>
+        <v>219</v>
+      </c>
+      <c r="O9" s="6">
+        <v>58</v>
+      </c>
+      <c r="P9" s="9">
+        <v>38</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1920,55 +1896,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L10" s="4">
-        <v>-10.9</v>
+        <v>-6.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O10" s="9">
-        <v>79</v>
-      </c>
-      <c r="P10" s="16">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>49</v>
-      </c>
-      <c r="R10" s="13">
-        <v>54</v>
+        <v>218</v>
+      </c>
+      <c r="O10" s="6">
+        <v>88</v>
+      </c>
+      <c r="P10" s="15">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>27</v>
+      </c>
+      <c r="R10" s="17">
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1976,55 +1952,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="L11" s="4">
-        <v>-15.9</v>
+        <v>-14.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O11" s="9">
-        <v>82</v>
-      </c>
-      <c r="P11" s="22">
-        <v>42</v>
-      </c>
-      <c r="Q11" s="23">
-        <v>32</v>
-      </c>
-      <c r="R11" s="24">
-        <v>60</v>
+        <v>218</v>
+      </c>
+      <c r="O11" s="6">
+        <v>90</v>
+      </c>
+      <c r="P11" s="12">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>46</v>
+      </c>
+      <c r="R11" s="15">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2032,55 +2008,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="L12" s="4">
-        <v>-14.9</v>
+        <v>-16.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="9">
-        <v>100</v>
-      </c>
-      <c r="P12" s="13">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>37</v>
-      </c>
-      <c r="R12" s="19">
-        <v>100</v>
+        <v>219</v>
+      </c>
+      <c r="O12" s="6">
+        <v>84</v>
+      </c>
+      <c r="P12" s="11">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>21</v>
+      </c>
+      <c r="R12" s="11">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2088,55 +2064,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="L13" s="4">
-        <v>-6.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O13" s="9">
-        <v>86</v>
-      </c>
-      <c r="P13" s="23">
-        <v>31</v>
-      </c>
-      <c r="Q13" s="23">
-        <v>31</v>
-      </c>
-      <c r="R13" s="16">
-        <v>43</v>
+        <v>220</v>
+      </c>
+      <c r="O13" s="6">
+        <v>55</v>
+      </c>
+      <c r="P13" s="9">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="20">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2144,55 +2120,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L14" s="4">
-        <v>-14.3</v>
+        <v>-11.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O14" s="9">
-        <v>63</v>
-      </c>
-      <c r="P14" s="12">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>36</v>
-      </c>
-      <c r="R14" s="24">
-        <v>58</v>
+        <v>218</v>
+      </c>
+      <c r="O14" s="6">
+        <v>64</v>
+      </c>
+      <c r="P14" s="21">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>52</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2200,55 +2176,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L15" s="4">
-        <v>-16.2</v>
+        <v>-16.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="O15" s="6">
-        <v>48</v>
-      </c>
-      <c r="P15" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>25</v>
-      </c>
-      <c r="R15" s="11">
-        <v>48</v>
+        <v>64</v>
+      </c>
+      <c r="P15" s="20">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>53</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2256,52 +2232,52 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L16" s="4">
-        <v>-12</v>
+        <v>-14.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O16" s="25">
-        <v>0</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="O16" s="6">
+        <v>44</v>
+      </c>
+      <c r="P16" s="16">
+        <v>33</v>
+      </c>
+      <c r="Q16" s="21">
+        <v>31</v>
       </c>
       <c r="R16" s="7">
         <v>0</v>
@@ -2312,55 +2288,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="L17" s="4">
-        <v>-11.4</v>
+        <v>-7.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O17" s="9">
-        <v>50</v>
-      </c>
-      <c r="P17" s="16">
-        <v>45</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>50</v>
-      </c>
-      <c r="R17" s="26">
-        <v>3</v>
+        <v>221</v>
+      </c>
+      <c r="O17" s="23">
+        <v>11</v>
+      </c>
+      <c r="P17" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>11</v>
+      </c>
+      <c r="R17" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2368,55 +2344,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L18" s="4">
-        <v>-16.1</v>
+        <v>-14.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O18" s="9">
-        <v>73</v>
-      </c>
-      <c r="P18" s="21">
-        <v>66</v>
-      </c>
-      <c r="Q18" s="21">
-        <v>65</v>
-      </c>
-      <c r="R18" s="26">
-        <v>4</v>
+        <v>218</v>
+      </c>
+      <c r="O18" s="25">
+        <v>8</v>
+      </c>
+      <c r="P18" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>8</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2424,55 +2400,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="L19" s="4">
-        <v>-14.8</v>
+        <v>-16.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O19" s="9">
-        <v>55</v>
-      </c>
-      <c r="P19" s="22">
-        <v>41</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>55</v>
-      </c>
-      <c r="R19" s="11">
-        <v>52</v>
+        <v>219</v>
+      </c>
+      <c r="O19" s="23">
+        <v>19</v>
+      </c>
+      <c r="P19" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="26">
+        <v>15</v>
+      </c>
+      <c r="R19" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2480,55 +2456,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-11.8</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="L20" s="4">
-        <v>-7.4</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="N20" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O20" s="9">
-        <v>55</v>
-      </c>
-      <c r="P20" s="8">
+        <v>218</v>
+      </c>
+      <c r="O20" s="23">
+        <v>27</v>
+      </c>
+      <c r="P20" s="24">
         <v>11</v>
       </c>
-      <c r="Q20" s="22">
-        <v>41</v>
-      </c>
-      <c r="R20" s="12">
-        <v>17</v>
+      <c r="Q20" s="18">
+        <v>27</v>
+      </c>
+      <c r="R20" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2536,55 +2512,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="L21" s="4">
-        <v>-14.6</v>
+        <v>-16.4</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O21" s="9">
-        <v>53</v>
-      </c>
-      <c r="P21" s="12">
-        <v>13</v>
-      </c>
-      <c r="Q21" s="22">
-        <v>38</v>
-      </c>
-      <c r="R21" s="27">
-        <v>20</v>
+        <v>218</v>
+      </c>
+      <c r="O21" s="23">
+        <v>28</v>
+      </c>
+      <c r="P21" s="24">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="21">
+        <v>28</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2592,55 +2568,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L22" s="4">
-        <v>-16.3</v>
+        <v>-7.9</v>
       </c>
       <c r="M22" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O22" s="9">
-        <v>46</v>
-      </c>
-      <c r="P22" s="8">
-        <v>9</v>
-      </c>
-      <c r="Q22" s="22">
-        <v>39</v>
-      </c>
-      <c r="R22" s="12">
-        <v>14</v>
+      <c r="O22" s="6">
+        <v>59</v>
+      </c>
+      <c r="P22" s="18">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>6</v>
+      </c>
+      <c r="R22" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2648,170 +2624,114 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-15</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L23" s="4">
-        <v>-11.8</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="O23" s="6">
-        <v>48</v>
-      </c>
-      <c r="P23" s="14">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="26">
+        <v>51</v>
+      </c>
+      <c r="P23" s="20">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>3</v>
+      </c>
+      <c r="R23" s="8">
         <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="2">
-        <v>20</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="O24" s="9">
-        <v>52</v>
-      </c>
-      <c r="P24" s="23">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="26">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A24">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K24">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L24">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2830,12 +2750,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2852,22 +2772,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O24">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q24">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="206">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260629--01</t>
-  </si>
-  <si>
-    <t>20260629--02</t>
-  </si>
-  <si>
-    <t>20260629--03</t>
-  </si>
-  <si>
-    <t>20260629--04</t>
-  </si>
-  <si>
     <t>20260630--01</t>
   </si>
   <si>
@@ -136,112 +124,100 @@
     <t>20260705--02</t>
   </si>
   <si>
+    <t>20260706--01</t>
+  </si>
+  <si>
+    <t>20260706--02</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>02:03</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
     <t>06:03</t>
   </si>
   <si>
-    <t>04:29</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>02:03</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>05:11</t>
+    <t>04:37</t>
   </si>
   <si>
     <t>06:04</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>02:09</t>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>01:42</t>
+  </si>
+  <si>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>00:15</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:42</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
     <t>03:02</t>
   </si>
   <si>
-    <t>05:07</t>
-  </si>
-  <si>
     <t>01:11</t>
   </si>
   <si>
     <t>03:04</t>
   </si>
   <si>
-    <t>04:49</t>
-  </si>
-  <si>
-    <t>00:27</t>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>00:26</t>
   </si>
   <si>
     <t>02:16</t>
   </si>
   <si>
-    <t>00:03:25</t>
-  </si>
-  <si>
-    <t>01:40:42</t>
-  </si>
-  <si>
-    <t>21:40:28</t>
-  </si>
-  <si>
-    <t>23:17:16</t>
+    <t>04:01</t>
   </si>
   <si>
     <t>00:54:28</t>
@@ -259,16 +235,16 @@
     <t>20:08:24</t>
   </si>
   <si>
-    <t>21:44:50</t>
+    <t>21:44:49</t>
   </si>
   <si>
     <t>23:21:53</t>
   </si>
   <si>
-    <t>00:59:23</t>
-  </si>
-  <si>
-    <t>20:58:34</t>
+    <t>00:59:22</t>
+  </si>
+  <si>
+    <t>20:58:33</t>
   </si>
   <si>
     <t>22:35:32</t>
@@ -280,13 +256,13 @@
     <t>20:12:16</t>
   </si>
   <si>
-    <t>21:49:09</t>
+    <t>21:49:08</t>
   </si>
   <si>
     <t>23:26:24</t>
   </si>
   <si>
-    <t>21:02:43</t>
+    <t>21:02:42</t>
   </si>
   <si>
     <t>22:39:53</t>
@@ -298,16 +274,10 @@
     <t>21:53:20</t>
   </si>
   <si>
-    <t>00:05:40</t>
-  </si>
-  <si>
-    <t>01:43:20</t>
-  </si>
-  <si>
-    <t>21:42:51</t>
-  </si>
-  <si>
-    <t>23:19:30</t>
+    <t>21:06:45</t>
+  </si>
+  <si>
+    <t>22:44:11</t>
   </si>
   <si>
     <t>00:56:56</t>
@@ -346,10 +316,10 @@
     <t>20:14:36</t>
   </si>
   <si>
-    <t>21:51:24</t>
-  </si>
-  <si>
-    <t>23:29:00</t>
+    <t>21:51:23</t>
+  </si>
+  <si>
+    <t>23:28:59</t>
   </si>
   <si>
     <t>21:04:57</t>
@@ -358,22 +328,16 @@
     <t>22:42:20</t>
   </si>
   <si>
-    <t>20:18:29</t>
-  </si>
-  <si>
-    <t>21:55:42</t>
-  </si>
-  <si>
-    <t>00:08:42</t>
-  </si>
-  <si>
-    <t>01:45:35</t>
-  </si>
-  <si>
-    <t>21:45:34</t>
-  </si>
-  <si>
-    <t>23:22:33</t>
+    <t>20:18:28</t>
+  </si>
+  <si>
+    <t>21:55:41</t>
+  </si>
+  <si>
+    <t>21:09:03</t>
+  </si>
+  <si>
+    <t>22:47:24</t>
   </si>
   <si>
     <t>00:59:29</t>
@@ -394,7 +358,7 @@
     <t>21:50:05</t>
   </si>
   <si>
-    <t>23:27:05</t>
+    <t>23:27:04</t>
   </si>
   <si>
     <t>01:03:49</t>
@@ -406,16 +370,16 @@
     <t>22:40:46</t>
   </si>
   <si>
-    <t>00:17:36</t>
+    <t>00:17:35</t>
   </si>
   <si>
     <t>20:17:26</t>
   </si>
   <si>
-    <t>21:54:25</t>
-  </si>
-  <si>
-    <t>23:31:18</t>
+    <t>21:54:24</t>
+  </si>
+  <si>
+    <t>23:31:17</t>
   </si>
   <si>
     <t>21:07:59</t>
@@ -424,22 +388,16 @@
     <t>22:44:55</t>
   </si>
   <si>
-    <t>20:21:31</t>
+    <t>20:21:30</t>
   </si>
   <si>
     <t>21:58:28</t>
   </si>
   <si>
-    <t>00:11:43</t>
-  </si>
-  <si>
-    <t>01:47:49</t>
-  </si>
-  <si>
-    <t>21:48:17</t>
-  </si>
-  <si>
-    <t>23:25:35</t>
+    <t>21:11:57</t>
+  </si>
+  <si>
+    <t>22:48:41</t>
   </si>
   <si>
     <t>01:02:02</t>
@@ -457,7 +415,7 @@
     <t>20:15:23</t>
   </si>
   <si>
-    <t>21:53:06</t>
+    <t>21:53:05</t>
   </si>
   <si>
     <t>23:29:58</t>
@@ -484,28 +442,22 @@
     <t>23:33:36</t>
   </si>
   <si>
-    <t>21:11:02</t>
-  </si>
-  <si>
-    <t>22:47:31</t>
-  </si>
-  <si>
-    <t>20:24:33</t>
+    <t>21:11:01</t>
+  </si>
+  <si>
+    <t>22:47:30</t>
+  </si>
+  <si>
+    <t>20:24:32</t>
   </si>
   <si>
     <t>22:01:15</t>
   </si>
   <si>
-    <t>00:13:58</t>
-  </si>
-  <si>
-    <t>01:50:27</t>
-  </si>
-  <si>
-    <t>21:50:41</t>
-  </si>
-  <si>
-    <t>23:27:50</t>
+    <t>21:14:51</t>
+  </si>
+  <si>
+    <t>22:49:59</t>
   </si>
   <si>
     <t>01:04:30</t>
@@ -526,13 +478,13 @@
     <t>21:55:21</t>
   </si>
   <si>
-    <t>23:32:17</t>
+    <t>23:32:16</t>
   </si>
   <si>
     <t>01:08:16</t>
   </si>
   <si>
-    <t>21:09:01</t>
+    <t>21:09:00</t>
   </si>
   <si>
     <t>22:46:01</t>
@@ -562,27 +514,27 @@
     <t>22:03:36</t>
   </si>
   <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>7°</t>
+    <t>21:17:09</t>
+  </si>
+  <si>
+    <t>22:53:12</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>0°</t>
   </si>
   <si>
     <t>3°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
     <t>30°</t>
   </si>
   <si>
@@ -604,16 +556,10 @@
     <t>23°</t>
   </si>
   <si>
-    <t>00:09:34</t>
-  </si>
-  <si>
-    <t>01:42:41</t>
-  </si>
-  <si>
-    <t>21:42:11</t>
-  </si>
-  <si>
-    <t>23:27:06</t>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>6°</t>
   </si>
   <si>
     <t>01:00:20</t>
@@ -634,7 +580,7 @@
     <t>23:23:11</t>
   </si>
   <si>
-    <t>21:05:57</t>
+    <t>21:05:56</t>
   </si>
   <si>
     <t>22:38:59</t>
@@ -643,31 +589,37 @@
     <t>20:21:26</t>
   </si>
   <si>
-    <t>21:54:28</t>
+    <t>21:54:27</t>
   </si>
   <si>
     <t>23:27:29</t>
   </si>
   <si>
-    <t>21:09:46</t>
-  </si>
-  <si>
-    <t>22:42:47</t>
+    <t>21:09:45</t>
+  </si>
+  <si>
+    <t>22:42:46</t>
   </si>
   <si>
     <t>20:24:57</t>
   </si>
   <si>
-    <t>21:57:58</t>
+    <t>21:57:57</t>
+  </si>
+  <si>
+    <t>21:13:04</t>
+  </si>
+  <si>
+    <t>22:46:04</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>2</t>
@@ -713,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -734,13 +686,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,91 +794,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,7 +806,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,7 +847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -967,6 +925,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1370,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1448,55 +1409,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="L2" s="4">
-        <v>-14.9</v>
+        <v>-12.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O2" s="6">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="8">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="R2" s="9">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1504,55 +1465,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="L3" s="4">
-        <v>-8.4</v>
+        <v>-10.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6">
-        <v>79</v>
-      </c>
-      <c r="P3" s="7">
+        <v>94</v>
+      </c>
+      <c r="P3" s="10">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="11">
         <v>0</v>
       </c>
-      <c r="Q3" s="8">
-        <v>3</v>
-      </c>
-      <c r="R3" s="10">
-        <v>84</v>
+      <c r="R3" s="12">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1560,55 +1521,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="L4" s="4">
-        <v>-13.9</v>
+        <v>-15.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="11">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>66</v>
-      </c>
-      <c r="R4" s="13">
-        <v>100</v>
+        <v>84</v>
+      </c>
+      <c r="P4" s="13">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>20</v>
+      </c>
+      <c r="R4" s="15">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1616,55 +1577,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.1</v>
+        <v>-14.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="O5" s="6">
-        <v>99</v>
-      </c>
-      <c r="P5" s="10">
-        <v>85</v>
+        <v>45</v>
+      </c>
+      <c r="P5" s="16">
+        <v>45</v>
       </c>
       <c r="Q5" s="11">
-        <v>54</v>
-      </c>
-      <c r="R5" s="14">
-        <v>96</v>
+        <v>0</v>
+      </c>
+      <c r="R5" s="17">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1672,55 +1633,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="L6" s="4">
-        <v>-12.2</v>
+        <v>-6.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O6" s="6">
-        <v>96</v>
-      </c>
-      <c r="P6" s="10">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>55</v>
-      </c>
-      <c r="R6" s="15">
-        <v>58</v>
+        <v>48</v>
+      </c>
+      <c r="P6" s="7">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>22</v>
+      </c>
+      <c r="R6" s="8">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1728,55 +1689,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="L7" s="4">
-        <v>-10.9</v>
+        <v>-14.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O7" s="6">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="P7" s="16">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>59</v>
-      </c>
-      <c r="R7" s="13">
-        <v>98</v>
+        <v>47</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>11</v>
+      </c>
+      <c r="R7" s="10">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1784,55 +1745,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="L8" s="4">
-        <v>-15.9</v>
+        <v>-16.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O8" s="6">
-        <v>91</v>
-      </c>
-      <c r="P8" s="7">
+        <v>203</v>
+      </c>
+      <c r="O8" s="19">
+        <v>35</v>
+      </c>
+      <c r="P8" s="11">
         <v>0</v>
       </c>
-      <c r="Q8" s="15">
-        <v>59</v>
-      </c>
-      <c r="R8" s="17">
-        <v>74</v>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="20">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1840,55 +1801,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L9" s="4">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="O9" s="6">
-        <v>58</v>
-      </c>
-      <c r="P9" s="9">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="7">
+        <v>44</v>
+      </c>
+      <c r="P9" s="16">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="11">
         <v>0</v>
       </c>
-      <c r="R9" s="9">
-        <v>40</v>
+      <c r="R9" s="16">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1896,55 +1857,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="L10" s="4">
-        <v>-6.9</v>
+        <v>-11.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O10" s="6">
-        <v>88</v>
-      </c>
-      <c r="P10" s="15">
-        <v>58</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>27</v>
-      </c>
-      <c r="R10" s="17">
-        <v>76</v>
+        <v>100</v>
+      </c>
+      <c r="P10" s="21">
+        <v>81</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>100</v>
+      </c>
+      <c r="R10" s="18">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1952,55 +1913,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="L11" s="4">
-        <v>-14.3</v>
+        <v>-16.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="O11" s="6">
-        <v>90</v>
-      </c>
-      <c r="P11" s="12">
-        <v>65</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>46</v>
-      </c>
-      <c r="R11" s="15">
-        <v>59</v>
+        <v>91</v>
+      </c>
+      <c r="P11" s="13">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>76</v>
+      </c>
+      <c r="R11" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2008,55 +1969,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.2</v>
+        <v>-14.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="O12" s="6">
-        <v>84</v>
-      </c>
-      <c r="P12" s="11">
-        <v>54</v>
-      </c>
-      <c r="Q12" s="20">
-        <v>21</v>
+        <v>97</v>
+      </c>
+      <c r="P12" s="23">
+        <v>94</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>42</v>
       </c>
       <c r="R12" s="11">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2064,55 +2025,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="L13" s="4">
-        <v>-12.1</v>
+        <v>-7.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O13" s="6">
-        <v>55</v>
-      </c>
-      <c r="P13" s="9">
+        <v>205</v>
+      </c>
+      <c r="O13" s="19">
         <v>41</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="P13" s="20">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>18</v>
+      </c>
+      <c r="R13" s="11">
         <v>0</v>
-      </c>
-      <c r="R13" s="20">
-        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2120,55 +2081,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="L14" s="4">
-        <v>-11.4</v>
+        <v>-14.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O14" s="6">
-        <v>64</v>
-      </c>
-      <c r="P14" s="21">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="22">
-        <v>52</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O14" s="19">
+        <v>42</v>
+      </c>
+      <c r="P14" s="24">
+        <v>39</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>16</v>
+      </c>
+      <c r="R14" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2176,54 +2137,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="L15" s="4">
-        <v>-16.1</v>
+        <v>-16.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O15" s="6">
-        <v>64</v>
-      </c>
-      <c r="P15" s="20">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>53</v>
-      </c>
-      <c r="R15" s="7">
+        <v>203</v>
+      </c>
+      <c r="O15" s="19">
+        <v>38</v>
+      </c>
+      <c r="P15" s="24">
+        <v>38</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>8</v>
+      </c>
+      <c r="R15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2232,55 +2193,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="L16" s="4">
-        <v>-14.8</v>
+        <v>-11.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O16" s="6">
-        <v>44</v>
-      </c>
-      <c r="P16" s="16">
-        <v>33</v>
-      </c>
-      <c r="Q16" s="21">
-        <v>31</v>
-      </c>
-      <c r="R16" s="7">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O16" s="26">
+        <v>6</v>
+      </c>
+      <c r="P16" s="27">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>6</v>
+      </c>
+      <c r="R16" s="27">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2288,55 +2249,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="L17" s="4">
-        <v>-7.4</v>
+        <v>-16.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O17" s="23">
-        <v>11</v>
-      </c>
-      <c r="P17" s="8">
+        <v>202</v>
+      </c>
+      <c r="O17" s="26">
+        <v>8</v>
+      </c>
+      <c r="P17" s="27">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="27">
         <v>5</v>
       </c>
-      <c r="Q17" s="24">
-        <v>11</v>
-      </c>
-      <c r="R17" s="7">
-        <v>1</v>
+      <c r="R17" s="18">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2344,55 +2305,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="L18" s="4">
-        <v>-14.6</v>
+        <v>-7.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O18" s="25">
-        <v>8</v>
-      </c>
-      <c r="P18" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>8</v>
-      </c>
-      <c r="R18" s="7">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="O18" s="6">
+        <v>79</v>
+      </c>
+      <c r="P18" s="15">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>24</v>
+      </c>
+      <c r="R18" s="16">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2400,55 +2361,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="L19" s="4">
-        <v>-16.3</v>
+        <v>-15</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O19" s="23">
-        <v>19</v>
-      </c>
-      <c r="P19" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q19" s="26">
-        <v>15</v>
-      </c>
-      <c r="R19" s="8">
-        <v>3</v>
+        <v>202</v>
+      </c>
+      <c r="O19" s="6">
+        <v>67</v>
+      </c>
+      <c r="P19" s="16">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>29</v>
+      </c>
+      <c r="R19" s="16">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2456,55 +2417,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="L20" s="4">
-        <v>-11.8</v>
+        <v>-12.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O20" s="23">
-        <v>27</v>
-      </c>
-      <c r="P20" s="24">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="18">
-        <v>27</v>
+        <v>202</v>
+      </c>
+      <c r="O20" s="6">
+        <v>78</v>
+      </c>
+      <c r="P20" s="17">
+        <v>25</v>
+      </c>
+      <c r="Q20" s="24">
+        <v>41</v>
       </c>
       <c r="R20" s="8">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2512,226 +2473,114 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="L21" s="4">
-        <v>-16.4</v>
+        <v>-16.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O21" s="23">
-        <v>28</v>
-      </c>
-      <c r="P21" s="24">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>28</v>
-      </c>
-      <c r="R21" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>31</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-7.9</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O22" s="6">
-        <v>59</v>
-      </c>
-      <c r="P22" s="18">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>6</v>
-      </c>
-      <c r="R22" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O23" s="6">
-        <v>51</v>
-      </c>
-      <c r="P23" s="20">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>3</v>
-      </c>
-      <c r="R23" s="8">
-        <v>4</v>
+        <v>204</v>
+      </c>
+      <c r="O21" s="6">
+        <v>80</v>
+      </c>
+      <c r="P21" s="25">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>40</v>
+      </c>
+      <c r="R21" s="27">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2750,12 +2599,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2772,22 +2621,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="199">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260630--01</t>
-  </si>
-  <si>
-    <t>20260630--02</t>
-  </si>
-  <si>
-    <t>20260630--03</t>
-  </si>
-  <si>
     <t>20260701--01</t>
   </si>
   <si>
@@ -130,163 +121,154 @@
     <t>20260706--02</t>
   </si>
   <si>
+    <t>20260707--01</t>
+  </si>
+  <si>
+    <t>20260707--02</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>04:18</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>02:02</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>02:37</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:01</t>
+  </si>
+  <si>
     <t>05:06</t>
   </si>
   <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>02:03</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>01:42</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>03:02</t>
-  </si>
-  <si>
-    <t>01:11</t>
-  </si>
-  <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>00:26</t>
-  </si>
-  <si>
-    <t>02:16</t>
-  </si>
-  <si>
-    <t>04:01</t>
-  </si>
-  <si>
-    <t>00:54:28</t>
-  </si>
-  <si>
-    <t>20:54:26</t>
-  </si>
-  <si>
-    <t>22:31:04</t>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>00:27</t>
+  </si>
+  <si>
+    <t>02:17</t>
+  </si>
+  <si>
+    <t>04:02</t>
+  </si>
+  <si>
+    <t>00:56</t>
   </si>
   <si>
     <t>00:08:12</t>
   </si>
   <si>
-    <t>20:08:24</t>
-  </si>
-  <si>
-    <t>21:44:49</t>
-  </si>
-  <si>
-    <t>23:21:53</t>
-  </si>
-  <si>
-    <t>00:59:22</t>
-  </si>
-  <si>
-    <t>20:58:33</t>
-  </si>
-  <si>
-    <t>22:35:32</t>
-  </si>
-  <si>
-    <t>00:12:53</t>
-  </si>
-  <si>
-    <t>20:12:16</t>
-  </si>
-  <si>
-    <t>21:49:08</t>
-  </si>
-  <si>
-    <t>23:26:24</t>
-  </si>
-  <si>
-    <t>21:02:42</t>
-  </si>
-  <si>
-    <t>22:39:53</t>
-  </si>
-  <si>
-    <t>20:16:14</t>
-  </si>
-  <si>
-    <t>21:53:20</t>
-  </si>
-  <si>
-    <t>21:06:45</t>
-  </si>
-  <si>
-    <t>22:44:11</t>
-  </si>
-  <si>
-    <t>00:56:56</t>
-  </si>
-  <si>
-    <t>20:56:55</t>
-  </si>
-  <si>
-    <t>22:33:18</t>
+    <t>20:08:23</t>
+  </si>
+  <si>
+    <t>21:44:48</t>
+  </si>
+  <si>
+    <t>23:21:52</t>
+  </si>
+  <si>
+    <t>00:59:21</t>
+  </si>
+  <si>
+    <t>20:58:30</t>
+  </si>
+  <si>
+    <t>22:35:29</t>
+  </si>
+  <si>
+    <t>00:12:50</t>
+  </si>
+  <si>
+    <t>20:12:09</t>
+  </si>
+  <si>
+    <t>21:49:01</t>
+  </si>
+  <si>
+    <t>23:26:17</t>
+  </si>
+  <si>
+    <t>21:02:31</t>
+  </si>
+  <si>
+    <t>22:39:41</t>
+  </si>
+  <si>
+    <t>20:15:56</t>
+  </si>
+  <si>
+    <t>21:53:02</t>
+  </si>
+  <si>
+    <t>21:06:20</t>
+  </si>
+  <si>
+    <t>22:43:45</t>
+  </si>
+  <si>
+    <t>20:19:34</t>
+  </si>
+  <si>
+    <t>21:56:52</t>
   </si>
   <si>
     <t>00:10:34</t>
@@ -295,337 +277,334 @@
     <t>20:11:03</t>
   </si>
   <si>
-    <t>21:47:05</t>
-  </si>
-  <si>
-    <t>23:24:12</t>
-  </si>
-  <si>
-    <t>01:02:48</t>
-  </si>
-  <si>
-    <t>21:00:50</t>
-  </si>
-  <si>
-    <t>22:37:48</t>
-  </si>
-  <si>
-    <t>00:15:44</t>
-  </si>
-  <si>
-    <t>20:14:36</t>
-  </si>
-  <si>
-    <t>21:51:23</t>
-  </si>
-  <si>
-    <t>23:28:59</t>
-  </si>
-  <si>
-    <t>21:04:57</t>
-  </si>
-  <si>
-    <t>22:42:20</t>
-  </si>
-  <si>
-    <t>20:18:28</t>
-  </si>
-  <si>
-    <t>21:55:41</t>
-  </si>
-  <si>
-    <t>21:09:03</t>
-  </si>
-  <si>
-    <t>22:47:24</t>
-  </si>
-  <si>
-    <t>00:59:29</t>
-  </si>
-  <si>
-    <t>20:59:24</t>
-  </si>
-  <si>
-    <t>22:36:20</t>
+    <t>21:47:04</t>
+  </si>
+  <si>
+    <t>23:24:11</t>
+  </si>
+  <si>
+    <t>01:02:47</t>
+  </si>
+  <si>
+    <t>21:00:47</t>
+  </si>
+  <si>
+    <t>22:37:45</t>
+  </si>
+  <si>
+    <t>00:15:41</t>
+  </si>
+  <si>
+    <t>20:14:29</t>
+  </si>
+  <si>
+    <t>21:51:16</t>
+  </si>
+  <si>
+    <t>23:28:52</t>
+  </si>
+  <si>
+    <t>21:04:45</t>
+  </si>
+  <si>
+    <t>22:42:08</t>
+  </si>
+  <si>
+    <t>20:18:11</t>
+  </si>
+  <si>
+    <t>21:55:23</t>
+  </si>
+  <si>
+    <t>21:08:38</t>
+  </si>
+  <si>
+    <t>22:46:58</t>
+  </si>
+  <si>
+    <t>20:21:50</t>
+  </si>
+  <si>
+    <t>21:59:38</t>
   </si>
   <si>
     <t>00:13:19</t>
   </si>
   <si>
-    <t>20:13:13</t>
+    <t>20:13:12</t>
+  </si>
+  <si>
+    <t>21:50:04</t>
+  </si>
+  <si>
+    <t>23:27:04</t>
+  </si>
+  <si>
+    <t>01:03:48</t>
+  </si>
+  <si>
+    <t>21:03:43</t>
+  </si>
+  <si>
+    <t>22:40:43</t>
+  </si>
+  <si>
+    <t>00:17:32</t>
+  </si>
+  <si>
+    <t>20:17:19</t>
+  </si>
+  <si>
+    <t>21:54:17</t>
+  </si>
+  <si>
+    <t>23:31:10</t>
+  </si>
+  <si>
+    <t>21:07:47</t>
+  </si>
+  <si>
+    <t>22:44:43</t>
+  </si>
+  <si>
+    <t>20:21:13</t>
+  </si>
+  <si>
+    <t>21:58:10</t>
+  </si>
+  <si>
+    <t>21:11:32</t>
+  </si>
+  <si>
+    <t>22:48:17</t>
+  </si>
+  <si>
+    <t>20:24:49</t>
+  </si>
+  <si>
+    <t>22:01:38</t>
+  </si>
+  <si>
+    <t>00:16:04</t>
+  </si>
+  <si>
+    <t>20:15:21</t>
+  </si>
+  <si>
+    <t>21:53:04</t>
+  </si>
+  <si>
+    <t>23:29:56</t>
+  </si>
+  <si>
+    <t>01:04:49</t>
+  </si>
+  <si>
+    <t>21:06:40</t>
+  </si>
+  <si>
+    <t>22:43:41</t>
+  </si>
+  <si>
+    <t>00:19:23</t>
+  </si>
+  <si>
+    <t>20:20:09</t>
+  </si>
+  <si>
+    <t>21:57:19</t>
+  </si>
+  <si>
+    <t>23:33:28</t>
+  </si>
+  <si>
+    <t>21:10:50</t>
+  </si>
+  <si>
+    <t>22:47:18</t>
+  </si>
+  <si>
+    <t>20:24:15</t>
+  </si>
+  <si>
+    <t>22:00:57</t>
+  </si>
+  <si>
+    <t>21:14:27</t>
+  </si>
+  <si>
+    <t>22:49:35</t>
+  </si>
+  <si>
+    <t>20:27:48</t>
+  </si>
+  <si>
+    <t>22:03:38</t>
+  </si>
+  <si>
+    <t>00:18:26</t>
+  </si>
+  <si>
+    <t>20:18:02</t>
+  </si>
+  <si>
+    <t>21:55:20</t>
+  </si>
+  <si>
+    <t>23:32:15</t>
+  </si>
+  <si>
+    <t>01:08:14</t>
+  </si>
+  <si>
+    <t>21:08:57</t>
+  </si>
+  <si>
+    <t>22:45:57</t>
+  </si>
+  <si>
+    <t>00:22:14</t>
+  </si>
+  <si>
+    <t>20:22:29</t>
+  </si>
+  <si>
+    <t>21:59:34</t>
+  </si>
+  <si>
+    <t>23:36:04</t>
+  </si>
+  <si>
+    <t>21:13:04</t>
+  </si>
+  <si>
+    <t>22:49:45</t>
+  </si>
+  <si>
+    <t>20:26:29</t>
+  </si>
+  <si>
+    <t>22:03:18</t>
+  </si>
+  <si>
+    <t>21:16:44</t>
+  </si>
+  <si>
+    <t>22:52:47</t>
+  </si>
+  <si>
+    <t>20:30:04</t>
+  </si>
+  <si>
+    <t>22:06:23</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>20:17:01</t>
   </si>
   <si>
     <t>21:50:05</t>
   </si>
   <si>
-    <t>23:27:04</t>
-  </si>
-  <si>
-    <t>01:03:49</t>
-  </si>
-  <si>
-    <t>21:03:47</t>
-  </si>
-  <si>
-    <t>22:40:46</t>
-  </si>
-  <si>
-    <t>00:17:35</t>
-  </si>
-  <si>
-    <t>20:17:26</t>
-  </si>
-  <si>
-    <t>21:54:24</t>
-  </si>
-  <si>
-    <t>23:31:17</t>
-  </si>
-  <si>
-    <t>21:07:59</t>
-  </si>
-  <si>
-    <t>22:44:55</t>
-  </si>
-  <si>
-    <t>20:21:30</t>
-  </si>
-  <si>
-    <t>21:58:28</t>
-  </si>
-  <si>
-    <t>21:11:57</t>
-  </si>
-  <si>
-    <t>22:48:41</t>
-  </si>
-  <si>
-    <t>01:02:02</t>
-  </si>
-  <si>
-    <t>21:01:54</t>
-  </si>
-  <si>
-    <t>22:39:23</t>
-  </si>
-  <si>
-    <t>00:16:04</t>
-  </si>
-  <si>
-    <t>20:15:23</t>
-  </si>
-  <si>
-    <t>21:53:05</t>
-  </si>
-  <si>
-    <t>23:29:58</t>
-  </si>
-  <si>
-    <t>01:04:51</t>
-  </si>
-  <si>
-    <t>21:06:43</t>
-  </si>
-  <si>
-    <t>22:43:45</t>
-  </si>
-  <si>
-    <t>00:19:27</t>
-  </si>
-  <si>
-    <t>20:20:16</t>
-  </si>
-  <si>
-    <t>21:57:26</t>
-  </si>
-  <si>
-    <t>23:33:36</t>
-  </si>
-  <si>
-    <t>21:11:01</t>
-  </si>
-  <si>
-    <t>22:47:30</t>
-  </si>
-  <si>
-    <t>20:24:32</t>
-  </si>
-  <si>
-    <t>22:01:15</t>
-  </si>
-  <si>
-    <t>21:14:51</t>
-  </si>
-  <si>
-    <t>22:49:59</t>
-  </si>
-  <si>
-    <t>01:04:30</t>
-  </si>
-  <si>
-    <t>21:04:24</t>
-  </si>
-  <si>
-    <t>22:41:38</t>
-  </si>
-  <si>
-    <t>00:18:26</t>
-  </si>
-  <si>
-    <t>20:18:03</t>
-  </si>
-  <si>
-    <t>21:55:21</t>
-  </si>
-  <si>
-    <t>23:32:16</t>
-  </si>
-  <si>
-    <t>01:08:16</t>
-  </si>
-  <si>
-    <t>21:09:00</t>
-  </si>
-  <si>
-    <t>22:46:01</t>
-  </si>
-  <si>
-    <t>00:22:18</t>
-  </si>
-  <si>
-    <t>20:22:36</t>
-  </si>
-  <si>
-    <t>21:59:41</t>
-  </si>
-  <si>
-    <t>23:36:11</t>
-  </si>
-  <si>
-    <t>21:13:16</t>
-  </si>
-  <si>
-    <t>22:49:57</t>
-  </si>
-  <si>
-    <t>20:26:47</t>
-  </si>
-  <si>
-    <t>22:03:36</t>
-  </si>
-  <si>
-    <t>21:17:09</t>
-  </si>
-  <si>
-    <t>22:53:12</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>01:00:20</t>
-  </si>
-  <si>
-    <t>21:00:24</t>
-  </si>
-  <si>
-    <t>22:33:33</t>
-  </si>
-  <si>
-    <t>20:17:02</t>
-  </si>
-  <si>
-    <t>21:50:07</t>
-  </si>
-  <si>
-    <t>23:23:11</t>
-  </si>
-  <si>
-    <t>21:05:56</t>
-  </si>
-  <si>
-    <t>22:38:59</t>
-  </si>
-  <si>
-    <t>20:21:26</t>
-  </si>
-  <si>
-    <t>21:54:27</t>
-  </si>
-  <si>
-    <t>23:27:29</t>
-  </si>
-  <si>
-    <t>21:09:45</t>
-  </si>
-  <si>
-    <t>22:42:46</t>
-  </si>
-  <si>
-    <t>20:24:57</t>
-  </si>
-  <si>
-    <t>21:57:57</t>
-  </si>
-  <si>
-    <t>21:13:04</t>
-  </si>
-  <si>
-    <t>22:46:04</t>
+    <t>23:23:10</t>
+  </si>
+  <si>
+    <t>21:05:53</t>
+  </si>
+  <si>
+    <t>22:38:55</t>
+  </si>
+  <si>
+    <t>20:21:19</t>
+  </si>
+  <si>
+    <t>21:54:21</t>
+  </si>
+  <si>
+    <t>23:27:22</t>
+  </si>
+  <si>
+    <t>21:09:34</t>
+  </si>
+  <si>
+    <t>22:42:35</t>
+  </si>
+  <si>
+    <t>20:24:40</t>
+  </si>
+  <si>
+    <t>21:57:40</t>
+  </si>
+  <si>
+    <t>21:12:40</t>
+  </si>
+  <si>
+    <t>22:45:40</t>
+  </si>
+  <si>
+    <t>20:27:35</t>
+  </si>
+  <si>
+    <t>22:00:34</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -665,7 +644,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,7 +665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +683,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,103 +773,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -922,12 +889,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1331,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1409,55 +1370,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.2</v>
+        <v>-14.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="P2" s="7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="8">
-        <v>37</v>
-      </c>
-      <c r="R2" s="9">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="R2" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1465,55 +1426,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L3" s="4">
-        <v>-10.9</v>
+        <v>-6.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="O3" s="6">
-        <v>94</v>
-      </c>
-      <c r="P3" s="10">
-        <v>63</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>0</v>
-      </c>
-      <c r="R3" s="12">
-        <v>88</v>
+        <v>60</v>
+      </c>
+      <c r="P3" s="9">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>60</v>
+      </c>
+      <c r="R3" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1521,55 +1482,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-14.3</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O4" s="6">
+        <v>99</v>
+      </c>
+      <c r="P4" s="9">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="12">
         <v>90</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-15.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O4" s="6">
-        <v>84</v>
-      </c>
-      <c r="P4" s="13">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>20</v>
-      </c>
-      <c r="R4" s="15">
-        <v>60</v>
+      <c r="R4" s="10">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1577,55 +1538,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O5" s="6">
+        <v>100</v>
+      </c>
+      <c r="P5" s="13">
         <v>41</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-14.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45</v>
-      </c>
-      <c r="P5" s="16">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>0</v>
-      </c>
-      <c r="R5" s="17">
-        <v>27</v>
+      <c r="Q5" s="8">
+        <v>56</v>
+      </c>
+      <c r="R5" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1633,55 +1594,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-6.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="O6" s="6">
-        <v>48</v>
-      </c>
-      <c r="P6" s="7">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>22</v>
-      </c>
-      <c r="R6" s="8">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="P6" s="15">
+        <v>74</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>21</v>
+      </c>
+      <c r="R6" s="17">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1689,55 +1650,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L7" s="4">
-        <v>-14.3</v>
+        <v>-11.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="O7" s="6">
-        <v>75</v>
-      </c>
-      <c r="P7" s="16">
-        <v>47</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>11</v>
-      </c>
-      <c r="R7" s="10">
-        <v>65</v>
+        <v>100</v>
+      </c>
+      <c r="P7" s="15">
+        <v>74</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>100</v>
+      </c>
+      <c r="R7" s="18">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1745,55 +1706,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.2</v>
+        <v>-16.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O8" s="19">
-        <v>35</v>
-      </c>
-      <c r="P8" s="11">
+        <v>196</v>
+      </c>
+      <c r="O8" s="6">
+        <v>78</v>
+      </c>
+      <c r="P8" s="19">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>70</v>
+      </c>
+      <c r="R8" s="18">
         <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="20">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1801,55 +1762,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4">
-        <v>-12.1</v>
+        <v>-14.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="O9" s="6">
-        <v>44</v>
-      </c>
-      <c r="P9" s="16">
-        <v>44</v>
-      </c>
-      <c r="Q9" s="11">
+        <v>79</v>
+      </c>
+      <c r="P9" s="19">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>8</v>
+      </c>
+      <c r="R9" s="18">
         <v>0</v>
-      </c>
-      <c r="R9" s="16">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1857,55 +1818,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-7.4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O10" s="6">
+        <v>49</v>
+      </c>
+      <c r="P10" s="13">
         <v>38</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-11.4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="21">
-        <v>81</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>100</v>
+      <c r="Q10" s="21">
+        <v>12</v>
       </c>
       <c r="R10" s="18">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1913,55 +1874,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L11" s="4">
-        <v>-16.1</v>
+        <v>-14.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="O11" s="6">
-        <v>91</v>
-      </c>
-      <c r="P11" s="13">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>76</v>
-      </c>
-      <c r="R11" s="17">
-        <v>23</v>
+        <v>60</v>
+      </c>
+      <c r="P11" s="8">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>6</v>
+      </c>
+      <c r="R11" s="18">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1969,55 +1930,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="L12" s="4">
-        <v>-14.8</v>
+        <v>-16.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O12" s="6">
-        <v>97</v>
-      </c>
-      <c r="P12" s="23">
         <v>94</v>
       </c>
-      <c r="Q12" s="24">
-        <v>42</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
+      <c r="P12" s="11">
+        <v>51</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>4</v>
+      </c>
+      <c r="R12" s="10">
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2025,54 +1986,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-11.8</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O13" s="6">
+        <v>57</v>
+      </c>
+      <c r="P13" s="11">
         <v>49</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-7.4</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="19">
-        <v>41</v>
-      </c>
-      <c r="P13" s="20">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>18</v>
-      </c>
-      <c r="R13" s="11">
+      <c r="Q13" s="22">
+        <v>43</v>
+      </c>
+      <c r="R13" s="18">
         <v>0</v>
       </c>
     </row>
@@ -2081,54 +2042,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="L14" s="4">
-        <v>-14.6</v>
+        <v>-16.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O14" s="19">
-        <v>42</v>
-      </c>
-      <c r="P14" s="24">
-        <v>39</v>
-      </c>
-      <c r="Q14" s="25">
-        <v>16</v>
-      </c>
-      <c r="R14" s="11">
+        <v>196</v>
+      </c>
+      <c r="O14" s="6">
+        <v>99</v>
+      </c>
+      <c r="P14" s="20">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>55</v>
+      </c>
+      <c r="R14" s="18">
         <v>1</v>
       </c>
     </row>
@@ -2137,55 +2098,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L15" s="4">
-        <v>-16.3</v>
+        <v>-7.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O15" s="19">
-        <v>38</v>
-      </c>
-      <c r="P15" s="24">
-        <v>38</v>
-      </c>
-      <c r="Q15" s="18">
-        <v>8</v>
-      </c>
-      <c r="R15" s="11">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O15" s="6">
+        <v>100</v>
+      </c>
+      <c r="P15" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>97</v>
+      </c>
+      <c r="R15" s="10">
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2193,55 +2154,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L16" s="4">
-        <v>-11.8</v>
+        <v>-15</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O16" s="26">
-        <v>6</v>
-      </c>
-      <c r="P16" s="27">
-        <v>6</v>
-      </c>
-      <c r="Q16" s="27">
-        <v>6</v>
-      </c>
-      <c r="R16" s="27">
-        <v>6</v>
+        <v>196</v>
+      </c>
+      <c r="O16" s="6">
+        <v>100</v>
+      </c>
+      <c r="P16" s="21">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>98</v>
+      </c>
+      <c r="R16" s="8">
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2249,55 +2210,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L17" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="N17" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O17" s="26">
-        <v>8</v>
-      </c>
-      <c r="P17" s="27">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="27">
-        <v>5</v>
-      </c>
-      <c r="R17" s="18">
-        <v>8</v>
+        <v>196</v>
+      </c>
+      <c r="O17" s="6">
+        <v>81</v>
+      </c>
+      <c r="P17" s="21">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>51</v>
+      </c>
+      <c r="R17" s="10">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2305,55 +2266,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="L18" s="4">
-        <v>-7.9</v>
+        <v>-16.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="O18" s="6">
-        <v>79</v>
-      </c>
-      <c r="P18" s="15">
-        <v>58</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>24</v>
-      </c>
-      <c r="R18" s="16">
-        <v>47</v>
+        <v>81</v>
+      </c>
+      <c r="P18" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>61</v>
+      </c>
+      <c r="R18" s="24">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2361,55 +2322,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="L19" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="O19" s="6">
-        <v>67</v>
-      </c>
-      <c r="P19" s="16">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>29</v>
-      </c>
-      <c r="R19" s="16">
-        <v>43</v>
+        <v>86</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>25</v>
+      </c>
+      <c r="R19" s="20">
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2417,170 +2378,114 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L20" s="4">
-        <v>-12.3</v>
+        <v>-15.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="O20" s="6">
-        <v>78</v>
-      </c>
-      <c r="P20" s="17">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="24">
-        <v>41</v>
-      </c>
-      <c r="R20" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-16.6</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O21" s="6">
-        <v>80</v>
-      </c>
-      <c r="P21" s="25">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="24">
-        <v>40</v>
-      </c>
-      <c r="R21" s="27">
-        <v>7</v>
+        <v>64</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="18">
+        <v>0</v>
+      </c>
+      <c r="R20" s="24">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2599,12 +2504,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2621,22 +2526,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="174">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260701--01</t>
-  </si>
-  <si>
-    <t>20260701--02</t>
-  </si>
-  <si>
-    <t>20260701--03</t>
-  </si>
-  <si>
-    <t>20260701--04</t>
-  </si>
-  <si>
     <t>20260702--01</t>
   </si>
   <si>
@@ -127,48 +115,39 @@
     <t>20260707--02</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>04:18</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>05:45</t>
+    <t>20260708--01</t>
   </si>
   <si>
     <t>02:02</t>
   </si>
   <si>
-    <t>05:53</t>
+    <t>05:52</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>03:42</t>
-  </si>
-  <si>
-    <t>05:40</t>
+    <t>03:43</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:11</t>
   </si>
   <si>
     <t>06:03</t>
   </si>
   <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
     <t>05:34</t>
   </si>
   <si>
@@ -184,22 +163,19 @@
     <t>04:00</t>
   </si>
   <si>
+    <t>04:48</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:01</t>
-  </si>
-  <si>
     <t>05:06</t>
   </si>
   <si>
     <t>01:10</t>
   </si>
   <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>04:49</t>
+    <t>03:04</t>
   </si>
   <si>
     <t>00:27</t>
@@ -211,25 +187,19 @@
     <t>04:02</t>
   </si>
   <si>
+    <t>05:44</t>
+  </si>
+  <si>
     <t>00:56</t>
   </si>
   <si>
-    <t>00:08:12</t>
-  </si>
-  <si>
-    <t>20:08:23</t>
-  </si>
-  <si>
-    <t>21:44:48</t>
-  </si>
-  <si>
-    <t>23:21:52</t>
+    <t>02:55</t>
   </si>
   <si>
     <t>00:59:21</t>
   </si>
   <si>
-    <t>20:58:30</t>
+    <t>20:58:31</t>
   </si>
   <si>
     <t>22:35:29</t>
@@ -238,163 +208,136 @@
     <t>00:12:50</t>
   </si>
   <si>
-    <t>20:12:09</t>
-  </si>
-  <si>
-    <t>21:49:01</t>
-  </si>
-  <si>
-    <t>23:26:17</t>
-  </si>
-  <si>
-    <t>21:02:31</t>
-  </si>
-  <si>
-    <t>22:39:41</t>
-  </si>
-  <si>
-    <t>20:15:56</t>
-  </si>
-  <si>
-    <t>21:53:02</t>
-  </si>
-  <si>
-    <t>21:06:20</t>
-  </si>
-  <si>
-    <t>22:43:45</t>
-  </si>
-  <si>
-    <t>20:19:34</t>
-  </si>
-  <si>
-    <t>21:56:52</t>
-  </si>
-  <si>
-    <t>00:10:34</t>
-  </si>
-  <si>
-    <t>20:11:03</t>
-  </si>
-  <si>
-    <t>21:47:04</t>
-  </si>
-  <si>
-    <t>23:24:11</t>
+    <t>20:12:11</t>
+  </si>
+  <si>
+    <t>21:49:03</t>
+  </si>
+  <si>
+    <t>23:26:18</t>
+  </si>
+  <si>
+    <t>21:02:33</t>
+  </si>
+  <si>
+    <t>22:39:43</t>
+  </si>
+  <si>
+    <t>20:16:00</t>
+  </si>
+  <si>
+    <t>21:53:06</t>
+  </si>
+  <si>
+    <t>21:06:25</t>
+  </si>
+  <si>
+    <t>22:43:51</t>
+  </si>
+  <si>
+    <t>20:19:41</t>
+  </si>
+  <si>
+    <t>21:56:59</t>
+  </si>
+  <si>
+    <t>21:10:06</t>
   </si>
   <si>
     <t>01:02:47</t>
   </si>
   <si>
-    <t>21:00:47</t>
-  </si>
-  <si>
-    <t>22:37:45</t>
+    <t>21:00:48</t>
+  </si>
+  <si>
+    <t>22:37:46</t>
   </si>
   <si>
     <t>00:15:41</t>
   </si>
   <si>
-    <t>20:14:29</t>
-  </si>
-  <si>
-    <t>21:51:16</t>
-  </si>
-  <si>
-    <t>23:28:52</t>
-  </si>
-  <si>
-    <t>21:04:45</t>
-  </si>
-  <si>
-    <t>22:42:08</t>
-  </si>
-  <si>
-    <t>20:18:11</t>
-  </si>
-  <si>
-    <t>21:55:23</t>
-  </si>
-  <si>
-    <t>21:08:38</t>
-  </si>
-  <si>
-    <t>22:46:58</t>
-  </si>
-  <si>
-    <t>20:21:50</t>
-  </si>
-  <si>
-    <t>21:59:38</t>
-  </si>
-  <si>
-    <t>00:13:19</t>
-  </si>
-  <si>
-    <t>20:13:12</t>
-  </si>
-  <si>
-    <t>21:50:04</t>
-  </si>
-  <si>
-    <t>23:27:04</t>
+    <t>20:14:31</t>
+  </si>
+  <si>
+    <t>21:51:18</t>
+  </si>
+  <si>
+    <t>23:28:54</t>
+  </si>
+  <si>
+    <t>21:04:48</t>
+  </si>
+  <si>
+    <t>22:42:10</t>
+  </si>
+  <si>
+    <t>20:18:15</t>
+  </si>
+  <si>
+    <t>21:55:27</t>
+  </si>
+  <si>
+    <t>21:08:43</t>
+  </si>
+  <si>
+    <t>22:47:03</t>
+  </si>
+  <si>
+    <t>20:21:57</t>
+  </si>
+  <si>
+    <t>21:59:45</t>
+  </si>
+  <si>
+    <t>21:12:38</t>
   </si>
   <si>
     <t>01:03:48</t>
   </si>
   <si>
-    <t>21:03:43</t>
+    <t>21:03:44</t>
   </si>
   <si>
     <t>22:40:43</t>
   </si>
   <si>
-    <t>00:17:32</t>
-  </si>
-  <si>
-    <t>20:17:19</t>
-  </si>
-  <si>
-    <t>21:54:17</t>
-  </si>
-  <si>
-    <t>23:31:10</t>
-  </si>
-  <si>
-    <t>21:07:47</t>
-  </si>
-  <si>
-    <t>22:44:43</t>
-  </si>
-  <si>
-    <t>20:21:13</t>
-  </si>
-  <si>
-    <t>21:58:10</t>
-  </si>
-  <si>
-    <t>21:11:32</t>
-  </si>
-  <si>
-    <t>22:48:17</t>
-  </si>
-  <si>
-    <t>20:24:49</t>
-  </si>
-  <si>
-    <t>22:01:38</t>
-  </si>
-  <si>
-    <t>00:16:04</t>
-  </si>
-  <si>
-    <t>20:15:21</t>
-  </si>
-  <si>
-    <t>21:53:04</t>
-  </si>
-  <si>
-    <t>23:29:56</t>
+    <t>00:17:33</t>
+  </si>
+  <si>
+    <t>20:17:20</t>
+  </si>
+  <si>
+    <t>21:54:19</t>
+  </si>
+  <si>
+    <t>23:31:12</t>
+  </si>
+  <si>
+    <t>21:07:50</t>
+  </si>
+  <si>
+    <t>22:44:45</t>
+  </si>
+  <si>
+    <t>20:21:16</t>
+  </si>
+  <si>
+    <t>21:58:14</t>
+  </si>
+  <si>
+    <t>21:11:37</t>
+  </si>
+  <si>
+    <t>22:48:22</t>
+  </si>
+  <si>
+    <t>20:24:56</t>
+  </si>
+  <si>
+    <t>22:01:45</t>
+  </si>
+  <si>
+    <t>21:15:02</t>
   </si>
   <si>
     <t>01:04:49</t>
@@ -403,123 +346,111 @@
     <t>21:06:40</t>
   </si>
   <si>
-    <t>22:43:41</t>
-  </si>
-  <si>
-    <t>00:19:23</t>
-  </si>
-  <si>
-    <t>20:20:09</t>
-  </si>
-  <si>
-    <t>21:57:19</t>
-  </si>
-  <si>
-    <t>23:33:28</t>
-  </si>
-  <si>
-    <t>21:10:50</t>
-  </si>
-  <si>
-    <t>22:47:18</t>
-  </si>
-  <si>
-    <t>20:24:15</t>
-  </si>
-  <si>
-    <t>22:00:57</t>
-  </si>
-  <si>
-    <t>21:14:27</t>
-  </si>
-  <si>
-    <t>22:49:35</t>
-  </si>
-  <si>
-    <t>20:27:48</t>
-  </si>
-  <si>
-    <t>22:03:38</t>
-  </si>
-  <si>
-    <t>00:18:26</t>
-  </si>
-  <si>
-    <t>20:18:02</t>
-  </si>
-  <si>
-    <t>21:55:20</t>
-  </si>
-  <si>
-    <t>23:32:15</t>
-  </si>
-  <si>
-    <t>01:08:14</t>
-  </si>
-  <si>
-    <t>21:08:57</t>
-  </si>
-  <si>
-    <t>22:45:57</t>
-  </si>
-  <si>
-    <t>00:22:14</t>
-  </si>
-  <si>
-    <t>20:22:29</t>
-  </si>
-  <si>
-    <t>21:59:34</t>
-  </si>
-  <si>
-    <t>23:36:04</t>
-  </si>
-  <si>
-    <t>21:13:04</t>
-  </si>
-  <si>
-    <t>22:49:45</t>
-  </si>
-  <si>
-    <t>20:26:29</t>
-  </si>
-  <si>
-    <t>22:03:18</t>
-  </si>
-  <si>
-    <t>21:16:44</t>
-  </si>
-  <si>
-    <t>22:52:47</t>
-  </si>
-  <si>
-    <t>20:30:04</t>
-  </si>
-  <si>
-    <t>22:06:23</t>
+    <t>22:43:42</t>
+  </si>
+  <si>
+    <t>00:19:24</t>
+  </si>
+  <si>
+    <t>20:20:10</t>
+  </si>
+  <si>
+    <t>21:57:20</t>
+  </si>
+  <si>
+    <t>23:33:30</t>
+  </si>
+  <si>
+    <t>21:10:52</t>
+  </si>
+  <si>
+    <t>22:47:21</t>
+  </si>
+  <si>
+    <t>20:24:18</t>
+  </si>
+  <si>
+    <t>22:01:01</t>
+  </si>
+  <si>
+    <t>21:14:32</t>
+  </si>
+  <si>
+    <t>22:49:40</t>
+  </si>
+  <si>
+    <t>20:27:55</t>
+  </si>
+  <si>
+    <t>22:03:45</t>
+  </si>
+  <si>
+    <t>21:17:26</t>
+  </si>
+  <si>
+    <t>01:08:15</t>
+  </si>
+  <si>
+    <t>21:08:58</t>
+  </si>
+  <si>
+    <t>22:45:58</t>
+  </si>
+  <si>
+    <t>00:22:15</t>
+  </si>
+  <si>
+    <t>20:22:30</t>
+  </si>
+  <si>
+    <t>21:59:35</t>
+  </si>
+  <si>
+    <t>23:36:05</t>
+  </si>
+  <si>
+    <t>21:13:07</t>
+  </si>
+  <si>
+    <t>22:49:47</t>
+  </si>
+  <si>
+    <t>20:26:33</t>
+  </si>
+  <si>
+    <t>22:03:22</t>
+  </si>
+  <si>
+    <t>21:16:49</t>
+  </si>
+  <si>
+    <t>22:52:52</t>
+  </si>
+  <si>
+    <t>20:30:11</t>
+  </si>
+  <si>
+    <t>22:06:30</t>
+  </si>
+  <si>
+    <t>21:19:58</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>3°</t>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>4°</t>
   </si>
   <si>
     <t>30°</t>
   </si>
   <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
     <t>19°</t>
   </si>
   <si>
@@ -544,73 +475,67 @@
     <t>13°</t>
   </si>
   <si>
-    <t>20:17:01</t>
-  </si>
-  <si>
-    <t>21:50:05</t>
-  </si>
-  <si>
-    <t>23:23:10</t>
-  </si>
-  <si>
-    <t>21:05:53</t>
-  </si>
-  <si>
-    <t>22:38:55</t>
-  </si>
-  <si>
-    <t>20:21:19</t>
-  </si>
-  <si>
-    <t>21:54:21</t>
-  </si>
-  <si>
-    <t>23:27:22</t>
-  </si>
-  <si>
-    <t>21:09:34</t>
-  </si>
-  <si>
-    <t>22:42:35</t>
-  </si>
-  <si>
-    <t>20:24:40</t>
-  </si>
-  <si>
-    <t>21:57:40</t>
-  </si>
-  <si>
-    <t>21:12:40</t>
-  </si>
-  <si>
-    <t>22:45:40</t>
-  </si>
-  <si>
-    <t>20:27:35</t>
-  </si>
-  <si>
-    <t>22:00:34</t>
+    <t>21:05:54</t>
+  </si>
+  <si>
+    <t>22:38:56</t>
+  </si>
+  <si>
+    <t>20:21:21</t>
+  </si>
+  <si>
+    <t>21:54:22</t>
+  </si>
+  <si>
+    <t>23:27:23</t>
+  </si>
+  <si>
+    <t>21:09:36</t>
+  </si>
+  <si>
+    <t>22:42:37</t>
+  </si>
+  <si>
+    <t>20:24:43</t>
+  </si>
+  <si>
+    <t>21:57:44</t>
+  </si>
+  <si>
+    <t>21:12:45</t>
+  </si>
+  <si>
+    <t>22:45:44</t>
+  </si>
+  <si>
+    <t>20:27:41</t>
+  </si>
+  <si>
+    <t>22:00:41</t>
+  </si>
+  <si>
+    <t>21:15:33</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -644,7 +569,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -665,19 +590,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,7 +626,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,13 +638,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,61 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,6 +820,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1292,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1370,55 +1304,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="O2" s="6">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="8">
-        <v>54</v>
-      </c>
-      <c r="R2" s="7">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1426,55 +1360,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="L3" s="4">
-        <v>-6.9</v>
+        <v>-11.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="O3" s="6">
         <v>60</v>
       </c>
-      <c r="P3" s="9">
-        <v>37</v>
+      <c r="P3" s="7">
+        <v>18</v>
       </c>
       <c r="Q3" s="10">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="R3" s="11">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1482,55 +1416,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="L4" s="4">
-        <v>-14.3</v>
+        <v>-16.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="O4" s="6">
-        <v>99</v>
-      </c>
-      <c r="P4" s="9">
-        <v>36</v>
+        <v>97</v>
+      </c>
+      <c r="P4" s="12">
+        <v>59</v>
       </c>
       <c r="Q4" s="12">
-        <v>90</v>
-      </c>
-      <c r="R4" s="10">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="R4" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1538,55 +1472,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.2</v>
+        <v>-14.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="O5" s="6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P5" s="13">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>56</v>
-      </c>
-      <c r="R5" s="14">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>89</v>
+      </c>
+      <c r="R5" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1594,55 +1528,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.1</v>
+        <v>-7.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O6" s="6">
-        <v>96</v>
-      </c>
-      <c r="P6" s="15">
-        <v>74</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>21</v>
-      </c>
-      <c r="R6" s="17">
-        <v>83</v>
+        <v>172</v>
+      </c>
+      <c r="O6" s="15">
+        <v>20</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1650,54 +1584,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="L7" s="4">
-        <v>-11.4</v>
+        <v>-14.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="15">
-        <v>74</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>100</v>
-      </c>
-      <c r="R7" s="18">
+        <v>171</v>
+      </c>
+      <c r="O7" s="15">
+        <v>22</v>
+      </c>
+      <c r="P7" s="7">
+        <v>22</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>6</v>
+      </c>
+      <c r="R7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1706,54 +1640,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.1</v>
+        <v>-16.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O8" s="6">
-        <v>78</v>
-      </c>
-      <c r="P8" s="19">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>70</v>
-      </c>
-      <c r="R8" s="18">
+        <v>173</v>
+      </c>
+      <c r="O8" s="17">
+        <v>17</v>
+      </c>
+      <c r="P8" s="18">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1762,55 +1696,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="L9" s="4">
-        <v>-14.8</v>
+        <v>-11.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="O9" s="6">
-        <v>79</v>
-      </c>
-      <c r="P9" s="19">
-        <v>78</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>8</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P9" s="12">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>84</v>
+      </c>
+      <c r="R9" s="12">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1818,55 +1752,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="L10" s="4">
-        <v>-7.4</v>
+        <v>-16.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="O10" s="6">
-        <v>49</v>
-      </c>
-      <c r="P10" s="13">
-        <v>38</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>12</v>
+        <v>92</v>
+      </c>
+      <c r="P10" s="12">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>84</v>
       </c>
       <c r="R10" s="18">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1874,55 +1808,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-7.9</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O11" s="6">
+        <v>87</v>
+      </c>
+      <c r="P11" s="10">
         <v>46</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-14.6</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O11" s="6">
-        <v>60</v>
-      </c>
-      <c r="P11" s="8">
-        <v>54</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>6</v>
-      </c>
-      <c r="R11" s="18">
-        <v>2</v>
+      <c r="Q11" s="19">
+        <v>25</v>
+      </c>
+      <c r="R11" s="20">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1930,55 +1864,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.3</v>
+        <v>-15</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="O12" s="6">
-        <v>94</v>
-      </c>
-      <c r="P12" s="11">
-        <v>51</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>4</v>
-      </c>
-      <c r="R12" s="10">
-        <v>61</v>
+        <v>89</v>
+      </c>
+      <c r="P12" s="21">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>30</v>
+      </c>
+      <c r="R12" s="22">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1986,55 +1920,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-11.8</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="N13" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="O13" s="6">
-        <v>57</v>
-      </c>
-      <c r="P13" s="11">
-        <v>49</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>43</v>
-      </c>
-      <c r="R13" s="18">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="P13" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>66</v>
+      </c>
+      <c r="R13" s="23">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2042,55 +1976,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-16.6</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="O14" s="6">
+        <v>86</v>
+      </c>
+      <c r="P14" s="18">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="12">
         <v>62</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O14" s="6">
-        <v>99</v>
-      </c>
-      <c r="P14" s="20">
-        <v>71</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>55</v>
-      </c>
-      <c r="R14" s="18">
-        <v>1</v>
+      <c r="R14" s="24">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2098,54 +2032,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O15" s="6">
+        <v>86</v>
+      </c>
+      <c r="P15" s="21">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="22">
         <v>31</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-7.9</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O15" s="6">
-        <v>100</v>
-      </c>
-      <c r="P15" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q15" s="23">
-        <v>97</v>
-      </c>
-      <c r="R15" s="10">
+      <c r="R15" s="12">
         <v>62</v>
       </c>
     </row>
@@ -2154,55 +2088,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="O16" s="6">
-        <v>100</v>
-      </c>
-      <c r="P16" s="21">
-        <v>9</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>98</v>
-      </c>
-      <c r="R16" s="8">
-        <v>56</v>
+        <v>93</v>
+      </c>
+      <c r="P16" s="25">
+        <v>78</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>13</v>
+      </c>
+      <c r="R16" s="24">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2210,282 +2144,114 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="L17" s="4">
-        <v>-12.3</v>
+        <v>-12.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O17" s="6">
-        <v>81</v>
-      </c>
-      <c r="P17" s="21">
-        <v>10</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>51</v>
-      </c>
-      <c r="R17" s="10">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-16.6</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O18" s="6">
-        <v>81</v>
-      </c>
-      <c r="P18" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>61</v>
-      </c>
-      <c r="R18" s="24">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2">
-        <v>29</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-8.4</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O19" s="6">
-        <v>86</v>
-      </c>
-      <c r="P19" s="18">
+        <v>171</v>
+      </c>
+      <c r="O17" s="15">
+        <v>32</v>
+      </c>
+      <c r="P17" s="18">
+        <v>17</v>
+      </c>
+      <c r="Q17" s="26">
+        <v>9</v>
+      </c>
+      <c r="R17" s="11">
         <v>0</v>
-      </c>
-      <c r="Q19" s="25">
-        <v>25</v>
-      </c>
-      <c r="R19" s="20">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O20" s="6">
-        <v>64</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="18">
-        <v>0</v>
-      </c>
-      <c r="R20" s="24">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2504,12 +2270,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2526,22 +2292,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260702--01</t>
-  </si>
-  <si>
-    <t>20260702--02</t>
-  </si>
-  <si>
-    <t>20260702--03</t>
-  </si>
-  <si>
     <t>20260703--01</t>
   </si>
   <si>
@@ -118,16 +109,10 @@
     <t>20260708--01</t>
   </si>
   <si>
-    <t>02:02</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>03:43</t>
+    <t>20260709--01</t>
+  </si>
+  <si>
+    <t>03:42</t>
   </si>
   <si>
     <t>05:39</t>
@@ -142,397 +127,364 @@
     <t>06:04</t>
   </si>
   <si>
-    <t>05:11</t>
+    <t>05:10</t>
   </si>
   <si>
     <t>06:03</t>
   </si>
   <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>02:37</t>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>02:36</t>
   </si>
   <si>
     <t>05:58</t>
   </si>
   <si>
-    <t>04:00</t>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:04</t>
   </si>
   <si>
     <t>04:48</t>
   </si>
   <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
-    <t>02:17</t>
-  </si>
-  <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>00:56</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>00:59:21</t>
-  </si>
-  <si>
-    <t>20:58:31</t>
-  </si>
-  <si>
-    <t>22:35:29</t>
-  </si>
-  <si>
-    <t>00:12:50</t>
-  </si>
-  <si>
-    <t>20:12:11</t>
-  </si>
-  <si>
-    <t>21:49:03</t>
-  </si>
-  <si>
-    <t>23:26:18</t>
-  </si>
-  <si>
-    <t>21:02:33</t>
-  </si>
-  <si>
-    <t>22:39:43</t>
-  </si>
-  <si>
-    <t>20:16:00</t>
-  </si>
-  <si>
-    <t>21:53:06</t>
-  </si>
-  <si>
-    <t>21:06:25</t>
-  </si>
-  <si>
-    <t>22:43:51</t>
-  </si>
-  <si>
-    <t>20:19:41</t>
-  </si>
-  <si>
-    <t>21:56:59</t>
-  </si>
-  <si>
-    <t>21:10:06</t>
-  </si>
-  <si>
-    <t>01:02:47</t>
-  </si>
-  <si>
-    <t>21:00:48</t>
-  </si>
-  <si>
-    <t>22:37:46</t>
-  </si>
-  <si>
-    <t>00:15:41</t>
-  </si>
-  <si>
-    <t>20:14:31</t>
-  </si>
-  <si>
-    <t>21:51:18</t>
-  </si>
-  <si>
-    <t>23:28:54</t>
-  </si>
-  <si>
-    <t>21:04:48</t>
-  </si>
-  <si>
-    <t>22:42:10</t>
-  </si>
-  <si>
-    <t>20:18:15</t>
-  </si>
-  <si>
-    <t>21:55:27</t>
-  </si>
-  <si>
-    <t>21:08:43</t>
-  </si>
-  <si>
-    <t>22:47:03</t>
-  </si>
-  <si>
-    <t>20:21:57</t>
-  </si>
-  <si>
-    <t>21:59:45</t>
-  </si>
-  <si>
-    <t>21:12:38</t>
-  </si>
-  <si>
-    <t>01:03:48</t>
-  </si>
-  <si>
-    <t>21:03:44</t>
-  </si>
-  <si>
-    <t>22:40:43</t>
+    <t>00:26</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>02:54</t>
+  </si>
+  <si>
+    <t>04:46</t>
+  </si>
+  <si>
+    <t>00:12:51</t>
+  </si>
+  <si>
+    <t>20:12:12</t>
+  </si>
+  <si>
+    <t>21:49:04</t>
+  </si>
+  <si>
+    <t>23:26:19</t>
+  </si>
+  <si>
+    <t>21:02:35</t>
+  </si>
+  <si>
+    <t>22:39:46</t>
+  </si>
+  <si>
+    <t>20:16:04</t>
+  </si>
+  <si>
+    <t>21:53:10</t>
+  </si>
+  <si>
+    <t>21:06:32</t>
+  </si>
+  <si>
+    <t>22:43:58</t>
+  </si>
+  <si>
+    <t>20:19:51</t>
+  </si>
+  <si>
+    <t>21:57:09</t>
+  </si>
+  <si>
+    <t>21:10:19</t>
+  </si>
+  <si>
+    <t>20:23:28</t>
+  </si>
+  <si>
+    <t>00:15:42</t>
+  </si>
+  <si>
+    <t>20:14:32</t>
+  </si>
+  <si>
+    <t>21:51:19</t>
+  </si>
+  <si>
+    <t>23:28:55</t>
+  </si>
+  <si>
+    <t>21:04:50</t>
+  </si>
+  <si>
+    <t>22:42:13</t>
+  </si>
+  <si>
+    <t>20:18:19</t>
+  </si>
+  <si>
+    <t>21:55:32</t>
+  </si>
+  <si>
+    <t>21:08:50</t>
+  </si>
+  <si>
+    <t>22:47:11</t>
+  </si>
+  <si>
+    <t>20:22:07</t>
+  </si>
+  <si>
+    <t>21:59:55</t>
+  </si>
+  <si>
+    <t>21:12:52</t>
+  </si>
+  <si>
+    <t>20:25:53</t>
   </si>
   <si>
     <t>00:17:33</t>
   </si>
   <si>
-    <t>20:17:20</t>
-  </si>
-  <si>
-    <t>21:54:19</t>
-  </si>
-  <si>
-    <t>23:31:12</t>
-  </si>
-  <si>
-    <t>21:07:50</t>
-  </si>
-  <si>
-    <t>22:44:45</t>
-  </si>
-  <si>
-    <t>20:21:16</t>
-  </si>
-  <si>
-    <t>21:58:14</t>
-  </si>
-  <si>
-    <t>21:11:37</t>
-  </si>
-  <si>
-    <t>22:48:22</t>
-  </si>
-  <si>
-    <t>20:24:56</t>
-  </si>
-  <si>
-    <t>22:01:45</t>
-  </si>
-  <si>
-    <t>21:15:02</t>
-  </si>
-  <si>
-    <t>01:04:49</t>
-  </si>
-  <si>
-    <t>21:06:40</t>
-  </si>
-  <si>
-    <t>22:43:42</t>
+    <t>20:17:21</t>
+  </si>
+  <si>
+    <t>21:54:20</t>
+  </si>
+  <si>
+    <t>23:31:13</t>
+  </si>
+  <si>
+    <t>21:07:52</t>
+  </si>
+  <si>
+    <t>22:44:48</t>
+  </si>
+  <si>
+    <t>20:21:20</t>
+  </si>
+  <si>
+    <t>21:58:18</t>
+  </si>
+  <si>
+    <t>21:11:44</t>
+  </si>
+  <si>
+    <t>22:48:29</t>
+  </si>
+  <si>
+    <t>20:25:06</t>
+  </si>
+  <si>
+    <t>22:01:55</t>
+  </si>
+  <si>
+    <t>21:15:16</t>
+  </si>
+  <si>
+    <t>20:28:32</t>
   </si>
   <si>
     <t>00:19:24</t>
   </si>
   <si>
-    <t>20:20:10</t>
-  </si>
-  <si>
-    <t>21:57:20</t>
-  </si>
-  <si>
-    <t>23:33:30</t>
-  </si>
-  <si>
-    <t>21:10:52</t>
-  </si>
-  <si>
-    <t>22:47:21</t>
-  </si>
-  <si>
-    <t>20:24:18</t>
-  </si>
-  <si>
-    <t>22:01:01</t>
-  </si>
-  <si>
-    <t>21:14:32</t>
-  </si>
-  <si>
-    <t>22:49:40</t>
-  </si>
-  <si>
-    <t>20:27:55</t>
-  </si>
-  <si>
-    <t>22:03:45</t>
-  </si>
-  <si>
-    <t>21:17:26</t>
-  </si>
-  <si>
-    <t>01:08:15</t>
-  </si>
-  <si>
-    <t>21:08:58</t>
-  </si>
-  <si>
-    <t>22:45:58</t>
+    <t>20:20:11</t>
+  </si>
+  <si>
+    <t>21:57:21</t>
+  </si>
+  <si>
+    <t>23:33:31</t>
+  </si>
+  <si>
+    <t>21:10:54</t>
+  </si>
+  <si>
+    <t>22:47:23</t>
+  </si>
+  <si>
+    <t>20:24:22</t>
+  </si>
+  <si>
+    <t>22:01:05</t>
+  </si>
+  <si>
+    <t>21:14:38</t>
+  </si>
+  <si>
+    <t>22:49:47</t>
+  </si>
+  <si>
+    <t>20:28:05</t>
+  </si>
+  <si>
+    <t>22:03:54</t>
+  </si>
+  <si>
+    <t>21:17:39</t>
+  </si>
+  <si>
+    <t>20:31:11</t>
   </si>
   <si>
     <t>00:22:15</t>
   </si>
   <si>
-    <t>20:22:30</t>
-  </si>
-  <si>
-    <t>21:59:35</t>
-  </si>
-  <si>
-    <t>23:36:05</t>
-  </si>
-  <si>
-    <t>21:13:07</t>
-  </si>
-  <si>
-    <t>22:49:47</t>
-  </si>
-  <si>
-    <t>20:26:33</t>
-  </si>
-  <si>
-    <t>22:03:22</t>
-  </si>
-  <si>
-    <t>21:16:49</t>
-  </si>
-  <si>
-    <t>22:52:52</t>
-  </si>
-  <si>
-    <t>20:30:11</t>
-  </si>
-  <si>
-    <t>22:06:30</t>
-  </si>
-  <si>
-    <t>21:19:58</t>
+    <t>20:22:31</t>
+  </si>
+  <si>
+    <t>21:59:36</t>
+  </si>
+  <si>
+    <t>23:36:06</t>
+  </si>
+  <si>
+    <t>21:13:09</t>
+  </si>
+  <si>
+    <t>22:49:49</t>
+  </si>
+  <si>
+    <t>20:26:37</t>
+  </si>
+  <si>
+    <t>22:03:26</t>
+  </si>
+  <si>
+    <t>21:16:56</t>
+  </si>
+  <si>
+    <t>22:52:59</t>
+  </si>
+  <si>
+    <t>20:30:20</t>
+  </si>
+  <si>
+    <t>22:06:39</t>
+  </si>
+  <si>
+    <t>21:20:11</t>
+  </si>
+  <si>
+    <t>20:33:35</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>15°</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>13°</t>
   </si>
   <si>
     <t>18°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>21:05:54</t>
-  </si>
-  <si>
-    <t>22:38:56</t>
-  </si>
-  <si>
     <t>20:21:21</t>
   </si>
   <si>
-    <t>21:54:22</t>
-  </si>
-  <si>
-    <t>23:27:23</t>
-  </si>
-  <si>
-    <t>21:09:36</t>
-  </si>
-  <si>
-    <t>22:42:37</t>
-  </si>
-  <si>
-    <t>20:24:43</t>
-  </si>
-  <si>
-    <t>21:57:44</t>
-  </si>
-  <si>
-    <t>21:12:45</t>
-  </si>
-  <si>
-    <t>22:45:44</t>
-  </si>
-  <si>
-    <t>20:27:41</t>
-  </si>
-  <si>
-    <t>22:00:41</t>
-  </si>
-  <si>
-    <t>21:15:33</t>
+    <t>21:54:23</t>
+  </si>
+  <si>
+    <t>23:27:24</t>
+  </si>
+  <si>
+    <t>21:09:38</t>
+  </si>
+  <si>
+    <t>22:42:39</t>
+  </si>
+  <si>
+    <t>20:24:47</t>
+  </si>
+  <si>
+    <t>21:57:48</t>
+  </si>
+  <si>
+    <t>21:12:51</t>
+  </si>
+  <si>
+    <t>22:45:51</t>
+  </si>
+  <si>
+    <t>20:27:50</t>
+  </si>
+  <si>
+    <t>22:00:50</t>
+  </si>
+  <si>
+    <t>21:15:46</t>
+  </si>
+  <si>
+    <t>20:30:39</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>3</t>
@@ -590,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,13 +554,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,79 +650,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1226,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1304,55 +1256,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.1</v>
+        <v>-14.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="8">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1360,55 +1312,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="L3" s="4">
-        <v>-11.4</v>
+        <v>-7.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="O3" s="6">
-        <v>60</v>
-      </c>
-      <c r="P3" s="7">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>44</v>
-      </c>
-      <c r="R3" s="11">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="P3" s="10">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>21</v>
+      </c>
+      <c r="R3" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1416,55 +1368,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="L4" s="4">
-        <v>-16.1</v>
+        <v>-14.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O4" s="6">
-        <v>97</v>
-      </c>
-      <c r="P4" s="12">
-        <v>59</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>58</v>
-      </c>
-      <c r="R4" s="11">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="O4" s="13">
+        <v>38</v>
+      </c>
+      <c r="P4" s="11">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>10</v>
+      </c>
+      <c r="R4" s="15">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1472,55 +1424,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="L5" s="4">
-        <v>-14.8</v>
+        <v>-16.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="O5" s="6">
-        <v>95</v>
-      </c>
-      <c r="P5" s="13">
-        <v>85</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>89</v>
-      </c>
-      <c r="R5" s="11">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="P5" s="16">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>31</v>
+      </c>
+      <c r="R5" s="18">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1528,55 +1480,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-11.8</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="6">
+        <v>100</v>
+      </c>
+      <c r="P6" s="19">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>96</v>
+      </c>
+      <c r="R6" s="16">
         <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-7.4</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O6" s="15">
-        <v>20</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1584,55 +1536,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-16.4</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O7" s="6">
+        <v>96</v>
+      </c>
+      <c r="P7" s="19">
         <v>53</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-14.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O7" s="15">
-        <v>22</v>
-      </c>
-      <c r="P7" s="7">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>6</v>
-      </c>
-      <c r="R7" s="11">
-        <v>0</v>
+      <c r="Q7" s="21">
+        <v>91</v>
+      </c>
+      <c r="R7" s="15">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1640,55 +1592,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-7.9</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" s="6">
+        <v>63</v>
+      </c>
+      <c r="P8" s="22">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>12</v>
+      </c>
+      <c r="R8" s="7">
         <v>50</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-16.3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="O8" s="17">
-        <v>17</v>
-      </c>
-      <c r="P8" s="18">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1696,55 +1648,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="L9" s="4">
-        <v>-11.8</v>
+        <v>-15</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="12">
-        <v>58</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>84</v>
-      </c>
-      <c r="R9" s="12">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="P9" s="7">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1752,55 +1704,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" s="6">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-16.4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O10" s="6">
-        <v>92</v>
-      </c>
-      <c r="P10" s="12">
-        <v>58</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>84</v>
-      </c>
-      <c r="R10" s="18">
-        <v>13</v>
+      <c r="P10" s="23">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>100</v>
+      </c>
+      <c r="R10" s="21">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1808,55 +1760,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="L11" s="4">
-        <v>-7.9</v>
+        <v>-16.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="O11" s="6">
-        <v>87</v>
-      </c>
-      <c r="P11" s="10">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>25</v>
-      </c>
-      <c r="R11" s="20">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="P11" s="7">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>93</v>
+      </c>
+      <c r="R11" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1864,55 +1816,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O12" s="6">
+        <v>83</v>
+      </c>
+      <c r="P12" s="17">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>83</v>
+      </c>
+      <c r="R12" s="25">
         <v>70</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O12" s="6">
-        <v>89</v>
-      </c>
-      <c r="P12" s="21">
-        <v>50</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>30</v>
-      </c>
-      <c r="R12" s="22">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1920,55 +1872,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="L13" s="4">
-        <v>-12.3</v>
+        <v>-15.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="O13" s="6">
-        <v>90</v>
-      </c>
-      <c r="P13" s="20">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>66</v>
-      </c>
-      <c r="R13" s="23">
-        <v>70</v>
+        <v>44</v>
+      </c>
+      <c r="P13" s="14">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>44</v>
+      </c>
+      <c r="R13" s="18">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1976,55 +1928,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="L14" s="4">
-        <v>-16.6</v>
+        <v>-12.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="O14" s="6">
-        <v>86</v>
-      </c>
-      <c r="P14" s="18">
+        <v>81</v>
+      </c>
+      <c r="P14" s="26">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="18">
         <v>13</v>
       </c>
-      <c r="Q14" s="12">
-        <v>62</v>
-      </c>
-      <c r="R14" s="24">
-        <v>74</v>
+      <c r="R14" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2032,226 +1984,114 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="L15" s="4">
-        <v>-8.4</v>
+        <v>-8.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="O15" s="6">
-        <v>86</v>
-      </c>
-      <c r="P15" s="21">
-        <v>52</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>31</v>
-      </c>
-      <c r="R15" s="12">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O16" s="6">
-        <v>93</v>
-      </c>
-      <c r="P16" s="25">
-        <v>78</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>13</v>
-      </c>
-      <c r="R16" s="24">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>18</v>
-      </c>
-      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P15" s="7">
         <v>49</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-12.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O17" s="15">
-        <v>32</v>
-      </c>
-      <c r="P17" s="18">
-        <v>17</v>
-      </c>
-      <c r="Q17" s="26">
-        <v>9</v>
-      </c>
-      <c r="R17" s="11">
+      <c r="Q15" s="10">
+        <v>37</v>
+      </c>
+      <c r="R15" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A15">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B15">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C15">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I15">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2270,12 +2110,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2292,22 +2132,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O15">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="123">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260703--01</t>
-  </si>
-  <si>
-    <t>20260703--02</t>
-  </si>
-  <si>
-    <t>20260703--03</t>
-  </si>
-  <si>
-    <t>20260703--04</t>
-  </si>
-  <si>
     <t>20260704--01</t>
   </si>
   <si>
@@ -112,18 +100,6 @@
     <t>20260709--01</t>
   </si>
   <si>
-    <t>03:42</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
     <t>06:04</t>
   </si>
   <si>
@@ -154,24 +130,21 @@
     <t>05:18</t>
   </si>
   <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>00:26</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>00:26</t>
-  </si>
-  <si>
-    <t>02:16</t>
-  </si>
-  <si>
-    <t>04:01</t>
-  </si>
-  <si>
     <t>05:43</t>
   </si>
   <si>
@@ -184,18 +157,6 @@
     <t>04:46</t>
   </si>
   <si>
-    <t>00:12:51</t>
-  </si>
-  <si>
-    <t>20:12:12</t>
-  </si>
-  <si>
-    <t>21:49:04</t>
-  </si>
-  <si>
-    <t>23:26:19</t>
-  </si>
-  <si>
     <t>21:02:35</t>
   </si>
   <si>
@@ -226,18 +187,6 @@
     <t>20:23:28</t>
   </si>
   <si>
-    <t>00:15:42</t>
-  </si>
-  <si>
-    <t>20:14:32</t>
-  </si>
-  <si>
-    <t>21:51:19</t>
-  </si>
-  <si>
-    <t>23:28:55</t>
-  </si>
-  <si>
     <t>21:04:50</t>
   </si>
   <si>
@@ -268,18 +217,6 @@
     <t>20:25:53</t>
   </si>
   <si>
-    <t>00:17:33</t>
-  </si>
-  <si>
-    <t>20:17:21</t>
-  </si>
-  <si>
-    <t>21:54:20</t>
-  </si>
-  <si>
-    <t>23:31:13</t>
-  </si>
-  <si>
     <t>21:07:52</t>
   </si>
   <si>
@@ -310,18 +247,6 @@
     <t>20:28:32</t>
   </si>
   <si>
-    <t>00:19:24</t>
-  </si>
-  <si>
-    <t>20:20:11</t>
-  </si>
-  <si>
-    <t>21:57:21</t>
-  </si>
-  <si>
-    <t>23:33:31</t>
-  </si>
-  <si>
     <t>21:10:54</t>
   </si>
   <si>
@@ -352,18 +277,6 @@
     <t>20:31:11</t>
   </si>
   <si>
-    <t>00:22:15</t>
-  </si>
-  <si>
-    <t>20:22:31</t>
-  </si>
-  <si>
-    <t>21:59:36</t>
-  </si>
-  <si>
-    <t>23:36:06</t>
-  </si>
-  <si>
     <t>21:13:09</t>
   </si>
   <si>
@@ -394,15 +307,6 @@
     <t>20:33:35</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
     <t>19°</t>
   </si>
   <si>
@@ -430,15 +334,6 @@
     <t>18°</t>
   </si>
   <si>
-    <t>20:21:21</t>
-  </si>
-  <si>
-    <t>21:54:23</t>
-  </si>
-  <si>
-    <t>23:27:24</t>
-  </si>
-  <si>
     <t>21:09:38</t>
   </si>
   <si>
@@ -469,22 +364,22 @@
     <t>20:30:39</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>3</t>
@@ -521,7 +416,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,121 +437,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -769,12 +652,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1178,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1256,55 +1133,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.8</v>
+        <v>-11.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R2" s="9">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1312,55 +1189,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="L3" s="4">
-        <v>-7.4</v>
+        <v>-16.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="O3" s="6">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="P3" s="10">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q3" s="11">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="R3" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1368,55 +1245,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-7.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-14.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O4" s="13">
-        <v>38</v>
-      </c>
-      <c r="P4" s="11">
-        <v>21</v>
+      <c r="P4" s="13">
+        <v>55</v>
       </c>
       <c r="Q4" s="14">
-        <v>10</v>
-      </c>
-      <c r="R4" s="15">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="R4" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1424,55 +1301,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.3</v>
+        <v>-15</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="O5" s="6">
-        <v>59</v>
-      </c>
-      <c r="P5" s="16">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="17">
-        <v>31</v>
-      </c>
-      <c r="R5" s="18">
-        <v>13</v>
+        <v>100</v>
+      </c>
+      <c r="P5" s="10">
+        <v>60</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>95</v>
+      </c>
+      <c r="R5" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1480,55 +1357,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-11.8</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="19">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="20">
-        <v>96</v>
-      </c>
-      <c r="R6" s="16">
-        <v>38</v>
+        <v>99</v>
+      </c>
+      <c r="P6" s="16">
+        <v>81</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>94</v>
+      </c>
+      <c r="R6" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1536,54 +1413,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="L7" s="4">
-        <v>-16.4</v>
+        <v>-16.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="O7" s="6">
-        <v>96</v>
-      </c>
-      <c r="P7" s="19">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="21">
         <v>91</v>
       </c>
-      <c r="R7" s="15">
+      <c r="P7" s="16">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>70</v>
+      </c>
+      <c r="R7" s="19">
         <v>27</v>
       </c>
     </row>
@@ -1592,55 +1469,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="L8" s="4">
-        <v>-7.9</v>
+        <v>-8.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="O8" s="6">
-        <v>63</v>
-      </c>
-      <c r="P8" s="22">
-        <v>43</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>12</v>
-      </c>
-      <c r="R8" s="7">
-        <v>50</v>
+        <v>98</v>
+      </c>
+      <c r="P8" s="7">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>53</v>
+      </c>
+      <c r="R8" s="20">
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1648,55 +1525,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="L9" s="4">
-        <v>-15</v>
+        <v>-15.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="O9" s="6">
+        <v>94</v>
+      </c>
+      <c r="P9" s="7">
         <v>66</v>
       </c>
-      <c r="P9" s="7">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>51</v>
+      <c r="Q9" s="7">
+        <v>66</v>
+      </c>
+      <c r="R9" s="21">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1704,55 +1581,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="L10" s="4">
-        <v>-12.3</v>
+        <v>-12.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="23">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>100</v>
-      </c>
-      <c r="R10" s="21">
-        <v>89</v>
+        <v>57</v>
+      </c>
+      <c r="P10" s="22">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>13</v>
+      </c>
+      <c r="R10" s="24">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1760,338 +1637,114 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L11" s="4">
-        <v>-16.6</v>
+        <v>-8.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="7">
-        <v>52</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>93</v>
-      </c>
-      <c r="R11" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-8.4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" s="6">
-        <v>83</v>
-      </c>
-      <c r="P12" s="17">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="24">
-        <v>83</v>
-      </c>
-      <c r="R12" s="25">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O13" s="6">
-        <v>44</v>
-      </c>
-      <c r="P13" s="14">
+        <v>78</v>
+      </c>
+      <c r="P11" s="16">
+        <v>78</v>
+      </c>
+      <c r="Q11" s="17">
         <v>12</v>
       </c>
-      <c r="Q13" s="22">
-        <v>44</v>
-      </c>
-      <c r="R13" s="18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="R11" s="9">
         <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-12.7</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="6">
-        <v>81</v>
-      </c>
-      <c r="P14" s="26">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>13</v>
-      </c>
-      <c r="R14" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>21</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O15" s="6">
-        <v>55</v>
-      </c>
-      <c r="P15" s="7">
-        <v>49</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>37</v>
-      </c>
-      <c r="R15" s="9">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A15">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2110,12 +1763,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2132,22 +1785,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260704--01</t>
-  </si>
-  <si>
-    <t>20260704--02</t>
-  </si>
-  <si>
     <t>20260705--01</t>
   </si>
   <si>
@@ -100,22 +94,19 @@
     <t>20260709--01</t>
   </si>
   <si>
+    <t>20260711--01</t>
+  </si>
+  <si>
     <t>06:04</t>
   </si>
   <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
     <t>05:33</t>
   </si>
   <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>02:36</t>
+    <t>02:35</t>
   </si>
   <si>
     <t>05:58</t>
@@ -130,10 +121,7 @@
     <t>05:18</t>
   </si>
   <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>00:26</t>
+    <t>03:10</t>
   </si>
   <si>
     <t>02:16</t>
@@ -157,40 +145,31 @@
     <t>04:46</t>
   </si>
   <si>
-    <t>21:02:35</t>
-  </si>
-  <si>
-    <t>22:39:46</t>
-  </si>
-  <si>
-    <t>20:16:04</t>
-  </si>
-  <si>
-    <t>21:53:10</t>
-  </si>
-  <si>
-    <t>21:06:32</t>
-  </si>
-  <si>
-    <t>22:43:58</t>
-  </si>
-  <si>
-    <t>20:19:51</t>
-  </si>
-  <si>
-    <t>21:57:09</t>
-  </si>
-  <si>
-    <t>21:10:19</t>
-  </si>
-  <si>
-    <t>20:23:28</t>
-  </si>
-  <si>
-    <t>21:04:50</t>
-  </si>
-  <si>
-    <t>22:42:13</t>
+    <t>20:16:05</t>
+  </si>
+  <si>
+    <t>21:53:11</t>
+  </si>
+  <si>
+    <t>21:06:33</t>
+  </si>
+  <si>
+    <t>22:43:59</t>
+  </si>
+  <si>
+    <t>20:19:52</t>
+  </si>
+  <si>
+    <t>21:57:10</t>
+  </si>
+  <si>
+    <t>21:10:21</t>
+  </si>
+  <si>
+    <t>20:23:30</t>
+  </si>
+  <si>
+    <t>20:27:03</t>
   </si>
   <si>
     <t>20:18:19</t>
@@ -199,184 +178,172 @@
     <t>21:55:32</t>
   </si>
   <si>
-    <t>21:08:50</t>
-  </si>
-  <si>
-    <t>22:47:11</t>
-  </si>
-  <si>
-    <t>20:22:07</t>
-  </si>
-  <si>
-    <t>21:59:55</t>
+    <t>21:08:51</t>
+  </si>
+  <si>
+    <t>22:47:12</t>
+  </si>
+  <si>
+    <t>20:22:08</t>
+  </si>
+  <si>
+    <t>21:59:56</t>
+  </si>
+  <si>
+    <t>21:12:54</t>
+  </si>
+  <si>
+    <t>20:25:55</t>
+  </si>
+  <si>
+    <t>20:30:05</t>
+  </si>
+  <si>
+    <t>20:21:21</t>
+  </si>
+  <si>
+    <t>21:58:19</t>
+  </si>
+  <si>
+    <t>21:11:45</t>
+  </si>
+  <si>
+    <t>22:48:30</t>
+  </si>
+  <si>
+    <t>20:25:07</t>
+  </si>
+  <si>
+    <t>22:01:56</t>
+  </si>
+  <si>
+    <t>21:15:18</t>
+  </si>
+  <si>
+    <t>20:28:35</t>
+  </si>
+  <si>
+    <t>20:31:40</t>
+  </si>
+  <si>
+    <t>20:24:23</t>
+  </si>
+  <si>
+    <t>22:01:05</t>
+  </si>
+  <si>
+    <t>21:14:39</t>
+  </si>
+  <si>
+    <t>22:49:47</t>
+  </si>
+  <si>
+    <t>20:28:06</t>
+  </si>
+  <si>
+    <t>22:03:55</t>
+  </si>
+  <si>
+    <t>21:17:41</t>
+  </si>
+  <si>
+    <t>20:31:13</t>
+  </si>
+  <si>
+    <t>20:33:15</t>
+  </si>
+  <si>
+    <t>20:26:37</t>
+  </si>
+  <si>
+    <t>22:03:26</t>
+  </si>
+  <si>
+    <t>21:16:57</t>
+  </si>
+  <si>
+    <t>22:53:00</t>
+  </si>
+  <si>
+    <t>20:30:22</t>
+  </si>
+  <si>
+    <t>22:06:41</t>
+  </si>
+  <si>
+    <t>21:20:13</t>
+  </si>
+  <si>
+    <t>20:33:38</t>
+  </si>
+  <si>
+    <t>20:36:15</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>20:24:48</t>
+  </si>
+  <si>
+    <t>21:57:48</t>
   </si>
   <si>
     <t>21:12:52</t>
   </si>
   <si>
-    <t>20:25:53</t>
-  </si>
-  <si>
-    <t>21:07:52</t>
-  </si>
-  <si>
-    <t>22:44:48</t>
-  </si>
-  <si>
-    <t>20:21:20</t>
-  </si>
-  <si>
-    <t>21:58:18</t>
-  </si>
-  <si>
-    <t>21:11:44</t>
-  </si>
-  <si>
-    <t>22:48:29</t>
-  </si>
-  <si>
-    <t>20:25:06</t>
-  </si>
-  <si>
-    <t>22:01:55</t>
-  </si>
-  <si>
-    <t>21:15:16</t>
-  </si>
-  <si>
-    <t>20:28:32</t>
-  </si>
-  <si>
-    <t>21:10:54</t>
-  </si>
-  <si>
-    <t>22:47:23</t>
-  </si>
-  <si>
-    <t>20:24:22</t>
-  </si>
-  <si>
-    <t>22:01:05</t>
-  </si>
-  <si>
-    <t>21:14:38</t>
-  </si>
-  <si>
-    <t>22:49:47</t>
-  </si>
-  <si>
-    <t>20:28:05</t>
-  </si>
-  <si>
-    <t>22:03:54</t>
-  </si>
-  <si>
-    <t>21:17:39</t>
-  </si>
-  <si>
-    <t>20:31:11</t>
-  </si>
-  <si>
-    <t>21:13:09</t>
-  </si>
-  <si>
-    <t>22:49:49</t>
-  </si>
-  <si>
-    <t>20:26:37</t>
-  </si>
-  <si>
-    <t>22:03:26</t>
-  </si>
-  <si>
-    <t>21:16:56</t>
-  </si>
-  <si>
-    <t>22:52:59</t>
-  </si>
-  <si>
-    <t>20:30:20</t>
-  </si>
-  <si>
-    <t>22:06:39</t>
-  </si>
-  <si>
-    <t>21:20:11</t>
-  </si>
-  <si>
-    <t>20:33:35</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>21:09:38</t>
-  </si>
-  <si>
-    <t>22:42:39</t>
-  </si>
-  <si>
-    <t>20:24:47</t>
-  </si>
-  <si>
-    <t>21:57:48</t>
-  </si>
-  <si>
-    <t>21:12:51</t>
-  </si>
-  <si>
-    <t>22:45:51</t>
-  </si>
-  <si>
-    <t>20:27:50</t>
-  </si>
-  <si>
-    <t>22:00:50</t>
-  </si>
-  <si>
-    <t>21:15:46</t>
-  </si>
-  <si>
-    <t>20:30:39</t>
+    <t>22:45:52</t>
+  </si>
+  <si>
+    <t>20:27:51</t>
+  </si>
+  <si>
+    <t>22:00:51</t>
+  </si>
+  <si>
+    <t>21:15:48</t>
+  </si>
+  <si>
+    <t>20:30:41</t>
+  </si>
+  <si>
+    <t>20:33:22</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>4</t>
@@ -416,7 +383,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,7 +404,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,13 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,67 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -649,9 +610,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1055,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1136,52 +1094,52 @@
         <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-7.9</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="6">
         <v>57</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-11.8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O2" s="6">
-        <v>100</v>
-      </c>
       <c r="P2" s="7">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="8">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="R2" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1189,55 +1147,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.4</v>
+        <v>-15</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O3" s="6">
-        <v>90</v>
-      </c>
-      <c r="P3" s="10">
-        <v>61</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>83</v>
-      </c>
-      <c r="R3" s="12">
-        <v>4</v>
+        <v>81</v>
+      </c>
+      <c r="P3" s="8">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>47</v>
+      </c>
+      <c r="R3" s="10">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1245,55 +1203,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="L4" s="4">
-        <v>-7.9</v>
+        <v>-12.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="13">
-        <v>55</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>46</v>
-      </c>
-      <c r="R4" s="8">
-        <v>100</v>
+      <c r="P4" s="11">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>82</v>
+      </c>
+      <c r="R4" s="13">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1301,55 +1259,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L5" s="4">
-        <v>-15</v>
+        <v>-16.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="O5" s="6">
         <v>100</v>
       </c>
       <c r="P5" s="10">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>95</v>
-      </c>
-      <c r="R5" s="8">
-        <v>100</v>
+        <v>77</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>56</v>
+      </c>
+      <c r="R5" s="15">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1357,55 +1315,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.3</v>
+        <v>-8.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O6" s="6">
-        <v>99</v>
-      </c>
-      <c r="P6" s="16">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>94</v>
-      </c>
-      <c r="R6" s="17">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="P6" s="14">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>70</v>
+      </c>
+      <c r="R6" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1413,55 +1371,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L7" s="4">
-        <v>-16.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="O7" s="6">
-        <v>91</v>
-      </c>
-      <c r="P7" s="16">
-        <v>80</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>70</v>
-      </c>
-      <c r="R7" s="19">
-        <v>27</v>
+        <v>100</v>
+      </c>
+      <c r="P7" s="17">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>76</v>
+      </c>
+      <c r="R7" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1469,55 +1427,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L8" s="4">
-        <v>-8.4</v>
+        <v>-12.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O8" s="6">
-        <v>98</v>
-      </c>
-      <c r="P8" s="7">
-        <v>65</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>53</v>
+        <v>109</v>
+      </c>
+      <c r="O8" s="18">
+        <v>33</v>
+      </c>
+      <c r="P8" s="19">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>6</v>
       </c>
       <c r="R8" s="20">
-        <v>75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1525,55 +1483,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.3</v>
+        <v>-8.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O9" s="6">
-        <v>94</v>
-      </c>
-      <c r="P9" s="7">
-        <v>66</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>66</v>
-      </c>
-      <c r="R9" s="21">
-        <v>34</v>
+        <v>109</v>
+      </c>
+      <c r="O9" s="21">
+        <v>13</v>
+      </c>
+      <c r="P9" s="22">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="23">
+        <v>0</v>
+      </c>
+      <c r="R9" s="23">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1581,170 +1539,114 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-9.4</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-12.7</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O10" s="6">
-        <v>57</v>
-      </c>
-      <c r="P10" s="22">
-        <v>52</v>
+        <v>110</v>
+      </c>
+      <c r="O10" s="21">
+        <v>9</v>
+      </c>
+      <c r="P10" s="19">
+        <v>7</v>
       </c>
       <c r="Q10" s="23">
-        <v>13</v>
-      </c>
-      <c r="R10" s="24">
+        <v>1</v>
+      </c>
+      <c r="R10" s="23">
         <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O11" s="6">
-        <v>78</v>
-      </c>
-      <c r="P11" s="16">
-        <v>78</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>12</v>
-      </c>
-      <c r="R11" s="9">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B10">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1763,12 +1665,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M10">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1785,22 +1687,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O10">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P10">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R10">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="90">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260705--01</t>
-  </si>
-  <si>
-    <t>20260705--02</t>
-  </si>
-  <si>
     <t>20260706--01</t>
   </si>
   <si>
@@ -97,34 +91,25 @@
     <t>20260711--01</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>02:35</t>
+    <t>02:36</t>
   </si>
   <si>
     <t>05:58</t>
   </si>
   <si>
-    <t>03:59</t>
-  </si>
-  <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>02:16</t>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>03:15</t>
   </si>
   <si>
     <t>04:01</t>
@@ -133,157 +118,118 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>02:54</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>20:16:05</t>
-  </si>
-  <si>
-    <t>21:53:11</t>
-  </si>
-  <si>
-    <t>21:06:33</t>
-  </si>
-  <si>
-    <t>22:43:59</t>
-  </si>
-  <si>
-    <t>20:19:52</t>
-  </si>
-  <si>
-    <t>21:57:10</t>
-  </si>
-  <si>
-    <t>21:10:21</t>
-  </si>
-  <si>
-    <t>20:23:30</t>
-  </si>
-  <si>
-    <t>20:27:03</t>
-  </si>
-  <si>
-    <t>20:18:19</t>
-  </si>
-  <si>
-    <t>21:55:32</t>
-  </si>
-  <si>
-    <t>21:08:51</t>
-  </si>
-  <si>
-    <t>22:47:12</t>
-  </si>
-  <si>
-    <t>20:22:08</t>
-  </si>
-  <si>
-    <t>21:59:56</t>
-  </si>
-  <si>
-    <t>21:12:54</t>
-  </si>
-  <si>
-    <t>20:25:55</t>
-  </si>
-  <si>
-    <t>20:30:05</t>
-  </si>
-  <si>
-    <t>20:21:21</t>
-  </si>
-  <si>
-    <t>21:58:19</t>
-  </si>
-  <si>
-    <t>21:11:45</t>
-  </si>
-  <si>
-    <t>22:48:30</t>
-  </si>
-  <si>
-    <t>20:25:07</t>
-  </si>
-  <si>
-    <t>22:01:56</t>
-  </si>
-  <si>
-    <t>21:15:18</t>
-  </si>
-  <si>
-    <t>20:28:35</t>
-  </si>
-  <si>
-    <t>20:31:40</t>
-  </si>
-  <si>
-    <t>20:24:23</t>
-  </si>
-  <si>
-    <t>22:01:05</t>
-  </si>
-  <si>
-    <t>21:14:39</t>
-  </si>
-  <si>
-    <t>22:49:47</t>
-  </si>
-  <si>
-    <t>20:28:06</t>
-  </si>
-  <si>
-    <t>22:03:55</t>
-  </si>
-  <si>
-    <t>21:17:41</t>
-  </si>
-  <si>
-    <t>20:31:13</t>
-  </si>
-  <si>
-    <t>20:33:15</t>
-  </si>
-  <si>
-    <t>20:26:37</t>
-  </si>
-  <si>
-    <t>22:03:26</t>
-  </si>
-  <si>
-    <t>21:16:57</t>
-  </si>
-  <si>
-    <t>22:53:00</t>
-  </si>
-  <si>
-    <t>20:30:22</t>
-  </si>
-  <si>
-    <t>22:06:41</t>
-  </si>
-  <si>
-    <t>21:20:13</t>
-  </si>
-  <si>
-    <t>20:33:38</t>
-  </si>
-  <si>
-    <t>20:36:15</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>23°</t>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>00:56</t>
+  </si>
+  <si>
+    <t>02:55</t>
+  </si>
+  <si>
+    <t>21:06:20</t>
+  </si>
+  <si>
+    <t>22:43:45</t>
+  </si>
+  <si>
+    <t>20:19:30</t>
+  </si>
+  <si>
+    <t>21:56:48</t>
+  </si>
+  <si>
+    <t>21:09:47</t>
+  </si>
+  <si>
+    <t>20:22:41</t>
+  </si>
+  <si>
+    <t>20:25:37</t>
+  </si>
+  <si>
+    <t>21:08:38</t>
+  </si>
+  <si>
+    <t>22:46:58</t>
+  </si>
+  <si>
+    <t>20:21:46</t>
+  </si>
+  <si>
+    <t>21:59:33</t>
+  </si>
+  <si>
+    <t>21:12:19</t>
+  </si>
+  <si>
+    <t>20:25:06</t>
+  </si>
+  <si>
+    <t>20:28:36</t>
+  </si>
+  <si>
+    <t>21:11:32</t>
+  </si>
+  <si>
+    <t>22:48:16</t>
+  </si>
+  <si>
+    <t>20:24:45</t>
+  </si>
+  <si>
+    <t>22:01:33</t>
+  </si>
+  <si>
+    <t>21:14:43</t>
+  </si>
+  <si>
+    <t>20:27:46</t>
+  </si>
+  <si>
+    <t>20:30:14</t>
+  </si>
+  <si>
+    <t>21:14:26</t>
+  </si>
+  <si>
+    <t>22:49:34</t>
+  </si>
+  <si>
+    <t>20:27:44</t>
+  </si>
+  <si>
+    <t>22:03:33</t>
+  </si>
+  <si>
+    <t>21:17:07</t>
+  </si>
+  <si>
+    <t>20:30:25</t>
+  </si>
+  <si>
+    <t>20:31:51</t>
+  </si>
+  <si>
+    <t>21:16:44</t>
+  </si>
+  <si>
+    <t>22:52:46</t>
+  </si>
+  <si>
+    <t>20:29:59</t>
+  </si>
+  <si>
+    <t>22:06:18</t>
+  </si>
+  <si>
+    <t>21:19:38</t>
+  </si>
+  <si>
+    <t>20:32:49</t>
+  </si>
+  <si>
+    <t>20:34:50</t>
   </si>
   <si>
     <t>22°</t>
@@ -304,52 +250,40 @@
     <t>10°</t>
   </si>
   <si>
-    <t>20:24:48</t>
-  </si>
-  <si>
-    <t>21:57:48</t>
-  </si>
-  <si>
-    <t>21:12:52</t>
-  </si>
-  <si>
-    <t>22:45:52</t>
-  </si>
-  <si>
-    <t>20:27:51</t>
-  </si>
-  <si>
-    <t>22:00:51</t>
-  </si>
-  <si>
-    <t>21:15:48</t>
-  </si>
-  <si>
-    <t>20:30:41</t>
-  </si>
-  <si>
-    <t>20:33:22</t>
+    <t>21:12:39</t>
+  </si>
+  <si>
+    <t>22:45:39</t>
+  </si>
+  <si>
+    <t>20:27:30</t>
+  </si>
+  <si>
+    <t>22:00:29</t>
+  </si>
+  <si>
+    <t>21:15:14</t>
+  </si>
+  <si>
+    <t>20:29:54</t>
+  </si>
+  <si>
+    <t>20:31:59</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -383,7 +317,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,37 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +356,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +368,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,24 +405,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,21 +499,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1091,55 +980,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-7.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="O2" s="6">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="8">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="R2" s="9">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1147,55 +1036,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-16.6</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="O3" s="6">
-        <v>81</v>
-      </c>
-      <c r="P3" s="8">
-        <v>45</v>
+        <v>100</v>
+      </c>
+      <c r="P3" s="10">
+        <v>64</v>
       </c>
       <c r="Q3" s="8">
-        <v>47</v>
-      </c>
-      <c r="R3" s="10">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="R3" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1203,55 +1092,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4">
-        <v>-12.3</v>
+        <v>-8.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="11">
-        <v>62</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>82</v>
-      </c>
-      <c r="R4" s="13">
-        <v>95</v>
+      <c r="P4" s="10">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>100</v>
+      </c>
+      <c r="R4" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1259,55 +1148,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.6</v>
+        <v>-15.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="O5" s="6">
         <v>100</v>
       </c>
-      <c r="P5" s="10">
-        <v>77</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>56</v>
-      </c>
-      <c r="R5" s="15">
-        <v>99</v>
+      <c r="P5" s="12">
+        <v>88</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>88</v>
+      </c>
+      <c r="R5" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1315,55 +1204,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="6">
+        <v>97</v>
+      </c>
+      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>40</v>
+      </c>
+      <c r="R6" s="12">
         <v>92</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-8.4</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="14">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>70</v>
-      </c>
-      <c r="R6" s="15">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1371,55 +1260,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.3</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="17">
-        <v>87</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>76</v>
-      </c>
-      <c r="R7" s="15">
-        <v>100</v>
+        <v>72</v>
+      </c>
+      <c r="P7" s="10">
+        <v>64</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>23</v>
+      </c>
+      <c r="R7" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1427,226 +1316,114 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O8" s="18">
-        <v>33</v>
-      </c>
-      <c r="P8" s="19">
-        <v>6</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>6</v>
-      </c>
-      <c r="R8" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O9" s="21">
+        <v>89</v>
+      </c>
+      <c r="O8" s="16">
         <v>13</v>
       </c>
-      <c r="P9" s="22">
-        <v>13</v>
-      </c>
-      <c r="Q9" s="23">
-        <v>0</v>
-      </c>
-      <c r="R9" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="O10" s="21">
-        <v>9</v>
-      </c>
-      <c r="P10" s="19">
-        <v>7</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>1</v>
-      </c>
-      <c r="R10" s="23">
+      <c r="P8" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>11</v>
+      </c>
+      <c r="R8" s="13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A10">
+  <conditionalFormatting sqref="A2:A8">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B10">
+  <conditionalFormatting sqref="B2:B8">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
+  <conditionalFormatting sqref="K2:K8">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1665,12 +1442,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M10">
+  <conditionalFormatting sqref="M2:M8">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
+  <conditionalFormatting sqref="N2:N8">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1687,22 +1464,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O10">
+  <conditionalFormatting sqref="O2:O8">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
+  <conditionalFormatting sqref="P2:P8">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q8">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R8">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260706--01</t>
-  </si>
-  <si>
-    <t>20260706--02</t>
-  </si>
-  <si>
     <t>20260707--01</t>
   </si>
   <si>
@@ -91,151 +85,103 @@
     <t>20260711--01</t>
   </si>
   <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>02:36</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:19</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:01</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>00:56</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>21:06:20</t>
-  </si>
-  <si>
-    <t>22:43:45</t>
-  </si>
-  <si>
-    <t>20:19:30</t>
-  </si>
-  <si>
-    <t>21:56:48</t>
-  </si>
-  <si>
-    <t>21:09:47</t>
-  </si>
-  <si>
-    <t>20:22:41</t>
-  </si>
-  <si>
-    <t>20:25:37</t>
-  </si>
-  <si>
-    <t>21:08:38</t>
-  </si>
-  <si>
-    <t>22:46:58</t>
-  </si>
-  <si>
-    <t>20:21:46</t>
-  </si>
-  <si>
-    <t>21:59:33</t>
-  </si>
-  <si>
-    <t>21:12:19</t>
-  </si>
-  <si>
-    <t>20:25:06</t>
-  </si>
-  <si>
-    <t>20:28:36</t>
-  </si>
-  <si>
-    <t>21:11:32</t>
-  </si>
-  <si>
-    <t>22:48:16</t>
-  </si>
-  <si>
-    <t>20:24:45</t>
-  </si>
-  <si>
-    <t>22:01:33</t>
-  </si>
-  <si>
-    <t>21:14:43</t>
-  </si>
-  <si>
-    <t>20:27:46</t>
-  </si>
-  <si>
-    <t>20:30:14</t>
-  </si>
-  <si>
-    <t>21:14:26</t>
-  </si>
-  <si>
-    <t>22:49:34</t>
-  </si>
-  <si>
-    <t>20:27:44</t>
-  </si>
-  <si>
-    <t>22:03:33</t>
-  </si>
-  <si>
-    <t>21:17:07</t>
-  </si>
-  <si>
-    <t>20:30:25</t>
-  </si>
-  <si>
-    <t>20:31:51</t>
-  </si>
-  <si>
-    <t>21:16:44</t>
-  </si>
-  <si>
-    <t>22:52:46</t>
-  </si>
-  <si>
-    <t>20:29:59</t>
-  </si>
-  <si>
-    <t>22:06:18</t>
-  </si>
-  <si>
-    <t>21:19:38</t>
-  </si>
-  <si>
-    <t>20:32:49</t>
-  </si>
-  <si>
-    <t>20:34:50</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>6°</t>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:13</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>02:54</t>
+  </si>
+  <si>
+    <t>20:19:38</t>
+  </si>
+  <si>
+    <t>21:56:56</t>
+  </si>
+  <si>
+    <t>21:10:01</t>
+  </si>
+  <si>
+    <t>20:23:04</t>
+  </si>
+  <si>
+    <t>20:26:22</t>
+  </si>
+  <si>
+    <t>20:21:54</t>
+  </si>
+  <si>
+    <t>21:59:42</t>
+  </si>
+  <si>
+    <t>21:12:34</t>
+  </si>
+  <si>
+    <t>20:25:29</t>
+  </si>
+  <si>
+    <t>20:29:22</t>
+  </si>
+  <si>
+    <t>20:24:52</t>
+  </si>
+  <si>
+    <t>22:01:41</t>
+  </si>
+  <si>
+    <t>21:14:57</t>
+  </si>
+  <si>
+    <t>20:28:08</t>
+  </si>
+  <si>
+    <t>20:30:59</t>
+  </si>
+  <si>
+    <t>20:27:51</t>
+  </si>
+  <si>
+    <t>22:03:41</t>
+  </si>
+  <si>
+    <t>21:17:21</t>
+  </si>
+  <si>
+    <t>20:30:47</t>
+  </si>
+  <si>
+    <t>20:32:35</t>
+  </si>
+  <si>
+    <t>20:30:07</t>
+  </si>
+  <si>
+    <t>22:06:26</t>
+  </si>
+  <si>
+    <t>21:19:53</t>
+  </si>
+  <si>
+    <t>20:33:11</t>
+  </si>
+  <si>
+    <t>20:35:34</t>
   </si>
   <si>
     <t>11°</t>
@@ -250,37 +196,31 @@
     <t>10°</t>
   </si>
   <si>
-    <t>21:12:39</t>
-  </si>
-  <si>
-    <t>22:45:39</t>
-  </si>
-  <si>
-    <t>20:27:30</t>
-  </si>
-  <si>
-    <t>22:00:29</t>
-  </si>
-  <si>
-    <t>21:15:14</t>
-  </si>
-  <si>
-    <t>20:29:54</t>
-  </si>
-  <si>
-    <t>20:31:59</t>
+    <t>20:27:37</t>
+  </si>
+  <si>
+    <t>22:00:37</t>
+  </si>
+  <si>
+    <t>21:15:28</t>
+  </si>
+  <si>
+    <t>20:30:16</t>
+  </si>
+  <si>
+    <t>20:32:42</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -317,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,24 +278,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,13 +296,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +326,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,9 +430,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -902,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -980,55 +911,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-12.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="Q2" s="8">
-        <v>71</v>
-      </c>
-      <c r="R2" s="9">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="R2" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1036,54 +967,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.6</v>
+        <v>-15.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
       </c>
-      <c r="P3" s="10">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>70</v>
-      </c>
-      <c r="R3" s="11">
+      <c r="P3" s="9">
+        <v>88</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>81</v>
+      </c>
+      <c r="R3" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1092,54 +1023,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-8.4</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="10">
-        <v>67</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>100</v>
-      </c>
-      <c r="R4" s="11">
+      <c r="P4" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>3</v>
+      </c>
+      <c r="R4" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1148,55 +1079,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.3</v>
+        <v>-8.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="12">
-        <v>88</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>88</v>
-      </c>
-      <c r="R5" s="11">
-        <v>100</v>
+        <v>67</v>
+      </c>
+      <c r="O5" s="13">
+        <v>41</v>
+      </c>
+      <c r="P5" s="14">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>14</v>
+      </c>
+      <c r="R5" s="16">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1204,226 +1135,114 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-9.4</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-12.7</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="6">
-        <v>97</v>
-      </c>
-      <c r="P6" s="13">
+      <c r="O6" s="17">
+        <v>12</v>
+      </c>
+      <c r="P6" s="16">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="11">
         <v>0</v>
       </c>
-      <c r="Q6" s="14">
-        <v>40</v>
-      </c>
-      <c r="R6" s="12">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="6">
-        <v>72</v>
-      </c>
-      <c r="P7" s="10">
-        <v>64</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>23</v>
-      </c>
-      <c r="R7" s="13">
+      <c r="R6" s="11">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O8" s="16">
-        <v>13</v>
-      </c>
-      <c r="P8" s="17">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>11</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A8">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1442,12 +1261,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1464,22 +1283,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O8">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P8">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q8">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260707--01</t>
-  </si>
-  <si>
-    <t>20260707--02</t>
-  </si>
-  <si>
     <t>20260708--01</t>
   </si>
   <si>
@@ -85,130 +79,82 @@
     <t>20260711--01</t>
   </si>
   <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>03:59</t>
-  </si>
-  <si>
     <t>04:47</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:13</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>00:55</t>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>03:11</t>
   </si>
   <si>
     <t>02:54</t>
   </si>
   <si>
-    <t>20:19:38</t>
-  </si>
-  <si>
-    <t>21:56:56</t>
-  </si>
-  <si>
-    <t>21:10:01</t>
-  </si>
-  <si>
-    <t>20:23:04</t>
-  </si>
-  <si>
-    <t>20:26:22</t>
-  </si>
-  <si>
-    <t>20:21:54</t>
-  </si>
-  <si>
-    <t>21:59:42</t>
-  </si>
-  <si>
-    <t>21:12:34</t>
-  </si>
-  <si>
-    <t>20:25:29</t>
-  </si>
-  <si>
-    <t>20:29:22</t>
-  </si>
-  <si>
-    <t>20:24:52</t>
-  </si>
-  <si>
-    <t>22:01:41</t>
-  </si>
-  <si>
-    <t>21:14:57</t>
-  </si>
-  <si>
-    <t>20:28:08</t>
-  </si>
-  <si>
-    <t>20:30:59</t>
-  </si>
-  <si>
-    <t>20:27:51</t>
-  </si>
-  <si>
-    <t>22:03:41</t>
-  </si>
-  <si>
-    <t>21:17:21</t>
-  </si>
-  <si>
-    <t>20:30:47</t>
-  </si>
-  <si>
-    <t>20:32:35</t>
-  </si>
-  <si>
-    <t>20:30:07</t>
-  </si>
-  <si>
-    <t>22:06:26</t>
-  </si>
-  <si>
-    <t>21:19:53</t>
-  </si>
-  <si>
-    <t>20:33:11</t>
-  </si>
-  <si>
-    <t>20:35:34</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>04:46</t>
+  </si>
+  <si>
+    <t>21:10:07</t>
+  </si>
+  <si>
+    <t>20:23:14</t>
+  </si>
+  <si>
+    <t>20:26:44</t>
+  </si>
+  <si>
+    <t>21:12:39</t>
+  </si>
+  <si>
+    <t>20:25:39</t>
+  </si>
+  <si>
+    <t>20:29:45</t>
+  </si>
+  <si>
+    <t>21:15:03</t>
+  </si>
+  <si>
+    <t>20:28:18</t>
+  </si>
+  <si>
+    <t>20:31:21</t>
+  </si>
+  <si>
+    <t>21:17:26</t>
+  </si>
+  <si>
+    <t>20:30:56</t>
+  </si>
+  <si>
+    <t>20:32:56</t>
+  </si>
+  <si>
+    <t>21:19:58</t>
+  </si>
+  <si>
+    <t>20:33:21</t>
+  </si>
+  <si>
+    <t>20:35:56</t>
+  </si>
+  <si>
+    <t>18°</t>
   </si>
   <si>
     <t>13°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
-    <t>20:27:37</t>
-  </si>
-  <si>
-    <t>22:00:37</t>
-  </si>
-  <si>
-    <t>21:15:28</t>
-  </si>
-  <si>
-    <t>20:30:16</t>
-  </si>
-  <si>
-    <t>20:32:42</t>
+    <t>21:15:33</t>
+  </si>
+  <si>
+    <t>20:30:25</t>
+  </si>
+  <si>
+    <t>20:33:04</t>
   </si>
   <si>
     <t>A+B</t>
@@ -218,9 +164,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -257,7 +200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,30 +221,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -314,13 +233,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,13 +251,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -421,15 +346,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -833,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -911,54 +827,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.4</v>
+        <v>-12.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
-      </c>
-      <c r="R2" s="8">
+        <v>4</v>
+      </c>
+      <c r="R2" s="9">
         <v>100</v>
       </c>
     </row>
@@ -967,55 +883,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="9">
-        <v>88</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>81</v>
-      </c>
-      <c r="R3" s="8">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="O3" s="10">
+        <v>14</v>
+      </c>
+      <c r="P3" s="11">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>2</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1023,226 +939,114 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.4</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="6">
+        <v>72</v>
+      </c>
+      <c r="P4" s="12">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="Q4" s="13">
+        <v>10</v>
+      </c>
+      <c r="R4" s="14">
         <v>43</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-12.7</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>3</v>
-      </c>
-      <c r="R4" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="13">
-        <v>41</v>
-      </c>
-      <c r="P5" s="14">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>14</v>
-      </c>
-      <c r="R5" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="17">
-        <v>12</v>
-      </c>
-      <c r="P6" s="16">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1261,12 +1065,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1283,22 +1087,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -70,49 +70,31 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260708--01</t>
-  </si>
-  <si>
     <t>20260709--01</t>
   </si>
   <si>
     <t>20260711--01</t>
   </si>
   <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>03:11</t>
-  </si>
-  <si>
-    <t>02:54</t>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:10</t>
   </si>
   <si>
     <t>04:46</t>
   </si>
   <si>
-    <t>21:10:07</t>
-  </si>
-  <si>
     <t>20:23:14</t>
   </si>
   <si>
-    <t>20:26:44</t>
-  </si>
-  <si>
-    <t>21:12:39</t>
+    <t>20:26:45</t>
   </si>
   <si>
     <t>20:25:39</t>
   </si>
   <si>
-    <t>20:29:45</t>
-  </si>
-  <si>
-    <t>21:15:03</t>
+    <t>20:29:46</t>
   </si>
   <si>
     <t>20:28:18</t>
@@ -121,34 +103,22 @@
     <t>20:31:21</t>
   </si>
   <si>
-    <t>21:17:26</t>
-  </si>
-  <si>
-    <t>20:30:56</t>
+    <t>20:30:57</t>
   </si>
   <si>
     <t>20:32:56</t>
   </si>
   <si>
-    <t>21:19:58</t>
-  </si>
-  <si>
     <t>20:33:21</t>
   </si>
   <si>
     <t>20:35:56</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
     <t>13°</t>
   </si>
   <si>
     <t>10°</t>
-  </si>
-  <si>
-    <t>21:15:33</t>
   </si>
   <si>
     <t>20:30:25</t>
@@ -200,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,7 +185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,37 +203,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -337,15 +289,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -749,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -827,55 +770,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="L2" s="4">
-        <v>-12.7</v>
+        <v>-8.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>4</v>
-      </c>
-      <c r="R2" s="9">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -883,170 +826,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="L3" s="4">
-        <v>-8.9</v>
+        <v>-9.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="10">
-        <v>14</v>
-      </c>
-      <c r="P3" s="11">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>2</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="6">
-        <v>72</v>
-      </c>
-      <c r="P4" s="12">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>10</v>
-      </c>
-      <c r="R4" s="14">
-        <v>43</v>
+      <c r="O3" s="9">
+        <v>44</v>
+      </c>
+      <c r="P3" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>4</v>
+      </c>
+      <c r="R3" s="11">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1065,12 +952,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1087,22 +974,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -70,70 +70,34 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260709--01</t>
-  </si>
-  <si>
     <t>20260711--01</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>20:23:14</t>
-  </si>
-  <si>
-    <t>20:26:45</t>
-  </si>
-  <si>
-    <t>20:25:39</t>
-  </si>
-  <si>
-    <t>20:29:46</t>
-  </si>
-  <si>
-    <t>20:28:18</t>
-  </si>
-  <si>
-    <t>20:31:21</t>
-  </si>
-  <si>
-    <t>20:30:57</t>
-  </si>
-  <si>
-    <t>20:32:56</t>
-  </si>
-  <si>
-    <t>20:33:21</t>
-  </si>
-  <si>
-    <t>20:35:56</t>
-  </si>
-  <si>
-    <t>13°</t>
+    <t>03:11</t>
+  </si>
+  <si>
+    <t>20:26:43</t>
+  </si>
+  <si>
+    <t>20:29:44</t>
+  </si>
+  <si>
+    <t>20:31:20</t>
+  </si>
+  <si>
+    <t>20:32:55</t>
+  </si>
+  <si>
+    <t>20:35:55</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>20:30:25</t>
-  </si>
-  <si>
-    <t>20:33:04</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>20:33:02</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -170,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,37 +149,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -256,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,15 +226,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -770,170 +707,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
         <v>29</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="6">
-        <v>8</v>
-      </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>7</v>
-      </c>
-      <c r="R2" s="7">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>25</v>
+      </c>
+      <c r="R2" s="8">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="9">
-        <v>44</v>
-      </c>
-      <c r="P3" s="10">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>4</v>
-      </c>
-      <c r="R3" s="11">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -952,12 +833,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -974,22 +855,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260711--01</t>
-  </si>
-  <si>
-    <t>03:11</t>
-  </si>
-  <si>
-    <t>20:26:43</t>
-  </si>
-  <si>
-    <t>20:29:44</t>
-  </si>
-  <si>
-    <t>20:31:20</t>
-  </si>
-  <si>
-    <t>20:32:55</t>
-  </si>
-  <si>
-    <t>20:35:55</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>20:33:02</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -110,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,24 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -218,15 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -702,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6">
-        <v>29</v>
-      </c>
-      <c r="P2" s="7">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>25</v>
-      </c>
-      <c r="R2" s="8">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -833,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -855,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,42 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260811--01</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>03:11</t>
+  </si>
+  <si>
+    <t>02:13:19</t>
+  </si>
+  <si>
+    <t>02:16:05</t>
+  </si>
+  <si>
+    <t>02:18:01</t>
+  </si>
+  <si>
+    <t>02:19:57</t>
+  </si>
+  <si>
+    <t>02:22:45</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>02:16:46</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -77,7 +113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +129,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +147,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +227,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +714,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="6">
+        <v>74</v>
+      </c>
+      <c r="P2" s="7">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>48</v>
+      </c>
+      <c r="R2" s="9">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +845,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +867,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -73,37 +73,70 @@
     <t>20260811--01</t>
   </si>
   <si>
-    <t>03:52</t>
-  </si>
-  <si>
-    <t>03:11</t>
-  </si>
-  <si>
-    <t>02:13:19</t>
-  </si>
-  <si>
-    <t>02:16:05</t>
-  </si>
-  <si>
-    <t>02:18:01</t>
-  </si>
-  <si>
-    <t>02:19:57</t>
-  </si>
-  <si>
-    <t>02:22:45</t>
+    <t>20260812--01</t>
+  </si>
+  <si>
+    <t>03:54</t>
+  </si>
+  <si>
+    <t>02:11</t>
+  </si>
+  <si>
+    <t>03:13</t>
+  </si>
+  <si>
+    <t>00:27</t>
+  </si>
+  <si>
+    <t>02:13:35</t>
+  </si>
+  <si>
+    <t>01:25:12</t>
+  </si>
+  <si>
+    <t>02:16:21</t>
+  </si>
+  <si>
+    <t>01:28:32</t>
+  </si>
+  <si>
+    <t>02:18:18</t>
+  </si>
+  <si>
+    <t>01:29:37</t>
+  </si>
+  <si>
+    <t>02:20:15</t>
+  </si>
+  <si>
+    <t>01:30:43</t>
+  </si>
+  <si>
+    <t>02:23:03</t>
+  </si>
+  <si>
+    <t>01:34:04</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>02:16:46</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>02:17:02</t>
+  </si>
+  <si>
+    <t>01:30:16</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -137,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,7 +185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,7 +197,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,6 +277,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -722,111 +764,167 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L2" s="4">
         <v>-12.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="6">
+        <v>20</v>
+      </c>
+      <c r="P2" s="7">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="6">
-        <v>74</v>
-      </c>
-      <c r="P2" s="7">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>48</v>
-      </c>
-      <c r="R2" s="9">
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-17.6</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="6">
+        <v>25</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -845,12 +943,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -867,22 +965,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Datum</t>
   </si>
@@ -76,46 +76,67 @@
     <t>20260812--01</t>
   </si>
   <si>
-    <t>03:54</t>
-  </si>
-  <si>
-    <t>02:11</t>
-  </si>
-  <si>
-    <t>03:13</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
-    <t>02:13:35</t>
-  </si>
-  <si>
-    <t>01:25:12</t>
-  </si>
-  <si>
-    <t>02:16:21</t>
-  </si>
-  <si>
-    <t>01:28:32</t>
-  </si>
-  <si>
-    <t>02:18:18</t>
-  </si>
-  <si>
-    <t>01:29:37</t>
-  </si>
-  <si>
-    <t>02:20:15</t>
-  </si>
-  <si>
-    <t>01:30:43</t>
-  </si>
-  <si>
-    <t>02:23:03</t>
-  </si>
-  <si>
-    <t>01:34:04</t>
+    <t>20260813--01</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>02:13</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>00:29</t>
+  </si>
+  <si>
+    <t>03:49</t>
+  </si>
+  <si>
+    <t>02:13:47</t>
+  </si>
+  <si>
+    <t>01:25:27</t>
+  </si>
+  <si>
+    <t>02:12:39</t>
+  </si>
+  <si>
+    <t>02:16:32</t>
+  </si>
+  <si>
+    <t>01:28:47</t>
+  </si>
+  <si>
+    <t>02:15:01</t>
+  </si>
+  <si>
+    <t>02:18:30</t>
+  </si>
+  <si>
+    <t>01:29:53</t>
+  </si>
+  <si>
+    <t>02:17:44</t>
+  </si>
+  <si>
+    <t>02:20:27</t>
+  </si>
+  <si>
+    <t>01:31:00</t>
+  </si>
+  <si>
+    <t>02:23:15</t>
+  </si>
+  <si>
+    <t>01:34:21</t>
+  </si>
+  <si>
+    <t>02:22:50</t>
   </si>
   <si>
     <t>12°</t>
@@ -124,10 +145,16 @@
     <t>11°</t>
   </si>
   <si>
-    <t>02:17:02</t>
-  </si>
-  <si>
-    <t>01:30:16</t>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>02:17:13</t>
+  </si>
+  <si>
+    <t>01:30:31</t>
+  </si>
+  <si>
+    <t>02:16:38</t>
   </si>
   <si>
     <t>A+B</t>
@@ -137,6 +164,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -170,7 +200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,7 +221,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,13 +245,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +316,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -683,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -764,52 +803,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4">
         <v>-12.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="P2" s="7">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="9">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="R2" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -820,111 +859,167 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-17.5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="9">
+        <v>1</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
         <v>23</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-12.8</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="6">
         <v>31</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-17.6</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="6">
-        <v>25</v>
-      </c>
-      <c r="P3" s="8">
+      <c r="P4" s="10">
         <v>0</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q4" s="10">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>25</v>
+      <c r="R4" s="11">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -943,12 +1038,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -965,22 +1060,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>Datum</t>
   </si>
@@ -79,64 +79,112 @@
     <t>20260813--01</t>
   </si>
   <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>02:13</t>
+    <t>20260814--01</t>
+  </si>
+  <si>
+    <t>20260814--02</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>02:14</t>
   </si>
   <si>
     <t>05:26</t>
   </si>
   <si>
-    <t>03:14</t>
-  </si>
-  <si>
-    <t>00:29</t>
-  </si>
-  <si>
-    <t>03:49</t>
-  </si>
-  <si>
-    <t>02:13:47</t>
-  </si>
-  <si>
-    <t>01:25:27</t>
-  </si>
-  <si>
-    <t>02:12:39</t>
-  </si>
-  <si>
-    <t>02:16:32</t>
-  </si>
-  <si>
-    <t>01:28:47</t>
-  </si>
-  <si>
-    <t>02:15:01</t>
-  </si>
-  <si>
-    <t>02:18:30</t>
-  </si>
-  <si>
-    <t>01:29:53</t>
-  </si>
-  <si>
-    <t>02:17:44</t>
-  </si>
-  <si>
-    <t>02:20:27</t>
-  </si>
-  <si>
-    <t>01:31:00</t>
-  </si>
-  <si>
-    <t>02:23:15</t>
-  </si>
-  <si>
-    <t>01:34:21</t>
-  </si>
-  <si>
-    <t>02:22:50</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>01:37</t>
+  </si>
+  <si>
+    <t>02:13:52</t>
+  </si>
+  <si>
+    <t>01:25:34</t>
+  </si>
+  <si>
+    <t>02:12:49</t>
+  </si>
+  <si>
+    <t>01:24:14</t>
+  </si>
+  <si>
+    <t>03:00:41</t>
+  </si>
+  <si>
+    <t>02:16:37</t>
+  </si>
+  <si>
+    <t>01:28:53</t>
+  </si>
+  <si>
+    <t>02:15:11</t>
+  </si>
+  <si>
+    <t>01:26:43</t>
+  </si>
+  <si>
+    <t>03:02:55</t>
+  </si>
+  <si>
+    <t>02:18:35</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>02:17:53</t>
+  </si>
+  <si>
+    <t>01:29:11</t>
+  </si>
+  <si>
+    <t>03:05:56</t>
+  </si>
+  <si>
+    <t>02:20:33</t>
+  </si>
+  <si>
+    <t>01:31:07</t>
+  </si>
+  <si>
+    <t>02:20:37</t>
+  </si>
+  <si>
+    <t>01:31:39</t>
+  </si>
+  <si>
+    <t>03:08:58</t>
+  </si>
+  <si>
+    <t>02:23:20</t>
+  </si>
+  <si>
+    <t>01:34:28</t>
+  </si>
+  <si>
+    <t>02:23:00</t>
+  </si>
+  <si>
+    <t>01:34:09</t>
+  </si>
+  <si>
+    <t>03:11:13</t>
   </si>
   <si>
     <t>12°</t>
@@ -148,13 +196,22 @@
     <t>19°</t>
   </si>
   <si>
-    <t>02:17:13</t>
-  </si>
-  <si>
-    <t>01:30:31</t>
-  </si>
-  <si>
-    <t>02:16:38</t>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>02:17:18</t>
+  </si>
+  <si>
+    <t>01:30:37</t>
+  </si>
+  <si>
+    <t>02:16:47</t>
+  </si>
+  <si>
+    <t>01:30:02</t>
   </si>
   <si>
     <t>A+B</t>
@@ -200,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,19 +272,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,12 +297,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -316,9 +367,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -722,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -803,52 +851,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L2" s="4">
         <v>-12.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O2" s="6">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="P2" s="7">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="Q2" s="8">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="R2" s="8">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -859,43 +907,43 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L3" s="4">
         <v>-17.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="O3" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="10">
         <v>0</v>
@@ -904,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -915,43 +963,43 @@
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="L4" s="4">
         <v>-12.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="6">
-        <v>31</v>
+        <v>69</v>
+      </c>
+      <c r="O4" s="9">
+        <v>2</v>
       </c>
       <c r="P4" s="10">
         <v>0</v>
@@ -959,67 +1007,179 @@
       <c r="Q4" s="10">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-18.1</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="9">
+        <v>1</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-7.2</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="9">
+        <v>2</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1038,12 +1198,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1060,22 +1220,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
   <si>
     <t>Datum</t>
   </si>
@@ -85,19 +85,37 @@
     <t>20260814--02</t>
   </si>
   <si>
+    <t>20260815--01</t>
+  </si>
+  <si>
+    <t>20260815--02</t>
+  </si>
+  <si>
+    <t>20260815--03</t>
+  </si>
+  <si>
     <t>03:56</t>
   </si>
   <si>
     <t>02:14</t>
   </si>
   <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:03</t>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>04:09</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>03:15</t>
@@ -109,82 +127,133 @@
     <t>03:50</t>
   </si>
   <si>
-    <t>01:37</t>
-  </si>
-  <si>
-    <t>02:13:52</t>
-  </si>
-  <si>
-    <t>01:25:34</t>
-  </si>
-  <si>
-    <t>02:12:49</t>
-  </si>
-  <si>
-    <t>01:24:14</t>
-  </si>
-  <si>
-    <t>03:00:41</t>
-  </si>
-  <si>
-    <t>02:16:37</t>
-  </si>
-  <si>
-    <t>01:28:53</t>
-  </si>
-  <si>
-    <t>02:15:11</t>
-  </si>
-  <si>
-    <t>01:26:43</t>
-  </si>
-  <si>
-    <t>03:02:55</t>
-  </si>
-  <si>
-    <t>02:18:35</t>
-  </si>
-  <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
-    <t>02:17:53</t>
-  </si>
-  <si>
-    <t>01:29:11</t>
-  </si>
-  <si>
-    <t>03:05:56</t>
-  </si>
-  <si>
-    <t>02:20:33</t>
-  </si>
-  <si>
-    <t>01:31:07</t>
-  </si>
-  <si>
-    <t>02:20:37</t>
-  </si>
-  <si>
-    <t>01:31:39</t>
-  </si>
-  <si>
-    <t>03:08:58</t>
-  </si>
-  <si>
-    <t>02:23:20</t>
-  </si>
-  <si>
-    <t>01:34:28</t>
-  </si>
-  <si>
-    <t>02:23:00</t>
-  </si>
-  <si>
-    <t>01:34:09</t>
-  </si>
-  <si>
-    <t>03:11:13</t>
+    <t>01:38</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>02:13:53</t>
+  </si>
+  <si>
+    <t>01:25:36</t>
+  </si>
+  <si>
+    <t>02:12:52</t>
+  </si>
+  <si>
+    <t>01:24:17</t>
+  </si>
+  <si>
+    <t>03:00:45</t>
+  </si>
+  <si>
+    <t>00:35:46</t>
+  </si>
+  <si>
+    <t>02:11:59</t>
+  </si>
+  <si>
+    <t>23:47:18</t>
+  </si>
+  <si>
+    <t>02:16:38</t>
+  </si>
+  <si>
+    <t>01:28:55</t>
+  </si>
+  <si>
+    <t>02:15:13</t>
+  </si>
+  <si>
+    <t>01:26:46</t>
+  </si>
+  <si>
+    <t>03:02:59</t>
+  </si>
+  <si>
+    <t>00:38:27</t>
+  </si>
+  <si>
+    <t>02:14:14</t>
+  </si>
+  <si>
+    <t>23:50:25</t>
+  </si>
+  <si>
+    <t>02:18:36</t>
+  </si>
+  <si>
+    <t>01:30:02</t>
+  </si>
+  <si>
+    <t>02:17:56</t>
+  </si>
+  <si>
+    <t>01:29:14</t>
+  </si>
+  <si>
+    <t>03:06:00</t>
+  </si>
+  <si>
+    <t>00:40:31</t>
+  </si>
+  <si>
+    <t>02:17:12</t>
+  </si>
+  <si>
+    <t>23:51:48</t>
+  </si>
+  <si>
+    <t>02:20:34</t>
+  </si>
+  <si>
+    <t>01:31:09</t>
+  </si>
+  <si>
+    <t>02:20:40</t>
+  </si>
+  <si>
+    <t>01:31:43</t>
+  </si>
+  <si>
+    <t>03:09:01</t>
+  </si>
+  <si>
+    <t>00:42:36</t>
+  </si>
+  <si>
+    <t>02:20:12</t>
+  </si>
+  <si>
+    <t>23:53:11</t>
+  </si>
+  <si>
+    <t>02:23:21</t>
+  </si>
+  <si>
+    <t>01:34:30</t>
+  </si>
+  <si>
+    <t>02:23:03</t>
+  </si>
+  <si>
+    <t>01:34:13</t>
+  </si>
+  <si>
+    <t>03:11:16</t>
+  </si>
+  <si>
+    <t>00:45:19</t>
+  </si>
+  <si>
+    <t>02:22:27</t>
+  </si>
+  <si>
+    <t>23:56:19</t>
   </si>
   <si>
     <t>12°</t>
@@ -202,21 +271,45 @@
     <t>10°</t>
   </si>
   <si>
-    <t>02:17:18</t>
-  </si>
-  <si>
-    <t>01:30:37</t>
-  </si>
-  <si>
-    <t>02:16:47</t>
-  </si>
-  <si>
-    <t>01:30:02</t>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>02:17:19</t>
+  </si>
+  <si>
+    <t>01:30:39</t>
+  </si>
+  <si>
+    <t>02:16:50</t>
+  </si>
+  <si>
+    <t>01:30:05</t>
+  </si>
+  <si>
+    <t>03:02:58</t>
+  </si>
+  <si>
+    <t>00:43:20</t>
+  </si>
+  <si>
+    <t>02:16:13</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -224,6 +317,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -257,7 +353,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,13 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,7 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -367,6 +493,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -770,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -851,52 +992,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="L2" s="4">
         <v>-12.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="O2" s="6">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="P2" s="7">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="8">
-        <v>35</v>
-      </c>
-      <c r="R2" s="8">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="R2" s="9">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -907,52 +1048,52 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="L3" s="4">
         <v>-17.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="9">
+        <v>99</v>
+      </c>
+      <c r="O3" s="10">
+        <v>2</v>
+      </c>
+      <c r="P3" s="8">
         <v>0</v>
       </c>
-      <c r="P3" s="10">
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>0</v>
+      <c r="R3" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -963,51 +1104,51 @@
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="L4" s="4">
         <v>-12.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="9">
-        <v>2</v>
-      </c>
-      <c r="P4" s="10">
+        <v>100</v>
+      </c>
+      <c r="O4" s="10">
+        <v>3</v>
+      </c>
+      <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="8">
         <v>2</v>
       </c>
     </row>
@@ -1019,52 +1160,52 @@
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="L5" s="4">
         <v>-18.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="9">
-        <v>1</v>
-      </c>
-      <c r="P5" s="10">
+        <v>100</v>
+      </c>
+      <c r="O5" s="11">
+        <v>28</v>
+      </c>
+      <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="10">
-        <v>1</v>
+      <c r="R5" s="12">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1075,111 +1216,279 @@
         <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L6" s="4">
         <v>-7.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" s="6">
+        <v>60</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="9">
-        <v>2</v>
-      </c>
-      <c r="P6" s="10">
+      <c r="I7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-22.2</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="10">
+        <v>4</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q7" s="14">
+        <v>3</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="10">
-        <v>2</v>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-13.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="10">
+        <v>4</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>3</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-24.9</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" s="11">
+        <v>23</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>6</v>
+      </c>
+      <c r="R9" s="15">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1198,12 +1507,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1220,22 +1529,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
   <si>
     <t>Datum</t>
   </si>
@@ -94,7 +94,22 @@
     <t>20260815--03</t>
   </si>
   <si>
-    <t>03:56</t>
+    <t>20260816--01</t>
+  </si>
+  <si>
+    <t>20260816--02</t>
+  </si>
+  <si>
+    <t>20260817--01</t>
+  </si>
+  <si>
+    <t>20260817--02</t>
+  </si>
+  <si>
+    <t>20260817--03</t>
+  </si>
+  <si>
+    <t>03:55</t>
   </si>
   <si>
     <t>02:14</t>
@@ -115,7 +130,22 @@
     <t>05:58</t>
   </si>
   <si>
-    <t>02:46</t>
+    <t>02:44</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>05:03</t>
   </si>
   <si>
     <t>03:15</t>
@@ -127,133 +157,217 @@
     <t>03:50</t>
   </si>
   <si>
-    <t>01:38</t>
+    <t>01:37</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:59</t>
-  </si>
-  <si>
-    <t>02:13:53</t>
-  </si>
-  <si>
-    <t>01:25:36</t>
-  </si>
-  <si>
-    <t>02:12:52</t>
-  </si>
-  <si>
-    <t>01:24:17</t>
-  </si>
-  <si>
-    <t>03:00:45</t>
-  </si>
-  <si>
-    <t>00:35:46</t>
-  </si>
-  <si>
-    <t>02:11:59</t>
-  </si>
-  <si>
-    <t>23:47:18</t>
-  </si>
-  <si>
-    <t>02:16:38</t>
-  </si>
-  <si>
-    <t>01:28:55</t>
-  </si>
-  <si>
-    <t>02:15:13</t>
-  </si>
-  <si>
-    <t>01:26:46</t>
-  </si>
-  <si>
-    <t>03:02:59</t>
-  </si>
-  <si>
-    <t>00:38:27</t>
-  </si>
-  <si>
-    <t>02:14:14</t>
-  </si>
-  <si>
-    <t>23:50:25</t>
-  </si>
-  <si>
-    <t>02:18:36</t>
-  </si>
-  <si>
-    <t>01:30:02</t>
-  </si>
-  <si>
-    <t>02:17:56</t>
-  </si>
-  <si>
-    <t>01:29:14</t>
-  </si>
-  <si>
-    <t>03:06:00</t>
-  </si>
-  <si>
-    <t>00:40:31</t>
-  </si>
-  <si>
-    <t>02:17:12</t>
-  </si>
-  <si>
-    <t>23:51:48</t>
-  </si>
-  <si>
-    <t>02:20:34</t>
-  </si>
-  <si>
-    <t>01:31:09</t>
-  </si>
-  <si>
-    <t>02:20:40</t>
-  </si>
-  <si>
-    <t>01:31:43</t>
-  </si>
-  <si>
-    <t>03:09:01</t>
-  </si>
-  <si>
-    <t>00:42:36</t>
-  </si>
-  <si>
-    <t>02:20:12</t>
-  </si>
-  <si>
-    <t>23:53:11</t>
-  </si>
-  <si>
-    <t>02:23:21</t>
-  </si>
-  <si>
-    <t>01:34:30</t>
-  </si>
-  <si>
-    <t>02:23:03</t>
-  </si>
-  <si>
-    <t>01:34:13</t>
-  </si>
-  <si>
-    <t>03:11:16</t>
-  </si>
-  <si>
-    <t>00:45:19</t>
-  </si>
-  <si>
-    <t>02:22:27</t>
-  </si>
-  <si>
-    <t>23:56:19</t>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>02:13:50</t>
+  </si>
+  <si>
+    <t>01:25:31</t>
+  </si>
+  <si>
+    <t>02:12:44</t>
+  </si>
+  <si>
+    <t>01:24:08</t>
+  </si>
+  <si>
+    <t>03:00:35</t>
+  </si>
+  <si>
+    <t>00:35:33</t>
+  </si>
+  <si>
+    <t>02:11:47</t>
+  </si>
+  <si>
+    <t>23:47:03</t>
+  </si>
+  <si>
+    <t>01:22:58</t>
+  </si>
+  <si>
+    <t>02:59:44</t>
+  </si>
+  <si>
+    <t>00:34:09</t>
+  </si>
+  <si>
+    <t>02:10:48</t>
+  </si>
+  <si>
+    <t>23:45:22</t>
+  </si>
+  <si>
+    <t>02:16:36</t>
+  </si>
+  <si>
+    <t>01:28:50</t>
+  </si>
+  <si>
+    <t>02:15:06</t>
+  </si>
+  <si>
+    <t>01:26:36</t>
+  </si>
+  <si>
+    <t>03:02:49</t>
+  </si>
+  <si>
+    <t>00:38:14</t>
+  </si>
+  <si>
+    <t>02:14:01</t>
+  </si>
+  <si>
+    <t>23:50:10</t>
+  </si>
+  <si>
+    <t>01:25:15</t>
+  </si>
+  <si>
+    <t>03:02:00</t>
+  </si>
+  <si>
+    <t>00:36:30</t>
+  </si>
+  <si>
+    <t>02:13:02</t>
+  </si>
+  <si>
+    <t>23:47:48</t>
+  </si>
+  <si>
+    <t>02:18:33</t>
+  </si>
+  <si>
+    <t>01:29:57</t>
+  </si>
+  <si>
+    <t>02:17:49</t>
+  </si>
+  <si>
+    <t>01:29:04</t>
+  </si>
+  <si>
+    <t>03:05:50</t>
+  </si>
+  <si>
+    <t>00:40:19</t>
+  </si>
+  <si>
+    <t>02:16:59</t>
+  </si>
+  <si>
+    <t>23:51:32</t>
+  </si>
+  <si>
+    <t>01:28:08</t>
+  </si>
+  <si>
+    <t>03:04:57</t>
+  </si>
+  <si>
+    <t>00:39:14</t>
+  </si>
+  <si>
+    <t>02:16:02</t>
+  </si>
+  <si>
+    <t>23:50:19</t>
+  </si>
+  <si>
+    <t>02:20:31</t>
+  </si>
+  <si>
+    <t>01:31:04</t>
+  </si>
+  <si>
+    <t>02:20:33</t>
+  </si>
+  <si>
+    <t>01:31:33</t>
+  </si>
+  <si>
+    <t>03:08:51</t>
+  </si>
+  <si>
+    <t>00:42:23</t>
+  </si>
+  <si>
+    <t>02:19:59</t>
+  </si>
+  <si>
+    <t>23:52:54</t>
+  </si>
+  <si>
+    <t>01:31:02</t>
+  </si>
+  <si>
+    <t>03:07:55</t>
+  </si>
+  <si>
+    <t>00:41:59</t>
+  </si>
+  <si>
+    <t>02:19:03</t>
+  </si>
+  <si>
+    <t>23:52:51</t>
+  </si>
+  <si>
+    <t>02:23:18</t>
+  </si>
+  <si>
+    <t>01:34:25</t>
+  </si>
+  <si>
+    <t>02:22:56</t>
+  </si>
+  <si>
+    <t>01:34:03</t>
+  </si>
+  <si>
+    <t>03:11:06</t>
+  </si>
+  <si>
+    <t>00:45:06</t>
+  </si>
+  <si>
+    <t>02:22:15</t>
+  </si>
+  <si>
+    <t>23:56:03</t>
+  </si>
+  <si>
+    <t>01:33:19</t>
+  </si>
+  <si>
+    <t>03:10:11</t>
+  </si>
+  <si>
+    <t>00:44:21</t>
+  </si>
+  <si>
+    <t>02:21:17</t>
+  </si>
+  <si>
+    <t>23:55:18</t>
   </si>
   <si>
     <t>12°</t>
@@ -280,33 +394,48 @@
     <t>0°</t>
   </si>
   <si>
-    <t>02:17:19</t>
-  </si>
-  <si>
-    <t>01:30:39</t>
-  </si>
-  <si>
-    <t>02:16:50</t>
-  </si>
-  <si>
-    <t>01:30:05</t>
-  </si>
-  <si>
-    <t>03:02:58</t>
-  </si>
-  <si>
-    <t>00:43:20</t>
-  </si>
-  <si>
-    <t>02:16:13</t>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>02:17:16</t>
+  </si>
+  <si>
+    <t>01:30:34</t>
+  </si>
+  <si>
+    <t>02:16:43</t>
+  </si>
+  <si>
+    <t>01:29:56</t>
+  </si>
+  <si>
+    <t>00:43:08</t>
+  </si>
+  <si>
+    <t>02:16:01</t>
+  </si>
+  <si>
+    <t>01:29:13</t>
+  </si>
+  <si>
+    <t>03:02:06</t>
+  </si>
+  <si>
+    <t>00:42:28</t>
+  </si>
+  <si>
+    <t>02:15:21</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -317,9 +446,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -353,7 +479,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +530,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -508,6 +664,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -911,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -992,52 +1163,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="L2" s="4">
         <v>-12.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="O2" s="6">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="P2" s="7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="R2" s="9">
-        <v>99</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1048,51 +1219,51 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="L3" s="4">
         <v>-17.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="O3" s="10">
         <v>2</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="7">
         <v>2</v>
       </c>
     </row>
@@ -1104,52 +1275,52 @@
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="L4" s="4">
         <v>-12.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="O4" s="10">
-        <v>3</v>
-      </c>
-      <c r="P4" s="8">
+        <v>5</v>
+      </c>
+      <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>2</v>
+      <c r="R4" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1160,52 +1331,52 @@
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="L5" s="4">
         <v>-18.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O5" s="11">
-        <v>28</v>
-      </c>
-      <c r="P5" s="8">
+        <v>143</v>
+      </c>
+      <c r="O5" s="10">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="12">
-        <v>28</v>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1216,52 +1387,52 @@
         <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
         <v>-7.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O6" s="6">
-        <v>60</v>
-      </c>
-      <c r="P6" s="8">
+        <v>143</v>
+      </c>
+      <c r="O6" s="10">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
-        <v>60</v>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1272,52 +1443,52 @@
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="L7" s="4">
         <v>-22.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="O7" s="10">
-        <v>4</v>
-      </c>
-      <c r="P7" s="8">
+        <v>5</v>
+      </c>
+      <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="14">
-        <v>3</v>
-      </c>
-      <c r="R7" s="8">
+      <c r="Q7" s="7">
         <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1328,52 +1499,52 @@
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="L8" s="4">
         <v>-13.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="O8" s="10">
-        <v>4</v>
-      </c>
-      <c r="P8" s="8">
+        <v>2</v>
+      </c>
+      <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="14">
-        <v>3</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="Q8" s="7">
         <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1384,111 +1555,391 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4">
         <v>-24.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O9" s="12">
+        <v>55</v>
+      </c>
+      <c r="P9" s="13">
+        <v>16</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>14</v>
+      </c>
+      <c r="R9" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-18.8</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O10" s="6">
+        <v>33</v>
+      </c>
+      <c r="P10" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+      <c r="R10" s="13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-7.8</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O11" s="6">
+        <v>26</v>
+      </c>
+      <c r="P11" s="15">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>2</v>
+      </c>
+      <c r="R11" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-22.9</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="12">
         <v>99</v>
       </c>
-      <c r="O9" s="11">
-        <v>23</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="14">
-        <v>6</v>
-      </c>
-      <c r="R9" s="15">
-        <v>11</v>
+      <c r="P12" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>74</v>
+      </c>
+      <c r="R12" s="17">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-14</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="12">
+        <v>99</v>
+      </c>
+      <c r="P13" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>71</v>
+      </c>
+      <c r="R13" s="19">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-25.6</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" s="12">
+        <v>100</v>
+      </c>
+      <c r="P14" s="16">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>77</v>
+      </c>
+      <c r="R14" s="20">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1507,12 +1958,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1529,22 +1980,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="163">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260811--01</t>
-  </si>
-  <si>
     <t>20260812--01</t>
   </si>
   <si>
@@ -109,13 +106,19 @@
     <t>20260817--03</t>
   </si>
   <si>
-    <t>03:55</t>
+    <t>20260818--01</t>
+  </si>
+  <si>
+    <t>20260818--02</t>
+  </si>
+  <si>
+    <t>20260818--03</t>
   </si>
   <si>
     <t>02:14</t>
   </si>
   <si>
-    <t>05:27</t>
+    <t>05:26</t>
   </si>
   <si>
     <t>04:57</t>
@@ -130,13 +133,13 @@
     <t>05:58</t>
   </si>
   <si>
-    <t>02:44</t>
+    <t>02:46</t>
   </si>
   <si>
     <t>05:47</t>
   </si>
   <si>
-    <t>05:55</t>
+    <t>05:56</t>
   </si>
   <si>
     <t>05:29</t>
@@ -148,7 +151,10 @@
     <t>05:03</t>
   </si>
   <si>
-    <t>03:15</t>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>04:21</t>
   </si>
   <si>
     <t>00:30</t>
@@ -157,295 +163,346 @@
     <t>03:50</t>
   </si>
   <si>
-    <t>01:37</t>
+    <t>01:38</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:58</t>
+    <t>03:59</t>
   </si>
   <si>
     <t>01:49</t>
   </si>
   <si>
-    <t>05:49</t>
+    <t>05:50</t>
   </si>
   <si>
     <t>03:42</t>
   </si>
   <si>
-    <t>02:13:50</t>
-  </si>
-  <si>
-    <t>01:25:31</t>
-  </si>
-  <si>
-    <t>02:12:44</t>
-  </si>
-  <si>
-    <t>01:24:08</t>
-  </si>
-  <si>
-    <t>03:00:35</t>
-  </si>
-  <si>
-    <t>00:35:33</t>
-  </si>
-  <si>
-    <t>02:11:47</t>
-  </si>
-  <si>
-    <t>23:47:03</t>
-  </si>
-  <si>
-    <t>01:22:58</t>
-  </si>
-  <si>
-    <t>02:59:44</t>
-  </si>
-  <si>
-    <t>00:34:09</t>
-  </si>
-  <si>
-    <t>02:10:48</t>
-  </si>
-  <si>
-    <t>23:45:22</t>
-  </si>
-  <si>
-    <t>02:16:36</t>
-  </si>
-  <si>
-    <t>01:28:50</t>
-  </si>
-  <si>
-    <t>02:15:06</t>
-  </si>
-  <si>
-    <t>01:26:36</t>
-  </si>
-  <si>
-    <t>03:02:49</t>
-  </si>
-  <si>
-    <t>00:38:14</t>
-  </si>
-  <si>
-    <t>02:14:01</t>
-  </si>
-  <si>
-    <t>23:50:10</t>
-  </si>
-  <si>
-    <t>01:25:15</t>
-  </si>
-  <si>
-    <t>03:02:00</t>
-  </si>
-  <si>
-    <t>00:36:30</t>
-  </si>
-  <si>
-    <t>02:13:02</t>
-  </si>
-  <si>
-    <t>23:47:48</t>
-  </si>
-  <si>
-    <t>02:18:33</t>
-  </si>
-  <si>
-    <t>01:29:57</t>
-  </si>
-  <si>
-    <t>02:17:49</t>
-  </si>
-  <si>
-    <t>01:29:04</t>
-  </si>
-  <si>
-    <t>03:05:50</t>
-  </si>
-  <si>
-    <t>00:40:19</t>
-  </si>
-  <si>
-    <t>02:16:59</t>
-  </si>
-  <si>
-    <t>23:51:32</t>
-  </si>
-  <si>
-    <t>01:28:08</t>
-  </si>
-  <si>
-    <t>03:04:57</t>
-  </si>
-  <si>
-    <t>00:39:14</t>
-  </si>
-  <si>
-    <t>02:16:02</t>
-  </si>
-  <si>
-    <t>23:50:19</t>
-  </si>
-  <si>
-    <t>02:20:31</t>
-  </si>
-  <si>
-    <t>01:31:04</t>
-  </si>
-  <si>
-    <t>02:20:33</t>
-  </si>
-  <si>
-    <t>01:31:33</t>
-  </si>
-  <si>
-    <t>03:08:51</t>
-  </si>
-  <si>
-    <t>00:42:23</t>
-  </si>
-  <si>
-    <t>02:19:59</t>
-  </si>
-  <si>
-    <t>23:52:54</t>
-  </si>
-  <si>
-    <t>01:31:02</t>
-  </si>
-  <si>
-    <t>03:07:55</t>
-  </si>
-  <si>
-    <t>00:41:59</t>
-  </si>
-  <si>
-    <t>02:19:03</t>
-  </si>
-  <si>
-    <t>23:52:51</t>
-  </si>
-  <si>
-    <t>02:23:18</t>
-  </si>
-  <si>
-    <t>01:34:25</t>
-  </si>
-  <si>
-    <t>02:22:56</t>
-  </si>
-  <si>
-    <t>01:34:03</t>
-  </si>
-  <si>
-    <t>03:11:06</t>
-  </si>
-  <si>
-    <t>00:45:06</t>
-  </si>
-  <si>
-    <t>02:22:15</t>
-  </si>
-  <si>
-    <t>23:56:03</t>
-  </si>
-  <si>
-    <t>01:33:19</t>
-  </si>
-  <si>
-    <t>03:10:11</t>
-  </si>
-  <si>
-    <t>00:44:21</t>
-  </si>
-  <si>
-    <t>02:21:17</t>
-  </si>
-  <si>
-    <t>23:55:18</t>
+    <t>01:26</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>01:25:32</t>
+  </si>
+  <si>
+    <t>02:12:47</t>
+  </si>
+  <si>
+    <t>01:24:13</t>
+  </si>
+  <si>
+    <t>03:00:40</t>
+  </si>
+  <si>
+    <t>00:35:41</t>
+  </si>
+  <si>
+    <t>02:11:54</t>
+  </si>
+  <si>
+    <t>23:47:13</t>
+  </si>
+  <si>
+    <t>01:23:09</t>
+  </si>
+  <si>
+    <t>02:59:55</t>
+  </si>
+  <si>
+    <t>00:34:24</t>
+  </si>
+  <si>
+    <t>02:11:03</t>
+  </si>
+  <si>
+    <t>23:45:41</t>
+  </si>
+  <si>
+    <t>01:22:10</t>
+  </si>
+  <si>
+    <t>02:59:08</t>
+  </si>
+  <si>
+    <t>22:57:00</t>
+  </si>
+  <si>
+    <t>01:28:51</t>
+  </si>
+  <si>
+    <t>02:15:09</t>
+  </si>
+  <si>
+    <t>01:26:41</t>
+  </si>
+  <si>
+    <t>03:02:54</t>
+  </si>
+  <si>
+    <t>00:38:22</t>
+  </si>
+  <si>
+    <t>02:14:09</t>
+  </si>
+  <si>
+    <t>23:50:20</t>
+  </si>
+  <si>
+    <t>01:25:26</t>
+  </si>
+  <si>
+    <t>03:02:11</t>
+  </si>
+  <si>
+    <t>00:36:45</t>
+  </si>
+  <si>
+    <t>02:13:17</t>
+  </si>
+  <si>
+    <t>23:48:07</t>
+  </si>
+  <si>
+    <t>01:24:24</t>
+  </si>
+  <si>
+    <t>03:01:32</t>
+  </si>
+  <si>
+    <t>22:59:37</t>
+  </si>
+  <si>
+    <t>01:29:58</t>
+  </si>
+  <si>
+    <t>02:17:52</t>
+  </si>
+  <si>
+    <t>01:29:09</t>
+  </si>
+  <si>
+    <t>03:05:55</t>
+  </si>
+  <si>
+    <t>00:40:26</t>
+  </si>
+  <si>
+    <t>02:17:07</t>
+  </si>
+  <si>
+    <t>23:51:43</t>
+  </si>
+  <si>
+    <t>01:28:19</t>
+  </si>
+  <si>
+    <t>03:05:08</t>
+  </si>
+  <si>
+    <t>00:39:29</t>
+  </si>
+  <si>
+    <t>02:16:17</t>
+  </si>
+  <si>
+    <t>23:50:38</t>
+  </si>
+  <si>
+    <t>01:27:24</t>
+  </si>
+  <si>
+    <t>03:04:11</t>
+  </si>
+  <si>
+    <t>23:01:47</t>
+  </si>
+  <si>
+    <t>01:31:05</t>
+  </si>
+  <si>
+    <t>02:20:35</t>
+  </si>
+  <si>
+    <t>01:31:38</t>
+  </si>
+  <si>
+    <t>03:08:56</t>
+  </si>
+  <si>
+    <t>00:42:31</t>
+  </si>
+  <si>
+    <t>02:20:07</t>
+  </si>
+  <si>
+    <t>23:53:06</t>
+  </si>
+  <si>
+    <t>01:31:13</t>
+  </si>
+  <si>
+    <t>03:08:07</t>
+  </si>
+  <si>
+    <t>00:42:14</t>
+  </si>
+  <si>
+    <t>02:19:18</t>
+  </si>
+  <si>
+    <t>23:53:10</t>
+  </si>
+  <si>
+    <t>01:30:25</t>
+  </si>
+  <si>
+    <t>03:06:51</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>01:34:26</t>
+  </si>
+  <si>
+    <t>02:22:58</t>
+  </si>
+  <si>
+    <t>01:34:08</t>
+  </si>
+  <si>
+    <t>03:11:11</t>
+  </si>
+  <si>
+    <t>00:45:14</t>
+  </si>
+  <si>
+    <t>02:22:23</t>
+  </si>
+  <si>
+    <t>23:56:14</t>
+  </si>
+  <si>
+    <t>01:33:31</t>
+  </si>
+  <si>
+    <t>03:10:23</t>
+  </si>
+  <si>
+    <t>00:44:36</t>
+  </si>
+  <si>
+    <t>02:21:33</t>
+  </si>
+  <si>
+    <t>23:55:38</t>
+  </si>
+  <si>
+    <t>01:32:40</t>
+  </si>
+  <si>
+    <t>03:09:15</t>
+  </si>
+  <si>
+    <t>23:06:36</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>20°</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>02:17:16</t>
-  </si>
-  <si>
-    <t>01:30:34</t>
-  </si>
-  <si>
-    <t>02:16:43</t>
-  </si>
-  <si>
-    <t>01:29:56</t>
-  </si>
-  <si>
-    <t>00:43:08</t>
-  </si>
-  <si>
-    <t>02:16:01</t>
-  </si>
-  <si>
-    <t>01:29:13</t>
-  </si>
-  <si>
-    <t>03:02:06</t>
-  </si>
-  <si>
-    <t>00:42:28</t>
-  </si>
-  <si>
-    <t>02:15:21</t>
+    <t>01:30:35</t>
+  </si>
+  <si>
+    <t>02:16:45</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>03:02:53</t>
+  </si>
+  <si>
+    <t>00:43:15</t>
+  </si>
+  <si>
+    <t>02:16:08</t>
+  </si>
+  <si>
+    <t>01:29:24</t>
+  </si>
+  <si>
+    <t>03:02:17</t>
+  </si>
+  <si>
+    <t>00:42:42</t>
+  </si>
+  <si>
+    <t>02:15:36</t>
+  </si>
+  <si>
+    <t>01:28:59</t>
+  </si>
+  <si>
+    <t>03:01:53</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -479,7 +536,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,7 +551,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +563,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,49 +641,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,12 +654,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,6 +754,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1160,55 +1244,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.3</v>
+        <v>-17.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="O2" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>32</v>
-      </c>
-      <c r="R2" s="9">
-        <v>23</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1216,45 +1300,45 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="L3" s="4">
-        <v>-17.5</v>
+        <v>-12.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O3" s="10">
+        <v>160</v>
+      </c>
+      <c r="O3" s="6">
         <v>2</v>
       </c>
       <c r="P3" s="7">
@@ -1272,46 +1356,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="L4" s="4">
-        <v>-12.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O4" s="10">
-        <v>5</v>
+        <v>160</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1319,8 +1403,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="11">
-        <v>4</v>
+      <c r="R4" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1328,45 +1412,45 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="L5" s="4">
-        <v>-18.1</v>
+        <v>-7.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O5" s="10">
+        <v>161</v>
+      </c>
+      <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="7">
@@ -1384,46 +1468,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="L6" s="4">
-        <v>-7.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="O6" s="6">
+        <v>2</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1432,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1440,46 +1524,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.2</v>
+        <v>-13.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O7" s="10">
-        <v>5</v>
+        <v>160</v>
+      </c>
+      <c r="O7" s="6">
+        <v>8</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1487,8 +1571,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>2</v>
+      <c r="R7" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1496,55 +1580,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="L8" s="4">
-        <v>-13.4</v>
+        <v>-24.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O8" s="10">
-        <v>2</v>
+        <v>159</v>
+      </c>
+      <c r="O8" s="9">
+        <v>48</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>2</v>
+      <c r="Q8" s="10">
+        <v>36</v>
+      </c>
+      <c r="R8" s="11">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1552,55 +1636,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-18.8</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O9" s="9">
+        <v>52</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>52</v>
+      </c>
+      <c r="R9" s="8">
         <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-24.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="12">
-        <v>55</v>
-      </c>
-      <c r="P9" s="13">
-        <v>16</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>14</v>
-      </c>
-      <c r="R9" s="14">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1608,55 +1692,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L10" s="4">
-        <v>-18.8</v>
+        <v>-7.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O10" s="6">
-        <v>33</v>
-      </c>
-      <c r="P10" s="13">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="13">
-        <v>14</v>
+        <v>160</v>
+      </c>
+      <c r="O10" s="13">
+        <v>37</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>37</v>
+      </c>
+      <c r="R10" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1664,55 +1748,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="L11" s="4">
-        <v>-7.8</v>
+        <v>-22.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O11" s="6">
-        <v>26</v>
+        <v>162</v>
+      </c>
+      <c r="O11" s="9">
+        <v>100</v>
       </c>
       <c r="P11" s="15">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>2</v>
-      </c>
-      <c r="R11" s="15">
-        <v>11</v>
+        <v>65</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>33</v>
+      </c>
+      <c r="R11" s="16">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1720,55 +1804,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="L12" s="4">
-        <v>-22.9</v>
+        <v>-14</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O12" s="12">
-        <v>99</v>
-      </c>
-      <c r="P12" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>74</v>
-      </c>
-      <c r="R12" s="17">
-        <v>83</v>
+        <v>160</v>
+      </c>
+      <c r="O12" s="9">
+        <v>98</v>
+      </c>
+      <c r="P12" s="17">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>13</v>
+      </c>
+      <c r="R12" s="19">
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1776,55 +1860,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="L13" s="4">
-        <v>-14</v>
+        <v>-25.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="12">
-        <v>99</v>
-      </c>
-      <c r="P13" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>71</v>
-      </c>
-      <c r="R13" s="19">
-        <v>81</v>
+        <v>162</v>
+      </c>
+      <c r="O13" s="13">
+        <v>27</v>
+      </c>
+      <c r="P13" s="20">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>7</v>
+      </c>
+      <c r="R13" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1832,114 +1916,226 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="L14" s="4">
-        <v>-25.6</v>
+        <v>-19.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O14" s="12">
+        <v>160</v>
+      </c>
+      <c r="O14" s="13">
+        <v>29</v>
+      </c>
+      <c r="P14" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="21">
+        <v>20</v>
+      </c>
+      <c r="R14" s="18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>22</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="P14" s="16">
-        <v>75</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>77</v>
-      </c>
-      <c r="R14" s="20">
-        <v>100</v>
+      <c r="H15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O15" s="9">
+        <v>76</v>
+      </c>
+      <c r="P15" s="8">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>30</v>
+      </c>
+      <c r="R15" s="22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-26.5</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="9">
+        <v>94</v>
+      </c>
+      <c r="P16" s="16">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>29</v>
+      </c>
+      <c r="R16" s="23">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1958,12 +2154,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1980,22 +2176,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="181">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260812--01</t>
-  </si>
-  <si>
     <t>20260813--01</t>
   </si>
   <si>
@@ -115,25 +112,34 @@
     <t>20260818--03</t>
   </si>
   <si>
-    <t>02:14</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:02</t>
+    <t>20260819--01</t>
+  </si>
+  <si>
+    <t>20260819--02</t>
+  </si>
+  <si>
+    <t>20260819--03</t>
+  </si>
+  <si>
+    <t>20260819--04</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:03</t>
   </si>
   <si>
     <t>04:09</t>
   </si>
   <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>02:46</t>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>02:45</t>
   </si>
   <si>
     <t>05:47</t>
@@ -142,7 +148,7 @@
     <t>05:56</t>
   </si>
   <si>
-    <t>05:29</t>
+    <t>05:30</t>
   </si>
   <si>
     <t>06:01</t>
@@ -157,19 +163,22 @@
     <t>04:21</t>
   </si>
   <si>
-    <t>00:30</t>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:08</t>
   </si>
   <si>
     <t>03:50</t>
   </si>
   <si>
-    <t>01:38</t>
+    <t>01:37</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:59</t>
+    <t>03:58</t>
   </si>
   <si>
     <t>01:49</t>
@@ -178,7 +187,7 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>03:42</t>
+    <t>03:43</t>
   </si>
   <si>
     <t>01:26</t>
@@ -187,255 +196,303 @@
     <t>04:58</t>
   </si>
   <si>
-    <t>01:25:32</t>
+    <t>02:43</t>
   </si>
   <si>
     <t>02:12:47</t>
   </si>
   <si>
-    <t>01:24:13</t>
-  </si>
-  <si>
-    <t>03:00:40</t>
-  </si>
-  <si>
-    <t>00:35:41</t>
-  </si>
-  <si>
-    <t>02:11:54</t>
-  </si>
-  <si>
-    <t>23:47:13</t>
-  </si>
-  <si>
-    <t>01:23:09</t>
-  </si>
-  <si>
-    <t>02:59:55</t>
-  </si>
-  <si>
-    <t>00:34:24</t>
-  </si>
-  <si>
-    <t>02:11:03</t>
-  </si>
-  <si>
-    <t>23:45:41</t>
-  </si>
-  <si>
-    <t>01:22:10</t>
-  </si>
-  <si>
-    <t>02:59:08</t>
-  </si>
-  <si>
-    <t>22:57:00</t>
-  </si>
-  <si>
-    <t>01:28:51</t>
-  </si>
-  <si>
-    <t>02:15:09</t>
+    <t>01:24:12</t>
+  </si>
+  <si>
+    <t>03:00:39</t>
+  </si>
+  <si>
+    <t>00:35:40</t>
+  </si>
+  <si>
+    <t>02:11:53</t>
+  </si>
+  <si>
+    <t>23:47:11</t>
+  </si>
+  <si>
+    <t>01:23:07</t>
+  </si>
+  <si>
+    <t>02:59:53</t>
+  </si>
+  <si>
+    <t>00:34:21</t>
+  </si>
+  <si>
+    <t>02:11:00</t>
+  </si>
+  <si>
+    <t>23:45:36</t>
+  </si>
+  <si>
+    <t>01:22:05</t>
+  </si>
+  <si>
+    <t>02:59:03</t>
+  </si>
+  <si>
+    <t>22:56:54</t>
+  </si>
+  <si>
+    <t>00:33:10</t>
+  </si>
+  <si>
+    <t>02:10:03</t>
+  </si>
+  <si>
+    <t>22:08:15</t>
+  </si>
+  <si>
+    <t>23:44:15</t>
+  </si>
+  <si>
+    <t>02:15:08</t>
   </si>
   <si>
     <t>01:26:41</t>
   </si>
   <si>
-    <t>03:02:54</t>
+    <t>03:02:53</t>
+  </si>
+  <si>
+    <t>00:38:21</t>
+  </si>
+  <si>
+    <t>02:14:08</t>
+  </si>
+  <si>
+    <t>23:50:18</t>
+  </si>
+  <si>
+    <t>01:25:24</t>
+  </si>
+  <si>
+    <t>03:02:09</t>
+  </si>
+  <si>
+    <t>00:36:41</t>
+  </si>
+  <si>
+    <t>02:13:14</t>
+  </si>
+  <si>
+    <t>23:48:03</t>
+  </si>
+  <si>
+    <t>01:24:19</t>
+  </si>
+  <si>
+    <t>03:01:27</t>
+  </si>
+  <si>
+    <t>22:59:31</t>
+  </si>
+  <si>
+    <t>00:35:25</t>
+  </si>
+  <si>
+    <t>02:12:22</t>
+  </si>
+  <si>
+    <t>22:11:14</t>
+  </si>
+  <si>
+    <t>23:46:31</t>
+  </si>
+  <si>
+    <t>02:17:51</t>
+  </si>
+  <si>
+    <t>01:29:09</t>
+  </si>
+  <si>
+    <t>03:05:54</t>
+  </si>
+  <si>
+    <t>00:40:25</t>
+  </si>
+  <si>
+    <t>02:17:06</t>
+  </si>
+  <si>
+    <t>23:51:41</t>
+  </si>
+  <si>
+    <t>01:28:17</t>
+  </si>
+  <si>
+    <t>03:05:06</t>
+  </si>
+  <si>
+    <t>00:39:26</t>
+  </si>
+  <si>
+    <t>02:16:14</t>
+  </si>
+  <si>
+    <t>23:50:34</t>
+  </si>
+  <si>
+    <t>01:27:19</t>
+  </si>
+  <si>
+    <t>03:04:07</t>
+  </si>
+  <si>
+    <t>23:01:41</t>
   </si>
   <si>
     <t>00:38:22</t>
   </si>
   <si>
-    <t>02:14:09</t>
-  </si>
-  <si>
-    <t>23:50:20</t>
-  </si>
-  <si>
-    <t>01:25:26</t>
-  </si>
-  <si>
-    <t>03:02:11</t>
-  </si>
-  <si>
-    <t>00:36:45</t>
-  </si>
-  <si>
-    <t>02:13:17</t>
-  </si>
-  <si>
-    <t>23:48:07</t>
-  </si>
-  <si>
-    <t>01:24:24</t>
-  </si>
-  <si>
-    <t>03:01:32</t>
-  </si>
-  <si>
-    <t>22:59:37</t>
-  </si>
-  <si>
-    <t>01:29:58</t>
-  </si>
-  <si>
-    <t>02:17:52</t>
-  </si>
-  <si>
-    <t>01:29:09</t>
-  </si>
-  <si>
-    <t>03:05:55</t>
-  </si>
-  <si>
-    <t>00:40:26</t>
-  </si>
-  <si>
-    <t>02:17:07</t>
-  </si>
-  <si>
-    <t>23:51:43</t>
-  </si>
-  <si>
-    <t>01:28:19</t>
-  </si>
-  <si>
-    <t>03:05:08</t>
-  </si>
-  <si>
-    <t>00:39:29</t>
-  </si>
-  <si>
-    <t>02:16:17</t>
-  </si>
-  <si>
-    <t>23:50:38</t>
-  </si>
-  <si>
-    <t>01:27:24</t>
-  </si>
-  <si>
-    <t>03:04:11</t>
-  </si>
-  <si>
-    <t>23:01:47</t>
-  </si>
-  <si>
-    <t>01:31:05</t>
+    <t>02:15:11</t>
+  </si>
+  <si>
+    <t>22:12:47</t>
+  </si>
+  <si>
+    <t>23:49:24</t>
   </si>
   <si>
     <t>02:20:35</t>
   </si>
   <si>
-    <t>01:31:38</t>
+    <t>01:31:37</t>
   </si>
   <si>
     <t>03:08:56</t>
   </si>
   <si>
-    <t>00:42:31</t>
-  </si>
-  <si>
-    <t>02:20:07</t>
+    <t>00:42:30</t>
+  </si>
+  <si>
+    <t>02:20:05</t>
+  </si>
+  <si>
+    <t>23:53:03</t>
+  </si>
+  <si>
+    <t>01:31:11</t>
+  </si>
+  <si>
+    <t>03:08:05</t>
+  </si>
+  <si>
+    <t>00:42:11</t>
+  </si>
+  <si>
+    <t>02:19:15</t>
   </si>
   <si>
     <t>23:53:06</t>
   </si>
   <si>
-    <t>01:31:13</t>
-  </si>
-  <si>
-    <t>03:08:07</t>
-  </si>
-  <si>
-    <t>00:42:14</t>
-  </si>
-  <si>
-    <t>02:19:18</t>
-  </si>
-  <si>
-    <t>23:53:10</t>
-  </si>
-  <si>
-    <t>01:30:25</t>
-  </si>
-  <si>
-    <t>03:06:51</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
-  </si>
-  <si>
-    <t>01:34:26</t>
+    <t>01:30:20</t>
+  </si>
+  <si>
+    <t>03:06:46</t>
+  </si>
+  <si>
+    <t>23:03:52</t>
+  </si>
+  <si>
+    <t>00:41:21</t>
+  </si>
+  <si>
+    <t>02:18:01</t>
+  </si>
+  <si>
+    <t>22:14:22</t>
+  </si>
+  <si>
+    <t>23:52:18</t>
   </si>
   <si>
     <t>02:22:58</t>
   </si>
   <si>
-    <t>01:34:08</t>
+    <t>01:34:07</t>
   </si>
   <si>
     <t>03:11:11</t>
   </si>
   <si>
-    <t>00:45:14</t>
-  </si>
-  <si>
-    <t>02:22:23</t>
-  </si>
-  <si>
-    <t>23:56:14</t>
-  </si>
-  <si>
-    <t>01:33:31</t>
-  </si>
-  <si>
-    <t>03:10:23</t>
-  </si>
-  <si>
-    <t>00:44:36</t>
-  </si>
-  <si>
-    <t>02:21:33</t>
-  </si>
-  <si>
-    <t>23:55:38</t>
-  </si>
-  <si>
-    <t>01:32:40</t>
-  </si>
-  <si>
-    <t>03:09:15</t>
-  </si>
-  <si>
-    <t>23:06:36</t>
+    <t>00:45:12</t>
+  </si>
+  <si>
+    <t>02:22:21</t>
+  </si>
+  <si>
+    <t>23:56:12</t>
+  </si>
+  <si>
+    <t>01:33:29</t>
+  </si>
+  <si>
+    <t>03:10:21</t>
+  </si>
+  <si>
+    <t>00:44:33</t>
+  </si>
+  <si>
+    <t>02:21:30</t>
+  </si>
+  <si>
+    <t>23:55:33</t>
+  </si>
+  <si>
+    <t>01:32:35</t>
+  </si>
+  <si>
+    <t>03:09:10</t>
+  </si>
+  <si>
+    <t>23:06:30</t>
+  </si>
+  <si>
+    <t>00:43:37</t>
+  </si>
+  <si>
+    <t>02:20:20</t>
+  </si>
+  <si>
+    <t>22:17:22</t>
+  </si>
+  <si>
+    <t>23:54:36</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>22°</t>
   </si>
   <si>
     <t>11°</t>
   </si>
   <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
@@ -448,7 +505,7 @@
     <t>12°</t>
   </si>
   <si>
-    <t>01:30:35</t>
+    <t>5°</t>
   </si>
   <si>
     <t>02:16:45</t>
@@ -457,52 +514,49 @@
     <t>01:30:00</t>
   </si>
   <si>
-    <t>03:02:53</t>
-  </si>
-  <si>
-    <t>00:43:15</t>
-  </si>
-  <si>
-    <t>02:16:08</t>
-  </si>
-  <si>
-    <t>01:29:24</t>
-  </si>
-  <si>
-    <t>03:02:17</t>
-  </si>
-  <si>
-    <t>00:42:42</t>
-  </si>
-  <si>
-    <t>02:15:36</t>
-  </si>
-  <si>
-    <t>01:28:59</t>
-  </si>
-  <si>
-    <t>03:01:53</t>
+    <t>00:43:14</t>
+  </si>
+  <si>
+    <t>02:16:07</t>
+  </si>
+  <si>
+    <t>01:29:22</t>
+  </si>
+  <si>
+    <t>03:02:15</t>
+  </si>
+  <si>
+    <t>00:42:39</t>
+  </si>
+  <si>
+    <t>02:15:32</t>
+  </si>
+  <si>
+    <t>01:28:54</t>
+  </si>
+  <si>
+    <t>03:01:48</t>
+  </si>
+  <si>
+    <t>00:42:23</t>
+  </si>
+  <si>
+    <t>02:15:18</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -569,13 +623,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,13 +635,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,55 +701,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1166,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1244,43 +1298,43 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="L2" s="4">
-        <v>-17.5</v>
+        <v>-12.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="O2" s="6">
         <v>2</v>
@@ -1300,46 +1354,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="L3" s="4">
-        <v>-12.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="O3" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -1348,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1356,43 +1410,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="L4" s="4">
-        <v>-18.1</v>
+        <v>-7.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -1412,46 +1466,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="L5" s="4">
-        <v>-7.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="O5" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1459,8 +1513,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1468,46 +1522,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L6" s="4">
-        <v>-22.2</v>
+        <v>-13.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="O6" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1516,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1524,46 +1578,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4">
-        <v>-13.4</v>
+        <v>-24.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O7" s="6">
-        <v>8</v>
+        <v>180</v>
+      </c>
+      <c r="O7" s="9">
+        <v>31</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1571,8 +1625,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>8</v>
+      <c r="R7" s="10">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1580,55 +1634,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="L8" s="4">
-        <v>-24.9</v>
+        <v>-18.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O8" s="9">
-        <v>48</v>
+        <v>178</v>
+      </c>
+      <c r="O8" s="11">
+        <v>77</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="10">
-        <v>36</v>
-      </c>
-      <c r="R8" s="11">
-        <v>31</v>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1636,55 +1690,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="L9" s="4">
-        <v>-18.8</v>
+        <v>-7.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="O9" s="9">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="12">
-        <v>52</v>
-      </c>
-      <c r="R9" s="8">
-        <v>12</v>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1692,55 +1746,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="L10" s="4">
-        <v>-7.7</v>
+        <v>-22.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O10" s="13">
-        <v>37</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>37</v>
+        <v>179</v>
+      </c>
+      <c r="O10" s="11">
+        <v>100</v>
+      </c>
+      <c r="P10" s="13">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>98</v>
       </c>
       <c r="R10" s="14">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1748,55 +1802,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="L11" s="4">
-        <v>-22.9</v>
+        <v>-14</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O11" s="9">
+        <v>178</v>
+      </c>
+      <c r="O11" s="11">
         <v>100</v>
       </c>
       <c r="P11" s="15">
-        <v>65</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>33</v>
-      </c>
-      <c r="R11" s="16">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>98</v>
+      </c>
+      <c r="R11" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1804,55 +1858,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="L12" s="4">
-        <v>-14</v>
+        <v>-25.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O12" s="9">
+        <v>179</v>
+      </c>
+      <c r="O12" s="11">
+        <v>99</v>
+      </c>
+      <c r="P12" s="16">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>53</v>
+      </c>
+      <c r="R12" s="14">
         <v>98</v>
-      </c>
-      <c r="P12" s="17">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>13</v>
-      </c>
-      <c r="R12" s="19">
-        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1860,55 +1914,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="L13" s="4">
-        <v>-25.5</v>
+        <v>-19.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="13">
-        <v>27</v>
-      </c>
-      <c r="P13" s="20">
-        <v>27</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>7</v>
-      </c>
-      <c r="R13" s="8">
-        <v>8</v>
+        <v>178</v>
+      </c>
+      <c r="O13" s="11">
+        <v>100</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>82</v>
+      </c>
+      <c r="R13" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1916,55 +1970,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O14" s="11">
+        <v>93</v>
+      </c>
+      <c r="P14" s="19">
         <v>43</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="Q14" s="13">
         <v>84</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-19.4</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O14" s="13">
-        <v>29</v>
-      </c>
-      <c r="P14" s="8">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>20</v>
-      </c>
-      <c r="R14" s="18">
-        <v>13</v>
+      <c r="R14" s="15">
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1972,55 +2026,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="L15" s="4">
-        <v>-8.300000000000001</v>
+        <v>-26.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O15" s="9">
-        <v>76</v>
-      </c>
-      <c r="P15" s="8">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>30</v>
-      </c>
-      <c r="R15" s="22">
-        <v>71</v>
+        <v>179</v>
+      </c>
+      <c r="O15" s="11">
+        <v>82</v>
+      </c>
+      <c r="P15" s="20">
+        <v>50</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>50</v>
+      </c>
+      <c r="R15" s="21">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2028,114 +2082,282 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-23.5</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O16" s="11">
+        <v>86</v>
+      </c>
+      <c r="P16" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>52</v>
+      </c>
+      <c r="R16" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>25</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-14.6</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O17" s="11">
+        <v>79</v>
+      </c>
+      <c r="P17" s="20">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>42</v>
+      </c>
+      <c r="R17" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O18" s="11">
+        <v>86</v>
+      </c>
+      <c r="P18" s="19">
         <v>46</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-26.5</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O16" s="9">
-        <v>94</v>
-      </c>
-      <c r="P16" s="16">
-        <v>94</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>29</v>
-      </c>
-      <c r="R16" s="23">
+      <c r="Q18" s="17">
+        <v>55</v>
+      </c>
+      <c r="R18" s="20">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-26.2</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="O19" s="11">
         <v>79</v>
+      </c>
+      <c r="P19" s="23">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>42</v>
+      </c>
+      <c r="R19" s="22">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A19">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B19">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C19">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D19">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F19">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J19">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K19">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2154,12 +2376,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M19">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N19">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2176,22 +2398,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O19">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P19">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q19">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R19">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260813--01</t>
-  </si>
-  <si>
     <t>20260814--01</t>
   </si>
   <si>
@@ -124,7 +121,13 @@
     <t>20260819--04</t>
   </si>
   <si>
-    <t>05:27</t>
+    <t>20260820--01</t>
+  </si>
+  <si>
+    <t>20260820--02</t>
+  </si>
+  <si>
+    <t>20260820--03</t>
   </si>
   <si>
     <t>04:56</t>
@@ -157,7 +160,7 @@
     <t>05:03</t>
   </si>
   <si>
-    <t>05:19</t>
+    <t>05:20</t>
   </si>
   <si>
     <t>04:21</t>
@@ -169,7 +172,16 @@
     <t>03:08</t>
   </si>
   <si>
-    <t>03:50</t>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:32</t>
   </si>
   <si>
     <t>01:37</t>
@@ -193,13 +205,16 @@
     <t>01:26</t>
   </si>
   <si>
-    <t>04:58</t>
+    <t>04:59</t>
   </si>
   <si>
     <t>02:43</t>
   </si>
   <si>
-    <t>02:12:47</t>
+    <t>00:11</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>01:24:12</t>
@@ -253,7 +268,13 @@
     <t>23:44:15</t>
   </si>
   <si>
-    <t>02:15:08</t>
+    <t>01:21:02</t>
+  </si>
+  <si>
+    <t>02:58:12</t>
+  </si>
+  <si>
+    <t>22:55:19</t>
   </si>
   <si>
     <t>01:26:41</t>
@@ -307,7 +328,13 @@
     <t>23:46:31</t>
   </si>
   <si>
-    <t>02:17:51</t>
+    <t>01:23:18</t>
+  </si>
+  <si>
+    <t>03:01:04</t>
+  </si>
+  <si>
+    <t>22:57:39</t>
   </si>
   <si>
     <t>01:29:09</t>
@@ -340,7 +367,7 @@
     <t>23:50:34</t>
   </si>
   <si>
-    <t>01:27:19</t>
+    <t>01:27:20</t>
   </si>
   <si>
     <t>03:04:07</t>
@@ -349,19 +376,25 @@
     <t>23:01:41</t>
   </si>
   <si>
-    <t>00:38:22</t>
+    <t>00:38:23</t>
   </si>
   <si>
     <t>02:15:11</t>
   </si>
   <si>
-    <t>22:12:47</t>
+    <t>22:12:48</t>
   </si>
   <si>
     <t>23:49:24</t>
   </si>
   <si>
-    <t>02:20:35</t>
+    <t>01:26:13</t>
+  </si>
+  <si>
+    <t>03:02:51</t>
+  </si>
+  <si>
+    <t>23:00:24</t>
   </si>
   <si>
     <t>01:31:37</t>
@@ -397,13 +430,13 @@
     <t>01:30:20</t>
   </si>
   <si>
-    <t>03:06:46</t>
+    <t>03:06:47</t>
   </si>
   <si>
     <t>23:03:52</t>
   </si>
   <si>
-    <t>00:41:21</t>
+    <t>00:41:22</t>
   </si>
   <si>
     <t>02:18:01</t>
@@ -412,10 +445,13 @@
     <t>22:14:22</t>
   </si>
   <si>
-    <t>23:52:18</t>
-  </si>
-  <si>
-    <t>02:22:58</t>
+    <t>23:52:19</t>
+  </si>
+  <si>
+    <t>03:04:39</t>
+  </si>
+  <si>
+    <t>23:03:11</t>
   </si>
   <si>
     <t>01:34:07</t>
@@ -445,7 +481,7 @@
     <t>02:21:30</t>
   </si>
   <si>
-    <t>23:55:33</t>
+    <t>23:55:34</t>
   </si>
   <si>
     <t>01:32:35</t>
@@ -460,7 +496,7 @@
     <t>00:43:37</t>
   </si>
   <si>
-    <t>02:20:20</t>
+    <t>02:20:21</t>
   </si>
   <si>
     <t>22:17:22</t>
@@ -469,7 +505,13 @@
     <t>23:54:36</t>
   </si>
   <si>
-    <t>19°</t>
+    <t>01:31:26</t>
+  </si>
+  <si>
+    <t>03:07:31</t>
+  </si>
+  <si>
+    <t>23:05:31</t>
   </si>
   <si>
     <t>18°</t>
@@ -508,7 +550,7 @@
     <t>5°</t>
   </si>
   <si>
-    <t>02:16:45</t>
+    <t>13°</t>
   </si>
   <si>
     <t>01:30:00</t>
@@ -542,6 +584,12 @@
   </si>
   <si>
     <t>02:15:18</t>
+  </si>
+  <si>
+    <t>01:28:58</t>
+  </si>
+  <si>
+    <t>03:01:53</t>
   </si>
   <si>
     <t>A+B</t>
@@ -590,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,7 +665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,7 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,13 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,7 +707,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,43 +725,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,9 +856,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1220,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1298,46 +1337,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="L2" s="4">
-        <v>-12.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="O2" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1346,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1354,43 +1393,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.1</v>
+        <v>-7.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -1410,46 +1449,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="L4" s="4">
-        <v>-7.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="O4" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1457,8 +1496,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="R4" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1466,46 +1505,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="L5" s="4">
-        <v>-22.2</v>
+        <v>-13.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O5" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1513,8 +1552,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>9</v>
+      <c r="R5" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1522,55 +1561,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="L6" s="4">
-        <v>-13.4</v>
+        <v>-24.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="O6" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+      <c r="Q6" s="8">
+        <v>6</v>
+      </c>
+      <c r="R6" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1578,55 +1617,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="L7" s="4">
-        <v>-24.9</v>
+        <v>-18.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="O7" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
-        <v>31</v>
+      <c r="Q7" s="10">
+        <v>38</v>
+      </c>
+      <c r="R7" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1634,55 +1673,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="L8" s="4">
-        <v>-18.8</v>
+        <v>-7.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="O8" s="11">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
-        <v>58</v>
+      <c r="Q8" s="12">
+        <v>56</v>
+      </c>
+      <c r="R8" s="13">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1690,55 +1729,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="L9" s="4">
-        <v>-7.7</v>
+        <v>-22.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O9" s="9">
-        <v>33</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
+        <v>195</v>
+      </c>
+      <c r="O9" s="11">
+        <v>77</v>
+      </c>
+      <c r="P9" s="13">
+        <v>21</v>
       </c>
       <c r="Q9" s="7">
         <v>0</v>
       </c>
-      <c r="R9" s="10">
-        <v>32</v>
+      <c r="R9" s="12">
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1746,52 +1785,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="L10" s="4">
-        <v>-22.9</v>
+        <v>-14</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O10" s="11">
         <v>100</v>
       </c>
-      <c r="P10" s="13">
-        <v>86</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>98</v>
+      <c r="P10" s="10">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>3</v>
       </c>
       <c r="R10" s="14">
         <v>100</v>
@@ -1802,55 +1841,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="L11" s="4">
-        <v>-14</v>
+        <v>-25.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="O11" s="11">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="P11" s="15">
-        <v>92</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>98</v>
-      </c>
-      <c r="R11" s="14">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>48</v>
+      </c>
+      <c r="R11" s="17">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1858,55 +1897,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="L12" s="4">
-        <v>-25.5</v>
+        <v>-19.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O12" s="11">
-        <v>99</v>
-      </c>
-      <c r="P12" s="16">
-        <v>13</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>53</v>
-      </c>
-      <c r="R12" s="14">
-        <v>98</v>
+        <v>70</v>
+      </c>
+      <c r="P12" s="18">
+        <v>64</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>26</v>
+      </c>
+      <c r="R12" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1914,55 +1953,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="L13" s="4">
-        <v>-19.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="O13" s="11">
-        <v>100</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>82</v>
-      </c>
-      <c r="R13" s="14">
-        <v>100</v>
+        <v>77</v>
+      </c>
+      <c r="P13" s="16">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1</v>
+      </c>
+      <c r="R13" s="13">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1970,55 +2009,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4">
-        <v>-8.300000000000001</v>
+        <v>-26.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="O14" s="11">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P14" s="19">
-        <v>43</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>84</v>
-      </c>
-      <c r="R14" s="15">
-        <v>89</v>
+        <v>23</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>12</v>
+      </c>
+      <c r="R14" s="21">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2026,55 +2065,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="L15" s="4">
-        <v>-26.5</v>
+        <v>-23.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="O15" s="11">
-        <v>82</v>
-      </c>
-      <c r="P15" s="20">
-        <v>50</v>
-      </c>
-      <c r="Q15" s="20">
-        <v>50</v>
-      </c>
-      <c r="R15" s="21">
-        <v>6</v>
+        <v>75</v>
+      </c>
+      <c r="P15" s="19">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>25</v>
+      </c>
+      <c r="R15" s="10">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2082,55 +2121,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="L16" s="4">
-        <v>-23.5</v>
+        <v>-14.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="O16" s="11">
-        <v>86</v>
-      </c>
-      <c r="P16" s="12">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="20">
-        <v>52</v>
-      </c>
-      <c r="R16" s="21">
-        <v>7</v>
+        <v>69</v>
+      </c>
+      <c r="P16" s="13">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>41</v>
+      </c>
+      <c r="R16" s="22">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2138,55 +2177,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="L17" s="4">
-        <v>-14.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O17" s="11">
-        <v>79</v>
-      </c>
-      <c r="P17" s="20">
-        <v>52</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>42</v>
-      </c>
-      <c r="R17" s="21">
-        <v>5</v>
+        <v>196</v>
+      </c>
+      <c r="O17" s="9">
+        <v>28</v>
+      </c>
+      <c r="P17" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>3</v>
+      </c>
+      <c r="R17" s="22">
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2194,55 +2233,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L18" s="4">
-        <v>-25.7</v>
+        <v>-26.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O18" s="11">
-        <v>86</v>
-      </c>
-      <c r="P18" s="19">
-        <v>46</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>55</v>
-      </c>
-      <c r="R18" s="20">
-        <v>52</v>
+        <v>195</v>
+      </c>
+      <c r="O18" s="9">
+        <v>25</v>
+      </c>
+      <c r="P18" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>4</v>
+      </c>
+      <c r="R18" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2250,114 +2289,226 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="L19" s="4">
-        <v>-26.2</v>
+        <v>-20</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O19" s="11">
-        <v>79</v>
-      </c>
-      <c r="P19" s="23">
-        <v>34</v>
-      </c>
-      <c r="Q19" s="22">
-        <v>42</v>
-      </c>
-      <c r="R19" s="22">
-        <v>41</v>
+        <v>194</v>
+      </c>
+      <c r="O19" s="9">
+        <v>15</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>5</v>
+      </c>
+      <c r="R19" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>14</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O20" s="11">
+        <v>37</v>
+      </c>
+      <c r="P20" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>20</v>
+      </c>
+      <c r="R20" s="17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-27.2</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O21" s="11">
+        <v>97</v>
+      </c>
+      <c r="P21" s="19">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="18">
+        <v>63</v>
+      </c>
+      <c r="R21" s="16">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B19">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C19">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2376,12 +2527,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2398,22 +2549,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P19">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q19">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260814--01</t>
-  </si>
-  <si>
-    <t>20260814--02</t>
-  </si>
-  <si>
     <t>20260815--01</t>
   </si>
   <si>
@@ -130,10 +124,16 @@
     <t>20260820--03</t>
   </si>
   <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:03</t>
+    <t>20260821--01</t>
+  </si>
+  <si>
+    <t>20260821--02</t>
+  </si>
+  <si>
+    <t>20260821--03</t>
+  </si>
+  <si>
+    <t>20260821--04</t>
   </si>
   <si>
     <t>04:09</t>
@@ -160,16 +160,16 @@
     <t>05:03</t>
   </si>
   <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:08</t>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>03:07</t>
   </si>
   <si>
     <t>05:48</t>
@@ -184,7 +184,16 @@
     <t>05:32</t>
   </si>
   <si>
-    <t>01:37</t>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>05:08</t>
+  </si>
+  <si>
+    <t>05:59</t>
   </si>
   <si>
     <t>00:00</t>
@@ -193,10 +202,10 @@
     <t>03:58</t>
   </si>
   <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>05:50</t>
+    <t>01:48</t>
+  </si>
+  <si>
+    <t>05:49</t>
   </si>
   <si>
     <t>03:43</t>
@@ -205,7 +214,7 @@
     <t>01:26</t>
   </si>
   <si>
-    <t>04:59</t>
+    <t>04:58</t>
   </si>
   <si>
     <t>02:43</t>
@@ -214,13 +223,7 @@
     <t>00:11</t>
   </si>
   <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>01:24:12</t>
-  </si>
-  <si>
-    <t>03:00:39</t>
+    <t>00:23</t>
   </si>
   <si>
     <t>00:35:40</t>
@@ -232,55 +235,61 @@
     <t>23:47:11</t>
   </si>
   <si>
-    <t>01:23:07</t>
+    <t>01:23:06</t>
   </si>
   <si>
     <t>02:59:53</t>
   </si>
   <si>
-    <t>00:34:21</t>
-  </si>
-  <si>
-    <t>02:11:00</t>
-  </si>
-  <si>
-    <t>23:45:36</t>
-  </si>
-  <si>
-    <t>01:22:05</t>
-  </si>
-  <si>
-    <t>02:59:03</t>
-  </si>
-  <si>
-    <t>22:56:54</t>
-  </si>
-  <si>
-    <t>00:33:10</t>
-  </si>
-  <si>
-    <t>02:10:03</t>
-  </si>
-  <si>
-    <t>22:08:15</t>
-  </si>
-  <si>
-    <t>23:44:15</t>
-  </si>
-  <si>
-    <t>01:21:02</t>
-  </si>
-  <si>
-    <t>02:58:12</t>
-  </si>
-  <si>
-    <t>22:55:19</t>
-  </si>
-  <si>
-    <t>01:26:41</t>
-  </si>
-  <si>
-    <t>03:02:53</t>
+    <t>00:34:20</t>
+  </si>
+  <si>
+    <t>02:10:59</t>
+  </si>
+  <si>
+    <t>23:45:34</t>
+  </si>
+  <si>
+    <t>01:22:03</t>
+  </si>
+  <si>
+    <t>02:59:01</t>
+  </si>
+  <si>
+    <t>22:56:51</t>
+  </si>
+  <si>
+    <t>00:33:07</t>
+  </si>
+  <si>
+    <t>02:10:00</t>
+  </si>
+  <si>
+    <t>22:08:11</t>
+  </si>
+  <si>
+    <t>23:44:10</t>
+  </si>
+  <si>
+    <t>01:20:57</t>
+  </si>
+  <si>
+    <t>02:58:07</t>
+  </si>
+  <si>
+    <t>22:55:13</t>
+  </si>
+  <si>
+    <t>00:31:53</t>
+  </si>
+  <si>
+    <t>02:08:56</t>
+  </si>
+  <si>
+    <t>22:06:16</t>
+  </si>
+  <si>
+    <t>23:42:47</t>
   </si>
   <si>
     <t>00:38:21</t>
@@ -292,55 +301,61 @@
     <t>23:50:18</t>
   </si>
   <si>
-    <t>01:25:24</t>
-  </si>
-  <si>
-    <t>03:02:09</t>
-  </si>
-  <si>
-    <t>00:36:41</t>
-  </si>
-  <si>
-    <t>02:13:14</t>
-  </si>
-  <si>
-    <t>23:48:03</t>
-  </si>
-  <si>
-    <t>01:24:19</t>
-  </si>
-  <si>
-    <t>03:01:27</t>
-  </si>
-  <si>
-    <t>22:59:31</t>
-  </si>
-  <si>
-    <t>00:35:25</t>
-  </si>
-  <si>
-    <t>02:12:22</t>
-  </si>
-  <si>
-    <t>22:11:14</t>
-  </si>
-  <si>
-    <t>23:46:31</t>
-  </si>
-  <si>
-    <t>01:23:18</t>
-  </si>
-  <si>
-    <t>03:01:04</t>
-  </si>
-  <si>
-    <t>22:57:39</t>
-  </si>
-  <si>
-    <t>01:29:09</t>
-  </si>
-  <si>
-    <t>03:05:54</t>
+    <t>01:25:23</t>
+  </si>
+  <si>
+    <t>03:02:08</t>
+  </si>
+  <si>
+    <t>00:36:40</t>
+  </si>
+  <si>
+    <t>02:13:13</t>
+  </si>
+  <si>
+    <t>23:48:01</t>
+  </si>
+  <si>
+    <t>01:24:17</t>
+  </si>
+  <si>
+    <t>03:01:25</t>
+  </si>
+  <si>
+    <t>22:59:28</t>
+  </si>
+  <si>
+    <t>00:35:22</t>
+  </si>
+  <si>
+    <t>02:12:18</t>
+  </si>
+  <si>
+    <t>22:11:10</t>
+  </si>
+  <si>
+    <t>23:46:26</t>
+  </si>
+  <si>
+    <t>01:23:13</t>
+  </si>
+  <si>
+    <t>03:00:59</t>
+  </si>
+  <si>
+    <t>22:57:32</t>
+  </si>
+  <si>
+    <t>00:34:07</t>
+  </si>
+  <si>
+    <t>02:11:31</t>
+  </si>
+  <si>
+    <t>22:08:41</t>
+  </si>
+  <si>
+    <t>23:45:01</t>
   </si>
   <si>
     <t>00:40:25</t>
@@ -349,58 +364,64 @@
     <t>02:17:06</t>
   </si>
   <si>
-    <t>23:51:41</t>
-  </si>
-  <si>
-    <t>01:28:17</t>
+    <t>23:51:40</t>
+  </si>
+  <si>
+    <t>01:28:16</t>
   </si>
   <si>
     <t>03:05:06</t>
   </si>
   <si>
-    <t>00:39:26</t>
-  </si>
-  <si>
-    <t>02:16:14</t>
-  </si>
-  <si>
-    <t>23:50:34</t>
-  </si>
-  <si>
-    <t>01:27:20</t>
-  </si>
-  <si>
-    <t>03:04:07</t>
-  </si>
-  <si>
-    <t>23:01:41</t>
-  </si>
-  <si>
-    <t>00:38:23</t>
-  </si>
-  <si>
-    <t>02:15:11</t>
-  </si>
-  <si>
-    <t>22:12:48</t>
-  </si>
-  <si>
-    <t>23:49:24</t>
-  </si>
-  <si>
-    <t>01:26:13</t>
-  </si>
-  <si>
-    <t>03:02:51</t>
-  </si>
-  <si>
-    <t>23:00:24</t>
-  </si>
-  <si>
-    <t>01:31:37</t>
-  </si>
-  <si>
-    <t>03:08:56</t>
+    <t>00:39:25</t>
+  </si>
+  <si>
+    <t>02:16:13</t>
+  </si>
+  <si>
+    <t>23:50:32</t>
+  </si>
+  <si>
+    <t>01:27:17</t>
+  </si>
+  <si>
+    <t>03:04:05</t>
+  </si>
+  <si>
+    <t>23:01:38</t>
+  </si>
+  <si>
+    <t>00:38:19</t>
+  </si>
+  <si>
+    <t>02:15:08</t>
+  </si>
+  <si>
+    <t>22:12:43</t>
+  </si>
+  <si>
+    <t>23:49:20</t>
+  </si>
+  <si>
+    <t>01:26:08</t>
+  </si>
+  <si>
+    <t>03:02:46</t>
+  </si>
+  <si>
+    <t>23:00:18</t>
+  </si>
+  <si>
+    <t>00:37:06</t>
+  </si>
+  <si>
+    <t>02:13:48</t>
+  </si>
+  <si>
+    <t>22:11:15</t>
+  </si>
+  <si>
+    <t>23:48:00</t>
   </si>
   <si>
     <t>00:42:30</t>
@@ -412,52 +433,61 @@
     <t>23:53:03</t>
   </si>
   <si>
-    <t>01:31:11</t>
-  </si>
-  <si>
-    <t>03:08:05</t>
-  </si>
-  <si>
-    <t>00:42:11</t>
-  </si>
-  <si>
-    <t>02:19:15</t>
-  </si>
-  <si>
-    <t>23:53:06</t>
-  </si>
-  <si>
-    <t>01:30:20</t>
-  </si>
-  <si>
-    <t>03:06:47</t>
-  </si>
-  <si>
-    <t>23:03:52</t>
-  </si>
-  <si>
-    <t>00:41:22</t>
-  </si>
-  <si>
-    <t>02:18:01</t>
-  </si>
-  <si>
-    <t>22:14:22</t>
-  </si>
-  <si>
-    <t>23:52:19</t>
-  </si>
-  <si>
-    <t>03:04:39</t>
-  </si>
-  <si>
-    <t>23:03:11</t>
-  </si>
-  <si>
-    <t>01:34:07</t>
-  </si>
-  <si>
-    <t>03:11:11</t>
+    <t>01:31:10</t>
+  </si>
+  <si>
+    <t>03:08:04</t>
+  </si>
+  <si>
+    <t>00:42:10</t>
+  </si>
+  <si>
+    <t>02:19:14</t>
+  </si>
+  <si>
+    <t>23:53:04</t>
+  </si>
+  <si>
+    <t>01:30:18</t>
+  </si>
+  <si>
+    <t>03:06:44</t>
+  </si>
+  <si>
+    <t>23:03:48</t>
+  </si>
+  <si>
+    <t>00:41:18</t>
+  </si>
+  <si>
+    <t>02:17:58</t>
+  </si>
+  <si>
+    <t>22:14:17</t>
+  </si>
+  <si>
+    <t>23:52:14</t>
+  </si>
+  <si>
+    <t>01:29:04</t>
+  </si>
+  <si>
+    <t>03:04:34</t>
+  </si>
+  <si>
+    <t>23:03:04</t>
+  </si>
+  <si>
+    <t>00:40:05</t>
+  </si>
+  <si>
+    <t>02:16:06</t>
+  </si>
+  <si>
+    <t>22:13:49</t>
+  </si>
+  <si>
+    <t>23:51:00</t>
   </si>
   <si>
     <t>00:45:12</t>
@@ -469,55 +499,61 @@
     <t>23:56:12</t>
   </si>
   <si>
-    <t>01:33:29</t>
-  </si>
-  <si>
-    <t>03:10:21</t>
-  </si>
-  <si>
-    <t>00:44:33</t>
-  </si>
-  <si>
-    <t>02:21:30</t>
-  </si>
-  <si>
-    <t>23:55:34</t>
-  </si>
-  <si>
-    <t>01:32:35</t>
-  </si>
-  <si>
-    <t>03:09:10</t>
-  </si>
-  <si>
-    <t>23:06:30</t>
-  </si>
-  <si>
-    <t>00:43:37</t>
-  </si>
-  <si>
-    <t>02:20:21</t>
-  </si>
-  <si>
-    <t>22:17:22</t>
-  </si>
-  <si>
-    <t>23:54:36</t>
-  </si>
-  <si>
-    <t>01:31:26</t>
-  </si>
-  <si>
-    <t>03:07:31</t>
-  </si>
-  <si>
-    <t>23:05:31</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>10°</t>
+    <t>01:33:28</t>
+  </si>
+  <si>
+    <t>03:10:20</t>
+  </si>
+  <si>
+    <t>00:44:32</t>
+  </si>
+  <si>
+    <t>02:21:29</t>
+  </si>
+  <si>
+    <t>23:55:32</t>
+  </si>
+  <si>
+    <t>01:32:33</t>
+  </si>
+  <si>
+    <t>03:09:08</t>
+  </si>
+  <si>
+    <t>23:06:27</t>
+  </si>
+  <si>
+    <t>00:43:34</t>
+  </si>
+  <si>
+    <t>02:20:17</t>
+  </si>
+  <si>
+    <t>22:17:17</t>
+  </si>
+  <si>
+    <t>23:54:31</t>
+  </si>
+  <si>
+    <t>01:31:21</t>
+  </si>
+  <si>
+    <t>03:07:26</t>
+  </si>
+  <si>
+    <t>23:05:25</t>
+  </si>
+  <si>
+    <t>00:42:20</t>
+  </si>
+  <si>
+    <t>02:18:40</t>
+  </si>
+  <si>
+    <t>22:16:15</t>
+  </si>
+  <si>
+    <t>23:53:14</t>
   </si>
   <si>
     <t>7°</t>
@@ -553,9 +589,6 @@
     <t>13°</t>
   </si>
   <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
     <t>00:43:14</t>
   </si>
   <si>
@@ -568,40 +601,40 @@
     <t>03:02:15</t>
   </si>
   <si>
-    <t>00:42:39</t>
-  </si>
-  <si>
-    <t>02:15:32</t>
-  </si>
-  <si>
-    <t>01:28:54</t>
-  </si>
-  <si>
-    <t>03:01:48</t>
-  </si>
-  <si>
-    <t>00:42:23</t>
-  </si>
-  <si>
-    <t>02:15:18</t>
-  </si>
-  <si>
-    <t>01:28:58</t>
-  </si>
-  <si>
-    <t>03:01:53</t>
+    <t>00:42:38</t>
+  </si>
+  <si>
+    <t>02:15:31</t>
+  </si>
+  <si>
+    <t>01:28:52</t>
+  </si>
+  <si>
+    <t>03:01:46</t>
+  </si>
+  <si>
+    <t>02:15:15</t>
+  </si>
+  <si>
+    <t>01:28:53</t>
+  </si>
+  <si>
+    <t>03:01:49</t>
+  </si>
+  <si>
+    <t>02:15:43</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -638,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,7 +710,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,13 +722,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,13 +752,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,31 +806,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -856,6 +925,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1259,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1337,46 +1424,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="L2" s="4">
-        <v>-18.1</v>
+        <v>-22.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1384,8 +1471,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1393,43 +1480,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="L3" s="4">
-        <v>-7.2</v>
+        <v>-13.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -1440,8 +1527,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="R3" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1449,55 +1536,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-22.2</v>
+        <v>-24.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O4" s="6">
-        <v>7</v>
+        <v>207</v>
+      </c>
+      <c r="O4" s="9">
+        <v>30</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
+      <c r="Q4" s="10">
+        <v>21</v>
       </c>
       <c r="R4" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1505,55 +1592,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="L5" s="4">
-        <v>-13.4</v>
+        <v>-18.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="O5" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
         <v>2</v>
+      </c>
+      <c r="R5" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1561,55 +1648,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="L6" s="4">
-        <v>-24.9</v>
+        <v>-7.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O6" s="6">
-        <v>13</v>
+        <v>206</v>
+      </c>
+      <c r="O6" s="11">
+        <v>61</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>6</v>
-      </c>
-      <c r="R6" s="8">
-        <v>5</v>
+      <c r="Q6" s="12">
+        <v>27</v>
+      </c>
+      <c r="R6" s="13">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1617,55 +1704,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="L7" s="4">
-        <v>-18.8</v>
+        <v>-22.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O7" s="9">
-        <v>38</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>38</v>
-      </c>
-      <c r="R7" s="8">
-        <v>3</v>
+        <v>205</v>
+      </c>
+      <c r="O7" s="11">
+        <v>100</v>
+      </c>
+      <c r="P7" s="14">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>50</v>
+      </c>
+      <c r="R7" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1673,55 +1760,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="L8" s="4">
-        <v>-7.7</v>
+        <v>-14</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="O8" s="11">
-        <v>57</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>56</v>
-      </c>
-      <c r="R8" s="13">
-        <v>21</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="17">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>98</v>
+      </c>
+      <c r="R8" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1729,55 +1816,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-22.9</v>
+        <v>-25.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="O9" s="11">
+        <v>87</v>
+      </c>
+      <c r="P9" s="18">
+        <v>59</v>
+      </c>
+      <c r="Q9" s="19">
         <v>77</v>
       </c>
-      <c r="P9" s="13">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="7">
+      <c r="R9" s="7">
         <v>0</v>
-      </c>
-      <c r="R9" s="12">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1785,55 +1872,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="L10" s="4">
-        <v>-14</v>
+        <v>-19.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="O10" s="11">
-        <v>100</v>
-      </c>
-      <c r="P10" s="10">
-        <v>42</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>3</v>
-      </c>
-      <c r="R10" s="14">
-        <v>100</v>
+        <v>84</v>
+      </c>
+      <c r="P10" s="20">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>50</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1841,55 +1928,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="L11" s="4">
-        <v>-25.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="O11" s="11">
-        <v>73</v>
-      </c>
-      <c r="P11" s="15">
-        <v>68</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>48</v>
-      </c>
-      <c r="R11" s="17">
-        <v>13</v>
+        <v>66</v>
+      </c>
+      <c r="P11" s="14">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>2</v>
+      </c>
+      <c r="R11" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1897,55 +1984,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-19.4</v>
+        <v>-26.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O12" s="11">
-        <v>70</v>
-      </c>
-      <c r="P12" s="18">
-        <v>64</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>26</v>
-      </c>
-      <c r="R12" s="8">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="21">
+        <v>78</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>93</v>
+      </c>
+      <c r="R12" s="17">
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1953,55 +2040,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="L13" s="4">
-        <v>-8.300000000000001</v>
+        <v>-23.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O13" s="11">
+        <v>100</v>
+      </c>
+      <c r="P13" s="19">
         <v>77</v>
       </c>
-      <c r="P13" s="16">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>1</v>
-      </c>
-      <c r="R13" s="13">
-        <v>19</v>
+      <c r="Q13" s="22">
+        <v>94</v>
+      </c>
+      <c r="R13" s="20">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2009,55 +2096,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.5</v>
+        <v>-14.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="O14" s="11">
+        <v>100</v>
+      </c>
+      <c r="P14" s="23">
         <v>72</v>
       </c>
-      <c r="P14" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q14" s="20">
-        <v>12</v>
-      </c>
-      <c r="R14" s="21">
-        <v>33</v>
+      <c r="Q14" s="17">
+        <v>92</v>
+      </c>
+      <c r="R14" s="24">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2065,55 +2152,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="L15" s="4">
-        <v>-23.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="O15" s="11">
-        <v>75</v>
-      </c>
-      <c r="P15" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q15" s="19">
-        <v>25</v>
-      </c>
-      <c r="R15" s="10">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="P15" s="25">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>20</v>
+      </c>
+      <c r="R15" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2121,55 +2208,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-14.6</v>
+        <v>-26.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O16" s="11">
-        <v>69</v>
-      </c>
-      <c r="P16" s="13">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="P16" s="25">
+        <v>14</v>
       </c>
       <c r="Q16" s="10">
-        <v>41</v>
-      </c>
-      <c r="R16" s="22">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2177,55 +2264,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="L17" s="4">
-        <v>-25.7</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O17" s="9">
-        <v>28</v>
-      </c>
-      <c r="P17" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>3</v>
-      </c>
-      <c r="R17" s="22">
-        <v>28</v>
+        <v>206</v>
+      </c>
+      <c r="O17" s="11">
+        <v>47</v>
+      </c>
+      <c r="P17" s="10">
+        <v>19</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>27</v>
+      </c>
+      <c r="R17" s="26">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2233,55 +2320,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="L18" s="4">
-        <v>-26.2</v>
+        <v>-8.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O18" s="9">
-        <v>25</v>
-      </c>
-      <c r="P18" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>4</v>
-      </c>
-      <c r="R18" s="19">
-        <v>25</v>
+        <v>207</v>
+      </c>
+      <c r="O18" s="11">
+        <v>66</v>
+      </c>
+      <c r="P18" s="27">
+        <v>41</v>
+      </c>
+      <c r="Q18" s="28">
+        <v>37</v>
+      </c>
+      <c r="R18" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2289,55 +2376,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-20</v>
+        <v>-27.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O19" s="9">
-        <v>15</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>5</v>
-      </c>
-      <c r="R19" s="17">
-        <v>15</v>
+        <v>205</v>
+      </c>
+      <c r="O19" s="11">
+        <v>74</v>
+      </c>
+      <c r="P19" s="12">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>29</v>
+      </c>
+      <c r="R19" s="18">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2345,55 +2432,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="L20" s="4">
-        <v>-8.9</v>
+        <v>-24.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="O20" s="11">
-        <v>37</v>
-      </c>
-      <c r="P20" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>20</v>
-      </c>
-      <c r="R20" s="17">
-        <v>17</v>
+        <v>79</v>
+      </c>
+      <c r="P20" s="10">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>25</v>
+      </c>
+      <c r="R20" s="18">
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2401,114 +2488,226 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="L21" s="4">
-        <v>-27.2</v>
+        <v>-15.3</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="O21" s="11">
-        <v>97</v>
-      </c>
-      <c r="P21" s="19">
-        <v>25</v>
-      </c>
-      <c r="Q21" s="18">
-        <v>63</v>
-      </c>
-      <c r="R21" s="16">
-        <v>50</v>
+        <v>90</v>
+      </c>
+      <c r="P21" s="25">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>30</v>
+      </c>
+      <c r="R21" s="21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>21</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-26.3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O22" s="11">
+        <v>98</v>
+      </c>
+      <c r="P22" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>43</v>
+      </c>
+      <c r="R22" s="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>31</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-26.9</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O23" s="11">
+        <v>94</v>
+      </c>
+      <c r="P23" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>32</v>
+      </c>
+      <c r="R23" s="20">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2527,12 +2726,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2549,22 +2748,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="204">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260815--01</t>
-  </si>
-  <si>
-    <t>20260815--02</t>
-  </si>
-  <si>
-    <t>20260815--03</t>
-  </si>
-  <si>
     <t>20260816--01</t>
   </si>
   <si>
@@ -136,169 +127,169 @@
     <t>20260821--04</t>
   </si>
   <si>
-    <t>04:09</t>
+    <t>20260822--01</t>
+  </si>
+  <si>
+    <t>20260822--02</t>
+  </si>
+  <si>
+    <t>20260822--03</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>05:02</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>04:20</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:07</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>04:28</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:42</t>
+  </si>
+  <si>
+    <t>01:26</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
     <t>02:45</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>05:19</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>03:07</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:08</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>03:58</t>
-  </si>
-  <si>
-    <t>01:48</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>03:43</t>
-  </si>
-  <si>
-    <t>01:26</t>
-  </si>
-  <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:11</t>
-  </si>
-  <si>
     <t>00:23</t>
   </si>
   <si>
-    <t>00:35:40</t>
-  </si>
-  <si>
-    <t>02:11:53</t>
-  </si>
-  <si>
-    <t>23:47:11</t>
-  </si>
-  <si>
     <t>01:23:06</t>
   </si>
   <si>
     <t>02:59:53</t>
   </si>
   <si>
-    <t>00:34:20</t>
-  </si>
-  <si>
-    <t>02:10:59</t>
-  </si>
-  <si>
-    <t>23:45:34</t>
-  </si>
-  <si>
-    <t>01:22:03</t>
-  </si>
-  <si>
-    <t>02:59:01</t>
-  </si>
-  <si>
-    <t>22:56:51</t>
-  </si>
-  <si>
-    <t>00:33:07</t>
-  </si>
-  <si>
-    <t>02:10:00</t>
-  </si>
-  <si>
-    <t>22:08:11</t>
-  </si>
-  <si>
-    <t>23:44:10</t>
-  </si>
-  <si>
-    <t>01:20:57</t>
-  </si>
-  <si>
-    <t>02:58:07</t>
-  </si>
-  <si>
-    <t>22:55:13</t>
-  </si>
-  <si>
-    <t>00:31:53</t>
-  </si>
-  <si>
-    <t>02:08:56</t>
-  </si>
-  <si>
-    <t>22:06:16</t>
-  </si>
-  <si>
-    <t>23:42:47</t>
-  </si>
-  <si>
-    <t>00:38:21</t>
-  </si>
-  <si>
-    <t>02:14:08</t>
-  </si>
-  <si>
-    <t>23:50:18</t>
+    <t>00:34:19</t>
+  </si>
+  <si>
+    <t>02:10:58</t>
+  </si>
+  <si>
+    <t>23:45:33</t>
+  </si>
+  <si>
+    <t>01:22:02</t>
+  </si>
+  <si>
+    <t>02:59:00</t>
+  </si>
+  <si>
+    <t>22:56:49</t>
+  </si>
+  <si>
+    <t>00:33:05</t>
+  </si>
+  <si>
+    <t>02:09:57</t>
+  </si>
+  <si>
+    <t>22:08:07</t>
+  </si>
+  <si>
+    <t>23:44:06</t>
+  </si>
+  <si>
+    <t>01:20:53</t>
+  </si>
+  <si>
+    <t>02:58:03</t>
+  </si>
+  <si>
+    <t>22:55:07</t>
+  </si>
+  <si>
+    <t>00:31:47</t>
+  </si>
+  <si>
+    <t>02:08:50</t>
+  </si>
+  <si>
+    <t>22:06:09</t>
+  </si>
+  <si>
+    <t>23:42:39</t>
+  </si>
+  <si>
+    <t>01:19:37</t>
+  </si>
+  <si>
+    <t>21:17:12</t>
+  </si>
+  <si>
+    <t>22:53:30</t>
   </si>
   <si>
     <t>01:25:23</t>
@@ -310,61 +301,58 @@
     <t>00:36:40</t>
   </si>
   <si>
-    <t>02:13:13</t>
-  </si>
-  <si>
-    <t>23:48:01</t>
-  </si>
-  <si>
-    <t>01:24:17</t>
-  </si>
-  <si>
-    <t>03:01:25</t>
-  </si>
-  <si>
-    <t>22:59:28</t>
-  </si>
-  <si>
-    <t>00:35:22</t>
-  </si>
-  <si>
-    <t>02:12:18</t>
-  </si>
-  <si>
-    <t>22:11:10</t>
-  </si>
-  <si>
-    <t>23:46:26</t>
-  </si>
-  <si>
-    <t>01:23:13</t>
-  </si>
-  <si>
-    <t>03:00:59</t>
-  </si>
-  <si>
-    <t>22:57:32</t>
-  </si>
-  <si>
-    <t>00:34:07</t>
-  </si>
-  <si>
-    <t>02:11:31</t>
-  </si>
-  <si>
-    <t>22:08:41</t>
-  </si>
-  <si>
-    <t>23:45:01</t>
-  </si>
-  <si>
-    <t>00:40:25</t>
-  </si>
-  <si>
-    <t>02:17:06</t>
-  </si>
-  <si>
-    <t>23:51:40</t>
+    <t>02:13:12</t>
+  </si>
+  <si>
+    <t>23:48:00</t>
+  </si>
+  <si>
+    <t>01:24:16</t>
+  </si>
+  <si>
+    <t>03:01:23</t>
+  </si>
+  <si>
+    <t>22:59:26</t>
+  </si>
+  <si>
+    <t>00:35:19</t>
+  </si>
+  <si>
+    <t>02:12:16</t>
+  </si>
+  <si>
+    <t>22:11:06</t>
+  </si>
+  <si>
+    <t>23:46:22</t>
+  </si>
+  <si>
+    <t>01:23:09</t>
+  </si>
+  <si>
+    <t>03:00:55</t>
+  </si>
+  <si>
+    <t>22:57:27</t>
+  </si>
+  <si>
+    <t>00:34:01</t>
+  </si>
+  <si>
+    <t>02:11:25</t>
+  </si>
+  <si>
+    <t>22:08:34</t>
+  </si>
+  <si>
+    <t>23:44:53</t>
+  </si>
+  <si>
+    <t>21:19:47</t>
+  </si>
+  <si>
+    <t>22:55:44</t>
   </si>
   <si>
     <t>01:28:16</t>
@@ -373,64 +361,64 @@
     <t>03:05:06</t>
   </si>
   <si>
-    <t>00:39:25</t>
-  </si>
-  <si>
-    <t>02:16:13</t>
-  </si>
-  <si>
-    <t>23:50:32</t>
-  </si>
-  <si>
-    <t>01:27:17</t>
-  </si>
-  <si>
-    <t>03:04:05</t>
-  </si>
-  <si>
-    <t>23:01:38</t>
-  </si>
-  <si>
-    <t>00:38:19</t>
-  </si>
-  <si>
-    <t>02:15:08</t>
-  </si>
-  <si>
-    <t>22:12:43</t>
-  </si>
-  <si>
-    <t>23:49:20</t>
-  </si>
-  <si>
-    <t>01:26:08</t>
-  </si>
-  <si>
-    <t>03:02:46</t>
-  </si>
-  <si>
-    <t>23:00:18</t>
-  </si>
-  <si>
-    <t>00:37:06</t>
-  </si>
-  <si>
-    <t>02:13:48</t>
-  </si>
-  <si>
-    <t>22:11:15</t>
-  </si>
-  <si>
-    <t>23:48:00</t>
-  </si>
-  <si>
-    <t>00:42:30</t>
-  </si>
-  <si>
-    <t>02:20:05</t>
-  </si>
-  <si>
-    <t>23:53:03</t>
+    <t>00:39:24</t>
+  </si>
+  <si>
+    <t>02:16:12</t>
+  </si>
+  <si>
+    <t>23:50:31</t>
+  </si>
+  <si>
+    <t>01:27:16</t>
+  </si>
+  <si>
+    <t>03:04:03</t>
+  </si>
+  <si>
+    <t>23:01:35</t>
+  </si>
+  <si>
+    <t>00:38:17</t>
+  </si>
+  <si>
+    <t>02:15:05</t>
+  </si>
+  <si>
+    <t>22:12:39</t>
+  </si>
+  <si>
+    <t>23:49:16</t>
+  </si>
+  <si>
+    <t>01:26:04</t>
+  </si>
+  <si>
+    <t>03:02:42</t>
+  </si>
+  <si>
+    <t>23:00:12</t>
+  </si>
+  <si>
+    <t>00:37:00</t>
+  </si>
+  <si>
+    <t>02:13:42</t>
+  </si>
+  <si>
+    <t>22:11:07</t>
+  </si>
+  <si>
+    <t>23:47:52</t>
+  </si>
+  <si>
+    <t>01:24:38</t>
+  </si>
+  <si>
+    <t>21:22:01</t>
+  </si>
+  <si>
+    <t>22:58:42</t>
   </si>
   <si>
     <t>01:31:10</t>
@@ -442,61 +430,61 @@
     <t>00:42:10</t>
   </si>
   <si>
-    <t>02:19:14</t>
-  </si>
-  <si>
-    <t>23:53:04</t>
-  </si>
-  <si>
-    <t>01:30:18</t>
-  </si>
-  <si>
-    <t>03:06:44</t>
-  </si>
-  <si>
-    <t>23:03:48</t>
-  </si>
-  <si>
-    <t>00:41:18</t>
-  </si>
-  <si>
-    <t>02:17:58</t>
-  </si>
-  <si>
-    <t>22:14:17</t>
-  </si>
-  <si>
-    <t>23:52:14</t>
-  </si>
-  <si>
-    <t>01:29:04</t>
-  </si>
-  <si>
-    <t>03:04:34</t>
-  </si>
-  <si>
-    <t>23:03:04</t>
-  </si>
-  <si>
-    <t>00:40:05</t>
-  </si>
-  <si>
-    <t>02:16:06</t>
-  </si>
-  <si>
-    <t>22:13:49</t>
-  </si>
-  <si>
-    <t>23:51:00</t>
-  </si>
-  <si>
-    <t>00:45:12</t>
-  </si>
-  <si>
-    <t>02:22:21</t>
-  </si>
-  <si>
-    <t>23:56:12</t>
+    <t>02:19:13</t>
+  </si>
+  <si>
+    <t>23:53:02</t>
+  </si>
+  <si>
+    <t>01:30:17</t>
+  </si>
+  <si>
+    <t>03:06:43</t>
+  </si>
+  <si>
+    <t>23:03:46</t>
+  </si>
+  <si>
+    <t>00:41:16</t>
+  </si>
+  <si>
+    <t>02:17:55</t>
+  </si>
+  <si>
+    <t>22:14:13</t>
+  </si>
+  <si>
+    <t>23:52:10</t>
+  </si>
+  <si>
+    <t>01:29:00</t>
+  </si>
+  <si>
+    <t>03:04:30</t>
+  </si>
+  <si>
+    <t>23:02:59</t>
+  </si>
+  <si>
+    <t>00:39:59</t>
+  </si>
+  <si>
+    <t>02:16:00</t>
+  </si>
+  <si>
+    <t>22:13:41</t>
+  </si>
+  <si>
+    <t>23:50:52</t>
+  </si>
+  <si>
+    <t>01:27:13</t>
+  </si>
+  <si>
+    <t>21:24:15</t>
+  </si>
+  <si>
+    <t>23:01:40</t>
   </si>
   <si>
     <t>01:33:28</t>
@@ -505,100 +493,100 @@
     <t>03:10:20</t>
   </si>
   <si>
-    <t>00:44:32</t>
-  </si>
-  <si>
-    <t>02:21:29</t>
-  </si>
-  <si>
-    <t>23:55:32</t>
-  </si>
-  <si>
-    <t>01:32:33</t>
-  </si>
-  <si>
-    <t>03:09:08</t>
-  </si>
-  <si>
-    <t>23:06:27</t>
-  </si>
-  <si>
-    <t>00:43:34</t>
-  </si>
-  <si>
-    <t>02:20:17</t>
-  </si>
-  <si>
-    <t>22:17:17</t>
-  </si>
-  <si>
-    <t>23:54:31</t>
-  </si>
-  <si>
-    <t>01:31:21</t>
-  </si>
-  <si>
-    <t>03:07:26</t>
-  </si>
-  <si>
-    <t>23:05:25</t>
-  </si>
-  <si>
-    <t>00:42:20</t>
-  </si>
-  <si>
-    <t>02:18:40</t>
-  </si>
-  <si>
-    <t>22:16:15</t>
-  </si>
-  <si>
-    <t>23:53:14</t>
-  </si>
-  <si>
-    <t>7°</t>
+    <t>00:44:31</t>
+  </si>
+  <si>
+    <t>02:21:28</t>
+  </si>
+  <si>
+    <t>23:55:30</t>
+  </si>
+  <si>
+    <t>01:32:31</t>
+  </si>
+  <si>
+    <t>03:09:07</t>
+  </si>
+  <si>
+    <t>23:06:25</t>
+  </si>
+  <si>
+    <t>00:43:31</t>
+  </si>
+  <si>
+    <t>02:20:15</t>
+  </si>
+  <si>
+    <t>22:17:13</t>
+  </si>
+  <si>
+    <t>23:54:27</t>
+  </si>
+  <si>
+    <t>01:31:17</t>
+  </si>
+  <si>
+    <t>03:07:22</t>
+  </si>
+  <si>
+    <t>23:05:19</t>
+  </si>
+  <si>
+    <t>00:42:14</t>
+  </si>
+  <si>
+    <t>02:18:34</t>
+  </si>
+  <si>
+    <t>22:16:07</t>
+  </si>
+  <si>
+    <t>23:53:06</t>
+  </si>
+  <si>
+    <t>01:29:39</t>
+  </si>
+  <si>
+    <t>21:26:51</t>
+  </si>
+  <si>
+    <t>23:03:55</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>5°</t>
   </si>
   <si>
     <t>25°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
     <t>13°</t>
   </si>
   <si>
-    <t>00:43:14</t>
-  </si>
-  <si>
-    <t>02:16:07</t>
-  </si>
-  <si>
-    <t>01:29:22</t>
-  </si>
-  <si>
-    <t>03:02:15</t>
+    <t>01:29:21</t>
+  </si>
+  <si>
+    <t>03:02:14</t>
   </si>
   <si>
     <t>00:42:38</t>
@@ -607,34 +595,34 @@
     <t>02:15:31</t>
   </si>
   <si>
-    <t>01:28:52</t>
-  </si>
-  <si>
-    <t>03:01:46</t>
-  </si>
-  <si>
-    <t>02:15:15</t>
-  </si>
-  <si>
-    <t>01:28:53</t>
-  </si>
-  <si>
-    <t>03:01:49</t>
-  </si>
-  <si>
-    <t>02:15:43</t>
+    <t>01:28:51</t>
+  </si>
+  <si>
+    <t>03:01:45</t>
+  </si>
+  <si>
+    <t>00:42:18</t>
+  </si>
+  <si>
+    <t>02:15:12</t>
+  </si>
+  <si>
+    <t>01:28:50</t>
+  </si>
+  <si>
+    <t>02:15:37</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -671,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -698,19 +686,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +704,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,19 +740,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,7 +764,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,31 +776,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,13 +794,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -943,6 +937,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1424,7 +1421,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
@@ -1439,40 +1436,40 @@
         <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.2</v>
+        <v>-18.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>3</v>
+      <c r="Q2" s="8">
+        <v>14</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1495,40 +1492,40 @@
         <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L3" s="4">
-        <v>-13.4</v>
+        <v>-7.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="O3" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="R3" s="9">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1536,13 +1533,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>72</v>
@@ -1551,40 +1548,40 @@
         <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="L4" s="4">
-        <v>-24.9</v>
+        <v>-22.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O4" s="9">
-        <v>30</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>21</v>
-      </c>
-      <c r="R4" s="8">
-        <v>4</v>
+        <v>202</v>
+      </c>
+      <c r="O4" s="10">
+        <v>100</v>
+      </c>
+      <c r="P4" s="11">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>100</v>
+      </c>
+      <c r="R4" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1592,13 +1589,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>73</v>
@@ -1607,40 +1604,40 @@
         <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L5" s="4">
-        <v>-18.8</v>
+        <v>-14</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O5" s="6">
-        <v>7</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>2</v>
-      </c>
-      <c r="R5" s="8">
-        <v>6</v>
+        <v>201</v>
+      </c>
+      <c r="O5" s="10">
+        <v>90</v>
+      </c>
+      <c r="P5" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>69</v>
+      </c>
+      <c r="R5" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1648,13 +1645,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>74</v>
@@ -1663,40 +1660,40 @@
         <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-7.7</v>
+        <v>-25.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O6" s="11">
-        <v>61</v>
-      </c>
-      <c r="P6" s="7">
+        <v>202</v>
+      </c>
+      <c r="O6" s="10">
+        <v>89</v>
+      </c>
+      <c r="P6" s="15">
+        <v>74</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>43</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>27</v>
-      </c>
-      <c r="R6" s="13">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1704,13 +1701,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>75</v>
@@ -1719,40 +1716,40 @@
         <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.9</v>
+        <v>-19.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O7" s="11">
-        <v>100</v>
+        <v>201</v>
+      </c>
+      <c r="O7" s="10">
+        <v>74</v>
       </c>
       <c r="P7" s="14">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="11">
         <v>28</v>
       </c>
-      <c r="Q7" s="15">
-        <v>50</v>
-      </c>
-      <c r="R7" s="16">
-        <v>100</v>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1760,13 +1757,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>76</v>
@@ -1775,40 +1772,40 @@
         <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L8" s="4">
-        <v>-14</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O8" s="11">
-        <v>100</v>
-      </c>
-      <c r="P8" s="17">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>98</v>
-      </c>
-      <c r="R8" s="16">
-        <v>100</v>
+        <v>201</v>
+      </c>
+      <c r="O8" s="10">
+        <v>66</v>
+      </c>
+      <c r="P8" s="14">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>26</v>
+      </c>
+      <c r="R8" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1816,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>77</v>
@@ -1831,40 +1828,40 @@
         <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-25.5</v>
+        <v>-26.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O9" s="11">
-        <v>87</v>
+        <v>202</v>
+      </c>
+      <c r="O9" s="10">
+        <v>97</v>
       </c>
       <c r="P9" s="18">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="19">
-        <v>77</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="R9" s="20">
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1872,13 +1869,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>78</v>
@@ -1887,40 +1884,40 @@
         <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L10" s="4">
-        <v>-19.4</v>
+        <v>-23.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O10" s="11">
-        <v>84</v>
-      </c>
-      <c r="P10" s="20">
-        <v>84</v>
-      </c>
-      <c r="Q10" s="15">
-        <v>50</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O10" s="10">
+        <v>100</v>
+      </c>
+      <c r="P10" s="18">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>65</v>
+      </c>
+      <c r="R10" s="21">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1928,7 +1925,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>48</v>
@@ -1943,40 +1940,40 @@
         <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L11" s="4">
-        <v>-8.300000000000001</v>
+        <v>-14.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O11" s="11">
-        <v>66</v>
-      </c>
-      <c r="P11" s="14">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>2</v>
-      </c>
-      <c r="R11" s="8">
-        <v>4</v>
+        <v>201</v>
+      </c>
+      <c r="O11" s="10">
+        <v>100</v>
+      </c>
+      <c r="P11" s="18">
+        <v>96</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>85</v>
+      </c>
+      <c r="R11" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1984,13 +1981,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>80</v>
@@ -1999,40 +1996,40 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-26.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="11">
-        <v>100</v>
-      </c>
-      <c r="P12" s="21">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>93</v>
-      </c>
-      <c r="R12" s="17">
-        <v>88</v>
+      <c r="O12" s="10">
+        <v>90</v>
+      </c>
+      <c r="P12" s="13">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>35</v>
+      </c>
+      <c r="R12" s="15">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2040,13 +2037,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>81</v>
@@ -2055,40 +2052,40 @@
         <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-23.5</v>
+        <v>-26.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="11">
-        <v>100</v>
-      </c>
-      <c r="P13" s="19">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>94</v>
-      </c>
-      <c r="R13" s="20">
-        <v>85</v>
+        <v>202</v>
+      </c>
+      <c r="O13" s="10">
+        <v>86</v>
+      </c>
+      <c r="P13" s="9">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>43</v>
+      </c>
+      <c r="R13" s="14">
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2096,10 +2093,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>67</v>
@@ -2111,40 +2108,40 @@
         <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-20</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L14" s="4">
-        <v>-14.6</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O14" s="11">
-        <v>100</v>
-      </c>
-      <c r="P14" s="23">
-        <v>72</v>
+        <v>201</v>
+      </c>
+      <c r="O14" s="10">
+        <v>80</v>
+      </c>
+      <c r="P14" s="24">
+        <v>41</v>
       </c>
       <c r="Q14" s="17">
-        <v>92</v>
-      </c>
-      <c r="R14" s="24">
-        <v>67</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="11">
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2152,13 +2149,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>83</v>
@@ -2167,40 +2164,40 @@
         <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="L15" s="4">
-        <v>-25.7</v>
+        <v>-9</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O15" s="11">
-        <v>35</v>
-      </c>
-      <c r="P15" s="25">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>20</v>
-      </c>
-      <c r="R15" s="7">
-        <v>1</v>
+      <c r="O15" s="10">
+        <v>66</v>
+      </c>
+      <c r="P15" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>53</v>
+      </c>
+      <c r="R15" s="25">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2208,13 +2205,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>84</v>
@@ -2223,40 +2220,40 @@
         <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-26.2</v>
+        <v>-27.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" s="11">
-        <v>38</v>
-      </c>
-      <c r="P16" s="25">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>22</v>
-      </c>
-      <c r="R16" s="7">
-        <v>2</v>
+        <v>202</v>
+      </c>
+      <c r="O16" s="10">
+        <v>92</v>
+      </c>
+      <c r="P16" s="26">
+        <v>19</v>
+      </c>
+      <c r="Q16" s="24">
+        <v>41</v>
+      </c>
+      <c r="R16" s="19">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2264,13 +2261,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>85</v>
@@ -2279,40 +2276,40 @@
         <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-24.3</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L17" s="4">
-        <v>-20</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="N17" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O17" s="11">
-        <v>47</v>
-      </c>
-      <c r="P17" s="10">
-        <v>19</v>
-      </c>
-      <c r="Q17" s="12">
-        <v>27</v>
-      </c>
-      <c r="R17" s="26">
-        <v>8</v>
+        <v>202</v>
+      </c>
+      <c r="O17" s="10">
+        <v>83</v>
+      </c>
+      <c r="P17" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>42</v>
+      </c>
+      <c r="R17" s="15">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2320,13 +2317,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>86</v>
@@ -2335,40 +2332,40 @@
         <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="L18" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O18" s="11">
-        <v>66</v>
-      </c>
-      <c r="P18" s="27">
-        <v>41</v>
-      </c>
-      <c r="Q18" s="28">
-        <v>37</v>
-      </c>
-      <c r="R18" s="8">
-        <v>6</v>
+      <c r="O18" s="10">
+        <v>65</v>
+      </c>
+      <c r="P18" s="8">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>38</v>
+      </c>
+      <c r="R18" s="27">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2376,13 +2373,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>87</v>
@@ -2391,40 +2388,40 @@
         <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-27.2</v>
+        <v>-26.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O19" s="11">
-        <v>74</v>
-      </c>
-      <c r="P19" s="12">
-        <v>24</v>
+        <v>202</v>
+      </c>
+      <c r="O19" s="10">
+        <v>81</v>
+      </c>
+      <c r="P19" s="26">
+        <v>22</v>
       </c>
       <c r="Q19" s="14">
-        <v>29</v>
-      </c>
-      <c r="R19" s="18">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="13">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2432,13 +2429,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>88</v>
@@ -2447,40 +2444,40 @@
         <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L20" s="4">
-        <v>-24.2</v>
+        <v>-26.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" s="11">
-        <v>79</v>
-      </c>
-      <c r="P20" s="10">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="12">
-        <v>25</v>
-      </c>
-      <c r="R20" s="18">
-        <v>62</v>
+        <v>202</v>
+      </c>
+      <c r="O20" s="10">
+        <v>75</v>
+      </c>
+      <c r="P20" s="26">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>57</v>
+      </c>
+      <c r="R20" s="9">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2488,55 +2485,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-20.8</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="L21" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O21" s="11">
-        <v>90</v>
-      </c>
-      <c r="P21" s="25">
-        <v>17</v>
+      <c r="O21" s="10">
+        <v>68</v>
+      </c>
+      <c r="P21" s="26">
+        <v>20</v>
       </c>
       <c r="Q21" s="14">
-        <v>30</v>
-      </c>
-      <c r="R21" s="21">
-        <v>80</v>
+        <v>57</v>
+      </c>
+      <c r="R21" s="16">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2544,55 +2541,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-26.3</v>
+        <v>-23.7</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="11">
-        <v>98</v>
-      </c>
-      <c r="P22" s="8">
+        <v>202</v>
+      </c>
+      <c r="O22" s="28">
+        <v>45</v>
+      </c>
+      <c r="P22" s="24">
+        <v>38</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>10</v>
+      </c>
+      <c r="R22" s="29">
         <v>6</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>43</v>
-      </c>
-      <c r="R22" s="17">
-        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2600,55 +2597,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>91</v>
       </c>
       <c r="L23" s="4">
-        <v>-26.9</v>
+        <v>-27.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="11">
-        <v>94</v>
-      </c>
-      <c r="P23" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="14">
-        <v>32</v>
-      </c>
-      <c r="R23" s="20">
-        <v>84</v>
+        <v>202</v>
+      </c>
+      <c r="O23" s="28">
+        <v>27</v>
+      </c>
+      <c r="P23" s="17">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>1</v>
+      </c>
+      <c r="R23" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="213">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260816--01</t>
-  </si>
-  <si>
-    <t>20260816--02</t>
-  </si>
-  <si>
     <t>20260817--01</t>
   </si>
   <si>
@@ -136,70 +130,82 @@
     <t>20260822--03</t>
   </si>
   <si>
-    <t>05:47</t>
+    <t>20260823--01</t>
+  </si>
+  <si>
+    <t>20260823--02</t>
+  </si>
+  <si>
+    <t>20260823--03</t>
+  </si>
+  <si>
+    <t>20260823--04</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>03:07</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>04:28</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>05:02</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:07</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>05:50</t>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>03:23</t>
   </si>
   <si>
     <t>00:00</t>
@@ -211,10 +217,10 @@
     <t>01:26</t>
   </si>
   <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>02:43</t>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>02:44</t>
   </si>
   <si>
     <t>00:10</t>
@@ -226,205 +232,217 @@
     <t>00:23</t>
   </si>
   <si>
-    <t>01:23:06</t>
-  </si>
-  <si>
-    <t>02:59:53</t>
-  </si>
-  <si>
-    <t>00:34:19</t>
+    <t>00:34:20</t>
   </si>
   <si>
     <t>02:10:58</t>
   </si>
   <si>
-    <t>23:45:33</t>
-  </si>
-  <si>
-    <t>01:22:02</t>
+    <t>23:45:34</t>
+  </si>
+  <si>
+    <t>01:22:03</t>
   </si>
   <si>
     <t>02:59:00</t>
   </si>
   <si>
-    <t>22:56:49</t>
-  </si>
-  <si>
-    <t>00:33:05</t>
-  </si>
-  <si>
-    <t>02:09:57</t>
-  </si>
-  <si>
-    <t>22:08:07</t>
-  </si>
-  <si>
-    <t>23:44:06</t>
-  </si>
-  <si>
-    <t>01:20:53</t>
-  </si>
-  <si>
-    <t>02:58:03</t>
-  </si>
-  <si>
-    <t>22:55:07</t>
-  </si>
-  <si>
-    <t>00:31:47</t>
-  </si>
-  <si>
-    <t>02:08:50</t>
-  </si>
-  <si>
-    <t>22:06:09</t>
-  </si>
-  <si>
-    <t>23:42:39</t>
-  </si>
-  <si>
-    <t>01:19:37</t>
-  </si>
-  <si>
-    <t>21:17:12</t>
-  </si>
-  <si>
-    <t>22:53:30</t>
-  </si>
-  <si>
-    <t>01:25:23</t>
-  </si>
-  <si>
-    <t>03:02:08</t>
+    <t>22:56:50</t>
+  </si>
+  <si>
+    <t>00:33:06</t>
+  </si>
+  <si>
+    <t>02:09:59</t>
+  </si>
+  <si>
+    <t>22:08:09</t>
+  </si>
+  <si>
+    <t>23:44:08</t>
+  </si>
+  <si>
+    <t>01:20:55</t>
+  </si>
+  <si>
+    <t>02:58:05</t>
+  </si>
+  <si>
+    <t>22:55:10</t>
+  </si>
+  <si>
+    <t>00:31:50</t>
+  </si>
+  <si>
+    <t>02:08:53</t>
+  </si>
+  <si>
+    <t>22:06:13</t>
+  </si>
+  <si>
+    <t>23:42:43</t>
+  </si>
+  <si>
+    <t>01:19:42</t>
+  </si>
+  <si>
+    <t>21:17:17</t>
+  </si>
+  <si>
+    <t>22:53:35</t>
+  </si>
+  <si>
+    <t>00:30:29</t>
+  </si>
+  <si>
+    <t>20:28:24</t>
+  </si>
+  <si>
+    <t>22:04:27</t>
+  </si>
+  <si>
+    <t>23:41:14</t>
   </si>
   <si>
     <t>00:36:40</t>
   </si>
   <si>
-    <t>02:13:12</t>
+    <t>02:13:13</t>
   </si>
   <si>
     <t>23:48:00</t>
   </si>
   <si>
-    <t>01:24:16</t>
-  </si>
-  <si>
-    <t>03:01:23</t>
-  </si>
-  <si>
-    <t>22:59:26</t>
-  </si>
-  <si>
-    <t>00:35:19</t>
-  </si>
-  <si>
-    <t>02:12:16</t>
-  </si>
-  <si>
-    <t>22:11:06</t>
-  </si>
-  <si>
-    <t>23:46:22</t>
-  </si>
-  <si>
-    <t>01:23:09</t>
-  </si>
-  <si>
-    <t>03:00:55</t>
-  </si>
-  <si>
-    <t>22:57:27</t>
-  </si>
-  <si>
-    <t>00:34:01</t>
-  </si>
-  <si>
-    <t>02:11:25</t>
-  </si>
-  <si>
-    <t>22:08:34</t>
-  </si>
-  <si>
-    <t>23:44:53</t>
-  </si>
-  <si>
-    <t>21:19:47</t>
-  </si>
-  <si>
-    <t>22:55:44</t>
-  </si>
-  <si>
-    <t>01:28:16</t>
-  </si>
-  <si>
-    <t>03:05:06</t>
+    <t>01:24:17</t>
+  </si>
+  <si>
+    <t>03:01:24</t>
+  </si>
+  <si>
+    <t>22:59:27</t>
+  </si>
+  <si>
+    <t>00:35:20</t>
+  </si>
+  <si>
+    <t>02:12:17</t>
+  </si>
+  <si>
+    <t>22:11:08</t>
+  </si>
+  <si>
+    <t>23:46:24</t>
+  </si>
+  <si>
+    <t>01:23:11</t>
+  </si>
+  <si>
+    <t>03:00:57</t>
+  </si>
+  <si>
+    <t>22:57:30</t>
+  </si>
+  <si>
+    <t>00:34:04</t>
+  </si>
+  <si>
+    <t>02:11:28</t>
+  </si>
+  <si>
+    <t>22:08:38</t>
+  </si>
+  <si>
+    <t>23:44:57</t>
+  </si>
+  <si>
+    <t>01:22:07</t>
+  </si>
+  <si>
+    <t>21:19:52</t>
+  </si>
+  <si>
+    <t>22:55:50</t>
+  </si>
+  <si>
+    <t>00:32:48</t>
+  </si>
+  <si>
+    <t>20:31:18</t>
+  </si>
+  <si>
+    <t>22:06:42</t>
+  </si>
+  <si>
+    <t>23:43:30</t>
   </si>
   <si>
     <t>00:39:24</t>
   </si>
   <si>
-    <t>02:16:12</t>
+    <t>02:16:13</t>
   </si>
   <si>
     <t>23:50:31</t>
   </si>
   <si>
-    <t>01:27:16</t>
-  </si>
-  <si>
-    <t>03:04:03</t>
-  </si>
-  <si>
-    <t>23:01:35</t>
-  </si>
-  <si>
-    <t>00:38:17</t>
-  </si>
-  <si>
-    <t>02:15:05</t>
-  </si>
-  <si>
-    <t>22:12:39</t>
-  </si>
-  <si>
-    <t>23:49:16</t>
-  </si>
-  <si>
-    <t>01:26:04</t>
-  </si>
-  <si>
-    <t>03:02:42</t>
-  </si>
-  <si>
-    <t>23:00:12</t>
-  </si>
-  <si>
-    <t>00:37:00</t>
-  </si>
-  <si>
-    <t>02:13:42</t>
-  </si>
-  <si>
-    <t>22:11:07</t>
-  </si>
-  <si>
-    <t>23:47:52</t>
-  </si>
-  <si>
-    <t>01:24:38</t>
-  </si>
-  <si>
-    <t>21:22:01</t>
-  </si>
-  <si>
-    <t>22:58:42</t>
-  </si>
-  <si>
-    <t>01:31:10</t>
-  </si>
-  <si>
-    <t>03:08:04</t>
+    <t>01:27:17</t>
+  </si>
+  <si>
+    <t>03:04:04</t>
+  </si>
+  <si>
+    <t>23:01:37</t>
+  </si>
+  <si>
+    <t>00:38:18</t>
+  </si>
+  <si>
+    <t>02:15:07</t>
+  </si>
+  <si>
+    <t>22:12:41</t>
+  </si>
+  <si>
+    <t>23:49:18</t>
+  </si>
+  <si>
+    <t>01:26:06</t>
+  </si>
+  <si>
+    <t>03:02:45</t>
+  </si>
+  <si>
+    <t>23:00:15</t>
+  </si>
+  <si>
+    <t>00:37:03</t>
+  </si>
+  <si>
+    <t>02:13:45</t>
+  </si>
+  <si>
+    <t>22:11:11</t>
+  </si>
+  <si>
+    <t>23:47:56</t>
+  </si>
+  <si>
+    <t>01:24:42</t>
+  </si>
+  <si>
+    <t>21:22:06</t>
+  </si>
+  <si>
+    <t>22:58:47</t>
+  </si>
+  <si>
+    <t>00:35:35</t>
+  </si>
+  <si>
+    <t>20:32:59</t>
+  </si>
+  <si>
+    <t>22:09:36</t>
   </si>
   <si>
     <t>00:42:10</t>
@@ -433,64 +451,67 @@
     <t>02:19:13</t>
   </si>
   <si>
-    <t>23:53:02</t>
-  </si>
-  <si>
-    <t>01:30:17</t>
-  </si>
-  <si>
-    <t>03:06:43</t>
-  </si>
-  <si>
-    <t>23:03:46</t>
-  </si>
-  <si>
-    <t>00:41:16</t>
-  </si>
-  <si>
-    <t>02:17:55</t>
-  </si>
-  <si>
-    <t>22:14:13</t>
-  </si>
-  <si>
-    <t>23:52:10</t>
-  </si>
-  <si>
-    <t>01:29:00</t>
-  </si>
-  <si>
-    <t>03:04:30</t>
-  </si>
-  <si>
-    <t>23:02:59</t>
-  </si>
-  <si>
-    <t>00:39:59</t>
-  </si>
-  <si>
-    <t>02:16:00</t>
-  </si>
-  <si>
-    <t>22:13:41</t>
-  </si>
-  <si>
-    <t>23:50:52</t>
-  </si>
-  <si>
-    <t>01:27:13</t>
-  </si>
-  <si>
-    <t>21:24:15</t>
-  </si>
-  <si>
-    <t>23:01:40</t>
-  </si>
-  <si>
-    <t>01:33:28</t>
-  </si>
-  <si>
-    <t>03:10:20</t>
+    <t>23:53:03</t>
+  </si>
+  <si>
+    <t>01:30:18</t>
+  </si>
+  <si>
+    <t>03:06:44</t>
+  </si>
+  <si>
+    <t>23:03:47</t>
+  </si>
+  <si>
+    <t>00:41:17</t>
+  </si>
+  <si>
+    <t>02:17:57</t>
+  </si>
+  <si>
+    <t>22:14:15</t>
+  </si>
+  <si>
+    <t>23:52:12</t>
+  </si>
+  <si>
+    <t>01:29:02</t>
+  </si>
+  <si>
+    <t>03:04:32</t>
+  </si>
+  <si>
+    <t>23:03:02</t>
+  </si>
+  <si>
+    <t>00:40:02</t>
+  </si>
+  <si>
+    <t>02:16:03</t>
+  </si>
+  <si>
+    <t>22:13:45</t>
+  </si>
+  <si>
+    <t>23:50:56</t>
+  </si>
+  <si>
+    <t>01:27:18</t>
+  </si>
+  <si>
+    <t>21:24:20</t>
+  </si>
+  <si>
+    <t>23:01:46</t>
+  </si>
+  <si>
+    <t>00:38:22</t>
+  </si>
+  <si>
+    <t>20:34:41</t>
+  </si>
+  <si>
+    <t>22:12:30</t>
   </si>
   <si>
     <t>00:44:31</t>
@@ -499,130 +520,136 @@
     <t>02:21:28</t>
   </si>
   <si>
-    <t>23:55:30</t>
-  </si>
-  <si>
-    <t>01:32:31</t>
-  </si>
-  <si>
-    <t>03:09:07</t>
-  </si>
-  <si>
-    <t>23:06:25</t>
-  </si>
-  <si>
-    <t>00:43:31</t>
-  </si>
-  <si>
-    <t>02:20:15</t>
-  </si>
-  <si>
-    <t>22:17:13</t>
-  </si>
-  <si>
-    <t>23:54:27</t>
-  </si>
-  <si>
-    <t>01:31:17</t>
-  </si>
-  <si>
-    <t>03:07:22</t>
-  </si>
-  <si>
-    <t>23:05:19</t>
-  </si>
-  <si>
-    <t>00:42:14</t>
-  </si>
-  <si>
-    <t>02:18:34</t>
-  </si>
-  <si>
-    <t>22:16:07</t>
-  </si>
-  <si>
-    <t>23:53:06</t>
-  </si>
-  <si>
-    <t>01:29:39</t>
-  </si>
-  <si>
-    <t>21:26:51</t>
-  </si>
-  <si>
-    <t>23:03:55</t>
-  </si>
-  <si>
-    <t>22°</t>
+    <t>23:55:31</t>
+  </si>
+  <si>
+    <t>01:32:32</t>
+  </si>
+  <si>
+    <t>03:09:08</t>
+  </si>
+  <si>
+    <t>23:06:26</t>
+  </si>
+  <si>
+    <t>00:43:32</t>
+  </si>
+  <si>
+    <t>02:20:16</t>
+  </si>
+  <si>
+    <t>22:17:16</t>
+  </si>
+  <si>
+    <t>23:54:29</t>
+  </si>
+  <si>
+    <t>01:31:19</t>
+  </si>
+  <si>
+    <t>03:07:24</t>
+  </si>
+  <si>
+    <t>23:05:22</t>
+  </si>
+  <si>
+    <t>00:42:17</t>
+  </si>
+  <si>
+    <t>02:18:38</t>
+  </si>
+  <si>
+    <t>22:16:11</t>
+  </si>
+  <si>
+    <t>23:53:11</t>
+  </si>
+  <si>
+    <t>01:29:43</t>
+  </si>
+  <si>
+    <t>21:26:56</t>
+  </si>
+  <si>
+    <t>23:04:01</t>
+  </si>
+  <si>
+    <t>00:40:42</t>
+  </si>
+  <si>
+    <t>20:37:36</t>
+  </si>
+  <si>
+    <t>22:14:47</t>
+  </si>
+  <si>
+    <t>23:51:35</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>25°</t>
   </si>
   <si>
     <t>11°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
     <t>13°</t>
   </si>
   <si>
-    <t>01:29:21</t>
-  </si>
-  <si>
-    <t>03:02:14</t>
-  </si>
-  <si>
     <t>00:42:38</t>
   </si>
   <si>
     <t>02:15:31</t>
   </si>
   <si>
-    <t>01:28:51</t>
+    <t>01:28:52</t>
   </si>
   <si>
     <t>03:01:45</t>
   </si>
   <si>
-    <t>00:42:18</t>
-  </si>
-  <si>
-    <t>02:15:12</t>
-  </si>
-  <si>
-    <t>01:28:50</t>
-  </si>
-  <si>
-    <t>02:15:37</t>
+    <t>00:42:19</t>
+  </si>
+  <si>
+    <t>02:15:13</t>
+  </si>
+  <si>
+    <t>03:01:47</t>
+  </si>
+  <si>
+    <t>02:15:40</t>
+  </si>
+  <si>
+    <t>01:29:51</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -659,7 +686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,7 +701,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +749,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +791,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,109 +815,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -934,12 +949,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1421,55 +1430,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L2" s="4">
-        <v>-18.8</v>
+        <v>-22.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="O2" s="6">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="8">
-        <v>14</v>
-      </c>
-      <c r="R2" s="7">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1477,55 +1486,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L3" s="4">
-        <v>-7.7</v>
+        <v>-14</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="O3" s="6">
-        <v>10</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="P3" s="8">
+        <v>74</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>43</v>
       </c>
       <c r="R3" s="9">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1533,55 +1542,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-25.5</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O4" s="6">
+        <v>98</v>
+      </c>
+      <c r="P4" s="11">
         <v>94</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-22.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O4" s="10">
-        <v>100</v>
-      </c>
-      <c r="P4" s="11">
-        <v>28</v>
-      </c>
       <c r="Q4" s="12">
-        <v>100</v>
-      </c>
-      <c r="R4" s="12">
-        <v>100</v>
+        <v>56</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1589,55 +1598,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="L5" s="4">
-        <v>-14</v>
+        <v>-19.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O5" s="10">
-        <v>90</v>
-      </c>
-      <c r="P5" s="11">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>69</v>
-      </c>
-      <c r="R5" s="14">
-        <v>55</v>
+        <v>211</v>
+      </c>
+      <c r="O5" s="6">
+        <v>92</v>
+      </c>
+      <c r="P5" s="14">
+        <v>92</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>20</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1645,55 +1654,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="L6" s="4">
-        <v>-25.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O6" s="10">
-        <v>89</v>
-      </c>
-      <c r="P6" s="15">
-        <v>74</v>
+        <v>211</v>
+      </c>
+      <c r="O6" s="6">
+        <v>75</v>
+      </c>
+      <c r="P6" s="8">
+        <v>75</v>
       </c>
       <c r="Q6" s="16">
-        <v>43</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="R6" s="13">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1701,55 +1710,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="L7" s="4">
-        <v>-19.4</v>
+        <v>-26.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O7" s="10">
-        <v>74</v>
+        <v>210</v>
+      </c>
+      <c r="O7" s="6">
+        <v>99</v>
       </c>
       <c r="P7" s="14">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="Q7" s="11">
-        <v>28</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="R7" s="17">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1757,55 +1766,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="L8" s="4">
-        <v>-8.300000000000001</v>
+        <v>-23.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O8" s="10">
-        <v>66</v>
-      </c>
-      <c r="P8" s="14">
-        <v>55</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>26</v>
-      </c>
-      <c r="R8" s="7">
-        <v>2</v>
+        <v>210</v>
+      </c>
+      <c r="O8" s="6">
+        <v>90</v>
+      </c>
+      <c r="P8" s="18">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>62</v>
+      </c>
+      <c r="R8" s="17">
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1813,55 +1822,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="L9" s="4">
-        <v>-26.5</v>
+        <v>-14.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O9" s="10">
-        <v>97</v>
-      </c>
-      <c r="P9" s="18">
-        <v>97</v>
-      </c>
-      <c r="Q9" s="19">
-        <v>92</v>
-      </c>
-      <c r="R9" s="20">
-        <v>58</v>
+        <v>211</v>
+      </c>
+      <c r="O9" s="6">
+        <v>98</v>
+      </c>
+      <c r="P9" s="8">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>63</v>
+      </c>
+      <c r="R9" s="21">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1869,55 +1878,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O10" s="6">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-23.5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O10" s="10">
-        <v>100</v>
-      </c>
-      <c r="P10" s="18">
-        <v>97</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>65</v>
-      </c>
-      <c r="R10" s="21">
-        <v>80</v>
+      <c r="P10" s="22">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>49</v>
+      </c>
+      <c r="R10" s="20">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1925,55 +1934,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="L11" s="4">
-        <v>-14.6</v>
+        <v>-26.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O11" s="10">
+        <v>210</v>
+      </c>
+      <c r="O11" s="6">
         <v>100</v>
       </c>
-      <c r="P11" s="18">
-        <v>96</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>85</v>
-      </c>
-      <c r="R11" s="12">
-        <v>100</v>
+      <c r="P11" s="15">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>50</v>
+      </c>
+      <c r="R11" s="23">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1981,55 +1990,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="L12" s="4">
-        <v>-25.7</v>
+        <v>-20</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O12" s="10">
-        <v>90</v>
-      </c>
-      <c r="P12" s="13">
-        <v>69</v>
-      </c>
-      <c r="Q12" s="23">
-        <v>35</v>
-      </c>
-      <c r="R12" s="15">
-        <v>73</v>
+        <v>211</v>
+      </c>
+      <c r="O12" s="6">
+        <v>97</v>
+      </c>
+      <c r="P12" s="24">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>94</v>
+      </c>
+      <c r="R12" s="10">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2037,55 +2046,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="L13" s="4">
-        <v>-26.2</v>
+        <v>-9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O13" s="10">
-        <v>86</v>
-      </c>
-      <c r="P13" s="9">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>43</v>
-      </c>
-      <c r="R13" s="14">
-        <v>56</v>
+        <v>212</v>
+      </c>
+      <c r="O13" s="6">
+        <v>99</v>
+      </c>
+      <c r="P13" s="12">
+        <v>57</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>51</v>
+      </c>
+      <c r="R13" s="25">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2093,55 +2102,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="L14" s="4">
-        <v>-20</v>
+        <v>-27.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O14" s="10">
-        <v>80</v>
-      </c>
-      <c r="P14" s="24">
-        <v>41</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>26</v>
-      </c>
-      <c r="R14" s="11">
-        <v>28</v>
+        <v>210</v>
+      </c>
+      <c r="O14" s="6">
+        <v>100</v>
+      </c>
+      <c r="P14" s="26">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>16</v>
+      </c>
+      <c r="R14" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2149,55 +2158,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="L15" s="4">
-        <v>-9</v>
+        <v>-24.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O15" s="10">
-        <v>66</v>
-      </c>
-      <c r="P15" s="8">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>53</v>
-      </c>
-      <c r="R15" s="25">
-        <v>12</v>
+        <v>210</v>
+      </c>
+      <c r="O15" s="6">
+        <v>100</v>
+      </c>
+      <c r="P15" s="16">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>16</v>
+      </c>
+      <c r="R15" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2205,55 +2214,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="L16" s="4">
-        <v>-27.2</v>
+        <v>-15.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O16" s="10">
-        <v>92</v>
-      </c>
-      <c r="P16" s="26">
+        <v>211</v>
+      </c>
+      <c r="O16" s="6">
+        <v>93</v>
+      </c>
+      <c r="P16" s="15">
         <v>19</v>
       </c>
-      <c r="Q16" s="24">
-        <v>41</v>
-      </c>
-      <c r="R16" s="19">
-        <v>90</v>
+      <c r="Q16" s="16">
+        <v>12</v>
+      </c>
+      <c r="R16" s="18">
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2261,55 +2270,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L17" s="4">
-        <v>-24.3</v>
+        <v>-26.3</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O17" s="10">
-        <v>83</v>
-      </c>
-      <c r="P17" s="8">
-        <v>16</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>42</v>
-      </c>
-      <c r="R17" s="15">
-        <v>77</v>
+        <v>210</v>
+      </c>
+      <c r="O17" s="6">
+        <v>97</v>
+      </c>
+      <c r="P17" s="11">
+        <v>94</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>36</v>
+      </c>
+      <c r="R17" s="26">
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2317,55 +2326,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>198</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>-15.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="10">
-        <v>65</v>
+        <v>210</v>
+      </c>
+      <c r="O18" s="6">
+        <v>81</v>
       </c>
       <c r="P18" s="8">
-        <v>13</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>38</v>
-      </c>
-      <c r="R18" s="27">
-        <v>52</v>
+        <v>75</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>24</v>
+      </c>
+      <c r="R18" s="16">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2376,52 +2385,52 @@
         <v>21</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="L19" s="4">
-        <v>-26.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O19" s="10">
-        <v>81</v>
-      </c>
-      <c r="P19" s="26">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="14">
-        <v>57</v>
-      </c>
-      <c r="R19" s="13">
-        <v>68</v>
+        <v>210</v>
+      </c>
+      <c r="O19" s="6">
+        <v>53</v>
+      </c>
+      <c r="P19" s="7">
+        <v>36</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="24">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2429,55 +2438,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L20" s="4">
-        <v>-26.9</v>
+        <v>-23.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O20" s="10">
-        <v>75</v>
-      </c>
-      <c r="P20" s="26">
-        <v>21</v>
-      </c>
-      <c r="Q20" s="14">
-        <v>57</v>
-      </c>
-      <c r="R20" s="9">
-        <v>63</v>
+        <v>210</v>
+      </c>
+      <c r="O20" s="6">
+        <v>98</v>
+      </c>
+      <c r="P20" s="20">
+        <v>66</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>93</v>
+      </c>
+      <c r="R20" s="22">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2485,55 +2494,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L21" s="4">
-        <v>-20.8</v>
+        <v>-27.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O21" s="10">
-        <v>68</v>
-      </c>
-      <c r="P21" s="26">
+        <v>210</v>
+      </c>
+      <c r="O21" s="6">
+        <v>100</v>
+      </c>
+      <c r="P21" s="8">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>100</v>
+      </c>
+      <c r="R21" s="15">
         <v>20</v>
-      </c>
-      <c r="Q21" s="14">
-        <v>57</v>
-      </c>
-      <c r="R21" s="16">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2541,55 +2550,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-25</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O22" s="6">
         <v>90</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-23.7</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O22" s="28">
-        <v>45</v>
-      </c>
-      <c r="P22" s="24">
-        <v>38</v>
-      </c>
-      <c r="Q22" s="25">
-        <v>10</v>
-      </c>
-      <c r="R22" s="29">
-        <v>6</v>
+      <c r="P22" s="23">
+        <v>48</v>
+      </c>
+      <c r="Q22" s="18">
+        <v>83</v>
+      </c>
+      <c r="R22" s="23">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2597,114 +2606,226 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O23" s="6">
+        <v>74</v>
+      </c>
+      <c r="P23" s="23">
+        <v>51</v>
+      </c>
+      <c r="Q23" s="23">
+        <v>52</v>
+      </c>
+      <c r="R23" s="19">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-26.9</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O24" s="6">
+        <v>81</v>
+      </c>
+      <c r="P24" s="27">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>76</v>
+      </c>
+      <c r="R24" s="25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-27.8</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O23" s="28">
+      <c r="B25" s="2">
         <v>27</v>
       </c>
-      <c r="P23" s="17">
-        <v>23</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>1</v>
-      </c>
-      <c r="R23" s="7">
-        <v>2</v>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-27.6</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O25" s="6">
+        <v>83</v>
+      </c>
+      <c r="P25" s="15">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="21">
+        <v>69</v>
+      </c>
+      <c r="R25" s="25">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2723,12 +2844,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2745,22 +2866,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="219">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260817--01</t>
-  </si>
-  <si>
-    <t>20260817--02</t>
-  </si>
-  <si>
-    <t>20260817--03</t>
-  </si>
-  <si>
     <t>20260818--01</t>
   </si>
   <si>
@@ -142,18 +133,21 @@
     <t>20260823--04</t>
   </si>
   <si>
-    <t>05:30</t>
+    <t>20260824--01</t>
+  </si>
+  <si>
+    <t>20260824--02</t>
+  </si>
+  <si>
+    <t>20260824--03</t>
+  </si>
+  <si>
+    <t>20260824--04</t>
   </si>
   <si>
     <t>06:00</t>
   </si>
   <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
     <t>05:20</t>
   </si>
   <si>
@@ -163,154 +157,157 @@
     <t>05:57</t>
   </si>
   <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>03:07</t>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:06</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>03:23</t>
   </si>
   <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>03:23</t>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>04:59</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:42</t>
-  </si>
-  <si>
-    <t>01:26</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>02:44</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>02:45</t>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>00:11</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>00:23</t>
   </si>
   <si>
-    <t>00:34:20</t>
-  </si>
-  <si>
-    <t>02:10:58</t>
-  </si>
-  <si>
-    <t>23:45:34</t>
-  </si>
-  <si>
     <t>01:22:03</t>
   </si>
   <si>
     <t>02:59:00</t>
   </si>
   <si>
-    <t>22:56:50</t>
-  </si>
-  <si>
-    <t>00:33:06</t>
-  </si>
-  <si>
-    <t>02:09:59</t>
-  </si>
-  <si>
-    <t>22:08:09</t>
-  </si>
-  <si>
-    <t>23:44:08</t>
-  </si>
-  <si>
-    <t>01:20:55</t>
-  </si>
-  <si>
-    <t>02:58:05</t>
-  </si>
-  <si>
-    <t>22:55:10</t>
-  </si>
-  <si>
-    <t>00:31:50</t>
-  </si>
-  <si>
-    <t>02:08:53</t>
-  </si>
-  <si>
-    <t>22:06:13</t>
-  </si>
-  <si>
-    <t>23:42:43</t>
-  </si>
-  <si>
-    <t>01:19:42</t>
-  </si>
-  <si>
-    <t>21:17:17</t>
-  </si>
-  <si>
-    <t>22:53:35</t>
-  </si>
-  <si>
-    <t>00:30:29</t>
-  </si>
-  <si>
-    <t>20:28:24</t>
-  </si>
-  <si>
-    <t>22:04:27</t>
-  </si>
-  <si>
-    <t>23:41:14</t>
-  </si>
-  <si>
-    <t>00:36:40</t>
-  </si>
-  <si>
-    <t>02:13:13</t>
-  </si>
-  <si>
-    <t>23:48:00</t>
+    <t>22:56:49</t>
+  </si>
+  <si>
+    <t>00:33:05</t>
+  </si>
+  <si>
+    <t>02:09:58</t>
+  </si>
+  <si>
+    <t>22:08:08</t>
+  </si>
+  <si>
+    <t>23:44:07</t>
+  </si>
+  <si>
+    <t>01:20:54</t>
+  </si>
+  <si>
+    <t>02:58:04</t>
+  </si>
+  <si>
+    <t>22:55:09</t>
+  </si>
+  <si>
+    <t>00:31:49</t>
+  </si>
+  <si>
+    <t>02:08:52</t>
+  </si>
+  <si>
+    <t>22:06:11</t>
+  </si>
+  <si>
+    <t>23:42:42</t>
+  </si>
+  <si>
+    <t>01:19:40</t>
+  </si>
+  <si>
+    <t>21:17:15</t>
+  </si>
+  <si>
+    <t>22:53:33</t>
+  </si>
+  <si>
+    <t>00:30:26</t>
+  </si>
+  <si>
+    <t>20:28:21</t>
+  </si>
+  <si>
+    <t>22:04:23</t>
+  </si>
+  <si>
+    <t>23:41:11</t>
+  </si>
+  <si>
+    <t>01:18:22</t>
+  </si>
+  <si>
+    <t>19:39:32</t>
+  </si>
+  <si>
+    <t>21:15:13</t>
+  </si>
+  <si>
+    <t>22:51:54</t>
   </si>
   <si>
     <t>01:24:17</t>
@@ -334,55 +331,58 @@
     <t>23:46:24</t>
   </si>
   <si>
-    <t>01:23:11</t>
-  </si>
-  <si>
-    <t>03:00:57</t>
-  </si>
-  <si>
-    <t>22:57:30</t>
-  </si>
-  <si>
-    <t>00:34:04</t>
-  </si>
-  <si>
-    <t>02:11:28</t>
-  </si>
-  <si>
-    <t>22:08:38</t>
-  </si>
-  <si>
-    <t>23:44:57</t>
-  </si>
-  <si>
-    <t>01:22:07</t>
-  </si>
-  <si>
-    <t>21:19:52</t>
-  </si>
-  <si>
-    <t>22:55:50</t>
-  </si>
-  <si>
-    <t>00:32:48</t>
-  </si>
-  <si>
-    <t>20:31:18</t>
-  </si>
-  <si>
-    <t>22:06:42</t>
-  </si>
-  <si>
-    <t>23:43:30</t>
-  </si>
-  <si>
-    <t>00:39:24</t>
-  </si>
-  <si>
-    <t>02:16:13</t>
-  </si>
-  <si>
-    <t>23:50:31</t>
+    <t>01:23:10</t>
+  </si>
+  <si>
+    <t>03:00:56</t>
+  </si>
+  <si>
+    <t>22:57:28</t>
+  </si>
+  <si>
+    <t>00:34:03</t>
+  </si>
+  <si>
+    <t>02:11:26</t>
+  </si>
+  <si>
+    <t>22:08:36</t>
+  </si>
+  <si>
+    <t>23:44:55</t>
+  </si>
+  <si>
+    <t>01:22:05</t>
+  </si>
+  <si>
+    <t>21:19:49</t>
+  </si>
+  <si>
+    <t>22:55:47</t>
+  </si>
+  <si>
+    <t>00:32:45</t>
+  </si>
+  <si>
+    <t>20:31:15</t>
+  </si>
+  <si>
+    <t>22:06:39</t>
+  </si>
+  <si>
+    <t>23:43:27</t>
+  </si>
+  <si>
+    <t>01:21:19</t>
+  </si>
+  <si>
+    <t>19:43:48</t>
+  </si>
+  <si>
+    <t>21:17:32</t>
+  </si>
+  <si>
+    <t>22:54:08</t>
   </si>
   <si>
     <t>01:27:17</t>
@@ -391,70 +391,73 @@
     <t>03:04:04</t>
   </si>
   <si>
-    <t>23:01:37</t>
+    <t>23:01:36</t>
   </si>
   <si>
     <t>00:38:18</t>
   </si>
   <si>
-    <t>02:15:07</t>
-  </si>
-  <si>
-    <t>22:12:41</t>
-  </si>
-  <si>
-    <t>23:49:18</t>
+    <t>02:15:06</t>
+  </si>
+  <si>
+    <t>22:12:40</t>
+  </si>
+  <si>
+    <t>23:49:17</t>
   </si>
   <si>
     <t>01:26:06</t>
   </si>
   <si>
-    <t>03:02:45</t>
-  </si>
-  <si>
-    <t>23:00:15</t>
-  </si>
-  <si>
-    <t>00:37:03</t>
-  </si>
-  <si>
-    <t>02:13:45</t>
-  </si>
-  <si>
-    <t>22:11:11</t>
-  </si>
-  <si>
-    <t>23:47:56</t>
-  </si>
-  <si>
-    <t>01:24:42</t>
-  </si>
-  <si>
-    <t>21:22:06</t>
-  </si>
-  <si>
-    <t>22:58:47</t>
-  </si>
-  <si>
-    <t>00:35:35</t>
-  </si>
-  <si>
-    <t>20:32:59</t>
-  </si>
-  <si>
-    <t>22:09:36</t>
-  </si>
-  <si>
-    <t>00:42:10</t>
-  </si>
-  <si>
-    <t>02:19:13</t>
-  </si>
-  <si>
-    <t>23:53:03</t>
-  </si>
-  <si>
-    <t>01:30:18</t>
+    <t>03:02:44</t>
+  </si>
+  <si>
+    <t>23:00:14</t>
+  </si>
+  <si>
+    <t>00:37:01</t>
+  </si>
+  <si>
+    <t>02:13:44</t>
+  </si>
+  <si>
+    <t>22:11:09</t>
+  </si>
+  <si>
+    <t>23:47:54</t>
+  </si>
+  <si>
+    <t>01:24:40</t>
+  </si>
+  <si>
+    <t>21:22:03</t>
+  </si>
+  <si>
+    <t>22:58:45</t>
+  </si>
+  <si>
+    <t>00:35:32</t>
+  </si>
+  <si>
+    <t>20:32:56</t>
+  </si>
+  <si>
+    <t>22:09:33</t>
+  </si>
+  <si>
+    <t>23:46:21</t>
+  </si>
+  <si>
+    <t>01:22:57</t>
+  </si>
+  <si>
+    <t>21:20:18</t>
+  </si>
+  <si>
+    <t>22:57:06</t>
+  </si>
+  <si>
+    <t>01:30:17</t>
   </si>
   <si>
     <t>03:06:44</t>
@@ -466,13 +469,13 @@
     <t>00:41:17</t>
   </si>
   <si>
-    <t>02:17:57</t>
-  </si>
-  <si>
-    <t>22:14:15</t>
-  </si>
-  <si>
-    <t>23:52:12</t>
+    <t>02:17:56</t>
+  </si>
+  <si>
+    <t>22:14:14</t>
+  </si>
+  <si>
+    <t>23:52:11</t>
   </si>
   <si>
     <t>01:29:02</t>
@@ -481,55 +484,61 @@
     <t>03:04:32</t>
   </si>
   <si>
-    <t>23:03:02</t>
-  </si>
-  <si>
-    <t>00:40:02</t>
-  </si>
-  <si>
-    <t>02:16:03</t>
-  </si>
-  <si>
-    <t>22:13:45</t>
-  </si>
-  <si>
-    <t>23:50:56</t>
-  </si>
-  <si>
-    <t>01:27:18</t>
-  </si>
-  <si>
-    <t>21:24:20</t>
-  </si>
-  <si>
-    <t>23:01:46</t>
-  </si>
-  <si>
-    <t>00:38:22</t>
-  </si>
-  <si>
-    <t>20:34:41</t>
-  </si>
-  <si>
-    <t>22:12:30</t>
-  </si>
-  <si>
-    <t>00:44:31</t>
-  </si>
-  <si>
-    <t>02:21:28</t>
-  </si>
-  <si>
-    <t>23:55:31</t>
+    <t>23:03:00</t>
+  </si>
+  <si>
+    <t>00:40:01</t>
+  </si>
+  <si>
+    <t>02:16:02</t>
+  </si>
+  <si>
+    <t>22:13:43</t>
+  </si>
+  <si>
+    <t>23:50:54</t>
+  </si>
+  <si>
+    <t>01:27:16</t>
+  </si>
+  <si>
+    <t>21:24:18</t>
+  </si>
+  <si>
+    <t>23:01:43</t>
+  </si>
+  <si>
+    <t>00:38:19</t>
+  </si>
+  <si>
+    <t>20:34:38</t>
+  </si>
+  <si>
+    <t>22:12:27</t>
+  </si>
+  <si>
+    <t>23:49:14</t>
+  </si>
+  <si>
+    <t>01:24:34</t>
+  </si>
+  <si>
+    <t>19:43:53</t>
+  </si>
+  <si>
+    <t>21:23:06</t>
+  </si>
+  <si>
+    <t>23:00:03</t>
   </si>
   <si>
     <t>01:32:32</t>
   </si>
   <si>
-    <t>03:09:08</t>
-  </si>
-  <si>
-    <t>23:06:26</t>
+    <t>03:09:07</t>
+  </si>
+  <si>
+    <t>23:06:25</t>
   </si>
   <si>
     <t>00:43:32</t>
@@ -538,69 +547,75 @@
     <t>02:20:16</t>
   </si>
   <si>
-    <t>22:17:16</t>
-  </si>
-  <si>
-    <t>23:54:29</t>
-  </si>
-  <si>
-    <t>01:31:19</t>
-  </si>
-  <si>
-    <t>03:07:24</t>
-  </si>
-  <si>
-    <t>23:05:22</t>
-  </si>
-  <si>
-    <t>00:42:17</t>
-  </si>
-  <si>
-    <t>02:18:38</t>
-  </si>
-  <si>
-    <t>22:16:11</t>
-  </si>
-  <si>
-    <t>23:53:11</t>
-  </si>
-  <si>
-    <t>01:29:43</t>
-  </si>
-  <si>
-    <t>21:26:56</t>
-  </si>
-  <si>
-    <t>23:04:01</t>
-  </si>
-  <si>
-    <t>00:40:42</t>
-  </si>
-  <si>
-    <t>20:37:36</t>
-  </si>
-  <si>
-    <t>22:14:47</t>
-  </si>
-  <si>
-    <t>23:51:35</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>28°</t>
+    <t>22:17:15</t>
+  </si>
+  <si>
+    <t>23:54:28</t>
+  </si>
+  <si>
+    <t>01:31:18</t>
+  </si>
+  <si>
+    <t>03:07:23</t>
+  </si>
+  <si>
+    <t>23:05:21</t>
+  </si>
+  <si>
+    <t>00:42:16</t>
+  </si>
+  <si>
+    <t>02:18:36</t>
+  </si>
+  <si>
+    <t>22:16:09</t>
+  </si>
+  <si>
+    <t>23:53:09</t>
+  </si>
+  <si>
+    <t>01:29:41</t>
+  </si>
+  <si>
+    <t>21:26:54</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>00:40:39</t>
+  </si>
+  <si>
+    <t>20:37:32</t>
+  </si>
+  <si>
+    <t>22:14:43</t>
+  </si>
+  <si>
+    <t>23:51:31</t>
+  </si>
+  <si>
+    <t>01:27:32</t>
+  </si>
+  <si>
+    <t>19:48:05</t>
+  </si>
+  <si>
+    <t>21:25:25</t>
+  </si>
+  <si>
+    <t>23:02:18</t>
+  </si>
+  <si>
+    <t>20°</t>
+  </si>
+  <si>
+    <t>12°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>20°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
@@ -613,10 +628,7 @@
     <t>13°</t>
   </si>
   <si>
-    <t>00:42:38</t>
-  </si>
-  <si>
-    <t>02:15:31</t>
+    <t>3°</t>
   </si>
   <si>
     <t>01:28:52</t>
@@ -631,25 +643,31 @@
     <t>02:15:13</t>
   </si>
   <si>
-    <t>03:01:47</t>
-  </si>
-  <si>
-    <t>02:15:40</t>
-  </si>
-  <si>
-    <t>01:29:51</t>
+    <t>01:28:51</t>
+  </si>
+  <si>
+    <t>03:01:46</t>
+  </si>
+  <si>
+    <t>02:15:39</t>
+  </si>
+  <si>
+    <t>01:29:49</t>
+  </si>
+  <si>
+    <t>19:40:23</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -686,7 +704,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -707,13 +725,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,43 +767,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,7 +803,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -791,43 +833,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -946,9 +958,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1352,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1430,55 +1439,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.9</v>
+        <v>-19.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="O2" s="6">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P2" s="7">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="8">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1486,55 +1495,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="O3" s="6">
+        <v>87</v>
+      </c>
+      <c r="P3" s="7">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>14</v>
+      </c>
+      <c r="R3" s="11">
         <v>30</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-14</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="6">
-        <v>96</v>
-      </c>
-      <c r="P3" s="8">
-        <v>74</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>43</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1542,55 +1551,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L4" s="4">
-        <v>-25.5</v>
+        <v>-26.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O4" s="6">
-        <v>98</v>
-      </c>
-      <c r="P4" s="11">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
+        <v>93</v>
       </c>
       <c r="Q4" s="12">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="R4" s="13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1598,55 +1607,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="L5" s="4">
-        <v>-19.4</v>
+        <v>-23.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="O5" s="6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P5" s="14">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q5" s="15">
-        <v>20</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="R5" s="12">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1654,55 +1663,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L6" s="4">
-        <v>-8.300000000000001</v>
+        <v>-14.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O6" s="6">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="P6" s="8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="16">
-        <v>12</v>
-      </c>
-      <c r="R6" s="13">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="R6" s="17">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1710,55 +1719,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>-26.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O7" s="6">
-        <v>99</v>
-      </c>
-      <c r="P7" s="14">
         <v>90</v>
       </c>
-      <c r="Q7" s="11">
-        <v>95</v>
-      </c>
-      <c r="R7" s="17">
-        <v>41</v>
+      <c r="P7" s="18">
+        <v>42</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>87</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1766,55 +1775,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.5</v>
+        <v>-26.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O8" s="6">
-        <v>90</v>
-      </c>
-      <c r="P8" s="18">
-        <v>87</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>62</v>
-      </c>
-      <c r="R8" s="17">
-        <v>42</v>
+        <v>61</v>
+      </c>
+      <c r="P8" s="20">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>49</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1822,55 +1831,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="L9" s="4">
-        <v>-14.6</v>
+        <v>-20</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="8">
-        <v>73</v>
-      </c>
-      <c r="Q9" s="20">
-        <v>63</v>
+        <v>96</v>
+      </c>
+      <c r="P9" s="19">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>94</v>
       </c>
       <c r="R9" s="21">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1878,55 +1887,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="L10" s="4">
-        <v>-25.7</v>
+        <v>-9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="22">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>49</v>
-      </c>
-      <c r="R10" s="20">
-        <v>63</v>
+        <v>87</v>
+      </c>
+      <c r="P10" s="17">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>84</v>
+      </c>
+      <c r="R10" s="18">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1934,55 +1943,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L11" s="4">
-        <v>-26.2</v>
+        <v>-27.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O11" s="6">
         <v>100</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="21">
         <v>20</v>
       </c>
-      <c r="Q11" s="23">
-        <v>50</v>
-      </c>
-      <c r="R11" s="23">
-        <v>50</v>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1990,55 +1999,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="L12" s="4">
-        <v>-20</v>
+        <v>-24.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="O12" s="6">
-        <v>97</v>
-      </c>
-      <c r="P12" s="24">
-        <v>28</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>94</v>
-      </c>
-      <c r="R12" s="10">
-        <v>45</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="21">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>2</v>
+      </c>
+      <c r="R12" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2046,55 +2055,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>198</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="L13" s="4">
-        <v>-9</v>
+        <v>-15.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="O13" s="6">
-        <v>99</v>
-      </c>
-      <c r="P13" s="12">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="23">
-        <v>51</v>
-      </c>
-      <c r="R13" s="25">
-        <v>78</v>
+        <v>94</v>
+      </c>
+      <c r="P13" s="10">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="12">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2102,54 +2111,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-27.2</v>
+        <v>-26.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O14" s="6">
         <v>100</v>
       </c>
-      <c r="P14" s="26">
-        <v>7</v>
-      </c>
-      <c r="Q14" s="22">
-        <v>16</v>
-      </c>
-      <c r="R14" s="9">
+      <c r="P14" s="16">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>100</v>
+      </c>
+      <c r="R14" s="13">
         <v>100</v>
       </c>
     </row>
@@ -2158,54 +2167,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4">
-        <v>-24.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O15" s="6">
         <v>100</v>
       </c>
-      <c r="P15" s="16">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>16</v>
-      </c>
-      <c r="R15" s="9">
+      <c r="P15" s="22">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>100</v>
+      </c>
+      <c r="R15" s="13">
         <v>100</v>
       </c>
     </row>
@@ -2214,55 +2223,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L16" s="4">
-        <v>-15.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="O16" s="6">
-        <v>93</v>
-      </c>
-      <c r="P16" s="15">
-        <v>19</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>12</v>
-      </c>
-      <c r="R16" s="18">
-        <v>87</v>
+        <v>100</v>
+      </c>
+      <c r="P16" s="23">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>100</v>
+      </c>
+      <c r="R16" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2270,55 +2279,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-23.7</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O17" s="6">
+        <v>65</v>
+      </c>
+      <c r="P17" s="24">
+        <v>65</v>
+      </c>
+      <c r="Q17" s="21">
         <v>21</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-26.3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O17" s="6">
-        <v>97</v>
-      </c>
-      <c r="P17" s="11">
-        <v>94</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>36</v>
-      </c>
-      <c r="R17" s="26">
-        <v>6</v>
+      <c r="R17" s="23">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2326,55 +2335,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-27.8</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O18" s="6">
         <v>64</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-26.9</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O18" s="6">
-        <v>81</v>
-      </c>
-      <c r="P18" s="8">
-        <v>75</v>
-      </c>
-      <c r="Q18" s="27">
-        <v>24</v>
-      </c>
-      <c r="R18" s="16">
-        <v>12</v>
+      <c r="P18" s="24">
+        <v>64</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>17</v>
+      </c>
+      <c r="R18" s="10">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2382,55 +2391,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-20.7</v>
+        <v>-25</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O19" s="6">
-        <v>53</v>
-      </c>
-      <c r="P19" s="7">
-        <v>36</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="24">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="P19" s="18">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="21">
+        <v>22</v>
+      </c>
+      <c r="R19" s="21">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2438,55 +2447,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L20" s="4">
-        <v>-23.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O20" s="6">
-        <v>98</v>
-      </c>
-      <c r="P20" s="20">
-        <v>66</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>93</v>
-      </c>
-      <c r="R20" s="22">
-        <v>17</v>
+        <v>54</v>
+      </c>
+      <c r="P20" s="7">
+        <v>54</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>35</v>
+      </c>
+      <c r="R20" s="18">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2494,55 +2503,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-26.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O21" s="6">
         <v>61</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-27.8</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O21" s="6">
-        <v>100</v>
-      </c>
-      <c r="P21" s="8">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>100</v>
-      </c>
-      <c r="R21" s="15">
-        <v>20</v>
+      <c r="P21" s="16">
+        <v>48</v>
+      </c>
+      <c r="Q21" s="18">
+        <v>40</v>
+      </c>
+      <c r="R21" s="26">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2550,55 +2559,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4">
-        <v>-25</v>
+        <v>-27.6</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O22" s="6">
-        <v>90</v>
-      </c>
-      <c r="P22" s="23">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="18">
-        <v>83</v>
-      </c>
-      <c r="R22" s="23">
-        <v>49</v>
+        <v>69</v>
+      </c>
+      <c r="P22" s="22">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>31</v>
+      </c>
+      <c r="R22" s="26">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2612,49 +2621,49 @@
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L23" s="4">
-        <v>-19.6</v>
+        <v>-21.5</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="O23" s="6">
-        <v>74</v>
-      </c>
-      <c r="P23" s="23">
-        <v>51</v>
+        <v>81</v>
+      </c>
+      <c r="P23" s="25">
+        <v>36</v>
       </c>
       <c r="Q23" s="23">
-        <v>52</v>
-      </c>
-      <c r="R23" s="19">
-        <v>59</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="26">
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2662,55 +2671,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="L24" s="4">
-        <v>-26.9</v>
+        <v>-14.3</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O24" s="6">
-        <v>81</v>
-      </c>
-      <c r="P24" s="27">
-        <v>24</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>76</v>
-      </c>
-      <c r="R24" s="25">
-        <v>80</v>
+        <v>100</v>
+      </c>
+      <c r="P24" s="14">
+        <v>91</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>86</v>
+      </c>
+      <c r="R24" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2718,114 +2727,170 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L25" s="4">
-        <v>-27.6</v>
+        <v>-24.3</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O25" s="6">
-        <v>83</v>
-      </c>
-      <c r="P25" s="15">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="21">
-        <v>69</v>
-      </c>
-      <c r="R25" s="25">
+        <v>100</v>
+      </c>
+      <c r="P25" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>80</v>
+      </c>
+      <c r="R25" s="13">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>30</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-28.5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O26" s="6">
+        <v>100</v>
+      </c>
+      <c r="P26" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q26" s="8">
         <v>79</v>
+      </c>
+      <c r="R26" s="12">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2844,12 +2909,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2866,22 +2931,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="213">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260818--01</t>
-  </si>
-  <si>
-    <t>20260818--02</t>
-  </si>
-  <si>
-    <t>20260818--03</t>
-  </si>
-  <si>
     <t>20260819--01</t>
   </si>
   <si>
@@ -142,16 +133,16 @@
     <t>20260824--03</t>
   </si>
   <si>
-    <t>20260824--04</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>04:20</t>
+    <t>20260825--01</t>
+  </si>
+  <si>
+    <t>20260825--02</t>
+  </si>
+  <si>
+    <t>20260825--03</t>
+  </si>
+  <si>
+    <t>20260825--04</t>
   </si>
   <si>
     <t>05:57</t>
@@ -190,34 +181,31 @@
     <t>05:11</t>
   </si>
   <si>
-    <t>04:29</t>
+    <t>04:28</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>03:16</t>
+  </si>
+  <si>
     <t>05:34</t>
   </si>
   <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>04:59</t>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>05:04</t>
   </si>
   <si>
     <t>00:00</t>
@@ -235,439 +223,433 @@
     <t>00:23</t>
   </si>
   <si>
-    <t>01:22:03</t>
-  </si>
-  <si>
-    <t>02:59:00</t>
-  </si>
-  <si>
-    <t>22:56:49</t>
-  </si>
-  <si>
     <t>00:33:05</t>
   </si>
   <si>
-    <t>02:09:58</t>
-  </si>
-  <si>
-    <t>22:08:08</t>
-  </si>
-  <si>
-    <t>23:44:07</t>
-  </si>
-  <si>
-    <t>01:20:54</t>
-  </si>
-  <si>
-    <t>02:58:04</t>
-  </si>
-  <si>
-    <t>22:55:09</t>
-  </si>
-  <si>
-    <t>00:31:49</t>
-  </si>
-  <si>
-    <t>02:08:52</t>
-  </si>
-  <si>
-    <t>22:06:11</t>
-  </si>
-  <si>
-    <t>23:42:42</t>
-  </si>
-  <si>
-    <t>01:19:40</t>
-  </si>
-  <si>
-    <t>21:17:15</t>
-  </si>
-  <si>
-    <t>22:53:33</t>
-  </si>
-  <si>
-    <t>00:30:26</t>
-  </si>
-  <si>
-    <t>20:28:21</t>
-  </si>
-  <si>
-    <t>22:04:23</t>
-  </si>
-  <si>
-    <t>23:41:11</t>
-  </si>
-  <si>
-    <t>01:18:22</t>
-  </si>
-  <si>
-    <t>19:39:32</t>
-  </si>
-  <si>
-    <t>21:15:13</t>
-  </si>
-  <si>
-    <t>22:51:54</t>
-  </si>
-  <si>
-    <t>01:24:17</t>
-  </si>
-  <si>
-    <t>03:01:24</t>
-  </si>
-  <si>
-    <t>22:59:27</t>
-  </si>
-  <si>
-    <t>00:35:20</t>
-  </si>
-  <si>
-    <t>02:12:17</t>
-  </si>
-  <si>
-    <t>22:11:08</t>
-  </si>
-  <si>
-    <t>23:46:24</t>
-  </si>
-  <si>
-    <t>01:23:10</t>
-  </si>
-  <si>
-    <t>03:00:56</t>
-  </si>
-  <si>
-    <t>22:57:28</t>
-  </si>
-  <si>
-    <t>00:34:03</t>
-  </si>
-  <si>
-    <t>02:11:26</t>
-  </si>
-  <si>
-    <t>22:08:36</t>
-  </si>
-  <si>
-    <t>23:44:55</t>
-  </si>
-  <si>
-    <t>01:22:05</t>
-  </si>
-  <si>
-    <t>21:19:49</t>
-  </si>
-  <si>
-    <t>22:55:47</t>
-  </si>
-  <si>
-    <t>00:32:45</t>
-  </si>
-  <si>
-    <t>20:31:15</t>
-  </si>
-  <si>
-    <t>22:06:39</t>
-  </si>
-  <si>
-    <t>23:43:27</t>
-  </si>
-  <si>
-    <t>01:21:19</t>
-  </si>
-  <si>
-    <t>19:43:48</t>
-  </si>
-  <si>
-    <t>21:17:32</t>
-  </si>
-  <si>
-    <t>22:54:08</t>
-  </si>
-  <si>
-    <t>01:27:17</t>
-  </si>
-  <si>
-    <t>03:04:04</t>
-  </si>
-  <si>
-    <t>23:01:36</t>
-  </si>
-  <si>
-    <t>00:38:18</t>
-  </si>
-  <si>
-    <t>02:15:06</t>
-  </si>
-  <si>
-    <t>22:12:40</t>
-  </si>
-  <si>
-    <t>23:49:17</t>
-  </si>
-  <si>
-    <t>01:26:06</t>
-  </si>
-  <si>
-    <t>03:02:44</t>
-  </si>
-  <si>
-    <t>23:00:14</t>
-  </si>
-  <si>
-    <t>00:37:01</t>
-  </si>
-  <si>
-    <t>02:13:44</t>
-  </si>
-  <si>
-    <t>22:11:09</t>
-  </si>
-  <si>
-    <t>23:47:54</t>
-  </si>
-  <si>
-    <t>01:24:40</t>
-  </si>
-  <si>
-    <t>21:22:03</t>
-  </si>
-  <si>
-    <t>22:58:45</t>
-  </si>
-  <si>
-    <t>00:35:32</t>
-  </si>
-  <si>
-    <t>20:32:56</t>
-  </si>
-  <si>
-    <t>22:09:33</t>
+    <t>02:09:57</t>
+  </si>
+  <si>
+    <t>22:08:06</t>
+  </si>
+  <si>
+    <t>23:44:05</t>
+  </si>
+  <si>
+    <t>01:20:51</t>
+  </si>
+  <si>
+    <t>02:58:01</t>
+  </si>
+  <si>
+    <t>22:55:03</t>
+  </si>
+  <si>
+    <t>00:31:43</t>
+  </si>
+  <si>
+    <t>02:08:46</t>
+  </si>
+  <si>
+    <t>22:06:01</t>
+  </si>
+  <si>
+    <t>23:42:32</t>
+  </si>
+  <si>
+    <t>01:19:29</t>
+  </si>
+  <si>
+    <t>21:17:00</t>
+  </si>
+  <si>
+    <t>22:53:18</t>
+  </si>
+  <si>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>20:28:00</t>
+  </si>
+  <si>
+    <t>22:04:02</t>
+  </si>
+  <si>
+    <t>23:40:49</t>
+  </si>
+  <si>
+    <t>01:17:59</t>
+  </si>
+  <si>
+    <t>21:14:44</t>
+  </si>
+  <si>
+    <t>22:51:24</t>
+  </si>
+  <si>
+    <t>00:28:28</t>
+  </si>
+  <si>
+    <t>20:25:26</t>
+  </si>
+  <si>
+    <t>22:01:57</t>
+  </si>
+  <si>
+    <t>23:38:55</t>
+  </si>
+  <si>
+    <t>00:35:19</t>
+  </si>
+  <si>
+    <t>02:12:16</t>
+  </si>
+  <si>
+    <t>22:11:05</t>
   </si>
   <si>
     <t>23:46:21</t>
   </si>
   <si>
-    <t>01:22:57</t>
-  </si>
-  <si>
-    <t>21:20:18</t>
-  </si>
-  <si>
-    <t>22:57:06</t>
-  </si>
-  <si>
-    <t>01:30:17</t>
-  </si>
-  <si>
-    <t>03:06:44</t>
-  </si>
-  <si>
-    <t>23:03:47</t>
-  </si>
-  <si>
-    <t>00:41:17</t>
-  </si>
-  <si>
-    <t>02:17:56</t>
-  </si>
-  <si>
-    <t>22:14:14</t>
-  </si>
-  <si>
-    <t>23:52:11</t>
-  </si>
-  <si>
-    <t>01:29:02</t>
-  </si>
-  <si>
-    <t>03:04:32</t>
-  </si>
-  <si>
-    <t>23:03:00</t>
-  </si>
-  <si>
-    <t>00:40:01</t>
-  </si>
-  <si>
-    <t>02:16:02</t>
-  </si>
-  <si>
-    <t>22:13:43</t>
-  </si>
-  <si>
-    <t>23:50:54</t>
-  </si>
-  <si>
-    <t>01:27:16</t>
-  </si>
-  <si>
-    <t>21:24:18</t>
-  </si>
-  <si>
-    <t>23:01:43</t>
-  </si>
-  <si>
-    <t>00:38:19</t>
-  </si>
-  <si>
-    <t>20:34:38</t>
-  </si>
-  <si>
-    <t>22:12:27</t>
+    <t>01:23:07</t>
+  </si>
+  <si>
+    <t>03:00:53</t>
+  </si>
+  <si>
+    <t>22:57:23</t>
+  </si>
+  <si>
+    <t>00:33:57</t>
+  </si>
+  <si>
+    <t>02:11:20</t>
+  </si>
+  <si>
+    <t>22:08:26</t>
+  </si>
+  <si>
+    <t>23:44:45</t>
+  </si>
+  <si>
+    <t>01:21:54</t>
+  </si>
+  <si>
+    <t>21:19:35</t>
+  </si>
+  <si>
+    <t>22:55:32</t>
+  </si>
+  <si>
+    <t>00:32:30</t>
+  </si>
+  <si>
+    <t>20:30:54</t>
+  </si>
+  <si>
+    <t>22:06:18</t>
+  </si>
+  <si>
+    <t>23:43:05</t>
+  </si>
+  <si>
+    <t>01:20:56</t>
+  </si>
+  <si>
+    <t>21:17:03</t>
+  </si>
+  <si>
+    <t>22:53:39</t>
+  </si>
+  <si>
+    <t>00:31:04</t>
+  </si>
+  <si>
+    <t>20:27:50</t>
+  </si>
+  <si>
+    <t>22:04:11</t>
+  </si>
+  <si>
+    <t>23:41:21</t>
+  </si>
+  <si>
+    <t>00:38:17</t>
+  </si>
+  <si>
+    <t>02:15:05</t>
+  </si>
+  <si>
+    <t>22:12:38</t>
   </si>
   <si>
     <t>23:49:14</t>
   </si>
   <si>
-    <t>01:24:34</t>
-  </si>
-  <si>
-    <t>19:43:53</t>
-  </si>
-  <si>
-    <t>21:23:06</t>
-  </si>
-  <si>
-    <t>23:00:03</t>
-  </si>
-  <si>
-    <t>01:32:32</t>
-  </si>
-  <si>
-    <t>03:09:07</t>
-  </si>
-  <si>
-    <t>23:06:25</t>
-  </si>
-  <si>
-    <t>00:43:32</t>
-  </si>
-  <si>
-    <t>02:20:16</t>
-  </si>
-  <si>
-    <t>22:17:15</t>
-  </si>
-  <si>
-    <t>23:54:28</t>
-  </si>
-  <si>
-    <t>01:31:18</t>
-  </si>
-  <si>
-    <t>03:07:23</t>
-  </si>
-  <si>
-    <t>23:05:21</t>
-  </si>
-  <si>
-    <t>00:42:16</t>
-  </si>
-  <si>
-    <t>02:18:36</t>
-  </si>
-  <si>
-    <t>22:16:09</t>
-  </si>
-  <si>
-    <t>23:53:09</t>
-  </si>
-  <si>
-    <t>01:29:41</t>
-  </si>
-  <si>
-    <t>21:26:54</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
-  </si>
-  <si>
-    <t>00:40:39</t>
-  </si>
-  <si>
-    <t>20:37:32</t>
-  </si>
-  <si>
-    <t>22:14:43</t>
-  </si>
-  <si>
-    <t>23:51:31</t>
-  </si>
-  <si>
-    <t>01:27:32</t>
-  </si>
-  <si>
-    <t>19:48:05</t>
-  </si>
-  <si>
-    <t>21:25:25</t>
-  </si>
-  <si>
-    <t>23:02:18</t>
-  </si>
-  <si>
-    <t>20°</t>
+    <t>01:26:03</t>
+  </si>
+  <si>
+    <t>03:02:41</t>
+  </si>
+  <si>
+    <t>23:00:08</t>
+  </si>
+  <si>
+    <t>00:36:56</t>
+  </si>
+  <si>
+    <t>02:13:38</t>
+  </si>
+  <si>
+    <t>22:10:59</t>
+  </si>
+  <si>
+    <t>23:47:44</t>
+  </si>
+  <si>
+    <t>01:24:30</t>
+  </si>
+  <si>
+    <t>21:21:49</t>
+  </si>
+  <si>
+    <t>22:58:29</t>
+  </si>
+  <si>
+    <t>00:35:17</t>
+  </si>
+  <si>
+    <t>20:32:35</t>
+  </si>
+  <si>
+    <t>22:09:11</t>
+  </si>
+  <si>
+    <t>23:45:59</t>
+  </si>
+  <si>
+    <t>01:22:34</t>
+  </si>
+  <si>
+    <t>21:19:50</t>
+  </si>
+  <si>
+    <t>22:56:36</t>
+  </si>
+  <si>
+    <t>00:33:16</t>
+  </si>
+  <si>
+    <t>20:30:25</t>
+  </si>
+  <si>
+    <t>22:07:10</t>
+  </si>
+  <si>
+    <t>23:43:53</t>
+  </si>
+  <si>
+    <t>00:41:16</t>
+  </si>
+  <si>
+    <t>02:17:55</t>
+  </si>
+  <si>
+    <t>22:14:11</t>
+  </si>
+  <si>
+    <t>23:52:08</t>
+  </si>
+  <si>
+    <t>01:28:59</t>
+  </si>
+  <si>
+    <t>03:04:29</t>
+  </si>
+  <si>
+    <t>23:02:55</t>
+  </si>
+  <si>
+    <t>00:39:55</t>
+  </si>
+  <si>
+    <t>02:15:56</t>
+  </si>
+  <si>
+    <t>22:13:33</t>
+  </si>
+  <si>
+    <t>23:50:44</t>
+  </si>
+  <si>
+    <t>01:27:05</t>
+  </si>
+  <si>
+    <t>21:24:03</t>
+  </si>
+  <si>
+    <t>23:01:28</t>
+  </si>
+  <si>
+    <t>00:38:03</t>
+  </si>
+  <si>
+    <t>20:34:16</t>
+  </si>
+  <si>
+    <t>22:12:05</t>
+  </si>
+  <si>
+    <t>23:48:52</t>
+  </si>
+  <si>
+    <t>01:24:12</t>
+  </si>
+  <si>
+    <t>21:22:37</t>
+  </si>
+  <si>
+    <t>22:59:34</t>
+  </si>
+  <si>
+    <t>00:35:28</t>
+  </si>
+  <si>
+    <t>20:33:01</t>
+  </si>
+  <si>
+    <t>22:10:08</t>
+  </si>
+  <si>
+    <t>23:46:25</t>
+  </si>
+  <si>
+    <t>00:43:31</t>
+  </si>
+  <si>
+    <t>02:20:15</t>
+  </si>
+  <si>
+    <t>22:17:12</t>
+  </si>
+  <si>
+    <t>23:54:25</t>
+  </si>
+  <si>
+    <t>01:31:15</t>
+  </si>
+  <si>
+    <t>03:07:20</t>
+  </si>
+  <si>
+    <t>23:05:15</t>
+  </si>
+  <si>
+    <t>00:42:10</t>
+  </si>
+  <si>
+    <t>02:18:30</t>
+  </si>
+  <si>
+    <t>22:15:59</t>
+  </si>
+  <si>
+    <t>23:52:59</t>
+  </si>
+  <si>
+    <t>01:29:31</t>
+  </si>
+  <si>
+    <t>21:26:39</t>
+  </si>
+  <si>
+    <t>23:03:43</t>
+  </si>
+  <si>
+    <t>00:40:23</t>
+  </si>
+  <si>
+    <t>20:37:11</t>
+  </si>
+  <si>
+    <t>22:14:22</t>
+  </si>
+  <si>
+    <t>23:51:09</t>
+  </si>
+  <si>
+    <t>01:27:10</t>
+  </si>
+  <si>
+    <t>21:24:56</t>
+  </si>
+  <si>
+    <t>23:01:49</t>
+  </si>
+  <si>
+    <t>00:38:05</t>
+  </si>
+  <si>
+    <t>20:35:26</t>
+  </si>
+  <si>
+    <t>22:12:23</t>
+  </si>
+  <si>
+    <t>23:48:51</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>13°</t>
   </si>
   <si>
     <t>12°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>01:28:52</t>
-  </si>
-  <si>
-    <t>03:01:45</t>
-  </si>
-  <si>
-    <t>00:42:19</t>
-  </si>
-  <si>
-    <t>02:15:13</t>
-  </si>
-  <si>
-    <t>01:28:51</t>
-  </si>
-  <si>
-    <t>03:01:46</t>
-  </si>
-  <si>
-    <t>02:15:39</t>
-  </si>
-  <si>
-    <t>01:29:49</t>
-  </si>
-  <si>
-    <t>19:40:23</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>00:42:18</t>
+  </si>
+  <si>
+    <t>02:15:12</t>
+  </si>
+  <si>
+    <t>01:28:48</t>
+  </si>
+  <si>
+    <t>03:01:43</t>
+  </si>
+  <si>
+    <t>02:15:33</t>
+  </si>
+  <si>
+    <t>01:29:39</t>
+  </si>
+  <si>
+    <t>20:26:32</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -704,7 +686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -725,7 +707,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,109 +827,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,6 +946,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1439,55 +1430,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-23.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O2" s="6">
+        <v>100</v>
+      </c>
+      <c r="P2" s="7">
         <v>66</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-19.4</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O2" s="6">
-        <v>89</v>
-      </c>
-      <c r="P2" s="7">
-        <v>54</v>
-      </c>
       <c r="Q2" s="8">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="R2" s="9">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1495,55 +1486,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L3" s="4">
-        <v>-8.300000000000001</v>
+        <v>-14.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="O3" s="6">
         <v>87</v>
       </c>
-      <c r="P3" s="7">
-        <v>55</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>14</v>
-      </c>
-      <c r="R3" s="11">
-        <v>30</v>
+      <c r="P3" s="10">
+        <v>51</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>20</v>
+      </c>
+      <c r="R3" s="9">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1551,55 +1542,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-26.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="P4" s="12">
-        <v>93</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>93</v>
-      </c>
-      <c r="R4" s="13">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>47</v>
+      </c>
+      <c r="R4" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1607,55 +1598,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-26.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O5" s="6">
         <v>68</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-23.5</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="14">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>72</v>
-      </c>
-      <c r="R5" s="12">
-        <v>97</v>
+      <c r="P5" s="15">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>47</v>
+      </c>
+      <c r="R5" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1663,55 +1654,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L6" s="4">
-        <v>-14.6</v>
+        <v>-20</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="O6" s="6">
-        <v>97</v>
-      </c>
-      <c r="P6" s="8">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="16">
+        <v>81</v>
+      </c>
+      <c r="P6" s="7">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>63</v>
+      </c>
+      <c r="R6" s="10">
         <v>52</v>
-      </c>
-      <c r="R6" s="17">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1719,55 +1710,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="L7" s="4">
-        <v>-25.7</v>
+        <v>-9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="O7" s="6">
-        <v>90</v>
-      </c>
-      <c r="P7" s="18">
-        <v>42</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>87</v>
-      </c>
-      <c r="R7" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P7" s="16">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>74</v>
+      </c>
+      <c r="R7" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1775,55 +1766,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L8" s="4">
-        <v>-26.2</v>
+        <v>-27.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O8" s="6">
-        <v>61</v>
-      </c>
-      <c r="P8" s="20">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>49</v>
-      </c>
-      <c r="R8" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="12">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>6</v>
+      </c>
+      <c r="R8" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1831,55 +1822,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-20</v>
+        <v>-24.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="O9" s="6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P9" s="19">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="12">
-        <v>94</v>
-      </c>
-      <c r="R9" s="21">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1887,55 +1878,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="L10" s="4">
-        <v>-9</v>
+        <v>-15.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="O10" s="6">
-        <v>87</v>
-      </c>
-      <c r="P10" s="17">
-        <v>76</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>84</v>
-      </c>
-      <c r="R10" s="18">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="P10" s="16">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>83</v>
+      </c>
+      <c r="R10" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1943,55 +1934,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L11" s="4">
-        <v>-27.2</v>
+        <v>-26.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O11" s="6">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="P11" s="21">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>100</v>
+        <v>62</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>74</v>
+      </c>
+      <c r="R11" s="10">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1999,55 +1990,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-24.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="21">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>2</v>
-      </c>
-      <c r="R12" s="13">
-        <v>100</v>
+        <v>87</v>
+      </c>
+      <c r="P12" s="20">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>76</v>
+      </c>
+      <c r="R12" s="10">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2055,55 +2046,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L13" s="4">
-        <v>-15.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="O13" s="6">
-        <v>94</v>
-      </c>
-      <c r="P13" s="10">
+        <v>47</v>
+      </c>
+      <c r="P13" s="14">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>40</v>
+      </c>
+      <c r="R13" s="23">
         <v>13</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2111,55 +2102,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.3</v>
+        <v>-23.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O14" s="6">
-        <v>100</v>
-      </c>
-      <c r="P14" s="16">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>100</v>
-      </c>
-      <c r="R14" s="13">
-        <v>100</v>
+        <v>78</v>
+      </c>
+      <c r="P14" s="23">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>66</v>
+      </c>
+      <c r="R14" s="12">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2167,55 +2158,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-26.9</v>
+        <v>-27.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O15" s="6">
-        <v>100</v>
-      </c>
-      <c r="P15" s="22">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>100</v>
-      </c>
-      <c r="R15" s="13">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="P15" s="10">
+        <v>49</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>35</v>
+      </c>
+      <c r="R15" s="24">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2223,55 +2214,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-20.7</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O16" s="6">
-        <v>100</v>
-      </c>
-      <c r="P16" s="23">
-        <v>10</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>100</v>
-      </c>
-      <c r="R16" s="13">
-        <v>100</v>
+        <v>76</v>
+      </c>
+      <c r="P16" s="18">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="19">
+        <v>71</v>
+      </c>
+      <c r="R16" s="11">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2279,55 +2270,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O17" s="6">
+        <v>96</v>
+      </c>
+      <c r="P17" s="13">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="19">
         <v>68</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-23.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O17" s="6">
-        <v>65</v>
-      </c>
-      <c r="P17" s="24">
-        <v>65</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>21</v>
-      </c>
-      <c r="R17" s="23">
-        <v>11</v>
+      <c r="R17" s="17">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2335,55 +2326,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-27.8</v>
+        <v>-26.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O18" s="6">
-        <v>64</v>
-      </c>
-      <c r="P18" s="24">
-        <v>64</v>
+        <v>99</v>
+      </c>
+      <c r="P18" s="21">
+        <v>60</v>
       </c>
       <c r="Q18" s="10">
-        <v>17</v>
-      </c>
-      <c r="R18" s="10">
-        <v>14</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="25">
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2391,55 +2382,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-25</v>
+        <v>-27.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O19" s="6">
-        <v>58</v>
-      </c>
-      <c r="P19" s="18">
-        <v>42</v>
+        <v>99</v>
+      </c>
+      <c r="P19" s="13">
+        <v>43</v>
       </c>
       <c r="Q19" s="21">
-        <v>22</v>
-      </c>
-      <c r="R19" s="21">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="R19" s="9">
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2450,52 +2441,52 @@
         <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-19.6</v>
+        <v>-21.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="O20" s="6">
-        <v>54</v>
-      </c>
-      <c r="P20" s="7">
-        <v>54</v>
-      </c>
-      <c r="Q20" s="25">
-        <v>35</v>
-      </c>
-      <c r="R20" s="18">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="P20" s="24">
+        <v>11</v>
+      </c>
+      <c r="Q20" s="26">
+        <v>81</v>
+      </c>
+      <c r="R20" s="8">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2503,55 +2494,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L21" s="4">
-        <v>-26.9</v>
+        <v>-24.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O21" s="6">
-        <v>61</v>
-      </c>
-      <c r="P21" s="16">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="18">
-        <v>40</v>
-      </c>
-      <c r="R21" s="26">
-        <v>61</v>
+        <v>81</v>
+      </c>
+      <c r="P21" s="12">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>39</v>
+      </c>
+      <c r="R21" s="7">
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2559,55 +2550,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-27.6</v>
+        <v>-28.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O22" s="6">
-        <v>69</v>
-      </c>
-      <c r="P22" s="22">
-        <v>44</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>31</v>
-      </c>
-      <c r="R22" s="26">
-        <v>61</v>
+        <v>73</v>
+      </c>
+      <c r="P22" s="12">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>34</v>
+      </c>
+      <c r="R22" s="27">
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2615,55 +2606,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-25.7</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O23" s="6">
         <v>68</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-21.5</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O23" s="6">
-        <v>81</v>
-      </c>
-      <c r="P23" s="25">
-        <v>36</v>
-      </c>
-      <c r="Q23" s="23">
-        <v>12</v>
-      </c>
-      <c r="R23" s="26">
-        <v>60</v>
+      <c r="P23" s="12">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>43</v>
+      </c>
+      <c r="R23" s="10">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2671,55 +2662,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="L24" s="4">
-        <v>-14.3</v>
+        <v>-20</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="O24" s="6">
         <v>100</v>
       </c>
-      <c r="P24" s="14">
+      <c r="P24" s="9">
+        <v>96</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>100</v>
+      </c>
+      <c r="R24" s="25">
         <v>91</v>
-      </c>
-      <c r="Q24" s="19">
-        <v>86</v>
-      </c>
-      <c r="R24" s="13">
-        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2727,55 +2718,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L25" s="4">
-        <v>-24.3</v>
+        <v>-27.5</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O25" s="6">
         <v>100</v>
       </c>
-      <c r="P25" s="8">
-        <v>80</v>
+      <c r="P25" s="9">
+        <v>93</v>
       </c>
       <c r="Q25" s="8">
-        <v>80</v>
-      </c>
-      <c r="R25" s="13">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="R25" s="17">
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2783,55 +2774,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L26" s="4">
-        <v>-28.5</v>
+        <v>-28.3</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O26" s="6">
         <v>100</v>
       </c>
-      <c r="P26" s="8">
-        <v>80</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>79</v>
-      </c>
-      <c r="R26" s="12">
-        <v>97</v>
+      <c r="P26" s="9">
+        <v>94</v>
+      </c>
+      <c r="Q26" s="25">
+        <v>88</v>
+      </c>
+      <c r="R26" s="19">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="208">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260819--01</t>
-  </si>
-  <si>
-    <t>20260819--02</t>
-  </si>
-  <si>
-    <t>20260819--03</t>
-  </si>
-  <si>
-    <t>20260819--04</t>
-  </si>
-  <si>
     <t>20260820--01</t>
   </si>
   <si>
@@ -145,52 +133,55 @@
     <t>20260825--04</t>
   </si>
   <si>
+    <t>20260826--01</t>
+  </si>
+  <si>
+    <t>20260826--02</t>
+  </si>
+  <si>
+    <t>20260826--03</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:06</t>
+    <t>04:36</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>04:28</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>03:21</t>
   </si>
   <si>
     <t>05:47</t>
   </si>
   <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>03:22</t>
+    <t>05:48</t>
   </si>
   <si>
     <t>03:16</t>
@@ -205,34 +196,31 @@
     <t>04:24</t>
   </si>
   <si>
-    <t>05:04</t>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>02:45</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>00:11</t>
-  </si>
-  <si>
-    <t>02:46</t>
-  </si>
-  <si>
     <t>00:23</t>
   </si>
   <si>
-    <t>00:33:05</t>
-  </si>
-  <si>
-    <t>02:09:57</t>
-  </si>
-  <si>
-    <t>22:08:06</t>
-  </si>
-  <si>
-    <t>23:44:05</t>
+    <t>01:08</t>
   </si>
   <si>
     <t>01:20:51</t>
@@ -244,385 +232,376 @@
     <t>22:55:03</t>
   </si>
   <si>
-    <t>00:31:43</t>
-  </si>
-  <si>
-    <t>02:08:46</t>
-  </si>
-  <si>
-    <t>22:06:01</t>
-  </si>
-  <si>
-    <t>23:42:32</t>
-  </si>
-  <si>
-    <t>01:19:29</t>
-  </si>
-  <si>
-    <t>21:17:00</t>
-  </si>
-  <si>
-    <t>22:53:18</t>
-  </si>
-  <si>
-    <t>00:30:10</t>
-  </si>
-  <si>
-    <t>20:28:00</t>
+    <t>00:31:42</t>
+  </si>
+  <si>
+    <t>02:08:45</t>
+  </si>
+  <si>
+    <t>22:06:00</t>
+  </si>
+  <si>
+    <t>23:42:30</t>
+  </si>
+  <si>
+    <t>01:19:27</t>
+  </si>
+  <si>
+    <t>21:16:57</t>
+  </si>
+  <si>
+    <t>22:53:15</t>
+  </si>
+  <si>
+    <t>00:30:07</t>
+  </si>
+  <si>
+    <t>20:27:56</t>
+  </si>
+  <si>
+    <t>22:03:57</t>
+  </si>
+  <si>
+    <t>23:40:44</t>
+  </si>
+  <si>
+    <t>01:17:54</t>
+  </si>
+  <si>
+    <t>21:14:38</t>
+  </si>
+  <si>
+    <t>22:51:17</t>
+  </si>
+  <si>
+    <t>00:28:20</t>
+  </si>
+  <si>
+    <t>20:25:17</t>
+  </si>
+  <si>
+    <t>22:01:48</t>
+  </si>
+  <si>
+    <t>23:38:45</t>
+  </si>
+  <si>
+    <t>19:35:57</t>
+  </si>
+  <si>
+    <t>21:12:15</t>
+  </si>
+  <si>
+    <t>22:49:07</t>
+  </si>
+  <si>
+    <t>01:23:07</t>
+  </si>
+  <si>
+    <t>03:00:53</t>
+  </si>
+  <si>
+    <t>22:57:22</t>
+  </si>
+  <si>
+    <t>00:33:57</t>
+  </si>
+  <si>
+    <t>02:11:19</t>
+  </si>
+  <si>
+    <t>22:08:25</t>
+  </si>
+  <si>
+    <t>23:44:44</t>
+  </si>
+  <si>
+    <t>01:21:52</t>
+  </si>
+  <si>
+    <t>21:19:32</t>
+  </si>
+  <si>
+    <t>22:55:29</t>
+  </si>
+  <si>
+    <t>00:32:27</t>
+  </si>
+  <si>
+    <t>20:30:50</t>
+  </si>
+  <si>
+    <t>22:06:13</t>
+  </si>
+  <si>
+    <t>23:43:00</t>
+  </si>
+  <si>
+    <t>21:16:56</t>
+  </si>
+  <si>
+    <t>22:53:32</t>
+  </si>
+  <si>
+    <t>00:30:57</t>
+  </si>
+  <si>
+    <t>20:27:41</t>
   </si>
   <si>
     <t>22:04:02</t>
   </si>
   <si>
-    <t>23:40:49</t>
-  </si>
-  <si>
-    <t>01:17:59</t>
-  </si>
-  <si>
-    <t>21:14:44</t>
-  </si>
-  <si>
-    <t>22:51:24</t>
-  </si>
-  <si>
-    <t>00:28:28</t>
-  </si>
-  <si>
-    <t>20:25:26</t>
-  </si>
-  <si>
-    <t>22:01:57</t>
-  </si>
-  <si>
-    <t>23:38:55</t>
-  </si>
-  <si>
-    <t>00:35:19</t>
-  </si>
-  <si>
-    <t>02:12:16</t>
-  </si>
-  <si>
-    <t>22:11:05</t>
-  </si>
-  <si>
-    <t>23:46:21</t>
-  </si>
-  <si>
-    <t>01:23:07</t>
-  </si>
-  <si>
-    <t>03:00:53</t>
-  </si>
-  <si>
-    <t>22:57:23</t>
-  </si>
-  <si>
-    <t>00:33:57</t>
-  </si>
-  <si>
-    <t>02:11:20</t>
-  </si>
-  <si>
-    <t>22:08:26</t>
-  </si>
-  <si>
-    <t>23:44:45</t>
-  </si>
-  <si>
-    <t>01:21:54</t>
-  </si>
-  <si>
-    <t>21:19:35</t>
-  </si>
-  <si>
-    <t>22:55:32</t>
-  </si>
-  <si>
-    <t>00:32:30</t>
-  </si>
-  <si>
-    <t>20:30:54</t>
-  </si>
-  <si>
-    <t>22:06:18</t>
-  </si>
-  <si>
-    <t>23:43:05</t>
-  </si>
-  <si>
-    <t>01:20:56</t>
-  </si>
-  <si>
-    <t>21:17:03</t>
-  </si>
-  <si>
-    <t>22:53:39</t>
-  </si>
-  <si>
-    <t>00:31:04</t>
-  </si>
-  <si>
-    <t>20:27:50</t>
-  </si>
-  <si>
-    <t>22:04:11</t>
-  </si>
-  <si>
-    <t>23:41:21</t>
-  </si>
-  <si>
-    <t>00:38:17</t>
-  </si>
-  <si>
-    <t>02:15:05</t>
-  </si>
-  <si>
-    <t>22:12:38</t>
-  </si>
-  <si>
-    <t>23:49:14</t>
-  </si>
-  <si>
-    <t>01:26:03</t>
-  </si>
-  <si>
-    <t>03:02:41</t>
-  </si>
-  <si>
-    <t>23:00:08</t>
-  </si>
-  <si>
-    <t>00:36:56</t>
-  </si>
-  <si>
-    <t>02:13:38</t>
-  </si>
-  <si>
-    <t>22:10:59</t>
-  </si>
-  <si>
-    <t>23:47:44</t>
-  </si>
-  <si>
-    <t>01:24:30</t>
-  </si>
-  <si>
-    <t>21:21:49</t>
-  </si>
-  <si>
-    <t>22:58:29</t>
-  </si>
-  <si>
-    <t>00:35:17</t>
-  </si>
-  <si>
-    <t>20:32:35</t>
-  </si>
-  <si>
-    <t>22:09:11</t>
-  </si>
-  <si>
-    <t>23:45:59</t>
-  </si>
-  <si>
-    <t>01:22:34</t>
-  </si>
-  <si>
-    <t>21:19:50</t>
-  </si>
-  <si>
-    <t>22:56:36</t>
-  </si>
-  <si>
-    <t>00:33:16</t>
-  </si>
-  <si>
-    <t>20:30:25</t>
-  </si>
-  <si>
-    <t>22:07:10</t>
-  </si>
-  <si>
-    <t>23:43:53</t>
-  </si>
-  <si>
-    <t>00:41:16</t>
-  </si>
-  <si>
-    <t>02:17:55</t>
-  </si>
-  <si>
-    <t>22:14:11</t>
-  </si>
-  <si>
-    <t>23:52:08</t>
-  </si>
-  <si>
-    <t>01:28:59</t>
-  </si>
-  <si>
-    <t>03:04:29</t>
-  </si>
-  <si>
-    <t>23:02:55</t>
-  </si>
-  <si>
-    <t>00:39:55</t>
-  </si>
-  <si>
-    <t>02:15:56</t>
-  </si>
-  <si>
-    <t>22:13:33</t>
-  </si>
-  <si>
-    <t>23:50:44</t>
+    <t>23:41:11</t>
+  </si>
+  <si>
+    <t>19:38:30</t>
+  </si>
+  <si>
+    <t>21:14:29</t>
+  </si>
+  <si>
+    <t>22:51:28</t>
+  </si>
+  <si>
+    <t>01:26:02</t>
+  </si>
+  <si>
+    <t>03:02:40</t>
+  </si>
+  <si>
+    <t>23:00:07</t>
+  </si>
+  <si>
+    <t>00:36:55</t>
+  </si>
+  <si>
+    <t>02:13:37</t>
+  </si>
+  <si>
+    <t>22:10:58</t>
+  </si>
+  <si>
+    <t>23:47:43</t>
+  </si>
+  <si>
+    <t>01:24:28</t>
+  </si>
+  <si>
+    <t>21:21:46</t>
+  </si>
+  <si>
+    <t>22:58:26</t>
+  </si>
+  <si>
+    <t>00:35:13</t>
+  </si>
+  <si>
+    <t>20:32:31</t>
+  </si>
+  <si>
+    <t>22:09:06</t>
+  </si>
+  <si>
+    <t>23:45:54</t>
+  </si>
+  <si>
+    <t>01:22:29</t>
+  </si>
+  <si>
+    <t>21:19:43</t>
+  </si>
+  <si>
+    <t>22:56:29</t>
+  </si>
+  <si>
+    <t>00:33:09</t>
+  </si>
+  <si>
+    <t>20:30:16</t>
+  </si>
+  <si>
+    <t>22:07:00</t>
+  </si>
+  <si>
+    <t>23:43:44</t>
+  </si>
+  <si>
+    <t>19:40:46</t>
+  </si>
+  <si>
+    <t>21:17:27</t>
+  </si>
+  <si>
+    <t>22:54:12</t>
+  </si>
+  <si>
+    <t>01:28:58</t>
+  </si>
+  <si>
+    <t>03:04:28</t>
+  </si>
+  <si>
+    <t>23:02:54</t>
+  </si>
+  <si>
+    <t>00:39:54</t>
+  </si>
+  <si>
+    <t>02:15:55</t>
+  </si>
+  <si>
+    <t>22:13:32</t>
+  </si>
+  <si>
+    <t>23:50:42</t>
+  </si>
+  <si>
+    <t>01:27:04</t>
+  </si>
+  <si>
+    <t>21:24:00</t>
+  </si>
+  <si>
+    <t>23:01:25</t>
+  </si>
+  <si>
+    <t>00:38:00</t>
+  </si>
+  <si>
+    <t>20:34:11</t>
+  </si>
+  <si>
+    <t>22:12:00</t>
+  </si>
+  <si>
+    <t>23:48:48</t>
+  </si>
+  <si>
+    <t>01:24:07</t>
+  </si>
+  <si>
+    <t>21:22:30</t>
+  </si>
+  <si>
+    <t>22:59:27</t>
+  </si>
+  <si>
+    <t>00:35:21</t>
+  </si>
+  <si>
+    <t>20:32:51</t>
+  </si>
+  <si>
+    <t>22:09:59</t>
+  </si>
+  <si>
+    <t>23:46:16</t>
+  </si>
+  <si>
+    <t>19:43:03</t>
+  </si>
+  <si>
+    <t>21:20:24</t>
+  </si>
+  <si>
+    <t>22:56:57</t>
+  </si>
+  <si>
+    <t>01:31:15</t>
+  </si>
+  <si>
+    <t>03:07:20</t>
+  </si>
+  <si>
+    <t>23:05:14</t>
+  </si>
+  <si>
+    <t>00:42:09</t>
+  </si>
+  <si>
+    <t>02:18:29</t>
+  </si>
+  <si>
+    <t>22:15:58</t>
+  </si>
+  <si>
+    <t>23:52:57</t>
+  </si>
+  <si>
+    <t>01:29:29</t>
+  </si>
+  <si>
+    <t>21:26:36</t>
+  </si>
+  <si>
+    <t>23:03:39</t>
+  </si>
+  <si>
+    <t>00:40:20</t>
+  </si>
+  <si>
+    <t>20:37:07</t>
+  </si>
+  <si>
+    <t>22:14:17</t>
+  </si>
+  <si>
+    <t>23:51:04</t>
   </si>
   <si>
     <t>01:27:05</t>
   </si>
   <si>
-    <t>21:24:03</t>
-  </si>
-  <si>
-    <t>23:01:28</t>
-  </si>
-  <si>
-    <t>00:38:03</t>
-  </si>
-  <si>
-    <t>20:34:16</t>
-  </si>
-  <si>
-    <t>22:12:05</t>
-  </si>
-  <si>
-    <t>23:48:52</t>
-  </si>
-  <si>
-    <t>01:24:12</t>
-  </si>
-  <si>
-    <t>21:22:37</t>
-  </si>
-  <si>
-    <t>22:59:34</t>
-  </si>
-  <si>
-    <t>00:35:28</t>
-  </si>
-  <si>
-    <t>20:33:01</t>
-  </si>
-  <si>
-    <t>22:10:08</t>
-  </si>
-  <si>
-    <t>23:46:25</t>
-  </si>
-  <si>
-    <t>00:43:31</t>
-  </si>
-  <si>
-    <t>02:20:15</t>
-  </si>
-  <si>
-    <t>22:17:12</t>
-  </si>
-  <si>
-    <t>23:54:25</t>
-  </si>
-  <si>
-    <t>01:31:15</t>
-  </si>
-  <si>
-    <t>03:07:20</t>
-  </si>
-  <si>
-    <t>23:05:15</t>
-  </si>
-  <si>
-    <t>00:42:10</t>
-  </si>
-  <si>
-    <t>02:18:30</t>
-  </si>
-  <si>
-    <t>22:15:59</t>
-  </si>
-  <si>
-    <t>23:52:59</t>
-  </si>
-  <si>
-    <t>01:29:31</t>
-  </si>
-  <si>
-    <t>21:26:39</t>
-  </si>
-  <si>
-    <t>23:03:43</t>
-  </si>
-  <si>
-    <t>00:40:23</t>
-  </si>
-  <si>
-    <t>20:37:11</t>
-  </si>
-  <si>
-    <t>22:14:22</t>
-  </si>
-  <si>
-    <t>23:51:09</t>
-  </si>
-  <si>
-    <t>01:27:10</t>
-  </si>
-  <si>
-    <t>21:24:56</t>
-  </si>
-  <si>
-    <t>23:01:49</t>
-  </si>
-  <si>
-    <t>00:38:05</t>
-  </si>
-  <si>
-    <t>20:35:26</t>
-  </si>
-  <si>
-    <t>22:12:23</t>
-  </si>
-  <si>
-    <t>23:48:51</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>25°</t>
+    <t>21:24:49</t>
+  </si>
+  <si>
+    <t>23:01:42</t>
+  </si>
+  <si>
+    <t>00:37:58</t>
+  </si>
+  <si>
+    <t>20:35:16</t>
+  </si>
+  <si>
+    <t>22:12:13</t>
+  </si>
+  <si>
+    <t>23:48:42</t>
+  </si>
+  <si>
+    <t>19:45:37</t>
+  </si>
+  <si>
+    <t>21:22:39</t>
+  </si>
+  <si>
+    <t>22:59:17</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>13°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
+    <t>-1°</t>
+  </si>
+  <si>
     <t>4°</t>
   </si>
   <si>
-    <t>00:42:18</t>
-  </si>
-  <si>
-    <t>02:15:12</t>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>1°</t>
   </si>
   <si>
     <t>01:28:48</t>
@@ -631,28 +610,34 @@
     <t>03:01:43</t>
   </si>
   <si>
-    <t>02:15:33</t>
-  </si>
-  <si>
-    <t>01:29:39</t>
-  </si>
-  <si>
-    <t>20:26:32</t>
+    <t>02:15:32</t>
+  </si>
+  <si>
+    <t>01:29:38</t>
+  </si>
+  <si>
+    <t>20:26:23</t>
+  </si>
+  <si>
+    <t>19:39:38</t>
+  </si>
+  <si>
+    <t>21:12:30</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -686,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,13 +686,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,19 +734,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,13 +752,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,43 +764,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -815,19 +788,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -937,18 +898,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1352,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1430,10 +1379,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>64</v>
@@ -1442,43 +1391,43 @@
         <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="L2" s="4">
-        <v>-23.5</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="P2" s="7">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>99</v>
-      </c>
-      <c r="R2" s="9">
-        <v>94</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1486,10 +1435,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>65</v>
@@ -1498,43 +1447,43 @@
         <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L3" s="4">
-        <v>-14.6</v>
+        <v>-9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="6">
-        <v>87</v>
-      </c>
-      <c r="P3" s="10">
-        <v>51</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>20</v>
-      </c>
-      <c r="R3" s="9">
-        <v>94</v>
+        <v>206</v>
+      </c>
+      <c r="O3" s="9">
+        <v>58</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>32</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1542,55 +1491,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-25.7</v>
+        <v>-27.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O4" s="6">
+        <v>207</v>
+      </c>
+      <c r="O4" s="9">
+        <v>100</v>
+      </c>
+      <c r="P4" s="11">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="12">
         <v>61</v>
       </c>
-      <c r="P4" s="12">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>47</v>
-      </c>
-      <c r="R4" s="14">
-        <v>0</v>
+      <c r="R4" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1598,55 +1547,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L5" s="4">
-        <v>-26.2</v>
+        <v>-24.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O5" s="6">
-        <v>68</v>
-      </c>
-      <c r="P5" s="15">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>47</v>
-      </c>
-      <c r="R5" s="14">
-        <v>2</v>
+        <v>207</v>
+      </c>
+      <c r="O5" s="9">
+        <v>100</v>
+      </c>
+      <c r="P5" s="10">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>55</v>
+      </c>
+      <c r="R5" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1654,55 +1603,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="L6" s="4">
-        <v>-20</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O6" s="6">
-        <v>81</v>
-      </c>
-      <c r="P6" s="7">
-        <v>65</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>63</v>
-      </c>
-      <c r="R6" s="10">
-        <v>52</v>
+        <v>205</v>
+      </c>
+      <c r="O6" s="9">
+        <v>100</v>
+      </c>
+      <c r="P6" s="15">
+        <v>42</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>24</v>
+      </c>
+      <c r="R6" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1710,54 +1659,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-26.3</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="L7" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O7" s="6">
+        <v>207</v>
+      </c>
+      <c r="O7" s="9">
         <v>100</v>
       </c>
-      <c r="P7" s="16">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>74</v>
-      </c>
-      <c r="R7" s="8">
+      <c r="P7" s="17">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>100</v>
+      </c>
+      <c r="R7" s="13">
         <v>100</v>
       </c>
     </row>
@@ -1766,54 +1715,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L8" s="4">
-        <v>-27.2</v>
+        <v>-26.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O8" s="6">
+        <v>207</v>
+      </c>
+      <c r="O8" s="9">
         <v>100</v>
       </c>
-      <c r="P8" s="12">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>6</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="P8" s="17">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>100</v>
+      </c>
+      <c r="R8" s="13">
         <v>100</v>
       </c>
     </row>
@@ -1822,55 +1771,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="L9" s="4">
-        <v>-24.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O9" s="6">
+        <v>207</v>
+      </c>
+      <c r="O9" s="9">
         <v>100</v>
       </c>
-      <c r="P9" s="19">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>23</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="P9" s="18">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="13">
         <v>100</v>
+      </c>
+      <c r="R9" s="18">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1881,52 +1830,52 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-15.3</v>
+        <v>-23.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="16">
-        <v>32</v>
+        <v>207</v>
+      </c>
+      <c r="O10" s="19">
+        <v>10</v>
+      </c>
+      <c r="P10" s="20">
+        <v>4</v>
       </c>
       <c r="Q10" s="20">
-        <v>83</v>
-      </c>
-      <c r="R10" s="8">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1934,55 +1883,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L11" s="4">
-        <v>-26.3</v>
+        <v>-27.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O11" s="6">
-        <v>77</v>
-      </c>
-      <c r="P11" s="21">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>74</v>
-      </c>
-      <c r="R11" s="10">
-        <v>50</v>
+        <v>207</v>
+      </c>
+      <c r="O11" s="19">
+        <v>2</v>
+      </c>
+      <c r="P11" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1990,55 +1939,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-26.9</v>
+        <v>-25</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O12" s="6">
-        <v>87</v>
-      </c>
-      <c r="P12" s="20">
-        <v>85</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>76</v>
-      </c>
-      <c r="R12" s="10">
-        <v>50</v>
+        <v>31</v>
+      </c>
+      <c r="P12" s="21">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2046,55 +1995,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="L13" s="4">
-        <v>-20.7</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O13" s="6">
-        <v>47</v>
-      </c>
-      <c r="P13" s="14">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>40</v>
-      </c>
-      <c r="R13" s="23">
-        <v>13</v>
+      <c r="O13" s="19">
+        <v>10</v>
+      </c>
+      <c r="P13" s="22">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2102,55 +2051,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L14" s="4">
-        <v>-23.7</v>
+        <v>-26.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O14" s="6">
-        <v>78</v>
-      </c>
-      <c r="P14" s="23">
-        <v>16</v>
+        <v>207</v>
+      </c>
+      <c r="O14" s="19">
+        <v>1</v>
+      </c>
+      <c r="P14" s="7">
+        <v>1</v>
       </c>
       <c r="Q14" s="7">
-        <v>66</v>
-      </c>
-      <c r="R14" s="12">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2158,55 +2107,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-27.8</v>
+        <v>-27.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O15" s="6">
-        <v>75</v>
-      </c>
-      <c r="P15" s="10">
-        <v>49</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>35</v>
-      </c>
-      <c r="R15" s="24">
-        <v>8</v>
+        <v>207</v>
+      </c>
+      <c r="O15" s="19">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2214,55 +2163,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-25</v>
+        <v>-21.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O16" s="6">
-        <v>76</v>
-      </c>
-      <c r="P16" s="18">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>71</v>
-      </c>
-      <c r="R16" s="11">
-        <v>19</v>
+        <v>206</v>
+      </c>
+      <c r="O16" s="19">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2270,55 +2219,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="4">
-        <v>-19.6</v>
+        <v>-24.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O17" s="6">
-        <v>96</v>
-      </c>
-      <c r="P17" s="13">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="19">
-        <v>68</v>
-      </c>
-      <c r="R17" s="17">
-        <v>76</v>
+        <v>207</v>
+      </c>
+      <c r="O17" s="19">
+        <v>13</v>
+      </c>
+      <c r="P17" s="20">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2326,55 +2275,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-26.9</v>
+        <v>-28.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O18" s="6">
-        <v>99</v>
-      </c>
-      <c r="P18" s="21">
-        <v>60</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>48</v>
-      </c>
-      <c r="R18" s="25">
-        <v>90</v>
+        <v>20</v>
+      </c>
+      <c r="P18" s="22">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2382,55 +2331,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-27.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O19" s="6">
-        <v>99</v>
-      </c>
-      <c r="P19" s="13">
-        <v>43</v>
-      </c>
-      <c r="Q19" s="21">
-        <v>59</v>
-      </c>
-      <c r="R19" s="9">
-        <v>93</v>
+        <v>40</v>
+      </c>
+      <c r="P19" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>20</v>
+      </c>
+      <c r="R19" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2438,55 +2387,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="L20" s="4">
-        <v>-21.5</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="24">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="26">
-        <v>81</v>
-      </c>
-      <c r="R20" s="8">
-        <v>99</v>
+        <v>207</v>
+      </c>
+      <c r="O20" s="9">
+        <v>78</v>
+      </c>
+      <c r="P20" s="21">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>50</v>
+      </c>
+      <c r="R20" s="23">
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2494,55 +2443,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L21" s="4">
-        <v>-24.2</v>
+        <v>-27.5</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O21" s="6">
-        <v>81</v>
-      </c>
-      <c r="P21" s="12">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="22">
+        <v>207</v>
+      </c>
+      <c r="O21" s="9">
+        <v>62</v>
+      </c>
+      <c r="P21" s="21">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="15">
         <v>39</v>
       </c>
       <c r="R21" s="7">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2550,55 +2499,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-28.5</v>
+        <v>-28.3</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O22" s="6">
-        <v>73</v>
-      </c>
-      <c r="P22" s="12">
-        <v>25</v>
+        <v>207</v>
+      </c>
+      <c r="O22" s="9">
+        <v>61</v>
+      </c>
+      <c r="P22" s="21">
+        <v>14</v>
       </c>
       <c r="Q22" s="15">
-        <v>34</v>
-      </c>
-      <c r="R22" s="27">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="R22" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2612,49 +2561,49 @@
         <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="L23" s="4">
-        <v>-25.7</v>
+        <v>-14.6</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O23" s="6">
-        <v>68</v>
-      </c>
-      <c r="P23" s="12">
-        <v>25</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>43</v>
-      </c>
-      <c r="R23" s="10">
-        <v>49</v>
+        <v>205</v>
+      </c>
+      <c r="O23" s="9">
+        <v>70</v>
+      </c>
+      <c r="P23" s="22">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>24</v>
+      </c>
+      <c r="R23" s="15">
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2662,55 +2611,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-24.7</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L24" s="4">
-        <v>-20</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="O24" s="6">
-        <v>100</v>
-      </c>
-      <c r="P24" s="9">
-        <v>96</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>100</v>
-      </c>
-      <c r="R24" s="25">
-        <v>91</v>
+        <v>41</v>
+      </c>
+      <c r="P24" s="20">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="22">
+        <v>10</v>
+      </c>
+      <c r="R24" s="18">
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2718,170 +2667,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L25" s="4">
-        <v>-27.5</v>
+        <v>-29.2</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O25" s="6">
-        <v>100</v>
-      </c>
-      <c r="P25" s="9">
-        <v>93</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>100</v>
-      </c>
-      <c r="R25" s="17">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>20</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-28.3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O26" s="6">
-        <v>100</v>
-      </c>
-      <c r="P26" s="9">
-        <v>94</v>
-      </c>
-      <c r="Q26" s="25">
-        <v>88</v>
-      </c>
-      <c r="R26" s="19">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="P25" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>2</v>
+      </c>
+      <c r="R25" s="16">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2900,12 +2793,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2922,22 +2815,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="211">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260820--01</t>
-  </si>
-  <si>
-    <t>20260820--02</t>
-  </si>
-  <si>
-    <t>20260820--03</t>
-  </si>
-  <si>
     <t>20260821--01</t>
   </si>
   <si>
@@ -142,28 +133,31 @@
     <t>20260826--03</t>
   </si>
   <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:32</t>
+    <t>20260827--01</t>
+  </si>
+  <si>
+    <t>20260827--02</t>
+  </si>
+  <si>
+    <t>20260827--03</t>
+  </si>
+  <si>
+    <t>20260827--04</t>
   </si>
   <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>04:36</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:58</t>
-  </si>
-  <si>
-    <t>05:12</t>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>05:11</t>
   </si>
   <si>
     <t>04:28</t>
@@ -172,24 +166,21 @@
     <t>05:56</t>
   </si>
   <si>
-    <t>05:33</t>
+    <t>05:34</t>
   </si>
   <si>
     <t>03:21</t>
   </si>
   <si>
+    <t>05:48</t>
+  </si>
+  <si>
     <t>05:47</t>
   </si>
   <si>
-    <t>05:48</t>
-  </si>
-  <si>
     <t>03:16</t>
   </si>
   <si>
-    <t>05:34</t>
-  </si>
-  <si>
     <t>05:55</t>
   </si>
   <si>
@@ -199,250 +190,262 @@
     <t>05:10</t>
   </si>
   <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>04:33</t>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>04:34</t>
   </si>
   <si>
     <t>05:29</t>
   </si>
   <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>02:45</t>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>02:59</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:23</t>
-  </si>
-  <si>
-    <t>01:08</t>
-  </si>
-  <si>
-    <t>01:20:51</t>
-  </si>
-  <si>
-    <t>02:58:01</t>
-  </si>
-  <si>
-    <t>22:55:03</t>
-  </si>
-  <si>
-    <t>00:31:42</t>
-  </si>
-  <si>
-    <t>02:08:45</t>
-  </si>
-  <si>
-    <t>22:06:00</t>
-  </si>
-  <si>
-    <t>23:42:30</t>
-  </si>
-  <si>
-    <t>01:19:27</t>
-  </si>
-  <si>
-    <t>21:16:57</t>
-  </si>
-  <si>
-    <t>22:53:15</t>
-  </si>
-  <si>
-    <t>00:30:07</t>
-  </si>
-  <si>
-    <t>20:27:56</t>
-  </si>
-  <si>
-    <t>22:03:57</t>
-  </si>
-  <si>
-    <t>23:40:44</t>
-  </si>
-  <si>
-    <t>01:17:54</t>
-  </si>
-  <si>
-    <t>21:14:38</t>
-  </si>
-  <si>
-    <t>22:51:17</t>
-  </si>
-  <si>
-    <t>00:28:20</t>
-  </si>
-  <si>
-    <t>20:25:17</t>
-  </si>
-  <si>
-    <t>22:01:48</t>
-  </si>
-  <si>
-    <t>23:38:45</t>
-  </si>
-  <si>
-    <t>19:35:57</t>
-  </si>
-  <si>
-    <t>21:12:15</t>
-  </si>
-  <si>
-    <t>22:49:07</t>
-  </si>
-  <si>
-    <t>01:23:07</t>
-  </si>
-  <si>
-    <t>03:00:53</t>
-  </si>
-  <si>
-    <t>22:57:22</t>
+    <t>00:22</t>
+  </si>
+  <si>
+    <t>01:07</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>00:27</t>
+  </si>
+  <si>
+    <t>00:31:43</t>
+  </si>
+  <si>
+    <t>02:08:46</t>
+  </si>
+  <si>
+    <t>22:06:02</t>
+  </si>
+  <si>
+    <t>23:42:32</t>
+  </si>
+  <si>
+    <t>01:19:29</t>
+  </si>
+  <si>
+    <t>21:17:00</t>
+  </si>
+  <si>
+    <t>22:53:18</t>
+  </si>
+  <si>
+    <t>00:30:11</t>
+  </si>
+  <si>
+    <t>20:28:01</t>
+  </si>
+  <si>
+    <t>22:04:02</t>
+  </si>
+  <si>
+    <t>23:40:49</t>
+  </si>
+  <si>
+    <t>01:18:00</t>
+  </si>
+  <si>
+    <t>21:14:46</t>
+  </si>
+  <si>
+    <t>22:51:26</t>
+  </si>
+  <si>
+    <t>00:28:29</t>
+  </si>
+  <si>
+    <t>20:25:28</t>
+  </si>
+  <si>
+    <t>22:01:59</t>
+  </si>
+  <si>
+    <t>23:38:57</t>
+  </si>
+  <si>
+    <t>19:36:11</t>
+  </si>
+  <si>
+    <t>21:12:30</t>
+  </si>
+  <si>
+    <t>22:49:22</t>
+  </si>
+  <si>
+    <t>18:46:56</t>
+  </si>
+  <si>
+    <t>20:22:59</t>
+  </si>
+  <si>
+    <t>21:59:46</t>
+  </si>
+  <si>
+    <t>23:36:57</t>
   </si>
   <si>
     <t>00:33:57</t>
   </si>
   <si>
-    <t>02:11:19</t>
-  </si>
-  <si>
-    <t>22:08:25</t>
-  </si>
-  <si>
-    <t>23:44:44</t>
-  </si>
-  <si>
-    <t>01:21:52</t>
-  </si>
-  <si>
-    <t>21:19:32</t>
-  </si>
-  <si>
-    <t>22:55:29</t>
-  </si>
-  <si>
-    <t>00:32:27</t>
-  </si>
-  <si>
-    <t>20:30:50</t>
-  </si>
-  <si>
-    <t>22:06:13</t>
-  </si>
-  <si>
-    <t>23:43:00</t>
-  </si>
-  <si>
-    <t>21:16:56</t>
-  </si>
-  <si>
-    <t>22:53:32</t>
-  </si>
-  <si>
-    <t>00:30:57</t>
-  </si>
-  <si>
-    <t>20:27:41</t>
-  </si>
-  <si>
-    <t>22:04:02</t>
-  </si>
-  <si>
-    <t>23:41:11</t>
-  </si>
-  <si>
-    <t>19:38:30</t>
-  </si>
-  <si>
-    <t>21:14:29</t>
-  </si>
-  <si>
-    <t>22:51:28</t>
-  </si>
-  <si>
-    <t>01:26:02</t>
-  </si>
-  <si>
-    <t>03:02:40</t>
-  </si>
-  <si>
-    <t>23:00:07</t>
+    <t>02:11:20</t>
+  </si>
+  <si>
+    <t>22:08:27</t>
+  </si>
+  <si>
+    <t>23:44:45</t>
+  </si>
+  <si>
+    <t>01:21:54</t>
+  </si>
+  <si>
+    <t>21:19:35</t>
+  </si>
+  <si>
+    <t>22:55:32</t>
+  </si>
+  <si>
+    <t>00:32:30</t>
+  </si>
+  <si>
+    <t>20:30:55</t>
+  </si>
+  <si>
+    <t>22:06:18</t>
+  </si>
+  <si>
+    <t>23:43:06</t>
+  </si>
+  <si>
+    <t>01:20:57</t>
+  </si>
+  <si>
+    <t>21:17:04</t>
+  </si>
+  <si>
+    <t>22:53:40</t>
+  </si>
+  <si>
+    <t>00:31:06</t>
+  </si>
+  <si>
+    <t>20:27:52</t>
+  </si>
+  <si>
+    <t>22:04:13</t>
+  </si>
+  <si>
+    <t>23:41:23</t>
+  </si>
+  <si>
+    <t>19:38:44</t>
+  </si>
+  <si>
+    <t>21:14:44</t>
+  </si>
+  <si>
+    <t>22:51:43</t>
+  </si>
+  <si>
+    <t>18:49:46</t>
+  </si>
+  <si>
+    <t>20:25:15</t>
+  </si>
+  <si>
+    <t>22:02:03</t>
+  </si>
+  <si>
+    <t>23:39:59</t>
   </si>
   <si>
     <t>00:36:55</t>
   </si>
   <si>
-    <t>02:13:37</t>
-  </si>
-  <si>
-    <t>22:10:58</t>
-  </si>
-  <si>
-    <t>23:47:43</t>
-  </si>
-  <si>
-    <t>01:24:28</t>
-  </si>
-  <si>
-    <t>21:21:46</t>
-  </si>
-  <si>
-    <t>22:58:26</t>
-  </si>
-  <si>
-    <t>00:35:13</t>
-  </si>
-  <si>
-    <t>20:32:31</t>
-  </si>
-  <si>
-    <t>22:09:06</t>
-  </si>
-  <si>
-    <t>23:45:54</t>
-  </si>
-  <si>
-    <t>01:22:29</t>
-  </si>
-  <si>
-    <t>21:19:43</t>
-  </si>
-  <si>
-    <t>22:56:29</t>
-  </si>
-  <si>
-    <t>00:33:09</t>
-  </si>
-  <si>
-    <t>20:30:16</t>
-  </si>
-  <si>
-    <t>22:07:00</t>
-  </si>
-  <si>
-    <t>23:43:44</t>
-  </si>
-  <si>
-    <t>19:40:46</t>
-  </si>
-  <si>
-    <t>21:17:27</t>
-  </si>
-  <si>
-    <t>22:54:12</t>
-  </si>
-  <si>
-    <t>01:28:58</t>
-  </si>
-  <si>
-    <t>03:04:28</t>
-  </si>
-  <si>
-    <t>23:02:54</t>
+    <t>02:13:38</t>
+  </si>
+  <si>
+    <t>22:10:59</t>
+  </si>
+  <si>
+    <t>23:47:44</t>
+  </si>
+  <si>
+    <t>01:24:30</t>
+  </si>
+  <si>
+    <t>21:21:49</t>
+  </si>
+  <si>
+    <t>22:58:30</t>
+  </si>
+  <si>
+    <t>00:35:17</t>
+  </si>
+  <si>
+    <t>20:32:36</t>
+  </si>
+  <si>
+    <t>22:09:12</t>
+  </si>
+  <si>
+    <t>23:45:59</t>
+  </si>
+  <si>
+    <t>01:22:35</t>
+  </si>
+  <si>
+    <t>21:19:51</t>
+  </si>
+  <si>
+    <t>22:56:37</t>
+  </si>
+  <si>
+    <t>00:33:17</t>
+  </si>
+  <si>
+    <t>20:30:27</t>
+  </si>
+  <si>
+    <t>22:07:11</t>
+  </si>
+  <si>
+    <t>23:43:55</t>
+  </si>
+  <si>
+    <t>19:41:01</t>
+  </si>
+  <si>
+    <t>21:17:42</t>
+  </si>
+  <si>
+    <t>22:54:27</t>
+  </si>
+  <si>
+    <t>18:51:32</t>
+  </si>
+  <si>
+    <t>20:28:08</t>
+  </si>
+  <si>
+    <t>22:04:55</t>
+  </si>
+  <si>
+    <t>23:41:29</t>
   </si>
   <si>
     <t>00:39:54</t>
@@ -451,193 +454,199 @@
     <t>02:15:55</t>
   </si>
   <si>
-    <t>22:13:32</t>
-  </si>
-  <si>
-    <t>23:50:42</t>
-  </si>
-  <si>
-    <t>01:27:04</t>
-  </si>
-  <si>
-    <t>21:24:00</t>
-  </si>
-  <si>
-    <t>23:01:25</t>
-  </si>
-  <si>
-    <t>00:38:00</t>
-  </si>
-  <si>
-    <t>20:34:11</t>
-  </si>
-  <si>
-    <t>22:12:00</t>
-  </si>
-  <si>
-    <t>23:48:48</t>
-  </si>
-  <si>
-    <t>01:24:07</t>
-  </si>
-  <si>
-    <t>21:22:30</t>
-  </si>
-  <si>
-    <t>22:59:27</t>
-  </si>
-  <si>
-    <t>00:35:21</t>
-  </si>
-  <si>
-    <t>20:32:51</t>
-  </si>
-  <si>
-    <t>22:09:59</t>
-  </si>
-  <si>
-    <t>23:46:16</t>
-  </si>
-  <si>
-    <t>19:43:03</t>
-  </si>
-  <si>
-    <t>21:20:24</t>
-  </si>
-  <si>
-    <t>22:56:57</t>
-  </si>
-  <si>
-    <t>01:31:15</t>
-  </si>
-  <si>
-    <t>03:07:20</t>
-  </si>
-  <si>
-    <t>23:05:14</t>
+    <t>22:13:33</t>
+  </si>
+  <si>
+    <t>23:50:44</t>
+  </si>
+  <si>
+    <t>01:27:05</t>
+  </si>
+  <si>
+    <t>21:24:03</t>
+  </si>
+  <si>
+    <t>23:01:28</t>
+  </si>
+  <si>
+    <t>00:38:04</t>
+  </si>
+  <si>
+    <t>20:34:16</t>
+  </si>
+  <si>
+    <t>22:12:06</t>
+  </si>
+  <si>
+    <t>23:48:53</t>
+  </si>
+  <si>
+    <t>01:24:13</t>
+  </si>
+  <si>
+    <t>21:22:38</t>
+  </si>
+  <si>
+    <t>22:59:35</t>
+  </si>
+  <si>
+    <t>00:35:30</t>
+  </si>
+  <si>
+    <t>20:33:02</t>
+  </si>
+  <si>
+    <t>22:10:10</t>
+  </si>
+  <si>
+    <t>23:46:27</t>
+  </si>
+  <si>
+    <t>19:43:18</t>
+  </si>
+  <si>
+    <t>21:20:39</t>
+  </si>
+  <si>
+    <t>22:57:12</t>
+  </si>
+  <si>
+    <t>18:53:19</t>
+  </si>
+  <si>
+    <t>20:31:03</t>
+  </si>
+  <si>
+    <t>22:07:47</t>
+  </si>
+  <si>
+    <t>23:42:58</t>
   </si>
   <si>
     <t>00:42:09</t>
   </si>
   <si>
-    <t>02:18:29</t>
-  </si>
-  <si>
-    <t>22:15:58</t>
-  </si>
-  <si>
-    <t>23:52:57</t>
-  </si>
-  <si>
-    <t>01:29:29</t>
-  </si>
-  <si>
-    <t>21:26:36</t>
-  </si>
-  <si>
-    <t>23:03:39</t>
-  </si>
-  <si>
-    <t>00:40:20</t>
-  </si>
-  <si>
-    <t>20:37:07</t>
-  </si>
-  <si>
-    <t>22:14:17</t>
-  </si>
-  <si>
-    <t>23:51:04</t>
-  </si>
-  <si>
-    <t>01:27:05</t>
-  </si>
-  <si>
-    <t>21:24:49</t>
-  </si>
-  <si>
-    <t>23:01:42</t>
-  </si>
-  <si>
-    <t>00:37:58</t>
-  </si>
-  <si>
-    <t>20:35:16</t>
-  </si>
-  <si>
-    <t>22:12:13</t>
-  </si>
-  <si>
-    <t>23:48:42</t>
-  </si>
-  <si>
-    <t>19:45:37</t>
-  </si>
-  <si>
-    <t>21:22:39</t>
-  </si>
-  <si>
-    <t>22:59:17</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>02:18:30</t>
+  </si>
+  <si>
+    <t>22:15:59</t>
+  </si>
+  <si>
+    <t>23:52:58</t>
+  </si>
+  <si>
+    <t>01:29:31</t>
+  </si>
+  <si>
+    <t>21:26:39</t>
+  </si>
+  <si>
+    <t>23:03:43</t>
+  </si>
+  <si>
+    <t>00:40:23</t>
+  </si>
+  <si>
+    <t>20:37:12</t>
+  </si>
+  <si>
+    <t>22:14:22</t>
+  </si>
+  <si>
+    <t>23:51:10</t>
+  </si>
+  <si>
+    <t>01:27:10</t>
+  </si>
+  <si>
+    <t>21:24:57</t>
+  </si>
+  <si>
+    <t>23:01:50</t>
+  </si>
+  <si>
+    <t>00:38:06</t>
+  </si>
+  <si>
+    <t>20:35:27</t>
+  </si>
+  <si>
+    <t>22:12:24</t>
+  </si>
+  <si>
+    <t>19:45:52</t>
+  </si>
+  <si>
+    <t>21:22:54</t>
+  </si>
+  <si>
+    <t>22:59:32</t>
+  </si>
+  <si>
+    <t>18:56:10</t>
+  </si>
+  <si>
+    <t>20:33:19</t>
+  </si>
+  <si>
+    <t>22:10:04</t>
+  </si>
+  <si>
+    <t>23:46:00</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>1°</t>
   </si>
   <si>
     <t>13°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>-1°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>01:28:48</t>
-  </si>
-  <si>
-    <t>03:01:43</t>
-  </si>
-  <si>
-    <t>02:15:32</t>
-  </si>
-  <si>
-    <t>01:29:38</t>
-  </si>
-  <si>
-    <t>20:26:23</t>
-  </si>
-  <si>
-    <t>19:39:38</t>
-  </si>
-  <si>
-    <t>21:12:30</t>
+    <t>02:15:33</t>
+  </si>
+  <si>
+    <t>01:29:39</t>
+  </si>
+  <si>
+    <t>20:26:33</t>
+  </si>
+  <si>
+    <t>19:39:51</t>
+  </si>
+  <si>
+    <t>21:12:44</t>
+  </si>
+  <si>
+    <t>18:52:51</t>
+  </si>
+  <si>
+    <t>20:25:42</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -686,37 +695,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,37 +743,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,6 +761,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -788,7 +785,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1301,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1379,10 +1388,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>64</v>
@@ -1391,43 +1400,43 @@
         <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>196</v>
+        <v>69</v>
       </c>
       <c r="L2" s="4">
-        <v>-20</v>
+        <v>-24.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O2" s="6">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="8">
-        <v>45</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1435,10 +1444,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>65</v>
@@ -1447,43 +1456,43 @@
         <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L3" s="4">
-        <v>-9</v>
+        <v>-15.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O3" s="9">
-        <v>58</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>32</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="O3" s="6">
+        <v>87</v>
+      </c>
+      <c r="P3" s="10">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>81</v>
+      </c>
+      <c r="R3" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1491,54 +1500,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-27.2</v>
+        <v>-26.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O4" s="9">
+        <v>208</v>
+      </c>
+      <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="11">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>61</v>
-      </c>
-      <c r="R4" s="13">
+      <c r="P4" s="12">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>100</v>
+      </c>
+      <c r="R4" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1547,54 +1556,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L5" s="4">
-        <v>-24.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O5" s="9">
+        <v>208</v>
+      </c>
+      <c r="O5" s="6">
         <v>100</v>
       </c>
-      <c r="P5" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>55</v>
-      </c>
-      <c r="R5" s="13">
+      <c r="P5" s="12">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>100</v>
+      </c>
+      <c r="R5" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1603,55 +1612,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="15">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>24</v>
+        <v>208</v>
+      </c>
+      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="P6" s="13">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>88</v>
       </c>
       <c r="R6" s="13">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1659,55 +1668,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>74</v>
       </c>
       <c r="L7" s="4">
-        <v>-26.3</v>
+        <v>-23.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O7" s="9">
-        <v>100</v>
-      </c>
-      <c r="P7" s="17">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>100</v>
-      </c>
-      <c r="R7" s="13">
-        <v>100</v>
+        <v>208</v>
+      </c>
+      <c r="O7" s="15">
+        <v>6</v>
+      </c>
+      <c r="P7" s="16">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>0</v>
+      </c>
+      <c r="R7" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1715,55 +1724,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L8" s="4">
-        <v>-26.9</v>
+        <v>-27.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O8" s="9">
-        <v>100</v>
-      </c>
-      <c r="P8" s="17">
-        <v>80</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>100</v>
-      </c>
-      <c r="R8" s="13">
-        <v>100</v>
+        <v>208</v>
+      </c>
+      <c r="O8" s="15">
+        <v>6</v>
+      </c>
+      <c r="P8" s="16">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>4</v>
+      </c>
+      <c r="R8" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1771,55 +1780,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-20.7</v>
+        <v>-25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" s="9">
-        <v>100</v>
-      </c>
-      <c r="P9" s="18">
-        <v>35</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>100</v>
-      </c>
-      <c r="R9" s="18">
-        <v>35</v>
+        <v>208</v>
+      </c>
+      <c r="O9" s="18">
+        <v>23</v>
+      </c>
+      <c r="P9" s="19">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>0</v>
+      </c>
+      <c r="R9" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1827,54 +1836,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O10" s="19">
-        <v>10</v>
-      </c>
-      <c r="P10" s="20">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>4</v>
-      </c>
-      <c r="R10" s="7">
+        <v>210</v>
+      </c>
+      <c r="O10" s="15">
+        <v>0</v>
+      </c>
+      <c r="P10" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>0</v>
+      </c>
+      <c r="R10" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1883,54 +1892,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L11" s="4">
-        <v>-27.8</v>
+        <v>-26.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O11" s="19">
-        <v>2</v>
-      </c>
-      <c r="P11" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
+        <v>208</v>
+      </c>
+      <c r="O11" s="15">
+        <v>13</v>
+      </c>
+      <c r="P11" s="16">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>0</v>
+      </c>
+      <c r="R11" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1939,54 +1948,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-25</v>
+        <v>-27.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O12" s="6">
-        <v>31</v>
-      </c>
-      <c r="P12" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
+        <v>208</v>
+      </c>
+      <c r="O12" s="15">
+        <v>0</v>
+      </c>
+      <c r="P12" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>0</v>
+      </c>
+      <c r="R12" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1998,51 +2007,51 @@
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L13" s="4">
-        <v>-19.6</v>
+        <v>-21.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O13" s="19">
-        <v>10</v>
-      </c>
-      <c r="P13" s="22">
-        <v>10</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
+        <v>210</v>
+      </c>
+      <c r="O13" s="15">
+        <v>4</v>
+      </c>
+      <c r="P13" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2051,54 +2060,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.9</v>
+        <v>-24.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O14" s="19">
+        <v>208</v>
+      </c>
+      <c r="O14" s="15">
+        <v>2</v>
+      </c>
+      <c r="P14" s="17">
         <v>1</v>
       </c>
-      <c r="P14" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
+      <c r="Q14" s="17">
+        <v>0</v>
+      </c>
+      <c r="R14" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2107,54 +2116,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-27.6</v>
+        <v>-28.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O15" s="19">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
+        <v>208</v>
+      </c>
+      <c r="O15" s="15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>0</v>
+      </c>
+      <c r="R15" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2163,54 +2172,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-21.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O16" s="19">
-        <v>0</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7">
+        <v>208</v>
+      </c>
+      <c r="O16" s="15">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2219,55 +2228,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L17" s="4">
-        <v>-24.2</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O17" s="19">
-        <v>13</v>
-      </c>
-      <c r="P17" s="20">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="O17" s="18">
+        <v>26</v>
+      </c>
+      <c r="P17" s="19">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2278,52 +2287,52 @@
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-28.5</v>
+        <v>-27.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O18" s="6">
-        <v>20</v>
-      </c>
-      <c r="P18" s="22">
-        <v>11</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="O18" s="18">
+        <v>31</v>
+      </c>
+      <c r="P18" s="19">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>0</v>
+      </c>
+      <c r="R18" s="16">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2331,55 +2340,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-25.7</v>
+        <v>-28.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O19" s="6">
-        <v>40</v>
-      </c>
-      <c r="P19" s="11">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>20</v>
-      </c>
-      <c r="R19" s="20">
-        <v>7</v>
+        <v>208</v>
+      </c>
+      <c r="O19" s="18">
+        <v>26</v>
+      </c>
+      <c r="P19" s="19">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2387,10 +2396,10 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>66</v>
@@ -2399,43 +2408,43 @@
         <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L20" s="4">
-        <v>-20</v>
+        <v>-14.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O20" s="9">
-        <v>78</v>
-      </c>
-      <c r="P20" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q20" s="23">
-        <v>50</v>
-      </c>
-      <c r="R20" s="23">
-        <v>51</v>
+        <v>209</v>
+      </c>
+      <c r="O20" s="18">
+        <v>22</v>
+      </c>
+      <c r="P20" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>11</v>
+      </c>
+      <c r="R20" s="21">
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2446,52 +2455,52 @@
         <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="L21" s="4">
-        <v>-27.5</v>
+        <v>-24.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O21" s="9">
-        <v>62</v>
-      </c>
-      <c r="P21" s="21">
-        <v>13</v>
-      </c>
-      <c r="Q21" s="15">
-        <v>39</v>
-      </c>
-      <c r="R21" s="7">
+        <v>208</v>
+      </c>
+      <c r="O21" s="18">
+        <v>27</v>
+      </c>
+      <c r="P21" s="17">
         <v>1</v>
+      </c>
+      <c r="Q21" s="21">
+        <v>21</v>
+      </c>
+      <c r="R21" s="22">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2499,55 +2508,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-28.3</v>
+        <v>-29.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O22" s="9">
-        <v>61</v>
-      </c>
-      <c r="P22" s="21">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="15">
-        <v>40</v>
-      </c>
-      <c r="R22" s="20">
-        <v>4</v>
+        <v>208</v>
+      </c>
+      <c r="O22" s="18">
+        <v>32</v>
+      </c>
+      <c r="P22" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>26</v>
+      </c>
+      <c r="R22" s="23">
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2555,55 +2564,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>194</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L23" s="4">
-        <v>-14.6</v>
+        <v>-8.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="9">
-        <v>70</v>
-      </c>
-      <c r="P23" s="22">
-        <v>11</v>
-      </c>
-      <c r="Q23" s="16">
-        <v>24</v>
-      </c>
-      <c r="R23" s="15">
-        <v>40</v>
+        <v>210</v>
+      </c>
+      <c r="O23" s="6">
+        <v>100</v>
+      </c>
+      <c r="P23" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="17">
+        <v>0</v>
+      </c>
+      <c r="R23" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2611,55 +2620,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L24" s="4">
-        <v>-24.7</v>
+        <v>-20.5</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O24" s="6">
-        <v>41</v>
-      </c>
-      <c r="P24" s="20">
+        <v>100</v>
+      </c>
+      <c r="P24" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="16">
         <v>5</v>
       </c>
-      <c r="Q24" s="22">
-        <v>10</v>
-      </c>
-      <c r="R24" s="18">
-        <v>34</v>
+      <c r="R24" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2667,114 +2676,170 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L25" s="4">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O25" s="6">
-        <v>25</v>
-      </c>
-      <c r="P25" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>2</v>
-      </c>
-      <c r="R25" s="16">
-        <v>25</v>
+        <v>100</v>
+      </c>
+      <c r="P25" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="19">
+        <v>15</v>
+      </c>
+      <c r="R25" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>13</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-29.1</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O26" s="6">
+        <v>100</v>
+      </c>
+      <c r="P26" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="23">
+        <v>30</v>
+      </c>
+      <c r="R26" s="9">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2793,12 +2858,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2815,22 +2880,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260821--01</t>
-  </si>
-  <si>
-    <t>20260821--02</t>
-  </si>
-  <si>
-    <t>20260821--03</t>
-  </si>
-  <si>
-    <t>20260821--04</t>
-  </si>
-  <si>
     <t>20260822--01</t>
   </si>
   <si>
@@ -145,94 +133,88 @@
     <t>20260827--04</t>
   </si>
   <si>
+    <t>20260828--01</t>
+  </si>
+  <si>
+    <t>20260828--02</t>
+  </si>
+  <si>
+    <t>20260828--03</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>04:27</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>03:21</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
     <t>05:57</t>
   </si>
   <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:28</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>03:21</t>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>03:32</t>
   </si>
   <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:04</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
     <t>05:44</t>
   </si>
   <si>
-    <t>02:59</t>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:15</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:22</t>
-  </si>
-  <si>
     <t>01:07</t>
   </si>
   <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
-    <t>00:31:43</t>
-  </si>
-  <si>
-    <t>02:08:46</t>
-  </si>
-  <si>
-    <t>22:06:02</t>
-  </si>
-  <si>
-    <t>23:42:32</t>
+    <t>03:04</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
+    <t>02:41</t>
   </si>
   <si>
     <t>01:19:29</t>
@@ -244,10 +226,10 @@
     <t>22:53:18</t>
   </si>
   <si>
-    <t>00:30:11</t>
-  </si>
-  <si>
-    <t>20:28:01</t>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>20:28:00</t>
   </si>
   <si>
     <t>22:04:02</t>
@@ -256,58 +238,55 @@
     <t>23:40:49</t>
   </si>
   <si>
-    <t>01:18:00</t>
-  </si>
-  <si>
-    <t>21:14:46</t>
-  </si>
-  <si>
-    <t>22:51:26</t>
-  </si>
-  <si>
-    <t>00:28:29</t>
-  </si>
-  <si>
-    <t>20:25:28</t>
-  </si>
-  <si>
-    <t>22:01:59</t>
-  </si>
-  <si>
-    <t>23:38:57</t>
-  </si>
-  <si>
-    <t>19:36:11</t>
-  </si>
-  <si>
-    <t>21:12:30</t>
-  </si>
-  <si>
-    <t>22:49:22</t>
-  </si>
-  <si>
-    <t>18:46:56</t>
-  </si>
-  <si>
-    <t>20:22:59</t>
-  </si>
-  <si>
-    <t>21:59:46</t>
-  </si>
-  <si>
-    <t>23:36:57</t>
-  </si>
-  <si>
-    <t>00:33:57</t>
-  </si>
-  <si>
-    <t>02:11:20</t>
-  </si>
-  <si>
-    <t>22:08:27</t>
-  </si>
-  <si>
-    <t>23:44:45</t>
+    <t>01:17:59</t>
+  </si>
+  <si>
+    <t>21:14:45</t>
+  </si>
+  <si>
+    <t>22:51:25</t>
+  </si>
+  <si>
+    <t>00:28:28</t>
+  </si>
+  <si>
+    <t>20:25:27</t>
+  </si>
+  <si>
+    <t>22:01:58</t>
+  </si>
+  <si>
+    <t>23:38:55</t>
+  </si>
+  <si>
+    <t>19:36:10</t>
+  </si>
+  <si>
+    <t>21:12:29</t>
+  </si>
+  <si>
+    <t>22:49:21</t>
+  </si>
+  <si>
+    <t>18:46:54</t>
+  </si>
+  <si>
+    <t>20:22:57</t>
+  </si>
+  <si>
+    <t>21:59:44</t>
+  </si>
+  <si>
+    <t>23:36:55</t>
+  </si>
+  <si>
+    <t>19:33:24</t>
+  </si>
+  <si>
+    <t>21:10:05</t>
+  </si>
+  <si>
+    <t>22:47:08</t>
   </si>
   <si>
     <t>01:21:54</t>
@@ -328,7 +307,7 @@
     <t>22:06:18</t>
   </si>
   <si>
-    <t>23:43:06</t>
+    <t>23:43:05</t>
   </si>
   <si>
     <t>01:20:57</t>
@@ -337,52 +316,49 @@
     <t>21:17:04</t>
   </si>
   <si>
-    <t>22:53:40</t>
-  </si>
-  <si>
-    <t>00:31:06</t>
-  </si>
-  <si>
-    <t>20:27:52</t>
-  </si>
-  <si>
-    <t>22:04:13</t>
-  </si>
-  <si>
-    <t>23:41:23</t>
-  </si>
-  <si>
-    <t>19:38:44</t>
-  </si>
-  <si>
-    <t>21:14:44</t>
-  </si>
-  <si>
-    <t>22:51:43</t>
-  </si>
-  <si>
-    <t>18:49:46</t>
-  </si>
-  <si>
-    <t>20:25:15</t>
-  </si>
-  <si>
-    <t>22:02:03</t>
-  </si>
-  <si>
-    <t>23:39:59</t>
-  </si>
-  <si>
-    <t>00:36:55</t>
-  </si>
-  <si>
-    <t>02:13:38</t>
-  </si>
-  <si>
-    <t>22:10:59</t>
-  </si>
-  <si>
-    <t>23:47:44</t>
+    <t>22:53:39</t>
+  </si>
+  <si>
+    <t>00:31:05</t>
+  </si>
+  <si>
+    <t>20:27:51</t>
+  </si>
+  <si>
+    <t>22:04:12</t>
+  </si>
+  <si>
+    <t>23:41:22</t>
+  </si>
+  <si>
+    <t>19:38:43</t>
+  </si>
+  <si>
+    <t>21:14:43</t>
+  </si>
+  <si>
+    <t>22:51:41</t>
+  </si>
+  <si>
+    <t>18:49:45</t>
+  </si>
+  <si>
+    <t>20:25:13</t>
+  </si>
+  <si>
+    <t>22:02:01</t>
+  </si>
+  <si>
+    <t>23:39:58</t>
+  </si>
+  <si>
+    <t>19:35:43</t>
+  </si>
+  <si>
+    <t>21:12:19</t>
+  </si>
+  <si>
+    <t>22:49:47</t>
   </si>
   <si>
     <t>01:24:30</t>
@@ -391,25 +367,25 @@
     <t>21:21:49</t>
   </si>
   <si>
-    <t>22:58:30</t>
-  </si>
-  <si>
-    <t>00:35:17</t>
-  </si>
-  <si>
-    <t>20:32:36</t>
-  </si>
-  <si>
-    <t>22:09:12</t>
+    <t>22:58:29</t>
+  </si>
+  <si>
+    <t>00:35:16</t>
+  </si>
+  <si>
+    <t>20:32:35</t>
+  </si>
+  <si>
+    <t>22:09:11</t>
   </si>
   <si>
     <t>23:45:59</t>
   </si>
   <si>
-    <t>01:22:35</t>
-  </si>
-  <si>
-    <t>21:19:51</t>
+    <t>01:22:34</t>
+  </si>
+  <si>
+    <t>21:19:50</t>
   </si>
   <si>
     <t>22:56:37</t>
@@ -418,220 +394,232 @@
     <t>00:33:17</t>
   </si>
   <si>
-    <t>20:30:27</t>
-  </si>
-  <si>
-    <t>22:07:11</t>
-  </si>
-  <si>
-    <t>23:43:55</t>
-  </si>
-  <si>
-    <t>19:41:01</t>
-  </si>
-  <si>
-    <t>21:17:42</t>
-  </si>
-  <si>
-    <t>22:54:27</t>
-  </si>
-  <si>
-    <t>18:51:32</t>
-  </si>
-  <si>
-    <t>20:28:08</t>
-  </si>
-  <si>
-    <t>22:04:55</t>
-  </si>
-  <si>
-    <t>23:41:29</t>
-  </si>
-  <si>
-    <t>00:39:54</t>
-  </si>
-  <si>
-    <t>02:15:55</t>
-  </si>
-  <si>
-    <t>22:13:33</t>
-  </si>
-  <si>
-    <t>23:50:44</t>
+    <t>20:30:26</t>
+  </si>
+  <si>
+    <t>22:07:10</t>
+  </si>
+  <si>
+    <t>23:43:54</t>
+  </si>
+  <si>
+    <t>19:40:59</t>
+  </si>
+  <si>
+    <t>21:17:40</t>
+  </si>
+  <si>
+    <t>22:54:26</t>
+  </si>
+  <si>
+    <t>18:51:31</t>
+  </si>
+  <si>
+    <t>20:28:06</t>
+  </si>
+  <si>
+    <t>22:04:53</t>
+  </si>
+  <si>
+    <t>23:41:27</t>
+  </si>
+  <si>
+    <t>19:38:30</t>
+  </si>
+  <si>
+    <t>21:15:16</t>
+  </si>
+  <si>
+    <t>22:51:54</t>
   </si>
   <si>
     <t>01:27:05</t>
   </si>
   <si>
-    <t>21:24:03</t>
-  </si>
-  <si>
-    <t>23:01:28</t>
-  </si>
-  <si>
-    <t>00:38:04</t>
+    <t>21:24:02</t>
+  </si>
+  <si>
+    <t>23:01:27</t>
+  </si>
+  <si>
+    <t>00:38:03</t>
   </si>
   <si>
     <t>20:34:16</t>
   </si>
   <si>
-    <t>22:12:06</t>
-  </si>
-  <si>
-    <t>23:48:53</t>
-  </si>
-  <si>
-    <t>01:24:13</t>
-  </si>
-  <si>
-    <t>21:22:38</t>
-  </si>
-  <si>
-    <t>22:59:35</t>
-  </si>
-  <si>
-    <t>00:35:30</t>
-  </si>
-  <si>
-    <t>20:33:02</t>
-  </si>
-  <si>
-    <t>22:10:10</t>
-  </si>
-  <si>
-    <t>23:46:27</t>
-  </si>
-  <si>
-    <t>19:43:18</t>
-  </si>
-  <si>
-    <t>21:20:39</t>
-  </si>
-  <si>
-    <t>22:57:12</t>
-  </si>
-  <si>
-    <t>18:53:19</t>
-  </si>
-  <si>
-    <t>20:31:03</t>
-  </si>
-  <si>
-    <t>22:07:47</t>
-  </si>
-  <si>
-    <t>23:42:58</t>
-  </si>
-  <si>
-    <t>00:42:09</t>
-  </si>
-  <si>
-    <t>02:18:30</t>
-  </si>
-  <si>
-    <t>22:15:59</t>
-  </si>
-  <si>
-    <t>23:52:58</t>
-  </si>
-  <si>
-    <t>01:29:31</t>
-  </si>
-  <si>
-    <t>21:26:39</t>
-  </si>
-  <si>
-    <t>23:03:43</t>
+    <t>22:12:05</t>
+  </si>
+  <si>
+    <t>23:48:52</t>
+  </si>
+  <si>
+    <t>01:24:12</t>
+  </si>
+  <si>
+    <t>21:22:37</t>
+  </si>
+  <si>
+    <t>22:59:34</t>
+  </si>
+  <si>
+    <t>00:35:29</t>
+  </si>
+  <si>
+    <t>20:33:01</t>
+  </si>
+  <si>
+    <t>22:10:09</t>
+  </si>
+  <si>
+    <t>23:46:26</t>
+  </si>
+  <si>
+    <t>19:43:16</t>
+  </si>
+  <si>
+    <t>21:20:38</t>
+  </si>
+  <si>
+    <t>22:57:10</t>
+  </si>
+  <si>
+    <t>18:53:17</t>
+  </si>
+  <si>
+    <t>20:31:01</t>
+  </si>
+  <si>
+    <t>22:07:45</t>
+  </si>
+  <si>
+    <t>23:42:56</t>
+  </si>
+  <si>
+    <t>19:41:18</t>
+  </si>
+  <si>
+    <t>21:18:12</t>
+  </si>
+  <si>
+    <t>22:54:02</t>
+  </si>
+  <si>
+    <t>01:29:30</t>
+  </si>
+  <si>
+    <t>21:26:38</t>
+  </si>
+  <si>
+    <t>23:03:42</t>
   </si>
   <si>
     <t>00:40:23</t>
   </si>
   <si>
-    <t>20:37:12</t>
+    <t>20:37:11</t>
   </si>
   <si>
     <t>22:14:22</t>
   </si>
   <si>
-    <t>23:51:10</t>
+    <t>23:51:09</t>
   </si>
   <si>
     <t>01:27:10</t>
   </si>
   <si>
-    <t>21:24:57</t>
-  </si>
-  <si>
-    <t>23:01:50</t>
-  </si>
-  <si>
-    <t>00:38:06</t>
-  </si>
-  <si>
-    <t>20:35:27</t>
-  </si>
-  <si>
-    <t>22:12:24</t>
-  </si>
-  <si>
-    <t>19:45:52</t>
-  </si>
-  <si>
-    <t>21:22:54</t>
-  </si>
-  <si>
-    <t>22:59:32</t>
-  </si>
-  <si>
-    <t>18:56:10</t>
-  </si>
-  <si>
-    <t>20:33:19</t>
-  </si>
-  <si>
-    <t>22:10:04</t>
-  </si>
-  <si>
-    <t>23:46:00</t>
+    <t>21:24:56</t>
+  </si>
+  <si>
+    <t>23:01:49</t>
+  </si>
+  <si>
+    <t>00:38:05</t>
+  </si>
+  <si>
+    <t>20:35:26</t>
+  </si>
+  <si>
+    <t>22:12:23</t>
+  </si>
+  <si>
+    <t>19:45:50</t>
+  </si>
+  <si>
+    <t>21:22:52</t>
+  </si>
+  <si>
+    <t>22:59:30</t>
+  </si>
+  <si>
+    <t>18:56:09</t>
+  </si>
+  <si>
+    <t>20:33:17</t>
+  </si>
+  <si>
+    <t>22:10:02</t>
+  </si>
+  <si>
+    <t>23:45:58</t>
+  </si>
+  <si>
+    <t>19:43:37</t>
+  </si>
+  <si>
+    <t>21:20:27</t>
+  </si>
+  <si>
+    <t>22:56:40</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
     <t>12°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
     <t>13°</t>
   </si>
   <si>
-    <t>02:15:33</t>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>5°</t>
   </si>
   <si>
     <t>01:29:39</t>
   </si>
   <si>
-    <t>20:26:33</t>
-  </si>
-  <si>
-    <t>19:39:51</t>
-  </si>
-  <si>
-    <t>21:12:44</t>
-  </si>
-  <si>
-    <t>18:52:51</t>
-  </si>
-  <si>
-    <t>20:25:42</t>
+    <t>20:26:32</t>
+  </si>
+  <si>
+    <t>19:39:50</t>
+  </si>
+  <si>
+    <t>21:12:42</t>
+  </si>
+  <si>
+    <t>18:52:49</t>
+  </si>
+  <si>
+    <t>20:25:41</t>
+  </si>
+  <si>
+    <t>19:38:24</t>
+  </si>
+  <si>
+    <t>21:11:14</t>
   </si>
   <si>
     <t>B</t>
@@ -643,10 +631,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -680,7 +668,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,7 +689,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,13 +749,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,73 +779,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -838,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -907,6 +913,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1310,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1388,55 +1403,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="L2" s="4">
-        <v>-24.3</v>
+        <v>-20.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P2" s="7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="8">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1447,52 +1462,52 @@
         <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="L3" s="4">
-        <v>-15.3</v>
+        <v>-23.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O3" s="6">
-        <v>87</v>
-      </c>
-      <c r="P3" s="10">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>81</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="O3" s="10">
+        <v>26</v>
+      </c>
+      <c r="P3" s="11">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>1</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1500,55 +1515,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L4" s="4">
-        <v>-26.3</v>
+        <v>-27.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>67</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>100</v>
-      </c>
-      <c r="R4" s="9">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="O4" s="10">
+        <v>30</v>
+      </c>
+      <c r="P4" s="11">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1556,55 +1571,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L5" s="4">
-        <v>-26.9</v>
+        <v>-25</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="12">
-        <v>64</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>100</v>
-      </c>
-      <c r="R5" s="9">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="O5" s="10">
+        <v>24</v>
+      </c>
+      <c r="P5" s="13">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1612,55 +1627,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
       <c r="L6" s="4">
-        <v>-20.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O6" s="6">
-        <v>95</v>
-      </c>
-      <c r="P6" s="13">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>88</v>
-      </c>
-      <c r="R6" s="13">
-        <v>60</v>
+        <v>205</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1668,54 +1683,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.7</v>
+        <v>-26.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" s="15">
-        <v>6</v>
-      </c>
-      <c r="P7" s="16">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>0</v>
-      </c>
-      <c r="R7" s="17">
+        <v>204</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1724,55 +1739,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L8" s="4">
-        <v>-27.8</v>
+        <v>-27.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O8" s="15">
-        <v>6</v>
-      </c>
-      <c r="P8" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>4</v>
-      </c>
-      <c r="R8" s="17">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O8" s="10">
+        <v>48</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>41</v>
+      </c>
+      <c r="R8" s="15">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1780,55 +1795,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L9" s="4">
-        <v>-25</v>
+        <v>-21.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O9" s="18">
-        <v>23</v>
-      </c>
-      <c r="P9" s="19">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O9" s="6">
+        <v>49</v>
+      </c>
+      <c r="P9" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>36</v>
       </c>
       <c r="R9" s="17">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1836,54 +1851,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L10" s="4">
-        <v>-19.6</v>
+        <v>-24.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O10" s="15">
-        <v>0</v>
-      </c>
-      <c r="P10" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>0</v>
-      </c>
-      <c r="R10" s="17">
+        <v>204</v>
+      </c>
+      <c r="O10" s="14">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1892,54 +1907,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L11" s="4">
-        <v>-26.9</v>
+        <v>-28.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O11" s="15">
-        <v>13</v>
-      </c>
-      <c r="P11" s="16">
-        <v>6</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>0</v>
-      </c>
-      <c r="R11" s="17">
+        <v>204</v>
+      </c>
+      <c r="O11" s="14">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1948,54 +1963,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L12" s="4">
-        <v>-27.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O12" s="15">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
+        <v>204</v>
+      </c>
+      <c r="O12" s="14">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2004,55 +2019,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="L13" s="4">
-        <v>-21.5</v>
+        <v>-20</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O13" s="15">
-        <v>4</v>
-      </c>
-      <c r="P13" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>0</v>
-      </c>
-      <c r="R13" s="17">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O13" s="6">
+        <v>95</v>
+      </c>
+      <c r="P13" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2060,55 +2075,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4">
-        <v>-24.2</v>
+        <v>-27.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O14" s="15">
-        <v>2</v>
-      </c>
-      <c r="P14" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>0</v>
-      </c>
-      <c r="R14" s="17">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O14" s="6">
+        <v>84</v>
+      </c>
+      <c r="P14" s="13">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>26</v>
+      </c>
+      <c r="R14" s="18">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2116,55 +2131,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L15" s="4">
-        <v>-28.5</v>
+        <v>-28.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O15" s="15">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O15" s="6">
+        <v>73</v>
+      </c>
+      <c r="P15" s="19">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>26</v>
+      </c>
+      <c r="R15" s="20">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2175,52 +2190,52 @@
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="L16" s="4">
-        <v>-25.7</v>
+        <v>-14.6</v>
       </c>
       <c r="M16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O16" s="15">
-        <v>0</v>
-      </c>
-      <c r="P16" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>0</v>
-      </c>
-      <c r="R16" s="17">
-        <v>0</v>
+      <c r="O16" s="6">
+        <v>90</v>
+      </c>
+      <c r="P16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>18</v>
+      </c>
+      <c r="R16" s="21">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2228,55 +2243,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-24.7</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O17" s="6">
+        <v>92</v>
+      </c>
+      <c r="P17" s="19">
+        <v>17</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>41</v>
+      </c>
+      <c r="R17" s="22">
         <v>84</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-20</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O17" s="18">
-        <v>26</v>
-      </c>
-      <c r="P17" s="19">
-        <v>14</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>0</v>
-      </c>
-      <c r="R17" s="16">
-        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2284,55 +2299,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L18" s="4">
-        <v>-27.5</v>
+        <v>-29.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O18" s="18">
-        <v>31</v>
+        <v>204</v>
+      </c>
+      <c r="O18" s="6">
+        <v>89</v>
       </c>
       <c r="P18" s="19">
-        <v>16</v>
-      </c>
-      <c r="Q18" s="17">
-        <v>0</v>
-      </c>
-      <c r="R18" s="16">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>46</v>
+      </c>
+      <c r="R18" s="23">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2340,55 +2355,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="L19" s="4">
-        <v>-28.3</v>
+        <v>-8.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O19" s="18">
-        <v>26</v>
-      </c>
-      <c r="P19" s="19">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>0</v>
-      </c>
-      <c r="R19" s="16">
-        <v>6</v>
+        <v>205</v>
+      </c>
+      <c r="O19" s="6">
+        <v>99</v>
+      </c>
+      <c r="P19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="21">
+        <v>79</v>
+      </c>
+      <c r="R19" s="18">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2396,55 +2411,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L20" s="4">
-        <v>-14.7</v>
+        <v>-20.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O20" s="18">
-        <v>22</v>
-      </c>
-      <c r="P20" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>11</v>
-      </c>
-      <c r="R20" s="21">
-        <v>22</v>
+        <v>206</v>
+      </c>
+      <c r="O20" s="6">
+        <v>100</v>
+      </c>
+      <c r="P20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="24">
+        <v>68</v>
+      </c>
+      <c r="R20" s="22">
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2452,55 +2467,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="L21" s="4">
-        <v>-24.7</v>
+        <v>-28.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O21" s="18">
-        <v>27</v>
-      </c>
-      <c r="P21" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>21</v>
-      </c>
-      <c r="R21" s="22">
-        <v>27</v>
+        <v>204</v>
+      </c>
+      <c r="O21" s="6">
+        <v>99</v>
+      </c>
+      <c r="P21" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>47</v>
+      </c>
+      <c r="R21" s="25">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2508,55 +2523,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L22" s="4">
-        <v>-29.2</v>
+        <v>-29.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" s="18">
-        <v>32</v>
-      </c>
-      <c r="P22" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="22">
-        <v>26</v>
-      </c>
-      <c r="R22" s="23">
-        <v>32</v>
+        <v>205</v>
+      </c>
+      <c r="O22" s="6">
+        <v>100</v>
+      </c>
+      <c r="P22" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="26">
+        <v>54</v>
+      </c>
+      <c r="R22" s="25">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2564,55 +2579,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L23" s="4">
-        <v>-8.4</v>
+        <v>-15</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="O23" s="6">
-        <v>100</v>
-      </c>
-      <c r="P23" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="17">
-        <v>0</v>
-      </c>
-      <c r="R23" s="9">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="P23" s="9">
+        <v>29</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>60</v>
+      </c>
+      <c r="R23" s="17">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2620,55 +2635,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-25.2</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O24" s="6">
+        <v>59</v>
+      </c>
+      <c r="P24" s="19">
+        <v>17</v>
+      </c>
+      <c r="Q24" s="9">
         <v>28</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-20.5</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O24" s="6">
-        <v>100</v>
-      </c>
-      <c r="P24" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="16">
-        <v>5</v>
-      </c>
-      <c r="R24" s="9">
-        <v>100</v>
+      <c r="R24" s="13">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2676,170 +2691,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L25" s="4">
-        <v>-28.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O25" s="6">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="O25" s="10">
+        <v>45</v>
       </c>
       <c r="P25" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="19">
-        <v>15</v>
-      </c>
-      <c r="R25" s="9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>13</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-29.1</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O26" s="6">
-        <v>100</v>
-      </c>
-      <c r="P26" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="23">
-        <v>30</v>
-      </c>
-      <c r="R26" s="9">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="Q25" s="17">
+        <v>11</v>
+      </c>
+      <c r="R25" s="13">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2858,12 +2817,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2880,22 +2839,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
